--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45286.94236111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C2" t="n">
-        <v>-7.831793520509489</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D2" t="n">
-        <v>113.2466810897037</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.857397909129135</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F2" t="n">
-        <v>113.4382355861878</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G2" t="n">
-        <v>97.6975188157603</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H2" t="n">
-        <v>21.29177185797789</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.164266725120617</v>
+        <v>0.1646129267166912</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9022584206042435</v>
+        <v>0.8936956683759264</v>
       </c>
       <c r="K2" t="n">
-        <v>1873</v>
+        <v>1965</v>
       </c>
       <c r="L2" t="n">
-        <v>1426</v>
+        <v>1797</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45286.94236111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.85060996644411</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O2" t="n">
-        <v>113.456851280788</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.857397909129135</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.4382355861878</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R2" t="n">
-        <v>97.6975188157603</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.208657569200279</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D3" t="n">
-        <v>113.4584573100887</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.951286861609271</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F3" t="n">
-        <v>113.3638879103665</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G3" t="n">
-        <v>340.0021181499238</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H3" t="n">
-        <v>30.45327467637573</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.168182244926749</v>
+        <v>0.1646129267166912</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9606432481129736</v>
+        <v>0.9625162531734641</v>
       </c>
       <c r="K3" t="n">
-        <v>627</v>
+        <v>1965</v>
       </c>
       <c r="L3" t="n">
-        <v>448</v>
+        <v>1797</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O3" t="n">
-        <v>113.40414682924</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.951286861609271</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.3638879103665</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R3" t="n">
-        <v>340.0021181499238</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.208657569200279</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4584573100887</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.951286861609271</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F4" t="n">
-        <v>113.3638879103665</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G4" t="n">
-        <v>340.0021181499238</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H4" t="n">
-        <v>30.45327467637573</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I4" t="n">
-        <v>0.168182244926749</v>
+        <v>0.1646129267166912</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9832796124696023</v>
+        <v>0.9845888442782867</v>
       </c>
       <c r="K4" t="n">
-        <v>627</v>
+        <v>1965</v>
       </c>
       <c r="L4" t="n">
-        <v>448</v>
+        <v>1797</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O4" t="n">
-        <v>113.40414682924</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.951286861609271</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.3638879103665</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R4" t="n">
-        <v>340.0021181499238</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -742,31 +742,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.208657569200279</v>
+        <v>-7.967866336324673</v>
       </c>
       <c r="D5" t="n">
-        <v>113.4584573100887</v>
+        <v>113.3691552709739</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.951286861609271</v>
+        <v>-7.967951901139388</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3638879103665</v>
+        <v>113.3782357441071</v>
       </c>
       <c r="G5" t="n">
-        <v>340.0021181499238</v>
+        <v>90.54577101877454</v>
       </c>
       <c r="H5" t="n">
-        <v>30.45327467637573</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.168182244926749</v>
+        <v>0.1653759356907702</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9932105326707832</v>
+        <v>0.9892536025145591</v>
       </c>
       <c r="K5" t="n">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="L5" t="n">
         <v>448</v>
@@ -781,13 +781,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.951286861609271</v>
+        <v>-7.967951901139388</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3638879103665</v>
+        <v>113.3782357441071</v>
       </c>
       <c r="R5" t="n">
-        <v>340.0021181499238</v>
+        <v>90.54577101877454</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -807,31 +807,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.531901106913145</v>
+        <v>-7.739146887920408</v>
       </c>
       <c r="D6" t="n">
-        <v>113.2794872685878</v>
+        <v>113.3114049991318</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.930529383855657</v>
+        <v>-7.962303886920907</v>
       </c>
       <c r="F6" t="n">
-        <v>113.417443101239</v>
+        <v>113.3977794683919</v>
       </c>
       <c r="G6" t="n">
-        <v>161.0808266160235</v>
+        <v>159.0276015613202</v>
       </c>
       <c r="H6" t="n">
-        <v>46.85936955945441</v>
+        <v>26.57544550752098</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1684599544418115</v>
+        <v>0.1659439523868861</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9974508915599198</v>
+        <v>0.9936003442377382</v>
       </c>
       <c r="K6" t="n">
-        <v>1311</v>
+        <v>725</v>
       </c>
       <c r="L6" t="n">
         <v>448</v>
@@ -846,13 +846,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.930529383855657</v>
+        <v>-7.962303886920907</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.417443101239</v>
+        <v>113.3977794683919</v>
       </c>
       <c r="R6" t="n">
-        <v>161.0808266160235</v>
+        <v>159.0276015613202</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -872,31 +872,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.869810460619095</v>
+        <v>-8.093563569211346</v>
       </c>
       <c r="D7" t="n">
-        <v>113.3457128157159</v>
+        <v>113.4692920141133</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.936370435203148</v>
+        <v>-7.931435726980411</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3571748709032</v>
+        <v>113.403276711635</v>
       </c>
       <c r="G7" t="n">
-        <v>170.3209584436106</v>
+        <v>338.0358262487478</v>
       </c>
       <c r="H7" t="n">
-        <v>7.508025301580254</v>
+        <v>19.43806299744516</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1685429864136532</v>
+        <v>0.1661979603811882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.997843388198434</v>
+        <v>0.9959529763682122</v>
       </c>
       <c r="K7" t="n">
-        <v>1150</v>
+        <v>190</v>
       </c>
       <c r="L7" t="n">
         <v>448</v>
@@ -911,13 +911,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.936370435203148</v>
+        <v>-7.931435726980411</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3571748709032</v>
+        <v>113.403276711635</v>
       </c>
       <c r="R7" t="n">
-        <v>170.3209584436106</v>
+        <v>338.0358262487478</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.959417135956648</v>
+        <v>-8.093563569211346</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3658636514925</v>
+        <v>113.4692920141133</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.951195265070214</v>
+        <v>-7.931435726980411</v>
       </c>
       <c r="F8" t="n">
-        <v>113.3695430662124</v>
+        <v>113.403276711635</v>
       </c>
       <c r="G8" t="n">
-        <v>23.90359554667464</v>
+        <v>338.0358262487478</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>19.43806299744516</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1689085651482239</v>
+        <v>0.1661979603811882</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9981337701624136</v>
+        <v>0.9975563416305804</v>
       </c>
       <c r="K8" t="n">
-        <v>640</v>
+        <v>190</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.951195265070214</v>
+        <v>-7.931435726980411</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.3695430662124</v>
+        <v>113.403276711635</v>
       </c>
       <c r="R8" t="n">
-        <v>23.90359554667464</v>
+        <v>338.0358262487478</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.959417135956648</v>
+        <v>-8.093563569211346</v>
       </c>
       <c r="D9" t="n">
-        <v>113.3658636514925</v>
+        <v>113.4692920141133</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.951195265070214</v>
+        <v>-7.931435726980411</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3695430662124</v>
+        <v>113.403276711635</v>
       </c>
       <c r="G9" t="n">
-        <v>23.90359554667464</v>
+        <v>338.0358262487478</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>19.43806299744516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1689085651482239</v>
+        <v>0.1661979603811882</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9990459968657742</v>
+        <v>0.9983277908384947</v>
       </c>
       <c r="K9" t="n">
-        <v>640</v>
+        <v>190</v>
       </c>
       <c r="L9" t="n">
         <v>448</v>
@@ -1041,13 +1041,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.951195265070214</v>
+        <v>-7.931435726980411</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3695430662124</v>
+        <v>113.403276711635</v>
       </c>
       <c r="R9" t="n">
-        <v>23.90359554667464</v>
+        <v>338.0358262487478</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.940949430445097</v>
+        <v>-7.768618352449146</v>
       </c>
       <c r="D10" t="n">
-        <v>113.4068218427101</v>
+        <v>113.3463166416934</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.949928015274325</v>
+        <v>-7.933782131718706</v>
       </c>
       <c r="F10" t="n">
-        <v>113.4063040862576</v>
+        <v>113.4054658036662</v>
       </c>
       <c r="G10" t="n">
-        <v>183.2686971081997</v>
+        <v>160.4710112477416</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>19.486862903997</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1689652400522595</v>
+        <v>0.1662716691075855</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9988240108406717</v>
+        <v>0.9984356112367626</v>
       </c>
       <c r="K10" t="n">
-        <v>448</v>
+        <v>1252</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.949928015274325</v>
+        <v>-7.933782131718706</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.4063040862576</v>
+        <v>113.4054658036662</v>
       </c>
       <c r="R10" t="n">
-        <v>183.2686971081997</v>
+        <v>160.4710112477416</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,31 +1132,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.94225617776886</v>
+        <v>-8.059946035647258</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3911801893767</v>
+        <v>113.3947294826529</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.950798921856563</v>
+        <v>-7.954542207798461</v>
       </c>
       <c r="F11" t="n">
-        <v>113.388342341465</v>
+        <v>113.4009919139456</v>
       </c>
       <c r="G11" t="n">
-        <v>198.211219644722</v>
+        <v>3.367520457399586</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>11.74063835907284</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1690502928567973</v>
+        <v>0.1664252184490007</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9986788944607562</v>
+        <v>0.9984730388684431</v>
       </c>
       <c r="K11" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.950798921856563</v>
+        <v>-7.954542207798461</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.388342341465</v>
+        <v>113.4009919139456</v>
       </c>
       <c r="R11" t="n">
-        <v>198.211219644722</v>
+        <v>3.367520457399586</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,28 +1197,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.963527118258762</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3786319735736</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.956262632938509</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3839849811543</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G12" t="n">
-        <v>36.12136735535188</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1690518337364024</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857859553508664</v>
+        <v>0.5857854261953833</v>
       </c>
       <c r="K12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.956262632938509</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3839849811543</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R12" t="n">
-        <v>36.12136735535188</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,28 +1262,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.963527118258762</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3786319735736</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.956262632938509</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3839849811543</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G13" t="n">
-        <v>36.12136735535188</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1690518337364024</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9993841743760419</v>
+        <v>0.9989539882682343</v>
       </c>
       <c r="K13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.956262632938509</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3839849811543</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R13" t="n">
-        <v>36.12136735535188</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,28 +1327,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.963773956544753</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D14" t="n">
-        <v>113.3795139107966</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.955972785666986</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3840317734423</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G14" t="n">
-        <v>29.83658933348778</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1691012091060435</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9993921630737944</v>
+        <v>0.9989109144345228</v>
       </c>
       <c r="K14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.955972785666986</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3840317734423</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R14" t="n">
-        <v>29.83658933348778</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,28 +1392,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.95555221532611</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3865829450222</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.946309450969368</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3890974658254</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G15" t="n">
-        <v>15.07971231123593</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H15" t="n">
-        <v>1.064400495541751</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1691065523703957</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9994675439123603</v>
+        <v>0.9988922953877242</v>
       </c>
       <c r="K15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.946309450969368</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3890974658254</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R15" t="n">
-        <v>15.07971231123593</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,28 +1457,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.957768984509786</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D16" t="n">
-        <v>113.386785384391</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.947001945510651</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F16" t="n">
-        <v>113.389507439791</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G16" t="n">
-        <v>14.05705789411996</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H16" t="n">
-        <v>1.234198015587429</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1691191903774521</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9994383496267546</v>
+        <v>0.9988831819049333</v>
       </c>
       <c r="K16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.947001945510651</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.389507439791</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R16" t="n">
-        <v>14.05705789411996</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,28 +1522,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.96632498173932</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3838059395913</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.956930504893148</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3895379602796</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G17" t="n">
-        <v>31.14357046980853</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H17" t="n">
-        <v>1.220522810982421</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1691204997863809</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9994891149126534</v>
+        <v>0.9989451601515402</v>
       </c>
       <c r="K17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.956930504893148</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3895379602796</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R17" t="n">
-        <v>31.14357046980853</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,28 +1587,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.962315552397376</v>
+        <v>-7.990383759784061</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3853804785782</v>
+        <v>113.395123045986</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.95223408992994</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3898836207061</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="G18" t="n">
-        <v>23.86369801356755</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2257976524183</v>
+        <v>4.200635350190051</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1691300295175486</v>
+        <v>0.1665235503995904</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9994652698169727</v>
+        <v>0.99893958175599</v>
       </c>
       <c r="K18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.95223408992994</v>
+        <v>-7.953271559793956</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3898836207061</v>
+        <v>113.4022490373181</v>
       </c>
       <c r="R18" t="n">
-        <v>23.86369801356755</v>
+        <v>10.76711912654551</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,28 +1652,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.962315552397376</v>
+        <v>-7.989818394386</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3853804785782</v>
+        <v>113.3941427213001</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.95223408992994</v>
+        <v>-7.952956176829034</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3898836207061</v>
+        <v>113.4014929748547</v>
       </c>
       <c r="G19" t="n">
-        <v>23.86369801356755</v>
+        <v>11.17106541725317</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2257976524183</v>
+        <v>4.178045297082416</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1691300295175486</v>
+        <v>0.166525757337932</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9995230031389237</v>
+        <v>0.9989847062346349</v>
       </c>
       <c r="K19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.95223408992994</v>
+        <v>-7.952956176829034</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3898836207061</v>
+        <v>113.4014929748547</v>
       </c>
       <c r="R19" t="n">
-        <v>23.86369801356755</v>
+        <v>11.17106541725317</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,28 +1717,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.961439162050143</v>
+        <v>-7.99481503342389</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3825113518822</v>
+        <v>113.3951026673724</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.953697077196289</v>
+        <v>-7.955343996878396</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3872566090177</v>
+        <v>113.4029362147204</v>
       </c>
       <c r="G20" t="n">
-        <v>31.25872232611368</v>
+        <v>11.11993773295876</v>
       </c>
       <c r="H20" t="n">
-        <v>1.00707117731044</v>
+        <v>4.472947684539269</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1691304883578331</v>
+        <v>0.1665352667269712</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9995421138050207</v>
+        <v>0.9991289347752638</v>
       </c>
       <c r="K20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.953697077196289</v>
+        <v>-7.955343996878396</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3872566090177</v>
+        <v>113.4029362147204</v>
       </c>
       <c r="R20" t="n">
-        <v>31.25872232611368</v>
+        <v>11.11993773295876</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,28 +1782,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.959102407798167</v>
+        <v>-7.993708646001968</v>
       </c>
       <c r="D21" t="n">
-        <v>113.382845937949</v>
+        <v>113.3950978019021</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.95081778365941</v>
+        <v>-7.956069486171489</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3865461966695</v>
+        <v>113.4024933956735</v>
       </c>
       <c r="G21" t="n">
-        <v>23.86215936254939</v>
+        <v>11.01189416605451</v>
       </c>
       <c r="H21" t="n">
-        <v>1.007309860118569</v>
+        <v>4.263783001733949</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1691306095896809</v>
+        <v>0.1665360987639568</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9995371943323561</v>
+        <v>0.999127220286662</v>
       </c>
       <c r="K21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.95081778365941</v>
+        <v>-7.956069486171489</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3865461966695</v>
+        <v>113.4024933956735</v>
       </c>
       <c r="R21" t="n">
-        <v>23.86215936254939</v>
+        <v>11.01189416605451</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,28 +1847,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.959102407798167</v>
+        <v>-7.993708646001968</v>
       </c>
       <c r="D22" t="n">
-        <v>113.382845937949</v>
+        <v>113.3950978019021</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.95081778365941</v>
+        <v>-7.956069486171489</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3865461966695</v>
+        <v>113.4024933956735</v>
       </c>
       <c r="G22" t="n">
-        <v>23.86215936254939</v>
+        <v>11.01189416605451</v>
       </c>
       <c r="H22" t="n">
-        <v>1.007309860118569</v>
+        <v>4.263783001733949</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1691306095896809</v>
+        <v>0.1665360987639568</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857863612599565</v>
+        <v>0.585786161224261</v>
       </c>
       <c r="K22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.95081778365941</v>
+        <v>-7.956069486171489</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3865461966695</v>
+        <v>113.4024933956735</v>
       </c>
       <c r="R22" t="n">
-        <v>23.86215936254939</v>
+        <v>11.01189416605451</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,28 +1912,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.959102407798167</v>
+        <v>-7.989088700924045</v>
       </c>
       <c r="D23" t="n">
-        <v>113.382845937949</v>
+        <v>113.3953112725736</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.95081778365941</v>
+        <v>-7.959182651636925</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3865461966695</v>
+        <v>113.4012811738371</v>
       </c>
       <c r="G23" t="n">
-        <v>23.86215936254939</v>
+        <v>11.18312010926024</v>
       </c>
       <c r="H23" t="n">
-        <v>1.007309860118569</v>
+        <v>3.389759822594767</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1691306095896809</v>
+        <v>0.1665398594185048</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999029124409823</v>
+        <v>0.999794207535229</v>
       </c>
       <c r="K23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.95081778365941</v>
+        <v>-7.959182651636925</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3865461966695</v>
+        <v>113.4012811738371</v>
       </c>
       <c r="R23" t="n">
-        <v>23.86215936254939</v>
+        <v>11.18312010926024</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,28 +1977,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.961629238806536</v>
+        <v>-7.99685361846482</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3830892847677</v>
+        <v>113.3951649650561</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.953595212711408</v>
+        <v>-7.959860169454527</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3880227337228</v>
+        <v>113.4025044586493</v>
       </c>
       <c r="G24" t="n">
-        <v>31.30648076017013</v>
+        <v>11.11635535000579</v>
       </c>
       <c r="H24" t="n">
-        <v>1.045575420472695</v>
+        <v>4.192130809431584</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1691306846924802</v>
+        <v>0.1665411264512923</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9999020951883362</v>
+        <v>0.9997940362708627</v>
       </c>
       <c r="K24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.953595212711408</v>
+        <v>-7.959860169454527</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3880227337228</v>
+        <v>113.4025044586493</v>
       </c>
       <c r="R24" t="n">
-        <v>31.30648076017013</v>
+        <v>11.11635535000579</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,28 +2042,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.961295109421289</v>
+        <v>-7.99685361846482</v>
       </c>
       <c r="D25" t="n">
-        <v>113.38272543288</v>
+        <v>113.3951649650561</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.953531681051446</v>
+        <v>-7.959860169454527</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3874864325805</v>
+        <v>113.4025044586493</v>
       </c>
       <c r="G25" t="n">
-        <v>31.27294228836683</v>
+        <v>11.11635535000579</v>
       </c>
       <c r="H25" t="n">
-        <v>1.009999667063136</v>
+        <v>4.192130809431584</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1691309170592525</v>
+        <v>0.1665411264512923</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999020428976343</v>
+        <v>0.9997996576645882</v>
       </c>
       <c r="K25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.953531681051446</v>
+        <v>-7.959860169454527</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3874864325805</v>
+        <v>113.4025044586493</v>
       </c>
       <c r="R25" t="n">
-        <v>31.27294228836683</v>
+        <v>11.11635535000579</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.961295109421289</v>
+        <v>-7.997459047635052</v>
       </c>
       <c r="D26" t="n">
-        <v>113.38272543288</v>
+        <v>113.3950372514955</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.953531681051446</v>
+        <v>-7.959661022160354</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3874864325805</v>
+        <v>113.4025243788368</v>
       </c>
       <c r="G26" t="n">
-        <v>31.27294228836683</v>
+        <v>11.09902332116694</v>
       </c>
       <c r="H26" t="n">
-        <v>1.009999667063136</v>
+        <v>4.283051616926871</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1691309170592525</v>
+        <v>0.1665411908531536</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9999015045352572</v>
+        <v>0.9998013218707889</v>
       </c>
       <c r="K26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.953531681051446</v>
+        <v>-7.959661022160354</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3874864325805</v>
+        <v>113.4025243788368</v>
       </c>
       <c r="R26" t="n">
-        <v>31.27294228836683</v>
+        <v>11.09902332116694</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,28 +2172,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.961668911362502</v>
+        <v>-7.997459047635052</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3831014566088</v>
+        <v>113.3950372514955</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.953526610926514</v>
+        <v>-7.959661022160354</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3880977211826</v>
+        <v>113.4025243788368</v>
       </c>
       <c r="G27" t="n">
-        <v>31.28779954308197</v>
+        <v>11.09902332116694</v>
       </c>
       <c r="H27" t="n">
-        <v>1.059456539918636</v>
+        <v>4.283051616926871</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1691310021904601</v>
+        <v>0.1665411908531536</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999092320626011</v>
+        <v>0.9998019949541535</v>
       </c>
       <c r="K27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.953526610926514</v>
+        <v>-7.959661022160354</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3880977211826</v>
+        <v>113.4025243788368</v>
       </c>
       <c r="R27" t="n">
-        <v>31.28779954308197</v>
+        <v>11.09902332116694</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,28 +2237,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.961314682342122</v>
+        <v>-7.996891409339454</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3838213445346</v>
+        <v>113.3951693909355</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.953088236650005</v>
+        <v>-7.959916973397714</v>
       </c>
       <c r="F28" t="n">
-        <v>113.387490336194</v>
+        <v>113.4024999693751</v>
       </c>
       <c r="G28" t="n">
-        <v>23.83156166885962</v>
+        <v>11.10875421493219</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>4.189867064482399</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1691310898307431</v>
+        <v>0.1665412149737711</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9999137158424972</v>
+        <v>0.999805869211807</v>
       </c>
       <c r="K28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.953088236650005</v>
+        <v>-7.959916973397714</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.387490336194</v>
+        <v>113.4024999693751</v>
       </c>
       <c r="R28" t="n">
-        <v>23.83156166885962</v>
+        <v>11.10875421493219</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,28 +2302,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.961314682342122</v>
+        <v>-7.996561903939893</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3838213445346</v>
+        <v>113.3949560269683</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.953088236650005</v>
+        <v>-7.959493816230616</v>
       </c>
       <c r="F29" t="n">
-        <v>113.387490336194</v>
+        <v>113.4023031609925</v>
       </c>
       <c r="G29" t="n">
-        <v>23.83156166885962</v>
+        <v>11.1057999471602</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>4.200436955603952</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1691310898307431</v>
+        <v>0.1665413094802773</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9999237595179655</v>
+        <v>0.9998043015475526</v>
       </c>
       <c r="K29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.953088236650005</v>
+        <v>-7.959493816230616</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.387490336194</v>
+        <v>113.4023031609925</v>
       </c>
       <c r="R29" t="n">
-        <v>23.83156166885962</v>
+        <v>11.1057999471602</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,28 +2367,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.959584740165238</v>
+        <v>-7.996561903939893</v>
       </c>
       <c r="D30" t="n">
-        <v>113.3839374558485</v>
+        <v>113.3949560269683</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.95130083175001</v>
+        <v>-7.959493816230616</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3876360525454</v>
+        <v>113.4023031609925</v>
       </c>
       <c r="G30" t="n">
-        <v>23.85444355202408</v>
+        <v>11.1057999471602</v>
       </c>
       <c r="H30" t="n">
-        <v>1.007162851242792</v>
+        <v>4.200436955603952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1691314946810981</v>
+        <v>0.1665413094802773</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9999273179235897</v>
+        <v>0.999804303902917</v>
       </c>
       <c r="K30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.95130083175001</v>
+        <v>-7.959493816230616</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3876360525454</v>
+        <v>113.4023031609925</v>
       </c>
       <c r="R30" t="n">
-        <v>23.85444355202408</v>
+        <v>11.1057999471602</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.960636905690947</v>
+        <v>-7.996503103243004</v>
       </c>
       <c r="D31" t="n">
-        <v>113.3834369836706</v>
+        <v>113.3949880857733</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.952390847492961</v>
+        <v>-7.959414169227383</v>
       </c>
       <c r="F31" t="n">
-        <v>113.387118129581</v>
+        <v>113.402340342715</v>
       </c>
       <c r="G31" t="n">
-        <v>23.85121290980576</v>
+        <v>11.10726204562896</v>
       </c>
       <c r="H31" t="n">
-        <v>1.002536012588844</v>
+        <v>4.202820240340311</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1691315605563635</v>
+        <v>0.1665413196770325</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9999426456379109</v>
+        <v>0.9998037489982229</v>
       </c>
       <c r="K31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.952390847492961</v>
+        <v>-7.959414169227383</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.387118129581</v>
+        <v>113.402340342715</v>
       </c>
       <c r="R31" t="n">
-        <v>23.85121290980576</v>
+        <v>11.10726204562896</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,28 +2497,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.960362062528639</v>
+        <v>-7.996503103243004</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3840698637267</v>
+        <v>113.3949880857733</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.95211464190579</v>
+        <v>-7.959414169227383</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3877537457368</v>
+        <v>113.402340342715</v>
       </c>
       <c r="G32" t="n">
-        <v>23.86347281041359</v>
+        <v>11.10726204562896</v>
       </c>
       <c r="H32" t="n">
-        <v>1.002796540972109</v>
+        <v>4.202820240340311</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1691316791816949</v>
+        <v>0.1665413196770325</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5857864389913261</v>
+        <v>0.5857864258143888</v>
       </c>
       <c r="K32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.95211464190579</v>
+        <v>-7.959414169227383</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3877537457368</v>
+        <v>113.402340342715</v>
       </c>
       <c r="R32" t="n">
-        <v>23.86347281041359</v>
+        <v>11.10726204562896</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,28 +2562,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.960011786082573</v>
+        <v>-7.996503103243004</v>
       </c>
       <c r="D33" t="n">
-        <v>113.3838975863181</v>
+        <v>113.3949880857733</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.951771093051076</v>
+        <v>-7.959414169227383</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3875769753172</v>
+        <v>113.402340342715</v>
       </c>
       <c r="G33" t="n">
-        <v>23.85492067091027</v>
+        <v>11.10726204562896</v>
       </c>
       <c r="H33" t="n">
-        <v>1.001912396850924</v>
+        <v>4.202820240340311</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1691316998773845</v>
+        <v>0.1665413196770325</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999985169405591</v>
+        <v>0.9999363065890025</v>
       </c>
       <c r="K33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.951771093051076</v>
+        <v>-7.959414169227383</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3875769753172</v>
+        <v>113.402340342715</v>
       </c>
       <c r="R33" t="n">
-        <v>23.85492067091027</v>
+        <v>11.10726204562896</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,28 +2627,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.960384910102285</v>
+        <v>-7.996505544976156</v>
       </c>
       <c r="D34" t="n">
-        <v>113.3838427475291</v>
+        <v>113.394989061038</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.952120465792567</v>
+        <v>-7.959486597397787</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3875332225805</v>
+        <v>113.4023271786867</v>
       </c>
       <c r="G34" t="n">
-        <v>23.85766709060859</v>
+        <v>11.10686799130573</v>
       </c>
       <c r="H34" t="n">
-        <v>1.00482139642122</v>
+        <v>4.194883912162578</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1691317527297641</v>
+        <v>0.1665413246358264</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9999982815914319</v>
+        <v>0.9086156675625433</v>
       </c>
       <c r="K34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.952120465792567</v>
+        <v>-7.959486597397787</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3875332225805</v>
+        <v>113.4023271786867</v>
       </c>
       <c r="R34" t="n">
-        <v>23.85766709060859</v>
+        <v>11.10686799130573</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,28 +2692,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.960562173733079</v>
+        <v>-7.996505544976156</v>
       </c>
       <c r="D35" t="n">
-        <v>113.3839381917242</v>
+        <v>113.394989061038</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.952256486942742</v>
+        <v>-7.959486597397787</v>
       </c>
       <c r="F35" t="n">
-        <v>113.3876468733991</v>
+        <v>113.4023271786867</v>
       </c>
       <c r="G35" t="n">
-        <v>23.85645941552906</v>
+        <v>11.10686799130573</v>
       </c>
       <c r="H35" t="n">
-        <v>1.009826385266561</v>
+        <v>4.194883912162578</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1691317713764188</v>
+        <v>0.1665413246358264</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8756343897652468</v>
+        <v>0.8816796326939546</v>
       </c>
       <c r="K35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.952256486942742</v>
+        <v>-7.959486597397787</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3876468733991</v>
+        <v>113.4023271786867</v>
       </c>
       <c r="R35" t="n">
-        <v>23.85645941552906</v>
+        <v>11.10686799130573</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.960562173733079</v>
+        <v>-7.996505544976156</v>
       </c>
       <c r="D36" t="n">
-        <v>113.3839381917242</v>
+        <v>113.394989061038</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.952256486942742</v>
+        <v>-7.959486597397787</v>
       </c>
       <c r="F36" t="n">
-        <v>113.3876468733991</v>
+        <v>113.4023271786867</v>
       </c>
       <c r="G36" t="n">
-        <v>23.85645941552906</v>
+        <v>11.10686799130573</v>
       </c>
       <c r="H36" t="n">
-        <v>1.009826385266561</v>
+        <v>4.194883912162578</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1691317713764188</v>
+        <v>0.1665413246358264</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9900651234295614</v>
+        <v>0.9572473335643685</v>
       </c>
       <c r="K36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.952256486942742</v>
+        <v>-7.959486597397787</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.3876468733991</v>
+        <v>113.4023271786867</v>
       </c>
       <c r="R36" t="n">
-        <v>23.85645941552906</v>
+        <v>11.10686799130573</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,28 +2822,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.960532044709543</v>
+        <v>-7.996530800283374</v>
       </c>
       <c r="D37" t="n">
-        <v>113.384012670176</v>
+        <v>113.3950289293184</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.952133971025067</v>
+        <v>-7.959443162897998</v>
       </c>
       <c r="F37" t="n">
-        <v>113.3877626358026</v>
+        <v>113.4023806549176</v>
       </c>
       <c r="G37" t="n">
-        <v>23.85664176573267</v>
+        <v>11.10685716348446</v>
       </c>
       <c r="H37" t="n">
-        <v>1.021060431852134</v>
+        <v>4.202667480027777</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1691317768416955</v>
+        <v>0.1665413253386005</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8937785903505203</v>
+        <v>0.9909478281651229</v>
       </c>
       <c r="K37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.952133971025067</v>
+        <v>-7.959443162897998</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.3877626358026</v>
+        <v>113.4023806549176</v>
       </c>
       <c r="R37" t="n">
-        <v>23.85664176573267</v>
+        <v>11.10685716348446</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.960532044709543</v>
+        <v>-7.99648326682805</v>
       </c>
       <c r="D38" t="n">
-        <v>113.384012670176</v>
+        <v>113.3949884778842</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.952133971025067</v>
+        <v>-7.9594465957314</v>
       </c>
       <c r="F38" t="n">
-        <v>113.3877626358026</v>
+        <v>113.4023300944364</v>
       </c>
       <c r="G38" t="n">
-        <v>23.85664176573267</v>
+        <v>11.10684787584805</v>
       </c>
       <c r="H38" t="n">
-        <v>1.021060431852134</v>
+        <v>4.196891999114677</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1691317768416955</v>
+        <v>0.1665413255135987</v>
       </c>
       <c r="J38" t="n">
-        <v>0.978548799043545</v>
+        <v>0.995868743601997</v>
       </c>
       <c r="K38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.952133971025067</v>
+        <v>-7.9594465957314</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3877626358026</v>
+        <v>113.4023300944364</v>
       </c>
       <c r="R38" t="n">
-        <v>23.85664176573267</v>
+        <v>11.10684787584805</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,28 +2952,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.960532044709543</v>
+        <v>-7.996492810271218</v>
       </c>
       <c r="D39" t="n">
-        <v>113.384012670176</v>
+        <v>113.3950181647336</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.952133971025067</v>
+        <v>-7.959441649416798</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3877626358026</v>
+        <v>113.402362654308</v>
       </c>
       <c r="G39" t="n">
-        <v>23.85664176573267</v>
+        <v>11.10684916663841</v>
       </c>
       <c r="H39" t="n">
-        <v>1.021060431852134</v>
+        <v>4.198533953639536</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1691317768416955</v>
+        <v>0.1665413256453119</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9890840119118978</v>
+        <v>0.9977837914557645</v>
       </c>
       <c r="K39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.952133971025067</v>
+        <v>-7.959441649416798</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3877626358026</v>
+        <v>113.402362654308</v>
       </c>
       <c r="R39" t="n">
-        <v>23.85664176573267</v>
+        <v>11.10684916663841</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,28 +3017,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.960536757879802</v>
+        <v>-7.996492810271218</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3839355736859</v>
+        <v>113.3950181647336</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.952161308058864</v>
+        <v>-7.959441649416798</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3876754256032</v>
+        <v>113.402362654308</v>
       </c>
       <c r="G40" t="n">
-        <v>23.85657480715593</v>
+        <v>11.10684916663841</v>
       </c>
       <c r="H40" t="n">
-        <v>1.018309240778816</v>
+        <v>4.198533953639536</v>
       </c>
       <c r="I40" t="n">
-        <v>0.169131778247999</v>
+        <v>0.1665413256453119</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9934588984306539</v>
+        <v>0.9982815614627019</v>
       </c>
       <c r="K40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.952161308058864</v>
+        <v>-7.959441649416798</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3876754256032</v>
+        <v>113.402362654308</v>
       </c>
       <c r="R40" t="n">
-        <v>23.85657480715593</v>
+        <v>11.10684916663841</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,28 +3082,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.960536757879802</v>
+        <v>-7.996494921436229</v>
       </c>
       <c r="D41" t="n">
-        <v>113.3839355736859</v>
+        <v>113.395010623664</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.952161308058864</v>
+        <v>-7.959449073924558</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3876754256032</v>
+        <v>113.4023540598685</v>
       </c>
       <c r="G41" t="n">
-        <v>23.85657480715593</v>
+        <v>11.10684877683737</v>
       </c>
       <c r="H41" t="n">
-        <v>1.018309240778816</v>
+        <v>4.197931855937335</v>
       </c>
       <c r="I41" t="n">
-        <v>0.169131778247999</v>
+        <v>0.1665413256695979</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9956164962254404</v>
+        <v>0.9987944573093912</v>
       </c>
       <c r="K41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.952161308058864</v>
+        <v>-7.959449073924558</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3876754256032</v>
+        <v>113.4023540598685</v>
       </c>
       <c r="R41" t="n">
-        <v>23.85657480715593</v>
+        <v>11.10684877683737</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,28 +3147,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.960486820794006</v>
+        <v>-7.996491544740389</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3839626759787</v>
+        <v>113.3950032905347</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.952139846182408</v>
+        <v>-7.959440315454129</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3876898183483</v>
+        <v>113.4023477944901</v>
       </c>
       <c r="G42" t="n">
-        <v>23.85660624643505</v>
+        <v>11.10685040521545</v>
       </c>
       <c r="H42" t="n">
-        <v>1.01484740301852</v>
+        <v>4.198541725947817</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1691317783917901</v>
+        <v>0.1665413256980411</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5857842003087439</v>
+        <v>0.5857862590011269</v>
       </c>
       <c r="K42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.952139846182408</v>
+        <v>-7.959440315454129</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3876898183483</v>
+        <v>113.4023477944901</v>
       </c>
       <c r="R42" t="n">
-        <v>23.85660624643505</v>
+        <v>11.10685040521545</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,28 +3212,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.960481589436879</v>
+        <v>-7.996462187592283</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3839673942054</v>
+        <v>113.3950130577606</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.952140418716488</v>
+        <v>-7.959440993885825</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3876919409409</v>
+        <v>113.402351608371</v>
       </c>
       <c r="G43" t="n">
-        <v>23.85658317093849</v>
+        <v>11.10685107520982</v>
       </c>
       <c r="H43" t="n">
-        <v>1.014141571252767</v>
+        <v>4.195138193600163</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1691317787184175</v>
+        <v>0.1665413257079993</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9995675072977078</v>
+        <v>0.999921673822152</v>
       </c>
       <c r="K43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.952140418716488</v>
+        <v>-7.959440993885825</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3876919409409</v>
+        <v>113.402351608371</v>
       </c>
       <c r="R43" t="n">
-        <v>23.85658317093849</v>
+        <v>11.10685107520982</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,28 +3277,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.960523563725919</v>
+        <v>-7.996462187592283</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3839720887466</v>
+        <v>113.3950130577606</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.952148662459409</v>
+        <v>-7.959440993885825</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3877116977691</v>
+        <v>113.402351608371</v>
       </c>
       <c r="G44" t="n">
-        <v>23.85658706876551</v>
+        <v>11.10685107520982</v>
       </c>
       <c r="H44" t="n">
-        <v>1.018242642588143</v>
+        <v>4.195138193600163</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1691317787514522</v>
+        <v>0.1665413257079993</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9375702020140879</v>
+        <v>0.9999473466556272</v>
       </c>
       <c r="K44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.952148662459409</v>
+        <v>-7.959440993885825</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3877116977691</v>
+        <v>113.402351608371</v>
       </c>
       <c r="R44" t="n">
-        <v>23.85658706876551</v>
+        <v>11.10685107520982</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,28 +3342,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.960532450591233</v>
+        <v>-7.996461782377835</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3839683833215</v>
+        <v>113.3950144945461</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.952152865518666</v>
+        <v>-7.959444751446957</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3877100835419</v>
+        <v>113.4023522198313</v>
       </c>
       <c r="G45" t="n">
-        <v>23.85658550431788</v>
+        <v>11.10685074302623</v>
       </c>
       <c r="H45" t="n">
-        <v>1.01881209867228</v>
+        <v>4.194666475555761</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1691317787607502</v>
+        <v>0.166541325709513</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9801524121900625</v>
+        <v>0.9999706751082291</v>
       </c>
       <c r="K45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.952152865518666</v>
+        <v>-7.959444751446957</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3877100835419</v>
+        <v>113.4023522198313</v>
       </c>
       <c r="R45" t="n">
-        <v>23.85658550431788</v>
+        <v>11.10685074302623</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.960522607720796</v>
+        <v>-7.996461782377835</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3839645855783</v>
+        <v>113.3950144945461</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.952141645299152</v>
+        <v>-7.959444751446957</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3877069006901</v>
+        <v>113.4023522198313</v>
       </c>
       <c r="G46" t="n">
-        <v>23.85658535258106</v>
+        <v>11.10685074302623</v>
       </c>
       <c r="H46" t="n">
-        <v>1.018979558887565</v>
+        <v>4.194666475555761</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1691317787888912</v>
+        <v>0.166541325709513</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9901145150911479</v>
+        <v>0.9999801921358658</v>
       </c>
       <c r="K46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.952141645299152</v>
+        <v>-7.959444751446957</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3877069006901</v>
+        <v>113.4023522198313</v>
       </c>
       <c r="R46" t="n">
-        <v>23.85658535258106</v>
+        <v>11.10685074302623</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,28 +3472,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.960528190242462</v>
+        <v>-7.996461679604253</v>
       </c>
       <c r="D47" t="n">
-        <v>113.38396676541</v>
+        <v>113.3950129894889</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.952148975890325</v>
+        <v>-7.959442274868937</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3877082998915</v>
+        <v>113.4023511853302</v>
       </c>
       <c r="G47" t="n">
-        <v>23.85658455506401</v>
+        <v>11.10685082017921</v>
       </c>
       <c r="H47" t="n">
-        <v>1.018767018129451</v>
+        <v>4.194935469079406</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1691317787953459</v>
+        <v>0.1665413257110328</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9954517822371847</v>
+        <v>0.9999938340435878</v>
       </c>
       <c r="K47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.952148975890325</v>
+        <v>-7.959442274868937</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3877082998915</v>
+        <v>113.4023511853302</v>
       </c>
       <c r="R47" t="n">
-        <v>23.85658455506401</v>
+        <v>11.10685082017921</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,28 +3537,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.960526723962381</v>
+        <v>-7.996461679604253</v>
       </c>
       <c r="D48" t="n">
-        <v>113.3839634508667</v>
+        <v>113.3950129894889</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.952147563768141</v>
+        <v>-7.959442274868937</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3877049610761</v>
+        <v>113.4023511853302</v>
       </c>
       <c r="G48" t="n">
-        <v>23.85658412282993</v>
+        <v>11.10685082017921</v>
       </c>
       <c r="H48" t="n">
-        <v>1.018760430084465</v>
+        <v>4.194935469079406</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1691317788054841</v>
+        <v>0.1665413257110328</v>
       </c>
       <c r="J48" t="n">
-        <v>0.99794455432769</v>
+        <v>0.9999957760319795</v>
       </c>
       <c r="K48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.952147563768141</v>
+        <v>-7.959442274868937</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3877049610761</v>
+        <v>113.4023511853302</v>
       </c>
       <c r="R48" t="n">
-        <v>23.85658412282993</v>
+        <v>11.10685082017921</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,28 +3602,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.960524835816051</v>
+        <v>-7.996494379034466</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3839655273843</v>
+        <v>113.3950073806979</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.95214469443126</v>
+        <v>-7.959443886510594</v>
       </c>
       <c r="F49" t="n">
-        <v>113.387707475685</v>
+        <v>113.4023517389919</v>
       </c>
       <c r="G49" t="n">
-        <v>23.85658407497402</v>
+        <v>11.10685087640107</v>
       </c>
       <c r="H49" t="n">
-        <v>1.018879725209245</v>
+        <v>4.198458245014469</v>
       </c>
       <c r="I49" t="n">
-        <v>0.169131778807909</v>
+        <v>0.1665413257121076</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9985995413858773</v>
+        <v>0.9999972455301572</v>
       </c>
       <c r="K49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.95214469443126</v>
+        <v>-7.959443886510594</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.387707475685</v>
+        <v>113.4023517389919</v>
       </c>
       <c r="R49" t="n">
-        <v>23.85658407497402</v>
+        <v>11.10685087640107</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,28 +3667,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.960524372035272</v>
+        <v>-7.996492737429502</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3839651135869</v>
+        <v>113.3950072867701</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.952145664804697</v>
+        <v>-7.959443384118067</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3877064215158</v>
+        <v>113.4023514192365</v>
       </c>
       <c r="G50" t="n">
-        <v>23.85658410161894</v>
+        <v>11.10685087961656</v>
       </c>
       <c r="H50" t="n">
-        <v>1.018705357509355</v>
+        <v>4.198329152918841</v>
       </c>
       <c r="I50" t="n">
-        <v>0.169131778808422</v>
+        <v>0.1665413257122775</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9993408661591909</v>
+        <v>0.9999980577450289</v>
       </c>
       <c r="K50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.952145664804697</v>
+        <v>-7.959443384118067</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3877064215158</v>
+        <v>113.4023514192365</v>
       </c>
       <c r="R50" t="n">
-        <v>23.85658410161894</v>
+        <v>11.10685087961656</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,28 +3732,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.960525225435631</v>
+        <v>-7.996492737429502</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3839632661074</v>
+        <v>113.3950072867701</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.952144626956691</v>
+        <v>-7.959443384118067</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3877054185246</v>
+        <v>113.4023514192365</v>
       </c>
       <c r="G51" t="n">
-        <v>23.85658414961688</v>
+        <v>11.10685087961656</v>
       </c>
       <c r="H51" t="n">
-        <v>1.018935300399315</v>
+        <v>4.198329152918841</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1691317788091306</v>
+        <v>0.1665413257122775</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9998896495106033</v>
+        <v>0.999999293079385</v>
       </c>
       <c r="K51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.952144626956691</v>
+        <v>-7.959443384118067</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3877054185246</v>
+        <v>113.4023514192365</v>
       </c>
       <c r="R51" t="n">
-        <v>23.85658414961688</v>
+        <v>11.10685087961656</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,28 +3797,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.960525040570624</v>
+        <v>-7.996492737429502</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3839646761777</v>
+        <v>113.3950072867701</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.952144656487059</v>
+        <v>-7.959443384118067</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3877067328595</v>
+        <v>113.4023514192365</v>
       </c>
       <c r="G52" t="n">
-        <v>23.85658413423836</v>
+        <v>11.10685087961656</v>
       </c>
       <c r="H52" t="n">
-        <v>1.018909233574163</v>
+        <v>4.198329152918841</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1691317788092065</v>
+        <v>0.1665413257122775</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5857864387432078</v>
+        <v>0.585786439812261</v>
       </c>
       <c r="K52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.952144656487059</v>
+        <v>-7.959443384118067</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3877067328595</v>
+        <v>113.4023514192365</v>
       </c>
       <c r="R52" t="n">
-        <v>23.85658413423836</v>
+        <v>11.10685087961656</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,28 +3862,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.960525114913601</v>
+        <v>-7.996492997899454</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3839641839783</v>
+        <v>113.3950075199112</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.952144366504116</v>
+        <v>-7.959443622580974</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3877064033383</v>
+        <v>113.4023516567522</v>
       </c>
       <c r="G53" t="n">
-        <v>23.85658413549177</v>
+        <v>11.10685089140399</v>
       </c>
       <c r="H53" t="n">
-        <v>1.018953529203177</v>
+        <v>4.19833164686026</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1691317788092801</v>
+        <v>0.1665413257124022</v>
       </c>
       <c r="J53" t="n">
-        <v>0.999999930157861</v>
+        <v>0.9999999274552044</v>
       </c>
       <c r="K53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.952144366504116</v>
+        <v>-7.959443622580974</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3877064033383</v>
+        <v>113.4023516567522</v>
       </c>
       <c r="R53" t="n">
-        <v>23.85658413549177</v>
+        <v>11.10685089140399</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,28 +3927,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.960525154566566</v>
+        <v>-7.996492997899454</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3839640516287</v>
+        <v>113.3950075199112</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.952144398849159</v>
+        <v>-7.959443622580974</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3877062742544</v>
+        <v>113.4023516567522</v>
       </c>
       <c r="G54" t="n">
-        <v>23.85658414832389</v>
+        <v>11.10685089140399</v>
       </c>
       <c r="H54" t="n">
-        <v>1.018954417818809</v>
+        <v>4.19833164686026</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1691317788093638</v>
+        <v>0.1665413257124022</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999525114551</v>
+        <v>0.9999999569259156</v>
       </c>
       <c r="K54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.952144398849159</v>
+        <v>-7.959443622580974</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3877062742544</v>
+        <v>113.4023516567522</v>
       </c>
       <c r="R54" t="n">
-        <v>23.85658414832389</v>
+        <v>11.10685089140399</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,28 +3992,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.960524991235676</v>
+        <v>-7.996492997899454</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3839642752151</v>
+        <v>113.3950075199112</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.952144713739896</v>
+        <v>-7.959443622580974</v>
       </c>
       <c r="F55" t="n">
-        <v>113.387706284305</v>
+        <v>113.4023516567522</v>
       </c>
       <c r="G55" t="n">
-        <v>23.85658414313681</v>
+        <v>11.10685089140399</v>
       </c>
       <c r="H55" t="n">
-        <v>1.018896274445531</v>
+        <v>4.19833164686026</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1691317788094159</v>
+        <v>0.1665413257124022</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999552206795</v>
+        <v>0.9999999775100311</v>
       </c>
       <c r="K55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.952144713739896</v>
+        <v>-7.959443622580974</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.387706284305</v>
+        <v>113.4023516567522</v>
       </c>
       <c r="R55" t="n">
-        <v>23.85658414313681</v>
+        <v>11.10685089140399</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,28 +4057,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.960524991235676</v>
+        <v>-7.996492892331339</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3839642752151</v>
+        <v>113.3950072780383</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.952144713739896</v>
+        <v>-7.95944353033487</v>
       </c>
       <c r="F56" t="n">
-        <v>113.387706284305</v>
+        <v>113.402351412236</v>
       </c>
       <c r="G56" t="n">
-        <v>23.85658414313681</v>
+        <v>11.10685089013937</v>
       </c>
       <c r="H56" t="n">
-        <v>1.018896274445531</v>
+        <v>4.198330137231753</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1691317788094159</v>
+        <v>0.1665413257124126</v>
       </c>
       <c r="J56" t="n">
-        <v>0.999999958481099</v>
+        <v>0.9999999881652472</v>
       </c>
       <c r="K56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.952144713739896</v>
+        <v>-7.95944353033487</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.387706284305</v>
+        <v>113.402351412236</v>
       </c>
       <c r="R56" t="n">
-        <v>23.85658414313681</v>
+        <v>11.10685089013937</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,28 +4122,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.960525350366972</v>
+        <v>-7.996492101663477</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3839641222978</v>
+        <v>113.3950074118184</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.952144612087235</v>
+        <v>-7.959443339309658</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3877063371386</v>
+        <v>113.4023514271492</v>
       </c>
       <c r="G57" t="n">
-        <v>23.85658414513238</v>
+        <v>11.10685089135784</v>
       </c>
       <c r="H57" t="n">
-        <v>1.018952297679982</v>
+        <v>4.198262187539755</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1691317788094223</v>
+        <v>0.1665413257124408</v>
       </c>
       <c r="J57" t="n">
-        <v>0.999999963521409</v>
+        <v>0.999999991136174</v>
       </c>
       <c r="K57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.952144612087235</v>
+        <v>-7.959443339309658</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3877063371386</v>
+        <v>113.4023514271492</v>
       </c>
       <c r="R57" t="n">
-        <v>23.85658414513238</v>
+        <v>11.10685089135784</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,28 +4187,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.960525350366972</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D58" t="n">
-        <v>113.3839641222978</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.952144612087235</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3877063371386</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G58" t="n">
-        <v>23.85658414513238</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H58" t="n">
-        <v>1.018952297679982</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1691317788094223</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J58" t="n">
-        <v>0.999999968541733</v>
+        <v>0.9999999959041495</v>
       </c>
       <c r="K58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.952144612087235</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3877063371386</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R58" t="n">
-        <v>23.85658414513238</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,28 +4252,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.960524991268286</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3839642646231</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.952144692367129</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F59" t="n">
-        <v>113.387706283271</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G59" t="n">
-        <v>23.85658414413128</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H59" t="n">
-        <v>1.018898876970717</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1691317788094316</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999741371062</v>
+        <v>0.9999999982209173</v>
       </c>
       <c r="K59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.952144692367129</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.387706283271</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R59" t="n">
-        <v>23.85658414413128</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,28 +4317,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.960524984179825</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3839641838584</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.952144573434711</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3877062524463</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G60" t="n">
-        <v>23.85658414437628</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H60" t="n">
-        <v>1.018912475229065</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1691317788094362</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999788825202</v>
+        <v>0.9999999995152891</v>
       </c>
       <c r="K60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.952144573434711</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3877062524463</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R60" t="n">
-        <v>23.85658414437628</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.960524984179825</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3839641838584</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.952144573434711</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3877062524463</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G61" t="n">
-        <v>23.85658414437628</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H61" t="n">
-        <v>1.018912475229065</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1691317788094362</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9999999863157361</v>
+        <v>0.9585908307947599</v>
       </c>
       <c r="K61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.952144573434711</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3877062524463</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R61" t="n">
-        <v>23.85658414437628</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,28 +4447,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.960524988988153</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3839641599688</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.952144635113933</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F62" t="n">
-        <v>113.387706203163</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G62" t="n">
-        <v>23.85658414435779</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H62" t="n">
-        <v>1.018905560729221</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1691317788094365</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857864397788425</v>
+        <v>0.5857057452249197</v>
       </c>
       <c r="K62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.952144635113933</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.387706203163</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R62" t="n">
-        <v>23.85658414435779</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,28 +4512,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.960524982144791</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D63" t="n">
-        <v>113.3839641991396</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.952144611122382</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3877062499907</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G63" t="n">
-        <v>23.85658414437706</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H63" t="n">
-        <v>1.018907645647171</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1691317788094367</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999999478457</v>
+        <v>0.9999999995775086</v>
       </c>
       <c r="K63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.952144611122382</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3877062499907</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R63" t="n">
-        <v>23.85658414437706</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,28 +4577,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.960525150521571</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3839641149879</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.952144598615</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3877062466081</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G64" t="n">
-        <v>23.85658414433643</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H64" t="n">
-        <v>1.018929637977172</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1691317788094373</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9999999999440683</v>
+        <v>0.8844967830942793</v>
       </c>
       <c r="K64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.952144598615</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3877062466081</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R64" t="n">
-        <v>23.85658414433643</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,28 +4642,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.960525150521571</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3839641149879</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.952144598615</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3877062466081</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G65" t="n">
-        <v>23.85658414433643</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H65" t="n">
-        <v>1.018929637977172</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1691317788094373</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8931312500208971</v>
+        <v>0.9006029382396817</v>
       </c>
       <c r="K65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.952144598615</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3877062466081</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R65" t="n">
-        <v>23.85658414433643</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,28 +4707,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.960525141929485</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D66" t="n">
-        <v>113.3839641023582</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.952144595999457</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3877062313097</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G66" t="n">
-        <v>23.85658414432832</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H66" t="n">
-        <v>1.018928911335133</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1691317788094374</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9840449370247391</v>
+        <v>0.9700495214691597</v>
       </c>
       <c r="K66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.952144595999457</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3877062313097</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R66" t="n">
-        <v>23.85658414432832</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,28 +4772,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.960525175204721</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D67" t="n">
-        <v>113.383964104229</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.952144619139962</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3877062377061</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G67" t="n">
-        <v>23.85658414432524</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H67" t="n">
-        <v>1.018930143539719</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1691317788094374</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J67" t="n">
-        <v>0.916392257309648</v>
+        <v>0.9865528009359226</v>
       </c>
       <c r="K67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.952144619139962</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3877062377061</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R67" t="n">
-        <v>23.85658414432524</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,28 +4837,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.960525142107536</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3839641115211</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.952144615236216</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3877062319626</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G68" t="n">
-        <v>23.85658414432531</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H68" t="n">
-        <v>1.018926594131404</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9827716258827326</v>
+        <v>0.9919298651047526</v>
       </c>
       <c r="K68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.952144615236216</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3877062319626</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R68" t="n">
-        <v>23.85658414432531</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,28 +4902,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.960525142107536</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3839641115211</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.952144615236216</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3877062319626</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G69" t="n">
-        <v>23.85658414432531</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H69" t="n">
-        <v>1.018926594131404</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J69" t="n">
-        <v>0.993058749594921</v>
+        <v>0.9957625648586879</v>
       </c>
       <c r="K69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.952144615236216</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3877062319626</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R69" t="n">
-        <v>23.85658414432531</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,28 +4967,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D70" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G70" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H70" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9947140553447563</v>
+        <v>0.9977391010127504</v>
       </c>
       <c r="K70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R70" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,28 +5032,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D71" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G71" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H71" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9303263855229162</v>
+        <v>0.9979117863815348</v>
       </c>
       <c r="K71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R71" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,28 +5097,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D72" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G72" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H72" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5855927137212986</v>
+        <v>0.5857852584277309</v>
       </c>
       <c r="K72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R72" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,28 +5162,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G73" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H73" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9994188452974608</v>
+        <v>0.9995944264398513</v>
       </c>
       <c r="K73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R73" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,28 +5227,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G74" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H74" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9635222448313182</v>
+        <v>0.9996184721650414</v>
       </c>
       <c r="K74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R74" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,28 +5292,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G75" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H75" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J75" t="n">
-        <v>0.999686364308439</v>
+        <v>0.9996899258226382</v>
       </c>
       <c r="K75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R75" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,28 +5357,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G76" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H76" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9997975784884184</v>
+        <v>0.9998717285234845</v>
       </c>
       <c r="K76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R76" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,28 +5422,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G77" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H77" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9999756408143011</v>
+        <v>0.9998819471930822</v>
       </c>
       <c r="K77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R77" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,28 +5487,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G78" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H78" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9999756408131815</v>
+        <v>0.9999414448958831</v>
       </c>
       <c r="K78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R78" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,28 +5552,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G79" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H79" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9999760286404076</v>
+        <v>0.99996620234971</v>
       </c>
       <c r="K79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R79" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,28 +5617,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G80" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H80" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9999870071609924</v>
+        <v>0.9999846125651255</v>
       </c>
       <c r="K80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R80" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,28 +5682,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G81" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H81" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9999932435568492</v>
+        <v>0.9999949556902388</v>
       </c>
       <c r="K81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R81" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,28 +5747,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G82" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H82" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857864397788288</v>
+        <v>0.5857864398031205</v>
       </c>
       <c r="K82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R82" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,28 +5812,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G83" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H83" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R83" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,28 +5877,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.960525173266147</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3839641017181</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G84" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H84" t="n">
-        <v>1.01893057002827</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.952144613693572</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3877062367616</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R84" t="n">
-        <v>23.85658414432817</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,28 +5942,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G85" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H85" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R85" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,28 +6007,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G86" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H86" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R86" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,25 +6072,25 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G87" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H87" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J87" t="n">
         <v>0.9999999999999998</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R87" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,25 +6137,25 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G88" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H88" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J88" t="n">
         <v>0.9999999999999998</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R88" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,25 +6202,25 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492584092066</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073206618</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="G89" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="H89" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321359725795</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124506</v>
       </c>
       <c r="J89" t="n">
         <v>0.9999999999999998</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443299555603</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514395022</v>
       </c>
       <c r="R89" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220932</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,28 +6267,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492647726609</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073529457</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="G90" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="H90" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198323798877798</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124514</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999989</v>
       </c>
       <c r="K90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="R90" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,28 +6332,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492647726609</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073529457</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="G91" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="H91" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198323798877798</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124514</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0.9263831001902727</v>
       </c>
       <c r="K91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="R91" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,28 +6397,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492647726609</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073529457</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="G92" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="H92" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198323798877798</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124514</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5857864397788425</v>
+        <v>0.5853512359782157</v>
       </c>
       <c r="K92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="R92" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,28 +6462,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492647726609</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073529457</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="G93" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="H93" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198323798877798</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124514</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0.9999999999999984</v>
       </c>
       <c r="K93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443341665116</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514760537</v>
       </c>
       <c r="R93" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220767</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,28 +6527,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G94" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H94" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0.9355593375424699</v>
       </c>
       <c r="K94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R94" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,28 +6592,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G95" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H95" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0.8834536852109889</v>
       </c>
       <c r="K95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R95" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,28 +6657,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G96" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H96" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J96" t="n">
-        <v>0.970822951434357</v>
+        <v>0.9456579653655832</v>
       </c>
       <c r="K96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R96" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,28 +6722,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G97" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H97" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J97" t="n">
-        <v>0.946730228027001</v>
+        <v>0.9770749257675437</v>
       </c>
       <c r="K97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R97" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,28 +6787,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G98" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H98" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9903531666889616</v>
+        <v>0.9878029602584926</v>
       </c>
       <c r="K98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R98" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,28 +6852,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G99" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H99" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9963610046126296</v>
+        <v>0.9963558781176564</v>
       </c>
       <c r="K99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R99" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,28 +6917,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G100" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H100" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9976129501145409</v>
+        <v>0.9978412783819535</v>
       </c>
       <c r="K100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R100" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,28 +6982,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636990905</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073300563</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="G101" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="H101" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322022060852</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124515</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9976551190537236</v>
+        <v>0.998233869651551</v>
       </c>
       <c r="K101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346609469</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514500562</v>
       </c>
       <c r="R101" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220874</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,28 +7047,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637204366</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326256</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="G102" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="H102" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321491558088</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5817371805906378</v>
+        <v>0.5857854668110557</v>
       </c>
       <c r="K102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="R102" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,28 +7112,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637204366</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326256</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="G103" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="H103" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321491558088</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J103" t="n">
-        <v>0.999215197937697</v>
+        <v>0.9999999999999971</v>
       </c>
       <c r="K103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="R103" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,28 +7177,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637204366</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326256</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="G104" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="H104" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321491558088</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9284508407569829</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="R104" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,28 +7242,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637204366</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326256</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="G105" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="H105" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321491558088</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9685875910982751</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443351504509</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514516976</v>
       </c>
       <c r="R105" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220861</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,28 +7307,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G106" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H106" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J106" t="n">
-        <v>0.984176046374356</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R106" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,28 +7372,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G107" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H107" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9895026206402672</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R107" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,28 +7437,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G108" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H108" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9945686069341809</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R108" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,28 +7502,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G109" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H109" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9964979998394764</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R109" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,28 +7567,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G110" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H110" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9982670958029953</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R110" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,28 +7632,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G111" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H111" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9990197908207936</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R111" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,28 +7697,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G112" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H112" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5857860893963442</v>
+        <v>0.5857864398123146</v>
       </c>
       <c r="K112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R112" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,25 +7762,25 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492631361938</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073356992</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="G113" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="H113" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321605081839</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J113" t="n">
         <v>1</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443344660257</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514549697</v>
       </c>
       <c r="R113" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220798</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,28 +7827,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637082704</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073307059</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="G114" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="H114" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321377903479</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="R114" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,28 +7892,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637082704</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073307059</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="G115" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="H115" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321377903479</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="R115" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,28 +7957,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637082704</v>
       </c>
       <c r="D116" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073307059</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="G116" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="H116" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321377903479</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="R116" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,28 +8022,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637082704</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073307059</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="G117" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="H117" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321377903479</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443352385827</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514495791</v>
       </c>
       <c r="R117" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220566</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492634704269</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073329196</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="G118" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="H118" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321521728682</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="R118" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,28 +8152,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492634704269</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073329196</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="G119" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="H119" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321521728682</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="R119" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,28 +8217,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492634704269</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073329196</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="G120" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="H120" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321521728682</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="R120" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,28 +8282,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492634704269</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073329196</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="G121" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="H121" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321521728682</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124516</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348738161</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520443</v>
       </c>
       <c r="R121" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089220422</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,28 +8347,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637662654</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073290671</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346540245</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514492139</v>
       </c>
       <c r="G122" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219783</v>
       </c>
       <c r="H122" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322106025437</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857864397788425</v>
+        <v>0.5857864398123146</v>
       </c>
       <c r="K122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443346540245</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514492139</v>
       </c>
       <c r="R122" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219783</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,28 +8412,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492638929497</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326659</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443350521477</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514522747</v>
       </c>
       <c r="G123" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219813</v>
       </c>
       <c r="H123" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321798438977</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443350521477</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514522747</v>
       </c>
       <c r="R123" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219813</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,28 +8477,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492638929497</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326659</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443350521477</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514522747</v>
       </c>
       <c r="G124" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219813</v>
       </c>
       <c r="H124" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321798438977</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0.9025431043643038</v>
       </c>
       <c r="K124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443350521477</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514522747</v>
       </c>
       <c r="R124" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219813</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,28 +8542,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G125" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H125" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0.8936035806071022</v>
       </c>
       <c r="K125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R125" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,28 +8607,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G126" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H126" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9196114514951105</v>
+        <v>0.9334307853784155</v>
       </c>
       <c r="K126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R126" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,28 +8672,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G127" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H127" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9068381478320633</v>
+        <v>0.977336597496686</v>
       </c>
       <c r="K127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R127" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,28 +8737,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G128" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H128" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9846036274929536</v>
+        <v>0.8818066871400528</v>
       </c>
       <c r="K128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R128" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,28 +8802,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G129" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H129" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9914506961677259</v>
+        <v>0.9596847862874449</v>
       </c>
       <c r="K129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R129" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,28 +8867,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G130" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H130" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J130" t="n">
-        <v>0.996271336449749</v>
+        <v>0.9718245328978098</v>
       </c>
       <c r="K130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R130" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,28 +8932,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G131" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H131" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9981121420709919</v>
+        <v>0.9873685035285413</v>
       </c>
       <c r="K131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R131" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,28 +8997,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G132" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H132" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5819171146298913</v>
+        <v>0.5857807839914929</v>
       </c>
       <c r="K132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R132" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,28 +9062,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D133" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G133" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H133" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9991433951462541</v>
+        <v>0.9992587145507036</v>
       </c>
       <c r="K133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R133" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,28 +9127,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D134" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G134" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H134" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9440056764527046</v>
+        <v>0.9993509829344496</v>
       </c>
       <c r="K134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R134" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,28 +9192,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492644649821</v>
       </c>
       <c r="D135" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073315269</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="G135" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="H135" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321694429744</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124517</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9740215389181714</v>
+        <v>0.9995010948483487</v>
       </c>
       <c r="K135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443357159659</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514509539</v>
       </c>
       <c r="R135" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219486</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,28 +9257,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D136" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G136" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H136" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9937316342567262</v>
+        <v>0.9997627336312898</v>
       </c>
       <c r="K136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R136" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,28 +9322,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D137" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G137" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H137" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J137" t="n">
-        <v>0.998884786202572</v>
+        <v>0.9998326787502788</v>
       </c>
       <c r="K137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R137" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,28 +9387,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D138" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G138" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H138" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0.9999216178442795</v>
       </c>
       <c r="K138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R138" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,28 +9452,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D139" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G139" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H139" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0.9999831921193196</v>
       </c>
       <c r="K139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R139" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,28 +9517,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D140" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G140" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H140" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0.9999871698765824</v>
       </c>
       <c r="K140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R140" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,28 +9582,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D141" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G141" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H141" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
+        <v>0.9999876002810782</v>
       </c>
       <c r="K141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R141" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,28 +9647,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637240565</v>
       </c>
       <c r="D142" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073280323</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="G142" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="H142" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321791687085</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857864397788425</v>
+        <v>0.5857864398045713</v>
       </c>
       <c r="K142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348892131</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514476293</v>
       </c>
       <c r="R142" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219505</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,28 +9712,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492637049576</v>
       </c>
       <c r="D143" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073322035</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443349064713</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514517284</v>
       </c>
       <c r="G143" t="n">
-        <v>23.85658414432697</v>
+        <v>11.1068508921925</v>
       </c>
       <c r="H143" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321750487523</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0.9999999381618503</v>
       </c>
       <c r="K143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443349064713</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514517284</v>
       </c>
       <c r="R143" t="n">
-        <v>23.85658414432697</v>
+        <v>11.1068508921925</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,28 +9777,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492639639535</v>
       </c>
       <c r="D144" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073306689</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443343951803</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514517206</v>
       </c>
       <c r="G144" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219156</v>
       </c>
       <c r="H144" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322623354177</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443343951803</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514517206</v>
       </c>
       <c r="R144" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089219156</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,28 +9842,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636551791</v>
       </c>
       <c r="D145" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326119</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348978319</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520552</v>
       </c>
       <c r="G145" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218757</v>
       </c>
       <c r="H145" t="n">
-        <v>1.01890940942808</v>
+        <v>4.19832170387035</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348978319</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520552</v>
       </c>
       <c r="R145" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218757</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,28 +9907,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636551791</v>
       </c>
       <c r="D146" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073326119</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348978319</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520552</v>
       </c>
       <c r="G146" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218757</v>
       </c>
       <c r="H146" t="n">
-        <v>1.01890940942808</v>
+        <v>4.19832170387035</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124518</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348978319</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514520552</v>
       </c>
       <c r="R146" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218757</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,28 +9972,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492636527028</v>
       </c>
       <c r="D147" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073329351</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443347302643</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514527056</v>
       </c>
       <c r="G147" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218751</v>
       </c>
       <c r="H147" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321890946898</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124519</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443347302643</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514527056</v>
       </c>
       <c r="R147" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218751</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,28 +10037,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492634377693</v>
       </c>
       <c r="D148" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073322339</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443347560597</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514515273</v>
       </c>
       <c r="G148" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218264</v>
       </c>
       <c r="H148" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198321618159794</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124519</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443347560597</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514515273</v>
       </c>
       <c r="R148" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218264</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,28 +10102,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492640304528</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073281443</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348145716</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514484966</v>
       </c>
       <c r="G149" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218194</v>
       </c>
       <c r="H149" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322223467372</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124519</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.959443348145716</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514484966</v>
       </c>
       <c r="R149" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089218194</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,28 +10167,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492640305561</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073283729</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.9594433497499</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514484074</v>
       </c>
       <c r="G150" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089217983</v>
       </c>
       <c r="H150" t="n">
-        <v>1.01890940942808</v>
+        <v>4.19832204180276</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.1665413257124519</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.9594433497499</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514484074</v>
       </c>
       <c r="R150" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089217983</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,28 +10232,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.960525000368167</v>
+        <v>-7.996492642011622</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3839641736545</v>
+        <v>113.3950073271609</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.95944335146288</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514471941</v>
       </c>
       <c r="G151" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089217502</v>
       </c>
       <c r="H151" t="n">
-        <v>1.01890940942808</v>
+        <v>4.198322041018889</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1691317788094375</v>
+        <v>0.166541325712452</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.952144614838879</v>
+        <v>-7.95944335146288</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3877062309833</v>
+        <v>113.4023514471941</v>
       </c>
       <c r="R151" t="n">
-        <v>23.85658414432697</v>
+        <v>11.10685089217502</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.153593526264119</v>
+        <v>-7.758869897387893</v>
       </c>
       <c r="D2" t="n">
-        <v>113.3311362201217</v>
+        <v>113.3313620128502</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.900241723811564</v>
       </c>
       <c r="F2" t="n">
-        <v>113.4647183977525</v>
+        <v>113.4042126851261</v>
       </c>
       <c r="G2" t="n">
-        <v>38.13208364715861</v>
+        <v>152.96024955412</v>
       </c>
       <c r="H2" t="n">
-        <v>23.8222295006408</v>
+        <v>17.64979847275782</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1646129267166912</v>
+        <v>0.170977603613874</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8936956683759264</v>
+        <v>0.848426528906747</v>
       </c>
       <c r="K2" t="n">
-        <v>1965</v>
+        <v>1252</v>
       </c>
       <c r="L2" t="n">
-        <v>1797</v>
+        <v>448</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O2" t="n">
-        <v>113.491685257373</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.900241723811564</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.4647183977525</v>
+        <v>113.4042126851261</v>
       </c>
       <c r="R2" t="n">
-        <v>38.13208364715861</v>
+        <v>152.96024955412</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.153593526264119</v>
+        <v>-7.993596736027385</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3311362201217</v>
+        <v>113.3979638491904</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.98655178101114</v>
       </c>
       <c r="F3" t="n">
-        <v>113.4647183977525</v>
+        <v>113.4036085074246</v>
       </c>
       <c r="G3" t="n">
-        <v>38.13208364715861</v>
+        <v>38.43084049780076</v>
       </c>
       <c r="H3" t="n">
-        <v>23.8222295006408</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1646129267166912</v>
+        <v>0.1717180389495196</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9625162531734641</v>
+        <v>0.8760281541333088</v>
       </c>
       <c r="K3" t="n">
-        <v>1965</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>1797</v>
+        <v>448</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O3" t="n">
-        <v>113.491685257373</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.98655178101114</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.4647183977525</v>
+        <v>113.4036085074246</v>
       </c>
       <c r="R3" t="n">
-        <v>38.13208364715861</v>
+        <v>38.43084049780076</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.153593526264119</v>
+        <v>-7.993596736027385</v>
       </c>
       <c r="D4" t="n">
-        <v>113.3311362201217</v>
+        <v>113.3979638491904</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.98655178101114</v>
       </c>
       <c r="F4" t="n">
-        <v>113.4647183977525</v>
+        <v>113.4036085074246</v>
       </c>
       <c r="G4" t="n">
-        <v>38.13208364715861</v>
+        <v>38.43084049780076</v>
       </c>
       <c r="H4" t="n">
-        <v>23.8222295006408</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1646129267166912</v>
+        <v>0.1717180389495196</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9845888442782867</v>
+        <v>0.9683215011049801</v>
       </c>
       <c r="K4" t="n">
-        <v>1965</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>1797</v>
+        <v>448</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O4" t="n">
-        <v>113.491685257373</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.98655178101114</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.4647183977525</v>
+        <v>113.4036085074246</v>
       </c>
       <c r="R4" t="n">
-        <v>38.13208364715861</v>
+        <v>38.43084049780076</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -742,31 +742,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.967866336324673</v>
+        <v>-8.126026477429207</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3691552709739</v>
+        <v>113.1881633270401</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.967951901139388</v>
+        <v>-7.949127122244501</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3782357441071</v>
+        <v>113.3738842397426</v>
       </c>
       <c r="G5" t="n">
-        <v>90.54577101877454</v>
+        <v>46.12405460523132</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>28.37351051231659</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1653759356907702</v>
+        <v>0.171922567619131</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9892536025145591</v>
+        <v>0.9896453092969095</v>
       </c>
       <c r="K5" t="n">
-        <v>640</v>
+        <v>870</v>
       </c>
       <c r="L5" t="n">
         <v>448</v>
@@ -781,13 +781,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.967951901139388</v>
+        <v>-7.949127122244501</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3782357441071</v>
+        <v>113.3738842397426</v>
       </c>
       <c r="R5" t="n">
-        <v>90.54577101877454</v>
+        <v>46.12405460523132</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -804,55 +804,55 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.739146887920408</v>
+        <v>-8.056712198943654</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3114049991318</v>
+        <v>113.2945758507509</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.962303886920907</v>
+        <v>-7.963348844637008</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3977794683919</v>
+        <v>113.3629913800458</v>
       </c>
       <c r="G6" t="n">
-        <v>159.0276015613202</v>
+        <v>35.97085753970362</v>
       </c>
       <c r="H6" t="n">
-        <v>26.57544550752098</v>
+        <v>12.82676379724179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1659439523868861</v>
+        <v>0.1723386602198647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9936003442377382</v>
+        <v>0.9932863402717761</v>
       </c>
       <c r="K6" t="n">
-        <v>725</v>
+        <v>1591</v>
       </c>
       <c r="L6" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O6" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.962303886920907</v>
+        <v>-7.963348844637008</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3977794683919</v>
+        <v>113.3629913800458</v>
       </c>
       <c r="R6" t="n">
-        <v>159.0276015613202</v>
+        <v>35.97085753970362</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -869,55 +869,55 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.093563569211346</v>
+        <v>-8.072415341362056</v>
       </c>
       <c r="D7" t="n">
-        <v>113.4692920141133</v>
+        <v>113.2893877946882</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.931435726980411</v>
+        <v>-7.966154533203673</v>
       </c>
       <c r="F7" t="n">
-        <v>113.403276711635</v>
+        <v>113.3667933008129</v>
       </c>
       <c r="G7" t="n">
-        <v>338.0358262487478</v>
+        <v>35.80925875647314</v>
       </c>
       <c r="H7" t="n">
-        <v>19.43806299744516</v>
+        <v>14.56881044281476</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1661979603811882</v>
+        <v>0.1723564481915239</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9959529763682122</v>
+        <v>0.9958326180805566</v>
       </c>
       <c r="K7" t="n">
-        <v>190</v>
+        <v>1690</v>
       </c>
       <c r="L7" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O7" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.931435726980411</v>
+        <v>-7.966154533203673</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.403276711635</v>
+        <v>113.3667933008129</v>
       </c>
       <c r="R7" t="n">
-        <v>338.0358262487478</v>
+        <v>35.80925875647314</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.093563569211346</v>
+        <v>-7.986152780045161</v>
       </c>
       <c r="D8" t="n">
-        <v>113.4692920141133</v>
+        <v>113.3989792028485</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.931435726980411</v>
+        <v>-7.977206946067169</v>
       </c>
       <c r="F8" t="n">
-        <v>113.403276711635</v>
+        <v>113.3999101703452</v>
       </c>
       <c r="G8" t="n">
-        <v>338.0358262487478</v>
+        <v>5.884137565270155</v>
       </c>
       <c r="H8" t="n">
-        <v>19.43806299744516</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1661979603811882</v>
+        <v>0.1723746132341398</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9975563416305804</v>
+        <v>0.9969147837346479</v>
       </c>
       <c r="K8" t="n">
-        <v>190</v>
+        <v>448</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.931435726980411</v>
+        <v>-7.977206946067169</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.403276711635</v>
+        <v>113.3999101703452</v>
       </c>
       <c r="R8" t="n">
-        <v>338.0358262487478</v>
+        <v>5.884137565270155</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -999,55 +999,55 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.093563569211346</v>
+        <v>-8.012981610206946</v>
       </c>
       <c r="D9" t="n">
-        <v>113.4692920141133</v>
+        <v>113.3256696182571</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.931435726980411</v>
+        <v>-7.950953023144121</v>
       </c>
       <c r="F9" t="n">
-        <v>113.403276711635</v>
+        <v>113.3611738685399</v>
       </c>
       <c r="G9" t="n">
-        <v>338.0358262487478</v>
+        <v>29.54876227601597</v>
       </c>
       <c r="H9" t="n">
-        <v>19.43806299744516</v>
+        <v>7.928276782439065</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1661979603811882</v>
+        <v>0.1723924412849851</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9983277908384947</v>
+        <v>0.9978783801538877</v>
       </c>
       <c r="K9" t="n">
-        <v>190</v>
+        <v>1705</v>
       </c>
       <c r="L9" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O9" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.931435726980411</v>
+        <v>-7.950953023144121</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.403276711635</v>
+        <v>113.3611738685399</v>
       </c>
       <c r="R9" t="n">
-        <v>338.0358262487478</v>
+        <v>29.54876227601597</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.768618352449146</v>
+        <v>-8.050166666356585</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3463166416934</v>
+        <v>113.3421240705891</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.933782131718706</v>
+        <v>-7.961421929378776</v>
       </c>
       <c r="F10" t="n">
-        <v>113.4054658036662</v>
+        <v>113.3951852207047</v>
       </c>
       <c r="G10" t="n">
-        <v>160.4710112477416</v>
+        <v>30.63264119999745</v>
       </c>
       <c r="H10" t="n">
-        <v>19.486862903997</v>
+        <v>11.46791253468468</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1662716691075855</v>
+        <v>0.1725555961059663</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9984356112367626</v>
+        <v>0.9985964650949529</v>
       </c>
       <c r="K10" t="n">
-        <v>1252</v>
+        <v>1004</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.933782131718706</v>
+        <v>-7.961421929378776</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.4054658036662</v>
+        <v>113.3951852207047</v>
       </c>
       <c r="R10" t="n">
-        <v>160.4710112477416</v>
+        <v>30.63264119999745</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,31 +1132,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.059946035647258</v>
+        <v>-8.050166666356585</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3947294826529</v>
+        <v>113.3421240705891</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.954542207798461</v>
+        <v>-7.961421929378776</v>
       </c>
       <c r="F11" t="n">
-        <v>113.4009919139456</v>
+        <v>113.3951852207047</v>
       </c>
       <c r="G11" t="n">
-        <v>3.367520457399586</v>
+        <v>30.63264119999745</v>
       </c>
       <c r="H11" t="n">
-        <v>11.74063835907284</v>
+        <v>11.46791253468468</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1664252184490007</v>
+        <v>0.1725555961059663</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9984730388684431</v>
+        <v>0.9991662669638218</v>
       </c>
       <c r="K11" t="n">
-        <v>107</v>
+        <v>1004</v>
       </c>
       <c r="L11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.954542207798461</v>
+        <v>-7.961421929378776</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.4009919139456</v>
+        <v>113.3951852207047</v>
       </c>
       <c r="R11" t="n">
-        <v>3.367520457399586</v>
+        <v>30.63264119999745</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.050166666356585</v>
       </c>
       <c r="D12" t="n">
-        <v>113.395123045986</v>
+        <v>113.3421240705891</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.961421929378776</v>
       </c>
       <c r="F12" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3951852207047</v>
       </c>
       <c r="G12" t="n">
-        <v>10.76711912654551</v>
+        <v>30.63264119999745</v>
       </c>
       <c r="H12" t="n">
-        <v>4.200635350190051</v>
+        <v>11.46791253468468</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.1725555961059663</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857854261953833</v>
+        <v>0.5857862304530788</v>
       </c>
       <c r="K12" t="n">
-        <v>448</v>
+        <v>1004</v>
       </c>
       <c r="L12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.961421929378776</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3951852207047</v>
       </c>
       <c r="R12" t="n">
-        <v>10.76711912654551</v>
+        <v>30.63264119999745</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,31 +1262,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.138909496048235</v>
       </c>
       <c r="D13" t="n">
-        <v>113.395123045986</v>
+        <v>113.188496719188</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.967331100339034</v>
       </c>
       <c r="F13" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3726875431818</v>
       </c>
       <c r="G13" t="n">
-        <v>10.76711912654551</v>
+        <v>46.75999594836188</v>
       </c>
       <c r="H13" t="n">
-        <v>4.200635350190051</v>
+        <v>27.84307593162957</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.1725658534015325</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9989539882682343</v>
+        <v>0.9997614319656556</v>
       </c>
       <c r="K13" t="n">
-        <v>448</v>
+        <v>230</v>
       </c>
       <c r="L13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.967331100339034</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3726875431818</v>
       </c>
       <c r="R13" t="n">
-        <v>10.76711912654551</v>
+        <v>46.75999594836188</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,31 +1327,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.133964112350778</v>
       </c>
       <c r="D14" t="n">
-        <v>113.395123045986</v>
+        <v>113.1921344795859</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.960698496567066</v>
       </c>
       <c r="F14" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3726341312996</v>
       </c>
       <c r="G14" t="n">
-        <v>10.76711912654551</v>
+        <v>45.90081265877914</v>
       </c>
       <c r="H14" t="n">
-        <v>4.200635350190051</v>
+        <v>27.67895738744387</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.1725790035651913</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9989109144345228</v>
+        <v>0.9998532159882639</v>
       </c>
       <c r="K14" t="n">
-        <v>448</v>
+        <v>671</v>
       </c>
       <c r="L14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.960698496567066</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3726341312996</v>
       </c>
       <c r="R14" t="n">
-        <v>10.76711912654551</v>
+        <v>45.90081265877914</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,31 +1392,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.058423645645544</v>
       </c>
       <c r="D15" t="n">
-        <v>113.395123045986</v>
+        <v>113.3438067126452</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.963700994655056</v>
       </c>
       <c r="F15" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3787456414393</v>
       </c>
       <c r="G15" t="n">
-        <v>10.76711912654551</v>
+        <v>20.06743474061498</v>
       </c>
       <c r="H15" t="n">
-        <v>4.200635350190051</v>
+        <v>11.213279015794</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.172587348060906</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9988922953877242</v>
+        <v>0.9998765245893947</v>
       </c>
       <c r="K15" t="n">
-        <v>448</v>
+        <v>1438</v>
       </c>
       <c r="L15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.963700994655056</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3787456414393</v>
       </c>
       <c r="R15" t="n">
-        <v>10.76711912654551</v>
+        <v>20.06743474061498</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,31 +1457,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.058921340873448</v>
       </c>
       <c r="D16" t="n">
-        <v>113.395123045986</v>
+        <v>113.3482511971719</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.959489586493329</v>
       </c>
       <c r="F16" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3854753081178</v>
       </c>
       <c r="G16" t="n">
-        <v>10.76711912654551</v>
+        <v>20.34318262735099</v>
       </c>
       <c r="H16" t="n">
-        <v>4.200635350190051</v>
+        <v>11.79159567167438</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.1726018237729497</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9988831819049333</v>
+        <v>0.9998812684985567</v>
       </c>
       <c r="K16" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.959489586493329</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3854753081178</v>
       </c>
       <c r="R16" t="n">
-        <v>10.76711912654551</v>
+        <v>20.34318262735099</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.063532153704026</v>
       </c>
       <c r="D17" t="n">
-        <v>113.395123045986</v>
+        <v>113.3393283151189</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.961403325694623</v>
       </c>
       <c r="F17" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3813386283987</v>
       </c>
       <c r="G17" t="n">
-        <v>10.76711912654551</v>
+        <v>22.1655037138142</v>
       </c>
       <c r="H17" t="n">
-        <v>4.200635350190051</v>
+        <v>12.26217073655936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.1726190942842914</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9989451601515402</v>
+        <v>0.9998615556002004</v>
       </c>
       <c r="K17" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.961403325694623</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.4022490373181</v>
+        <v>113.3813386283987</v>
       </c>
       <c r="R17" t="n">
-        <v>10.76711912654551</v>
+        <v>22.1655037138142</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.990383759784061</v>
+        <v>-8.061838968193639</v>
       </c>
       <c r="D18" t="n">
-        <v>113.395123045986</v>
+        <v>113.3396839744847</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.957606164997337</v>
       </c>
       <c r="F18" t="n">
-        <v>113.4022490373181</v>
+        <v>113.381234627831</v>
       </c>
       <c r="G18" t="n">
-        <v>10.76711912654551</v>
+        <v>21.5442432910529</v>
       </c>
       <c r="H18" t="n">
-        <v>4.200635350190051</v>
+        <v>12.46048817679355</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1665235503995904</v>
+        <v>0.1726226021853366</v>
       </c>
       <c r="J18" t="n">
-        <v>0.99893958175599</v>
+        <v>0.9998739224991265</v>
       </c>
       <c r="K18" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.953271559793956</v>
+        <v>-7.957606164997337</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.4022490373181</v>
+        <v>113.381234627831</v>
       </c>
       <c r="R18" t="n">
-        <v>10.76711912654551</v>
+        <v>21.5442432910529</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.989818394386</v>
+        <v>-8.059854541077739</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3941427213001</v>
+        <v>113.3427534392312</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.952956176829034</v>
+        <v>-7.95765033259031</v>
       </c>
       <c r="F19" t="n">
-        <v>113.4014929748547</v>
+        <v>113.3837726565298</v>
       </c>
       <c r="G19" t="n">
-        <v>11.17106541725317</v>
+        <v>21.67728117529937</v>
       </c>
       <c r="H19" t="n">
-        <v>4.178045297082416</v>
+        <v>12.22922541155783</v>
       </c>
       <c r="I19" t="n">
-        <v>0.166525757337932</v>
+        <v>0.1726243648276834</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9989847062346349</v>
+        <v>0.9999045495419379</v>
       </c>
       <c r="K19" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.952956176829034</v>
+        <v>-7.95765033259031</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.4014929748547</v>
+        <v>113.3837726565298</v>
       </c>
       <c r="R19" t="n">
-        <v>11.17106541725317</v>
+        <v>21.67728117529937</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.99481503342389</v>
+        <v>-8.062474818097195</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3951026673724</v>
+        <v>113.3415688419264</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.955343996878396</v>
+        <v>-7.95858078020991</v>
       </c>
       <c r="F20" t="n">
-        <v>113.4029362147204</v>
+        <v>113.3831764448753</v>
       </c>
       <c r="G20" t="n">
-        <v>11.11993773295876</v>
+        <v>21.63486461387023</v>
       </c>
       <c r="H20" t="n">
-        <v>4.472947684539269</v>
+        <v>12.42776492022879</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1665352667269712</v>
+        <v>0.172624579090728</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9991289347752638</v>
+        <v>0.9999148488104418</v>
       </c>
       <c r="K20" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.955343996878396</v>
+        <v>-7.95858078020991</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.4029362147204</v>
+        <v>113.3831764448753</v>
       </c>
       <c r="R20" t="n">
-        <v>11.11993773295876</v>
+        <v>21.63486461387023</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.993708646001968</v>
+        <v>-8.064922708311267</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3950978019021</v>
+        <v>113.3405748436671</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.956069486171489</v>
+        <v>-7.959477552114903</v>
       </c>
       <c r="F21" t="n">
-        <v>113.4024933956735</v>
+        <v>113.3831008161651</v>
       </c>
       <c r="G21" t="n">
-        <v>11.01189416605451</v>
+        <v>21.77288681099294</v>
       </c>
       <c r="H21" t="n">
-        <v>4.263783001733949</v>
+        <v>12.62540134285114</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1665360987639568</v>
+        <v>0.1726264292473598</v>
       </c>
       <c r="J21" t="n">
-        <v>0.999127220286662</v>
+        <v>0.9999263335758874</v>
       </c>
       <c r="K21" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.956069486171489</v>
+        <v>-7.959477552114903</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.4024933956735</v>
+        <v>113.3831008161651</v>
       </c>
       <c r="R21" t="n">
-        <v>11.01189416605451</v>
+        <v>21.77288681099294</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.993708646001968</v>
+        <v>-8.064922708311267</v>
       </c>
       <c r="D22" t="n">
-        <v>113.3950978019021</v>
+        <v>113.3405748436671</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.956069486171489</v>
+        <v>-7.959477552114903</v>
       </c>
       <c r="F22" t="n">
-        <v>113.4024933956735</v>
+        <v>113.3831008161651</v>
       </c>
       <c r="G22" t="n">
-        <v>11.01189416605451</v>
+        <v>21.77288681099294</v>
       </c>
       <c r="H22" t="n">
-        <v>4.263783001733949</v>
+        <v>12.62540134285114</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1665360987639568</v>
+        <v>0.1726264292473598</v>
       </c>
       <c r="J22" t="n">
-        <v>0.585786161224261</v>
+        <v>0.5857864376357882</v>
       </c>
       <c r="K22" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.956069486171489</v>
+        <v>-7.959477552114903</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.4024933956735</v>
+        <v>113.3831008161651</v>
       </c>
       <c r="R22" t="n">
-        <v>11.01189416605451</v>
+        <v>21.77288681099294</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.989088700924045</v>
+        <v>-8.062054973168523</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3953112725736</v>
+        <v>113.3403595296541</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.959182651636925</v>
+        <v>-7.959347539034096</v>
       </c>
       <c r="F23" t="n">
-        <v>113.4012811738371</v>
+        <v>113.381880939577</v>
       </c>
       <c r="G23" t="n">
-        <v>11.18312010926024</v>
+        <v>21.82030554376683</v>
       </c>
       <c r="H23" t="n">
-        <v>3.389759822594767</v>
+        <v>12.30167834812455</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1665398594185048</v>
+        <v>0.172627142999938</v>
       </c>
       <c r="J23" t="n">
-        <v>0.999794207535229</v>
+        <v>0.9999482802624661</v>
       </c>
       <c r="K23" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.959182651636925</v>
+        <v>-7.959347539034096</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.4012811738371</v>
+        <v>113.381880939577</v>
       </c>
       <c r="R23" t="n">
-        <v>11.18312010926024</v>
+        <v>21.82030554376683</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.99685361846482</v>
+        <v>-8.062054973168523</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3951649650561</v>
+        <v>113.3403595296541</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.959860169454527</v>
+        <v>-7.959347539034096</v>
       </c>
       <c r="F24" t="n">
-        <v>113.4025044586493</v>
+        <v>113.381880939577</v>
       </c>
       <c r="G24" t="n">
-        <v>11.11635535000579</v>
+        <v>21.82030554376683</v>
       </c>
       <c r="H24" t="n">
-        <v>4.192130809431584</v>
+        <v>12.30167834812455</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1665411264512923</v>
+        <v>0.172627142999938</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9997940362708627</v>
+        <v>0.9999472106387636</v>
       </c>
       <c r="K24" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.959860169454527</v>
+        <v>-7.959347539034096</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.4025044586493</v>
+        <v>113.381880939577</v>
       </c>
       <c r="R24" t="n">
-        <v>11.11635535000579</v>
+        <v>21.82030554376683</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.99685361846482</v>
+        <v>-8.060658484824932</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3951649650561</v>
+        <v>113.3416374647604</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.959860169454527</v>
+        <v>-7.958667515723249</v>
       </c>
       <c r="F25" t="n">
-        <v>113.4025044586493</v>
+        <v>113.3828545544675</v>
       </c>
       <c r="G25" t="n">
-        <v>11.11635535000579</v>
+        <v>21.81329761172898</v>
       </c>
       <c r="H25" t="n">
-        <v>4.192130809431584</v>
+        <v>12.21526830718335</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1665411264512923</v>
+        <v>0.1726273907238148</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9997996576645882</v>
+        <v>0.9999467846184487</v>
       </c>
       <c r="K25" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.959860169454527</v>
+        <v>-7.958667515723249</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.4025044586493</v>
+        <v>113.3828545544675</v>
       </c>
       <c r="R25" t="n">
-        <v>11.11635535000579</v>
+        <v>21.81329761172898</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.997459047635052</v>
+        <v>-8.060658484824932</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3950372514955</v>
+        <v>113.3416374647604</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.959661022160354</v>
+        <v>-7.958667515723249</v>
       </c>
       <c r="F26" t="n">
-        <v>113.4025243788368</v>
+        <v>113.3828545544675</v>
       </c>
       <c r="G26" t="n">
-        <v>11.09902332116694</v>
+        <v>21.81329761172898</v>
       </c>
       <c r="H26" t="n">
-        <v>4.283051616926871</v>
+        <v>12.21526830718335</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1665411908531536</v>
+        <v>0.1726273907238148</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9998013218707889</v>
+        <v>0.9999463607635352</v>
       </c>
       <c r="K26" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.959661022160354</v>
+        <v>-7.958667515723249</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.4025243788368</v>
+        <v>113.3828545544675</v>
       </c>
       <c r="R26" t="n">
-        <v>11.09902332116694</v>
+        <v>21.81329761172898</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.997459047635052</v>
+        <v>-8.061341513969014</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3950372514955</v>
+        <v>113.3408533158868</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.959661022160354</v>
+        <v>-7.958614646481205</v>
       </c>
       <c r="F27" t="n">
-        <v>113.4025243788368</v>
+        <v>113.3823753393074</v>
       </c>
       <c r="G27" t="n">
-        <v>11.09902332116694</v>
+        <v>21.81689263783882</v>
       </c>
       <c r="H27" t="n">
-        <v>4.283051616926871</v>
+        <v>12.30371260583434</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1665411908531536</v>
+        <v>0.1726274559640359</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9998019949541535</v>
+        <v>0.9999459750304748</v>
       </c>
       <c r="K27" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.959661022160354</v>
+        <v>-7.958614646481205</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.4025243788368</v>
+        <v>113.3823753393074</v>
       </c>
       <c r="R27" t="n">
-        <v>11.09902332116694</v>
+        <v>21.81689263783882</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.996891409339454</v>
+        <v>-8.061341513969014</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3951693909355</v>
+        <v>113.3408533158868</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.959916973397714</v>
+        <v>-7.958614646481205</v>
       </c>
       <c r="F28" t="n">
-        <v>113.4024999693751</v>
+        <v>113.3823753393074</v>
       </c>
       <c r="G28" t="n">
-        <v>11.10875421493219</v>
+        <v>21.81689263783882</v>
       </c>
       <c r="H28" t="n">
-        <v>4.189867064482399</v>
+        <v>12.30371260583434</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1665412149737711</v>
+        <v>0.1726274559640359</v>
       </c>
       <c r="J28" t="n">
-        <v>0.999805869211807</v>
+        <v>0.999945844597167</v>
       </c>
       <c r="K28" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.959916973397714</v>
+        <v>-7.958614646481205</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.4024999693751</v>
+        <v>113.3823753393074</v>
       </c>
       <c r="R28" t="n">
-        <v>11.10875421493219</v>
+        <v>21.81689263783882</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.996561903939893</v>
+        <v>-8.061552061448616</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3949560269683</v>
+        <v>113.3407094288754</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.959493816230616</v>
+        <v>-7.958753217408495</v>
       </c>
       <c r="F29" t="n">
-        <v>113.4023031609925</v>
+        <v>113.3822534898266</v>
       </c>
       <c r="G29" t="n">
-        <v>11.1057999471602</v>
+        <v>21.81352942719412</v>
       </c>
       <c r="H29" t="n">
-        <v>4.200436955603952</v>
+        <v>12.31204393517703</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1665413094802773</v>
+        <v>0.1726274723403671</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9998043015475526</v>
+        <v>0.9999492197379297</v>
       </c>
       <c r="K29" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.959493816230616</v>
+        <v>-7.958753217408495</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.4023031609925</v>
+        <v>113.3822534898266</v>
       </c>
       <c r="R29" t="n">
-        <v>11.1057999471602</v>
+        <v>21.81352942719412</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.996561903939893</v>
+        <v>-8.060615052001811</v>
       </c>
       <c r="D30" t="n">
-        <v>113.3949560269683</v>
+        <v>113.3412921084304</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.959493816230616</v>
+        <v>-7.958671554258573</v>
       </c>
       <c r="F30" t="n">
-        <v>113.4023031609925</v>
+        <v>113.3824907920324</v>
       </c>
       <c r="G30" t="n">
-        <v>11.1057999471602</v>
+        <v>21.81367062205648</v>
       </c>
       <c r="H30" t="n">
-        <v>4.200436955603952</v>
+        <v>12.20961467134593</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1665413094802773</v>
+        <v>0.1726274769253296</v>
       </c>
       <c r="J30" t="n">
-        <v>0.999804303902917</v>
+        <v>0.9999489633521461</v>
       </c>
       <c r="K30" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.959493816230616</v>
+        <v>-7.958671554258573</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.4023031609925</v>
+        <v>113.3824907920324</v>
       </c>
       <c r="R30" t="n">
-        <v>11.1057999471602</v>
+        <v>21.81367062205648</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.996503103243004</v>
+        <v>-7.904362523902446</v>
       </c>
       <c r="D31" t="n">
-        <v>113.3949880857733</v>
+        <v>113.4043620808579</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.959414169227383</v>
+        <v>-7.958555161382233</v>
       </c>
       <c r="F31" t="n">
-        <v>113.402340342715</v>
+        <v>113.3824594138636</v>
       </c>
       <c r="G31" t="n">
-        <v>11.10726204562896</v>
+        <v>201.8145607201867</v>
       </c>
       <c r="H31" t="n">
-        <v>4.202820240340311</v>
+        <v>6.490807391867424</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1665413196770325</v>
+        <v>0.1726274845895527</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9998037489982229</v>
+        <v>0.9999541408786627</v>
       </c>
       <c r="K31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.959414169227383</v>
+        <v>-7.958555161382233</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.402340342715</v>
+        <v>113.3824594138636</v>
       </c>
       <c r="R31" t="n">
-        <v>11.10726204562896</v>
+        <v>201.8145607201867</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.996503103243004</v>
+        <v>-8.061087579117167</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3949880857733</v>
+        <v>113.3410358217306</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.959414169227383</v>
+        <v>-7.958705787511212</v>
       </c>
       <c r="F32" t="n">
-        <v>113.402340342715</v>
+        <v>113.3824132987942</v>
       </c>
       <c r="G32" t="n">
-        <v>11.10726204562896</v>
+        <v>21.81446605006386</v>
       </c>
       <c r="H32" t="n">
-        <v>4.202820240340311</v>
+        <v>12.26217549551867</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1665413196770325</v>
+        <v>0.1726274908511014</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5857864258143888</v>
+        <v>0.5358983867452493</v>
       </c>
       <c r="K32" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.959414169227383</v>
+        <v>-7.958705787511212</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.402340342715</v>
+        <v>113.3824132987942</v>
       </c>
       <c r="R32" t="n">
-        <v>11.10726204562896</v>
+        <v>21.81446605006386</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,28 +2562,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.996503103243004</v>
+        <v>-7.904598259658232</v>
       </c>
       <c r="D33" t="n">
-        <v>113.3949880857733</v>
+        <v>113.404177336508</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.959414169227383</v>
+        <v>-7.958673216816945</v>
       </c>
       <c r="F33" t="n">
-        <v>113.402340342715</v>
+        <v>113.3823222964956</v>
       </c>
       <c r="G33" t="n">
-        <v>11.10726204562896</v>
+        <v>201.814496734282</v>
       </c>
       <c r="H33" t="n">
-        <v>4.202820240340311</v>
+        <v>6.476709440632503</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1665413196770325</v>
+        <v>0.1726274914041381</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999363065890025</v>
+        <v>0.9999673015692158</v>
       </c>
       <c r="K33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.959414169227383</v>
+        <v>-7.958673216816945</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.402340342715</v>
+        <v>113.3823222964956</v>
       </c>
       <c r="R33" t="n">
-        <v>11.10726204562896</v>
+        <v>201.814496734282</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,28 +2627,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.996505544976156</v>
+        <v>-7.904598259658232</v>
       </c>
       <c r="D34" t="n">
-        <v>113.394989061038</v>
+        <v>113.404177336508</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.959486597397787</v>
+        <v>-7.958673216816945</v>
       </c>
       <c r="F34" t="n">
-        <v>113.4023271786867</v>
+        <v>113.3823222964956</v>
       </c>
       <c r="G34" t="n">
-        <v>11.10686799130573</v>
+        <v>201.814496734282</v>
       </c>
       <c r="H34" t="n">
-        <v>4.194883912162578</v>
+        <v>6.476709440632503</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1665413246358264</v>
+        <v>0.1726274914041381</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9086156675625433</v>
+        <v>0.9999742689309731</v>
       </c>
       <c r="K34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.959486597397787</v>
+        <v>-7.958673216816945</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.4023271786867</v>
+        <v>113.3823222964956</v>
       </c>
       <c r="R34" t="n">
-        <v>11.10686799130573</v>
+        <v>201.814496734282</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,28 +2692,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.996505544976156</v>
+        <v>-7.904493207279992</v>
       </c>
       <c r="D35" t="n">
-        <v>113.394989061038</v>
+        <v>113.4042168183158</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.959486597397787</v>
+        <v>-7.958670182761678</v>
       </c>
       <c r="F35" t="n">
-        <v>113.4023271786867</v>
+        <v>113.3823206482044</v>
       </c>
       <c r="G35" t="n">
-        <v>11.10686799130573</v>
+        <v>201.8144045814301</v>
       </c>
       <c r="H35" t="n">
-        <v>4.194883912162578</v>
+        <v>6.488924411776442</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1665413246358264</v>
+        <v>0.1726274927663074</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8816796326939546</v>
+        <v>0.9999853063278347</v>
       </c>
       <c r="K35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.959486597397787</v>
+        <v>-7.958670182761678</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.4023271786867</v>
+        <v>113.3823206482044</v>
       </c>
       <c r="R35" t="n">
-        <v>11.10686799130573</v>
+        <v>201.8144045814301</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.996505544976156</v>
+        <v>-7.904493207279992</v>
       </c>
       <c r="D36" t="n">
-        <v>113.394989061038</v>
+        <v>113.4042168183158</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.959486597397787</v>
+        <v>-7.958670182761678</v>
       </c>
       <c r="F36" t="n">
-        <v>113.4023271786867</v>
+        <v>113.3823206482044</v>
       </c>
       <c r="G36" t="n">
-        <v>11.10686799130573</v>
+        <v>201.8144045814301</v>
       </c>
       <c r="H36" t="n">
-        <v>4.194883912162578</v>
+        <v>6.488924411776442</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1665413246358264</v>
+        <v>0.1726274927663074</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9572473335643685</v>
+        <v>0.9999932994191194</v>
       </c>
       <c r="K36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.959486597397787</v>
+        <v>-7.958670182761678</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.4023271786867</v>
+        <v>113.3823206482044</v>
       </c>
       <c r="R36" t="n">
-        <v>11.10686799130573</v>
+        <v>201.8144045814301</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,28 +2822,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.996530800283374</v>
+        <v>-7.904509525705922</v>
       </c>
       <c r="D37" t="n">
-        <v>113.3950289293184</v>
+        <v>113.4042472303964</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.959443162897998</v>
+        <v>-7.958634265706793</v>
       </c>
       <c r="F37" t="n">
-        <v>113.4023806549176</v>
+        <v>113.3823721996971</v>
       </c>
       <c r="G37" t="n">
-        <v>11.10685716348446</v>
+        <v>201.8143812837272</v>
       </c>
       <c r="H37" t="n">
-        <v>4.202667480027777</v>
+        <v>6.48266690432815</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1665413253386005</v>
+        <v>0.1726274931465417</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9909478281651229</v>
+        <v>0.9999950875292951</v>
       </c>
       <c r="K37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.959443162897998</v>
+        <v>-7.958634265706793</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.4023806549176</v>
+        <v>113.3823721996971</v>
       </c>
       <c r="R37" t="n">
-        <v>11.10685716348446</v>
+        <v>201.8143812837272</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.99648326682805</v>
+        <v>-7.904509525705922</v>
       </c>
       <c r="D38" t="n">
-        <v>113.3949884778842</v>
+        <v>113.4042472303964</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.9594465957314</v>
+        <v>-7.958634265706793</v>
       </c>
       <c r="F38" t="n">
-        <v>113.4023300944364</v>
+        <v>113.3823721996971</v>
       </c>
       <c r="G38" t="n">
-        <v>11.10684787584805</v>
+        <v>201.8143812837272</v>
       </c>
       <c r="H38" t="n">
-        <v>4.196891999114677</v>
+        <v>6.48266690432815</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1665413255135987</v>
+        <v>0.1726274931465417</v>
       </c>
       <c r="J38" t="n">
-        <v>0.995868743601997</v>
+        <v>0.9330145036862169</v>
       </c>
       <c r="K38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.9594465957314</v>
+        <v>-7.958634265706793</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.4023300944364</v>
+        <v>113.3823721996971</v>
       </c>
       <c r="R38" t="n">
-        <v>11.10684787584805</v>
+        <v>201.8143812837272</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,28 +2952,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.996492810271218</v>
+        <v>-7.904509525705922</v>
       </c>
       <c r="D39" t="n">
-        <v>113.3950181647336</v>
+        <v>113.4042472303964</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.959441649416798</v>
+        <v>-7.958634265706793</v>
       </c>
       <c r="F39" t="n">
-        <v>113.402362654308</v>
+        <v>113.3823721996971</v>
       </c>
       <c r="G39" t="n">
-        <v>11.10684916663841</v>
+        <v>201.8143812837272</v>
       </c>
       <c r="H39" t="n">
-        <v>4.198533953639536</v>
+        <v>6.48266690432815</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1665413256453119</v>
+        <v>0.1726274931465417</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9977837914557645</v>
+        <v>0.921111599946363</v>
       </c>
       <c r="K39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.959441649416798</v>
+        <v>-7.958634265706793</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.402362654308</v>
+        <v>113.3823721996971</v>
       </c>
       <c r="R39" t="n">
-        <v>11.10684916663841</v>
+        <v>201.8143812837272</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,31 +3017,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.996492810271218</v>
+        <v>-8.060626283481596</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3950181647336</v>
+        <v>113.3411552204863</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.959441649416798</v>
+        <v>-7.958640949327056</v>
       </c>
       <c r="F40" t="n">
-        <v>113.402362654308</v>
+        <v>113.3823723770843</v>
       </c>
       <c r="G40" t="n">
-        <v>11.10684916663841</v>
+        <v>21.81442309315776</v>
       </c>
       <c r="H40" t="n">
-        <v>4.198533953639536</v>
+        <v>12.21468944171813</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1665413256453119</v>
+        <v>0.1726274932659926</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9982815614627019</v>
+        <v>0.9683626670546697</v>
       </c>
       <c r="K40" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.959441649416798</v>
+        <v>-7.958640949327056</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.402362654308</v>
+        <v>113.3823723770843</v>
       </c>
       <c r="R40" t="n">
-        <v>11.10684916663841</v>
+        <v>21.81442309315776</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,31 +3082,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.996494921436229</v>
+        <v>-8.060561651614661</v>
       </c>
       <c r="D41" t="n">
-        <v>113.395010623664</v>
+        <v>113.3411661325726</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.959449073924558</v>
+        <v>-7.958637124424174</v>
       </c>
       <c r="F41" t="n">
-        <v>113.4023540598685</v>
+        <v>113.3823586731278</v>
       </c>
       <c r="G41" t="n">
-        <v>11.10684877683737</v>
+        <v>21.81440333334779</v>
       </c>
       <c r="H41" t="n">
-        <v>4.197931855937335</v>
+        <v>12.20740511073507</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1665413256695979</v>
+        <v>0.1726274935082803</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9987944573093912</v>
+        <v>0.9836688105172422</v>
       </c>
       <c r="K41" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.959449073924558</v>
+        <v>-7.958637124424174</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.4023540598685</v>
+        <v>113.3823586731278</v>
       </c>
       <c r="R41" t="n">
-        <v>11.10684877683737</v>
+        <v>21.81440333334779</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.996491544740389</v>
+        <v>-8.060622357306507</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3950032905347</v>
+        <v>113.3411594521408</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.959440315454129</v>
+        <v>-7.958656279673325</v>
       </c>
       <c r="F42" t="n">
-        <v>113.4023477944901</v>
+        <v>113.3823687966077</v>
       </c>
       <c r="G42" t="n">
-        <v>11.10685040521545</v>
+        <v>21.81440805291589</v>
       </c>
       <c r="H42" t="n">
-        <v>4.198541725947817</v>
+        <v>12.21238186939866</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1665413256980411</v>
+        <v>0.1726274935519024</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5857862590011269</v>
+        <v>0.5857712416433664</v>
       </c>
       <c r="K42" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.959440315454129</v>
+        <v>-7.958656279673325</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.4023477944901</v>
+        <v>113.3823687966077</v>
       </c>
       <c r="R42" t="n">
-        <v>11.10685040521545</v>
+        <v>21.81440805291589</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.996462187592283</v>
+        <v>-8.060617205259986</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3950130577606</v>
+        <v>113.3411567748006</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.959440993885825</v>
+        <v>-7.958654815447919</v>
       </c>
       <c r="F43" t="n">
-        <v>113.402351608371</v>
+        <v>113.3823646229705</v>
       </c>
       <c r="G43" t="n">
-        <v>11.10685107520982</v>
+        <v>21.81440529097791</v>
       </c>
       <c r="H43" t="n">
-        <v>4.195138193600163</v>
+        <v>12.21193995594912</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1665413257079993</v>
+        <v>0.1726274935986735</v>
       </c>
       <c r="J43" t="n">
-        <v>0.999921673822152</v>
+        <v>0.9979339967584213</v>
       </c>
       <c r="K43" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.959440993885825</v>
+        <v>-7.958654815447919</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.402351608371</v>
+        <v>113.3823646229705</v>
       </c>
       <c r="R43" t="n">
-        <v>11.10685107520982</v>
+        <v>21.81440529097791</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,31 +3277,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.996462187592283</v>
+        <v>-8.060619567973795</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3950130577606</v>
+        <v>113.3411549062798</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.959440993885825</v>
+        <v>-7.958653656212997</v>
       </c>
       <c r="F44" t="n">
-        <v>113.402351608371</v>
+        <v>113.3823641730674</v>
       </c>
       <c r="G44" t="n">
-        <v>11.10685107520982</v>
+        <v>21.81440307366077</v>
       </c>
       <c r="H44" t="n">
-        <v>4.195138193600163</v>
+        <v>12.2123615788233</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1665413257079993</v>
+        <v>0.1726274936141486</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9999473466556272</v>
+        <v>0.9994062444669992</v>
       </c>
       <c r="K44" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.959440993885825</v>
+        <v>-7.958653656212997</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.402351608371</v>
+        <v>113.3823641730674</v>
       </c>
       <c r="R44" t="n">
-        <v>11.10685107520982</v>
+        <v>21.81440307366077</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,31 +3342,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.996461782377835</v>
+        <v>-8.060619567973795</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3950144945461</v>
+        <v>113.3411549062798</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.959444751446957</v>
+        <v>-7.958653656212997</v>
       </c>
       <c r="F45" t="n">
-        <v>113.4023522198313</v>
+        <v>113.3823641730674</v>
       </c>
       <c r="G45" t="n">
-        <v>11.10685074302623</v>
+        <v>21.81440307366077</v>
       </c>
       <c r="H45" t="n">
-        <v>4.194666475555761</v>
+        <v>12.2123615788233</v>
       </c>
       <c r="I45" t="n">
-        <v>0.166541325709513</v>
+        <v>0.1726274936141486</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9999706751082291</v>
+        <v>0.9999999972068199</v>
       </c>
       <c r="K45" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.959444751446957</v>
+        <v>-7.958653656212997</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.4023522198313</v>
+        <v>113.3823641730674</v>
       </c>
       <c r="R45" t="n">
-        <v>11.10685074302623</v>
+        <v>21.81440307366077</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,31 +3407,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.996461782377835</v>
+        <v>-8.060619567973795</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3950144945461</v>
+        <v>113.3411549062798</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.959444751446957</v>
+        <v>-7.958653656212997</v>
       </c>
       <c r="F46" t="n">
-        <v>113.4023522198313</v>
+        <v>113.3823641730674</v>
       </c>
       <c r="G46" t="n">
-        <v>11.10685074302623</v>
+        <v>21.81440307366077</v>
       </c>
       <c r="H46" t="n">
-        <v>4.194666475555761</v>
+        <v>12.2123615788233</v>
       </c>
       <c r="I46" t="n">
-        <v>0.166541325709513</v>
+        <v>0.1726274936141486</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9999801921358658</v>
+        <v>0.9999999978932603</v>
       </c>
       <c r="K46" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.959444751446957</v>
+        <v>-7.958653656212997</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.4023522198313</v>
+        <v>113.3823641730674</v>
       </c>
       <c r="R46" t="n">
-        <v>11.10685074302623</v>
+        <v>21.81440307366077</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.996461679604253</v>
+        <v>-8.060586510380341</v>
       </c>
       <c r="D47" t="n">
-        <v>113.3950129894889</v>
+        <v>113.3411706128098</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.959442274868937</v>
+        <v>-7.958652321753555</v>
       </c>
       <c r="F47" t="n">
-        <v>113.4023511853302</v>
+        <v>113.3823670599739</v>
       </c>
       <c r="G47" t="n">
-        <v>11.10685082017921</v>
+        <v>21.81440358330093</v>
       </c>
       <c r="H47" t="n">
-        <v>4.194935469079406</v>
+        <v>12.20856224930362</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1665413257110328</v>
+        <v>0.1726274936220604</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999938340435878</v>
+        <v>0.9999999978703087</v>
       </c>
       <c r="K47" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.959442274868937</v>
+        <v>-7.958652321753555</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.4023511853302</v>
+        <v>113.3823670599739</v>
       </c>
       <c r="R47" t="n">
-        <v>11.10685082017921</v>
+        <v>21.81440358330093</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,31 +3537,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.996461679604253</v>
+        <v>-8.060586510380341</v>
       </c>
       <c r="D48" t="n">
-        <v>113.3950129894889</v>
+        <v>113.3411706128098</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.959442274868937</v>
+        <v>-7.958652321753555</v>
       </c>
       <c r="F48" t="n">
-        <v>113.4023511853302</v>
+        <v>113.3823670599739</v>
       </c>
       <c r="G48" t="n">
-        <v>11.10685082017921</v>
+        <v>21.81440358330093</v>
       </c>
       <c r="H48" t="n">
-        <v>4.194935469079406</v>
+        <v>12.20856224930362</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1665413257110328</v>
+        <v>0.1726274936220604</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999957760319795</v>
+        <v>0.9999999982128225</v>
       </c>
       <c r="K48" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.959442274868937</v>
+        <v>-7.958652321753555</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.4023511853302</v>
+        <v>113.3823670599739</v>
       </c>
       <c r="R48" t="n">
-        <v>11.10685082017921</v>
+        <v>21.81440358330093</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,31 +3602,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.996494379034466</v>
+        <v>-8.060586415188473</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3950073806979</v>
+        <v>113.3411705231763</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.959443886510594</v>
+        <v>-7.958654729011141</v>
       </c>
       <c r="F49" t="n">
-        <v>113.4023517389919</v>
+        <v>113.3823659595946</v>
       </c>
       <c r="G49" t="n">
-        <v>11.10685087640107</v>
+        <v>21.81440375105121</v>
       </c>
       <c r="H49" t="n">
-        <v>4.198458245014469</v>
+        <v>12.20826255357767</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1665413257121076</v>
+        <v>0.1726274936221907</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999972455301572</v>
+        <v>0.9999999982860746</v>
       </c>
       <c r="K49" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.959443886510594</v>
+        <v>-7.958654729011141</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.4023517389919</v>
+        <v>113.3823659595946</v>
       </c>
       <c r="R49" t="n">
-        <v>11.10685087640107</v>
+        <v>21.81440375105121</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,31 +3667,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.996492737429502</v>
+        <v>-8.060587228495759</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3950072867701</v>
+        <v>113.3411696357523</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.959443384118067</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="F50" t="n">
-        <v>113.4023514192365</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="G50" t="n">
-        <v>11.10685087961656</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="H50" t="n">
-        <v>4.198329152918841</v>
+        <v>12.20854977866646</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1665413257122775</v>
+        <v>0.1726274936241491</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9999980577450289</v>
+        <v>0.999999998604391</v>
       </c>
       <c r="K50" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.959443384118067</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.4023514192365</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="R50" t="n">
-        <v>11.10685087961656</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.996492737429502</v>
+        <v>-8.060587228495759</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3950072867701</v>
+        <v>113.3411696357523</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.959443384118067</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="F51" t="n">
-        <v>113.4023514192365</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="G51" t="n">
-        <v>11.10685087961656</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="H51" t="n">
-        <v>4.198329152918841</v>
+        <v>12.20854977866646</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1665413257122775</v>
+        <v>0.1726274936241491</v>
       </c>
       <c r="J51" t="n">
-        <v>0.999999293079385</v>
+        <v>0.9999999987370671</v>
       </c>
       <c r="K51" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.959443384118067</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.4023514192365</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="R51" t="n">
-        <v>11.10685087961656</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,31 +3797,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.996492737429502</v>
+        <v>-8.060587228495759</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3950072867701</v>
+        <v>113.3411696357523</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.959443384118067</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="F52" t="n">
-        <v>113.4023514192365</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="G52" t="n">
-        <v>11.10685087961656</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="H52" t="n">
-        <v>4.198329152918841</v>
+        <v>12.20854977866646</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1665413257122775</v>
+        <v>0.1726274936241491</v>
       </c>
       <c r="J52" t="n">
-        <v>0.585786439812261</v>
+        <v>0.5857864397352656</v>
       </c>
       <c r="K52" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.959443384118067</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.4023514192365</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="R52" t="n">
-        <v>11.10685087961656</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,31 +3862,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.996492997899454</v>
+        <v>-8.060587228495759</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3950075199112</v>
+        <v>113.3411696357523</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.959443622580974</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="F53" t="n">
-        <v>113.4023516567522</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="G53" t="n">
-        <v>11.10685089140399</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="H53" t="n">
-        <v>4.19833164686026</v>
+        <v>12.20854977866646</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1665413257124022</v>
+        <v>0.1726274936241491</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999999274552044</v>
+        <v>0.9999999993295676</v>
       </c>
       <c r="K53" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.959443622580974</v>
+        <v>-7.958653144071719</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.4023516567522</v>
+        <v>113.3823660411164</v>
       </c>
       <c r="R53" t="n">
-        <v>11.10685089140399</v>
+        <v>21.8144036935562</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,31 +3927,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.996492997899454</v>
+        <v>-8.060585740626935</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3950075199112</v>
+        <v>113.3411698353432</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.959443622580974</v>
+        <v>-7.958652668189295</v>
       </c>
       <c r="F54" t="n">
-        <v>113.4023516567522</v>
+        <v>113.3823658316647</v>
       </c>
       <c r="G54" t="n">
-        <v>11.10685089140399</v>
+        <v>21.8144036879257</v>
       </c>
       <c r="H54" t="n">
-        <v>4.19833164686026</v>
+        <v>12.20842857599401</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1665413257124022</v>
+        <v>0.1726274936242325</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999569259156</v>
+        <v>0.9999999996574165</v>
       </c>
       <c r="K54" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.959443622580974</v>
+        <v>-7.958652668189295</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.4023516567522</v>
+        <v>113.3823658316647</v>
       </c>
       <c r="R54" t="n">
-        <v>11.10685089140399</v>
+        <v>21.8144036879257</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,31 +3992,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.996492997899454</v>
+        <v>-8.060587100631528</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3950075199112</v>
+        <v>113.3411693644776</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.959443622580974</v>
+        <v>-7.958652646535901</v>
       </c>
       <c r="F55" t="n">
-        <v>113.4023516567522</v>
+        <v>113.3823659191701</v>
       </c>
       <c r="G55" t="n">
-        <v>11.10685089140399</v>
+        <v>21.81440368381895</v>
       </c>
       <c r="H55" t="n">
-        <v>4.19833164686026</v>
+        <v>12.20859405217419</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1665413257124022</v>
+        <v>0.1726274936242743</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999775100311</v>
+        <v>0.9999999996700724</v>
       </c>
       <c r="K55" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.959443622580974</v>
+        <v>-7.958652646535901</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.4023516567522</v>
+        <v>113.3823659191701</v>
       </c>
       <c r="R55" t="n">
-        <v>11.10685089140399</v>
+        <v>21.81440368381895</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.996492892331339</v>
+        <v>-8.060587100631528</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3950072780383</v>
+        <v>113.3411693644776</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.95944353033487</v>
+        <v>-7.958652646535901</v>
       </c>
       <c r="F56" t="n">
-        <v>113.402351412236</v>
+        <v>113.3823659191701</v>
       </c>
       <c r="G56" t="n">
-        <v>11.10685089013937</v>
+        <v>21.81440368381895</v>
       </c>
       <c r="H56" t="n">
-        <v>4.198330137231753</v>
+        <v>12.20859405217419</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1665413257124126</v>
+        <v>0.1726274936242743</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999999881652472</v>
+        <v>0.9999999997513245</v>
       </c>
       <c r="K56" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.95944353033487</v>
+        <v>-7.958652646535901</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.402351412236</v>
+        <v>113.3823659191701</v>
       </c>
       <c r="R56" t="n">
-        <v>11.10685089013937</v>
+        <v>21.81440368381895</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,31 +4122,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.996492101663477</v>
+        <v>-8.060587110437133</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3950074118184</v>
+        <v>113.3411695320496</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.959443339309658</v>
+        <v>-7.958652994481755</v>
       </c>
       <c r="F57" t="n">
-        <v>113.4023514271492</v>
+        <v>113.3823659501199</v>
       </c>
       <c r="G57" t="n">
-        <v>11.10685089135784</v>
+        <v>21.81440368310755</v>
       </c>
       <c r="H57" t="n">
-        <v>4.198262187539755</v>
+        <v>12.20855355418263</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1665413257124408</v>
+        <v>0.1726274936243011</v>
       </c>
       <c r="J57" t="n">
-        <v>0.999999991136174</v>
+        <v>0.9999999998455273</v>
       </c>
       <c r="K57" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.959443339309658</v>
+        <v>-7.958652994481755</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.4023514271492</v>
+        <v>113.3823659501199</v>
       </c>
       <c r="R57" t="n">
-        <v>11.10685089135784</v>
+        <v>21.81440368310755</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,31 +4187,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587110437133</v>
       </c>
       <c r="D58" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411695320496</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652994481755</v>
       </c>
       <c r="F58" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823659501199</v>
       </c>
       <c r="G58" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368310755</v>
       </c>
       <c r="H58" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20855355418263</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243011</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9999999959041495</v>
+        <v>0.9999999998807791</v>
       </c>
       <c r="K58" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652994481755</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823659501199</v>
       </c>
       <c r="R58" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368310755</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,31 +4252,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587084105935</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411694990144</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652971332723</v>
       </c>
       <c r="F59" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823659157964</v>
       </c>
       <c r="G59" t="n">
-        <v>11.10685089220932</v>
+        <v>21.8144036831476</v>
       </c>
       <c r="H59" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20855317306935</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243059</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999982209173</v>
+        <v>0.9999999999511355</v>
       </c>
       <c r="K59" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652971332723</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823659157964</v>
       </c>
       <c r="R59" t="n">
-        <v>11.10685089220932</v>
+        <v>21.8144036831476</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,31 +4317,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587193082524</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411692613749</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652998738623</v>
       </c>
       <c r="F60" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657111294</v>
       </c>
       <c r="G60" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368499198</v>
       </c>
       <c r="H60" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856294267276</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243127</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999995152891</v>
+        <v>0.9999999999590707</v>
       </c>
       <c r="K60" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652998738623</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657111294</v>
       </c>
       <c r="R60" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368499198</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,31 +4382,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587230769816</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693164356</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958653004173714</v>
       </c>
       <c r="F61" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657792238</v>
       </c>
       <c r="G61" t="n">
-        <v>11.10685089220932</v>
+        <v>21.8144036843594</v>
       </c>
       <c r="H61" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856680535645</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243231</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9585908307947599</v>
+        <v>0.999999999963102</v>
       </c>
       <c r="K61" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958653004173714</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657792238</v>
       </c>
       <c r="R61" t="n">
-        <v>11.10685089220932</v>
+        <v>21.8144036843594</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587119377441</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411694148225</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652955515679</v>
       </c>
       <c r="F62" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823658522515</v>
       </c>
       <c r="G62" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368395639</v>
       </c>
       <c r="H62" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20855929184265</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243231</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857057452249197</v>
+        <v>0.5857864397352656</v>
       </c>
       <c r="K62" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652955515679</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823658522515</v>
       </c>
       <c r="R62" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368395639</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,31 +4512,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.06058723145237</v>
       </c>
       <c r="D63" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693167726</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958653034848904</v>
       </c>
       <c r="F63" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657674417</v>
       </c>
       <c r="G63" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368394272</v>
       </c>
       <c r="H63" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856321320266</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243249</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999995775086</v>
+        <v>0.9999999999999105</v>
       </c>
       <c r="K63" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958653034848904</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657674417</v>
       </c>
       <c r="R63" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368394272</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,31 +4577,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.06058708131965</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693387599</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652951040516</v>
       </c>
       <c r="F64" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657626167</v>
       </c>
       <c r="G64" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368409608</v>
       </c>
       <c r="H64" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20855526977622</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243269</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8844967830942793</v>
+        <v>0.9276199366493693</v>
       </c>
       <c r="K64" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652951040516</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657626167</v>
       </c>
       <c r="R64" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368409608</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,31 +4642,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587155971596</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411692903796</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652955827715</v>
       </c>
       <c r="F65" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657424719</v>
       </c>
       <c r="G65" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368405764</v>
       </c>
       <c r="H65" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856363723854</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243272</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9006029382396817</v>
+        <v>0.9878442305847307</v>
       </c>
       <c r="K65" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652955827715</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657424719</v>
       </c>
       <c r="R65" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368405764</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,31 +4707,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587235550557</v>
       </c>
       <c r="D66" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693032338</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652977509895</v>
       </c>
       <c r="F66" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657787266</v>
       </c>
       <c r="G66" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406009</v>
       </c>
       <c r="H66" t="n">
-        <v>4.198321359725795</v>
+        <v>12.2085705713407</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243276</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9700495214691597</v>
+        <v>0.9935908428645369</v>
       </c>
       <c r="K66" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652977509895</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657787266</v>
       </c>
       <c r="R66" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406009</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,31 +4772,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587235550557</v>
       </c>
       <c r="D67" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693032338</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652977509895</v>
       </c>
       <c r="F67" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657787266</v>
       </c>
       <c r="G67" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406009</v>
       </c>
       <c r="H67" t="n">
-        <v>4.198321359725795</v>
+        <v>12.2085705713407</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243276</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9865528009359226</v>
+        <v>0.9948926343477994</v>
       </c>
       <c r="K67" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652977509895</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657787266</v>
       </c>
       <c r="R67" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406009</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,31 +4837,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587160231828</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693256967</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652982609677</v>
       </c>
       <c r="F68" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657686898</v>
       </c>
       <c r="G68" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406207</v>
       </c>
       <c r="H68" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856093988606</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9919298651047526</v>
+        <v>0.9965034137193443</v>
       </c>
       <c r="K68" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652982609677</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657686898</v>
       </c>
       <c r="R68" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406207</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,31 +4902,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F69" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G69" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H69" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9957625648586879</v>
+        <v>0.9264510354374216</v>
       </c>
       <c r="K69" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R69" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,31 +4967,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D70" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F70" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G70" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H70" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9977391010127504</v>
+        <v>0.9785874279911531</v>
       </c>
       <c r="K70" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R70" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D71" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F71" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G71" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H71" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9979117863815348</v>
+        <v>0.9910993383802941</v>
       </c>
       <c r="K71" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R71" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,31 +5097,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D72" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F72" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G72" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H72" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5857852584277309</v>
+        <v>0.535878960202093</v>
       </c>
       <c r="K72" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R72" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,31 +5162,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F73" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G73" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H73" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9995944264398513</v>
+        <v>0.9937936419052401</v>
       </c>
       <c r="K73" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R73" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,31 +5227,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F74" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G74" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H74" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9996184721650414</v>
+        <v>0.9938258218686054</v>
       </c>
       <c r="K74" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R74" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,31 +5292,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F75" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G75" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H75" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9996899258226382</v>
+        <v>0.9965604051090238</v>
       </c>
       <c r="K75" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R75" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,31 +5357,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F76" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G76" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H76" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9998717285234845</v>
+        <v>0.9974704303505828</v>
       </c>
       <c r="K76" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R76" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,31 +5422,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F77" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G77" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H77" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9998819471930822</v>
+        <v>0.9977129937949676</v>
       </c>
       <c r="K77" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R77" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,31 +5487,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F78" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G78" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H78" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9999414448958831</v>
+        <v>0.9980001379602316</v>
       </c>
       <c r="K78" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R78" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F79" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G79" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H79" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J79" t="n">
-        <v>0.99996620234971</v>
+        <v>0.9989476387202305</v>
       </c>
       <c r="K79" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R79" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,31 +5617,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F80" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G80" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H80" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9999846125651255</v>
+        <v>0.9996627057619057</v>
       </c>
       <c r="K80" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R80" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,31 +5682,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F81" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G81" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H81" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9999949556902388</v>
+        <v>0.999783639677524</v>
       </c>
       <c r="K81" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R81" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,31 +5747,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F82" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G82" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H82" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857864398031205</v>
+        <v>0.5857864397352656</v>
       </c>
       <c r="K82" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R82" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,31 +5812,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F83" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G83" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H83" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9999999999999738</v>
       </c>
       <c r="K83" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R83" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,31 +5877,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F84" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G84" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H84" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9999999999999738</v>
       </c>
       <c r="K84" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R84" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,31 +5942,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F85" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G85" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H85" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9999999999999736</v>
       </c>
       <c r="K85" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R85" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F86" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G86" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H86" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9999999999999736</v>
       </c>
       <c r="K86" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R86" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,31 +6072,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F87" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G87" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H87" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999736</v>
       </c>
       <c r="K87" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R87" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,31 +6137,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F88" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G88" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H88" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999736</v>
       </c>
       <c r="K88" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R88" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,31 +6202,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.996492584092066</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3950073206618</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F89" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G89" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H89" t="n">
-        <v>4.198321359725795</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1665413257124506</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999736</v>
       </c>
       <c r="K89" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.959443299555603</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.4023514395022</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R89" t="n">
-        <v>11.10685089220932</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,31 +6267,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.996492647726609</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3950073529457</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F90" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G90" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H90" t="n">
-        <v>4.198323798877798</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1665413257124514</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9999999999999989</v>
+        <v>0.9999999999999734</v>
       </c>
       <c r="K90" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R90" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,31 +6332,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.996492647726609</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3950073529457</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F91" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G91" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H91" t="n">
-        <v>4.198323798877798</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1665413257124514</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9263831001902727</v>
+        <v>0.9999999999999734</v>
       </c>
       <c r="K91" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R91" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,31 +6397,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.996492647726609</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3950073529457</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F92" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G92" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H92" t="n">
-        <v>4.198323798877798</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1665413257124514</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5853512359782157</v>
+        <v>0.5857864397352656</v>
       </c>
       <c r="K92" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R92" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,31 +6462,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.996492647726609</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3950073529457</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F93" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G93" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H93" t="n">
-        <v>4.198323798877798</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1665413257124514</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9999999999999984</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="K93" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.959443341665116</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.4023514760537</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R93" t="n">
-        <v>11.10685089220767</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,31 +6527,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F94" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G94" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H94" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9355593375424699</v>
+        <v>0.9141547975213861</v>
       </c>
       <c r="K94" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R94" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,31 +6592,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F95" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G95" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H95" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J95" t="n">
-        <v>0.8834536852109889</v>
+        <v>0.9815054459273047</v>
       </c>
       <c r="K95" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R95" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,31 +6657,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F96" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G96" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H96" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9456579653655832</v>
+        <v>0.9907038433819619</v>
       </c>
       <c r="K96" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R96" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,31 +6722,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F97" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G97" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H97" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9770749257675437</v>
+        <v>0.9967217073627571</v>
       </c>
       <c r="K97" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R97" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,31 +6787,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F98" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G98" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H98" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9878029602584926</v>
+        <v>0.9979842987798817</v>
       </c>
       <c r="K98" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R98" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,31 +6852,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F99" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G99" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H99" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9963558781176564</v>
+        <v>0.9035263664577083</v>
       </c>
       <c r="K99" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R99" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,31 +6917,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F100" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G100" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H100" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9978412783819535</v>
+        <v>0.9833374049075508</v>
       </c>
       <c r="K100" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R100" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,31 +6982,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.996492636990905</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3950073300563</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F101" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G101" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H101" t="n">
-        <v>4.198322022060852</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1665413257124515</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J101" t="n">
-        <v>0.998233869651551</v>
+        <v>0.991667856995898</v>
       </c>
       <c r="K101" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.959443346609469</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.4023514500562</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R101" t="n">
-        <v>11.10685089220874</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,31 +7047,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.996492637204366</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3950073326256</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F102" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G102" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H102" t="n">
-        <v>4.198321491558088</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5857854668110557</v>
+        <v>0.5358883682353043</v>
       </c>
       <c r="K102" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R102" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,31 +7112,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.996492637204366</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3950073326256</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F103" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G103" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H103" t="n">
-        <v>4.198321491558088</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9999999999999971</v>
+        <v>0.9963042156199449</v>
       </c>
       <c r="K103" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R103" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,31 +7177,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.996492637204366</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3950073326256</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F104" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G104" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H104" t="n">
-        <v>4.198321491558088</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9972115956976858</v>
       </c>
       <c r="K104" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R104" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,31 +7242,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.996492637204366</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3950073326256</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F105" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G105" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H105" t="n">
-        <v>4.198321491558088</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9986172496189454</v>
       </c>
       <c r="K105" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.959443351504509</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.4023514516976</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R105" t="n">
-        <v>11.10685089220861</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,31 +7307,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F106" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G106" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H106" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9986259937925681</v>
       </c>
       <c r="K106" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R106" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,31 +7372,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F107" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G107" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H107" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9992534587937837</v>
       </c>
       <c r="K107" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R107" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,31 +7437,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F108" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G108" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H108" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9993865396928029</v>
       </c>
       <c r="K108" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R108" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F109" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G109" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H109" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9994481697003974</v>
       </c>
       <c r="K109" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R109" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,31 +7567,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F110" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G110" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H110" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9997988650587409</v>
       </c>
       <c r="K110" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R110" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,31 +7632,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F111" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G111" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H111" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9999753441792408</v>
       </c>
       <c r="K111" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R111" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,31 +7697,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F112" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G112" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H112" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5857864398123146</v>
+        <v>0.5857864397352638</v>
       </c>
       <c r="K112" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R112" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,31 +7762,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.996492631361938</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3950073356992</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F113" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G113" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H113" t="n">
-        <v>4.198321605081839</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K113" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.959443344660257</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.4023514549697</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R113" t="n">
-        <v>11.10685089220798</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,31 +7827,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.996492637082704</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3950073307059</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F114" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G114" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H114" t="n">
-        <v>4.198321377903479</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J114" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K114" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R114" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,31 +7892,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.996492637082704</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3950073307059</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F115" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G115" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H115" t="n">
-        <v>4.198321377903479</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J115" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K115" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R115" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,31 +7957,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.996492637082704</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D116" t="n">
-        <v>113.3950073307059</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F116" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G116" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H116" t="n">
-        <v>4.198321377903479</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J116" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K116" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R116" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.996492637082704</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3950073307059</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F117" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G117" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H117" t="n">
-        <v>4.198321377903479</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J117" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K117" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.959443352385827</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.4023514495791</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R117" t="n">
-        <v>11.10685089220566</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,31 +8087,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.996492634704269</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3950073329196</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F118" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G118" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H118" t="n">
-        <v>4.198321521728682</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J118" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K118" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R118" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,31 +8152,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.996492634704269</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3950073329196</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F119" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G119" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H119" t="n">
-        <v>4.198321521728682</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J119" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K119" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R119" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,31 +8217,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.996492634704269</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3950073329196</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F120" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G120" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H120" t="n">
-        <v>4.198321521728682</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J120" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K120" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R120" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,31 +8282,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.996492634704269</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3950073329196</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F121" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G121" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H121" t="n">
-        <v>4.198321521728682</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1665413257124516</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J121" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K121" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.959443348738161</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.4023514520443</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R121" t="n">
-        <v>11.10685089220422</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,31 +8347,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.996492637662654</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3950073290671</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.959443346540245</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F122" t="n">
-        <v>113.4023514492139</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G122" t="n">
-        <v>11.10685089219783</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H122" t="n">
-        <v>4.198322106025437</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857864398123146</v>
+        <v>0.5857864397352656</v>
       </c>
       <c r="K122" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.959443346540245</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.4023514492139</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R122" t="n">
-        <v>11.10685089219783</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,31 +8412,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.996492638929497</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3950073326659</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.959443350521477</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F123" t="n">
-        <v>113.4023514522747</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G123" t="n">
-        <v>11.10685089219813</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H123" t="n">
-        <v>4.198321798438977</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J123" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.959443350521477</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.4023514522747</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R123" t="n">
-        <v>11.10685089219813</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,31 +8477,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.996492638929497</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3950073326659</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.959443350521477</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F124" t="n">
-        <v>113.4023514522747</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G124" t="n">
-        <v>11.10685089219813</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H124" t="n">
-        <v>4.198321798438977</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9025431043643038</v>
+        <v>0.9261776022764491</v>
       </c>
       <c r="K124" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.959443350521477</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.4023514522747</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R124" t="n">
-        <v>11.10685089219813</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,31 +8542,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F125" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G125" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H125" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J125" t="n">
-        <v>0.8936035806071022</v>
+        <v>0.981869612415996</v>
       </c>
       <c r="K125" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R125" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,31 +8607,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F126" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G126" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H126" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9334307853784155</v>
+        <v>0.9933728063118151</v>
       </c>
       <c r="K126" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R126" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,31 +8672,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F127" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G127" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H127" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J127" t="n">
-        <v>0.977336597496686</v>
+        <v>0.9940949597417921</v>
       </c>
       <c r="K127" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R127" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,31 +8737,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F128" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G128" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H128" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J128" t="n">
-        <v>0.8818066871400528</v>
+        <v>0.9953414224164435</v>
       </c>
       <c r="K128" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R128" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,31 +8802,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F129" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G129" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H129" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9596847862874449</v>
+        <v>0.8957536511648081</v>
       </c>
       <c r="K129" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R129" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F130" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G130" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H130" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9718245328978098</v>
+        <v>0.9748601096777615</v>
       </c>
       <c r="K130" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R130" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,31 +8932,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F131" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G131" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H131" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9873685035285413</v>
+        <v>0.9951341657187575</v>
       </c>
       <c r="K131" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R131" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F132" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G132" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H132" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5857807839914929</v>
+        <v>0.5358948459504742</v>
       </c>
       <c r="K132" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R132" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,31 +9062,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D133" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F133" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G133" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H133" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9992587145507036</v>
+        <v>0.9975065537351386</v>
       </c>
       <c r="K133" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R133" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,31 +9127,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D134" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F134" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G134" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H134" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9993509829344496</v>
+        <v>0.9974821947336754</v>
       </c>
       <c r="K134" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R134" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,31 +9192,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.996492644649821</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D135" t="n">
-        <v>113.3950073315269</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F135" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G135" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H135" t="n">
-        <v>4.198321694429744</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1665413257124517</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9995010948483487</v>
+        <v>0.9978773826364659</v>
       </c>
       <c r="K135" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.959443357159659</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.4023514509539</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R135" t="n">
-        <v>11.10685089219486</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,31 +9257,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D136" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F136" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G136" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H136" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9997627336312898</v>
+        <v>0.9984349473875361</v>
       </c>
       <c r="K136" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R136" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,31 +9322,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D137" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F137" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G137" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H137" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9998326787502788</v>
+        <v>0.9984667121472744</v>
       </c>
       <c r="K137" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R137" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D138" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F138" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G138" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H138" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9999216178442795</v>
+        <v>0.9986021745672522</v>
       </c>
       <c r="K138" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R138" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,31 +9452,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D139" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F139" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G139" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H139" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9999831921193196</v>
+        <v>0.9986929663404566</v>
       </c>
       <c r="K139" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R139" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,31 +9517,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D140" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F140" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G140" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H140" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9999871698765824</v>
+        <v>0.9988881322025019</v>
       </c>
       <c r="K140" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R140" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,31 +9582,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D141" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F141" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G141" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H141" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9999876002810782</v>
+        <v>0.9996280488982814</v>
       </c>
       <c r="K141" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R141" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,31 +9647,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.996492637240565</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D142" t="n">
-        <v>113.3950073280323</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F142" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G142" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H142" t="n">
-        <v>4.198321791687085</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857864398045713</v>
+        <v>0.5857864378914066</v>
       </c>
       <c r="K142" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.959443348892131</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.4023514476293</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R142" t="n">
-        <v>11.10685089219505</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.996492637049576</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D143" t="n">
-        <v>113.3950073322035</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.959443349064713</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F143" t="n">
-        <v>113.4023514517284</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G143" t="n">
-        <v>11.1068508921925</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H143" t="n">
-        <v>4.198321750487523</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9999999381618503</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K143" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.959443349064713</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.4023514517284</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R143" t="n">
-        <v>11.1068508921925</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,31 +9777,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.996492639639535</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D144" t="n">
-        <v>113.3950073306689</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.959443343951803</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F144" t="n">
-        <v>113.4023514517206</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G144" t="n">
-        <v>11.10685089219156</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H144" t="n">
-        <v>4.198322623354177</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J144" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K144" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.959443343951803</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.4023514517206</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R144" t="n">
-        <v>11.10685089219156</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,31 +9842,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.996492636551791</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D145" t="n">
-        <v>113.3950073326119</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.959443348978319</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F145" t="n">
-        <v>113.4023514520552</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G145" t="n">
-        <v>11.10685089218757</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H145" t="n">
-        <v>4.19832170387035</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J145" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K145" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.959443348978319</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.4023514520552</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R145" t="n">
-        <v>11.10685089218757</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,31 +9907,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.996492636551791</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D146" t="n">
-        <v>113.3950073326119</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.959443348978319</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F146" t="n">
-        <v>113.4023514520552</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G146" t="n">
-        <v>11.10685089218757</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H146" t="n">
-        <v>4.19832170387035</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1665413257124518</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J146" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K146" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.959443348978319</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.4023514520552</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R146" t="n">
-        <v>11.10685089218757</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,31 +9972,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.996492636527028</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D147" t="n">
-        <v>113.3950073329351</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.959443347302643</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F147" t="n">
-        <v>113.4023514527056</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G147" t="n">
-        <v>11.10685089218751</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H147" t="n">
-        <v>4.198321890946898</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1665413257124519</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J147" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K147" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.959443347302643</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.4023514527056</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R147" t="n">
-        <v>11.10685089218751</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,31 +10037,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.996492634377693</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D148" t="n">
-        <v>113.3950073322339</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.959443347560597</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F148" t="n">
-        <v>113.4023514515273</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G148" t="n">
-        <v>11.10685089218264</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H148" t="n">
-        <v>4.198321618159794</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1665413257124519</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J148" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K148" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.959443347560597</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.4023514515273</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R148" t="n">
-        <v>11.10685089218264</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,31 +10102,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.996492640304528</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3950073281443</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.959443348145716</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F149" t="n">
-        <v>113.4023514484966</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G149" t="n">
-        <v>11.10685089218194</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H149" t="n">
-        <v>4.198322223467372</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1665413257124519</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J149" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K149" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.959443348145716</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.4023514484966</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R149" t="n">
-        <v>11.10685089218194</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,31 +10167,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.996492640305561</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3950073283729</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.9594433497499</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F150" t="n">
-        <v>113.4023514484074</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G150" t="n">
-        <v>11.10685089217983</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H150" t="n">
-        <v>4.19832204180276</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1665413257124519</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K150" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.9594433497499</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.4023514484074</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R150" t="n">
-        <v>11.10685089217983</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,31 +10232,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.996492642011622</v>
+        <v>-8.060587153218956</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3950073271609</v>
+        <v>113.3411693293282</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.95944335146288</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="F151" t="n">
-        <v>113.4023514471941</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="G151" t="n">
-        <v>11.10685089217502</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="H151" t="n">
-        <v>4.198322041018889</v>
+        <v>12.20856082819068</v>
       </c>
       <c r="I151" t="n">
-        <v>0.166541325712452</v>
+        <v>0.1726274936243277</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K151" t="n">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="L151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.95944335146288</v>
+        <v>-7.958652976529417</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.4023514471941</v>
+        <v>113.3823657719438</v>
       </c>
       <c r="R151" t="n">
-        <v>11.10685089217502</v>
+        <v>21.81440368406435</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C2" t="n">
-        <v>-7.758869897387893</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D2" t="n">
-        <v>113.3313620128502</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.900241723811564</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F2" t="n">
-        <v>113.4042126851261</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G2" t="n">
-        <v>152.96024955412</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H2" t="n">
-        <v>17.64979847275782</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.170977603613874</v>
+        <v>0.1671673548520525</v>
       </c>
       <c r="J2" t="n">
-        <v>0.848426528906747</v>
+        <v>0.8922371708293431</v>
       </c>
       <c r="K2" t="n">
-        <v>1252</v>
+        <v>1965</v>
       </c>
       <c r="L2" t="n">
-        <v>448</v>
+        <v>1797</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O2" t="n">
-        <v>113.40414682924</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.900241723811564</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.4042126851261</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R2" t="n">
-        <v>152.96024955412</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.993596736027385</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3979638491904</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.98655178101114</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F3" t="n">
-        <v>113.4036085074246</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G3" t="n">
-        <v>38.43084049780076</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1717180389495196</v>
+        <v>0.1671673548520525</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8760281541333088</v>
+        <v>0.9603030880641853</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>1965</v>
       </c>
       <c r="L3" t="n">
-        <v>448</v>
+        <v>1797</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O3" t="n">
-        <v>113.40414682924</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.98655178101114</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.4036085074246</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R3" t="n">
-        <v>38.43084049780076</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -677,28 +677,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.993596736027385</v>
+        <v>-7.963264109685748</v>
       </c>
       <c r="D4" t="n">
-        <v>113.3979638491904</v>
+        <v>113.4064375270518</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.98655178101114</v>
+        <v>-7.966625587708326</v>
       </c>
       <c r="F4" t="n">
-        <v>113.4036085074246</v>
+        <v>113.4148601466131</v>
       </c>
       <c r="G4" t="n">
-        <v>38.43084049780076</v>
+        <v>111.9494698432437</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1717180389495196</v>
+        <v>0.1682221770288521</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9683215011049801</v>
+        <v>0.9774849780836027</v>
       </c>
       <c r="K4" t="n">
         <v>448</v>
@@ -716,13 +716,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.98655178101114</v>
+        <v>-7.966625587708326</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.4036085074246</v>
+        <v>113.4148601466131</v>
       </c>
       <c r="R4" t="n">
-        <v>38.43084049780076</v>
+        <v>111.9494698432437</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -742,31 +742,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.126026477429207</v>
+        <v>-7.958700702975671</v>
       </c>
       <c r="D5" t="n">
-        <v>113.1881633270401</v>
+        <v>113.3984403084908</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.949127122244501</v>
+        <v>-7.968030485669297</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3738842397426</v>
+        <v>113.4159133833603</v>
       </c>
       <c r="G5" t="n">
-        <v>46.12405460523132</v>
+        <v>118.3325847337771</v>
       </c>
       <c r="H5" t="n">
-        <v>28.37351051231659</v>
+        <v>2.186029232032917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.171922567619131</v>
+        <v>0.1682871435082686</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9896453092969095</v>
+        <v>0.9939403160332684</v>
       </c>
       <c r="K5" t="n">
-        <v>870</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
         <v>448</v>
@@ -781,13 +781,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.949127122244501</v>
+        <v>-7.968030485669297</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3738842397426</v>
+        <v>113.4159133833603</v>
       </c>
       <c r="R5" t="n">
-        <v>46.12405460523132</v>
+        <v>118.3325847337771</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -804,55 +804,55 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-8.056712198943654</v>
+        <v>-7.949860007626683</v>
       </c>
       <c r="D6" t="n">
-        <v>113.2945758507509</v>
+        <v>113.3538712550597</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.963348844637008</v>
+        <v>-7.946513023815009</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3629913800458</v>
+        <v>113.3622994131996</v>
       </c>
       <c r="G6" t="n">
-        <v>35.97085753970362</v>
+        <v>68.15122051178177</v>
       </c>
       <c r="H6" t="n">
-        <v>12.82676379724179</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1723386602198647</v>
+        <v>0.1685502676131463</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9932863402717761</v>
+        <v>0.9958600420628068</v>
       </c>
       <c r="K6" t="n">
-        <v>1591</v>
+        <v>640</v>
       </c>
       <c r="L6" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O6" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.963348844637008</v>
+        <v>-7.946513023815009</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3629913800458</v>
+        <v>113.3622994131996</v>
       </c>
       <c r="R6" t="n">
-        <v>35.97085753970362</v>
+        <v>68.15122051178177</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -869,55 +869,55 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.072415341362056</v>
+        <v>-7.778411924554954</v>
       </c>
       <c r="D7" t="n">
-        <v>113.2893877946882</v>
+        <v>113.3255315235373</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.966154533203673</v>
+        <v>-7.960514775216507</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3667933008129</v>
+        <v>113.4121969375984</v>
       </c>
       <c r="G7" t="n">
-        <v>35.80925875647314</v>
+        <v>154.7651939515681</v>
       </c>
       <c r="H7" t="n">
-        <v>14.56881044281476</v>
+        <v>22.38625773496128</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1723564481915239</v>
+        <v>0.1688952712594764</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9958326180805566</v>
+        <v>0.9975888412332371</v>
       </c>
       <c r="K7" t="n">
-        <v>1690</v>
+        <v>1909</v>
       </c>
       <c r="L7" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O7" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.966154533203673</v>
+        <v>-7.960514775216507</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3667933008129</v>
+        <v>113.4121969375984</v>
       </c>
       <c r="R7" t="n">
-        <v>35.80925875647314</v>
+        <v>154.7651939515681</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.986152780045161</v>
+        <v>-7.778411924554954</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3989792028485</v>
+        <v>113.3255315235373</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.977206946067169</v>
+        <v>-7.960514775216507</v>
       </c>
       <c r="F8" t="n">
-        <v>113.3999101703452</v>
+        <v>113.4121969375984</v>
       </c>
       <c r="G8" t="n">
-        <v>5.884137565270155</v>
+        <v>154.7651939515681</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>22.38625773496128</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1723746132341398</v>
+        <v>0.1688952712594764</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9969147837346479</v>
+        <v>0.9984667530564295</v>
       </c>
       <c r="K8" t="n">
-        <v>448</v>
+        <v>1909</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.977206946067169</v>
+        <v>-7.960514775216507</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.3999101703452</v>
+        <v>113.4121969375984</v>
       </c>
       <c r="R8" t="n">
-        <v>5.884137565270155</v>
+        <v>154.7651939515681</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -999,55 +999,55 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.012981610206946</v>
+        <v>-7.919697559386807</v>
       </c>
       <c r="D9" t="n">
-        <v>113.3256696182571</v>
+        <v>113.3863659928242</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.950953023144121</v>
+        <v>-7.92819530240732</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3611738685399</v>
+        <v>113.389338229728</v>
       </c>
       <c r="G9" t="n">
-        <v>29.54876227601597</v>
+        <v>160.8926769137976</v>
       </c>
       <c r="H9" t="n">
-        <v>7.928276782439065</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1723924412849851</v>
+        <v>0.1691810546819559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9978783801538877</v>
+        <v>0.9985874748239016</v>
       </c>
       <c r="K9" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L9" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O9" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.950953023144121</v>
+        <v>-7.92819530240732</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3611738685399</v>
+        <v>113.389338229728</v>
       </c>
       <c r="R9" t="n">
-        <v>29.54876227601597</v>
+        <v>160.8926769137976</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.050166666356585</v>
+        <v>-7.927574870414333</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3421240705891</v>
+        <v>113.3860729544726</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.961421929378776</v>
+        <v>-7.936395861962063</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3951852207047</v>
+        <v>113.3878414575412</v>
       </c>
       <c r="G10" t="n">
-        <v>30.63264119999745</v>
+        <v>168.7690005667855</v>
       </c>
       <c r="H10" t="n">
-        <v>11.46791253468468</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1725555961059663</v>
+        <v>0.1693107374601433</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9985964650949529</v>
+        <v>0.9982587934176675</v>
       </c>
       <c r="K10" t="n">
-        <v>1004</v>
+        <v>448</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.961421929378776</v>
+        <v>-7.936395861962063</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3951852207047</v>
+        <v>113.3878414575412</v>
       </c>
       <c r="R10" t="n">
-        <v>30.63264119999745</v>
+        <v>168.7690005667855</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,31 +1132,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.050166666356585</v>
+        <v>-7.927574870414333</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3421240705891</v>
+        <v>113.3860729544726</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.961421929378776</v>
+        <v>-7.936395861962063</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3951852207047</v>
+        <v>113.3878414575412</v>
       </c>
       <c r="G11" t="n">
-        <v>30.63264119999745</v>
+        <v>168.7690005667855</v>
       </c>
       <c r="H11" t="n">
-        <v>11.46791253468468</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1725555961059663</v>
+        <v>0.1693107374601433</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9991662669638218</v>
+        <v>0.9983725603364841</v>
       </c>
       <c r="K11" t="n">
-        <v>1004</v>
+        <v>448</v>
       </c>
       <c r="L11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.961421929378776</v>
+        <v>-7.936395861962063</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3951852207047</v>
+        <v>113.3878414575412</v>
       </c>
       <c r="R11" t="n">
-        <v>30.63264119999745</v>
+        <v>168.7690005667855</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-8.050166666356585</v>
+        <v>-7.851691490845276</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3421240705891</v>
+        <v>113.4589139680096</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.961421929378776</v>
+        <v>-7.974148199168034</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3951852207047</v>
+        <v>113.393801561749</v>
       </c>
       <c r="G12" t="n">
-        <v>30.63264119999745</v>
+        <v>207.7692819605994</v>
       </c>
       <c r="H12" t="n">
-        <v>11.46791253468468</v>
+        <v>15.38952161731767</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1725555961059663</v>
+        <v>0.1693338216791876</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857862304530788</v>
+        <v>0.5857853518158063</v>
       </c>
       <c r="K12" t="n">
-        <v>1004</v>
+        <v>1426</v>
       </c>
       <c r="L12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.961421929378776</v>
+        <v>-7.974148199168034</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3951852207047</v>
+        <v>113.393801561749</v>
       </c>
       <c r="R12" t="n">
-        <v>30.63264119999745</v>
+        <v>207.7692819605994</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,31 +1262,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-8.138909496048235</v>
+        <v>-7.883387947947598</v>
       </c>
       <c r="D13" t="n">
-        <v>113.188496719188</v>
+        <v>113.4173405482411</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.967331100339034</v>
+        <v>-7.949109876521227</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3726875431818</v>
+        <v>113.3882337145641</v>
       </c>
       <c r="G13" t="n">
-        <v>46.75999594836188</v>
+        <v>203.683046913467</v>
       </c>
       <c r="H13" t="n">
-        <v>27.84307593162957</v>
+        <v>7.98013186790247</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1725658534015325</v>
+        <v>0.1694988756166519</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9997614319656556</v>
+        <v>0.9993684200314595</v>
       </c>
       <c r="K13" t="n">
-        <v>230</v>
+        <v>448</v>
       </c>
       <c r="L13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.967331100339034</v>
+        <v>-7.949109876521227</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3726875431818</v>
+        <v>113.3882337145641</v>
       </c>
       <c r="R13" t="n">
-        <v>46.75999594836188</v>
+        <v>203.683046913467</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,31 +1327,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-8.133964112350778</v>
+        <v>-7.883387947947598</v>
       </c>
       <c r="D14" t="n">
-        <v>113.1921344795859</v>
+        <v>113.4173405482411</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.960698496567066</v>
+        <v>-7.949109876521227</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3726341312996</v>
+        <v>113.3882337145641</v>
       </c>
       <c r="G14" t="n">
-        <v>45.90081265877914</v>
+        <v>203.683046913467</v>
       </c>
       <c r="H14" t="n">
-        <v>27.67895738744387</v>
+        <v>7.98013186790247</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1725790035651913</v>
+        <v>0.1694988756166519</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9998532159882639</v>
+        <v>0.9993610188615443</v>
       </c>
       <c r="K14" t="n">
-        <v>671</v>
+        <v>448</v>
       </c>
       <c r="L14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.960698496567066</v>
+        <v>-7.949109876521227</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3726341312996</v>
+        <v>113.3882337145641</v>
       </c>
       <c r="R14" t="n">
-        <v>45.90081265877914</v>
+        <v>203.683046913467</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,31 +1392,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-8.058423645645544</v>
+        <v>-7.950907011494536</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3438067126452</v>
+        <v>113.3995920884386</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.963700994655056</v>
+        <v>-7.959263001754305</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3787456414393</v>
+        <v>113.3962348205603</v>
       </c>
       <c r="G15" t="n">
-        <v>20.06743474061498</v>
+        <v>201.6980394812829</v>
       </c>
       <c r="H15" t="n">
-        <v>11.213279015794</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.172587348060906</v>
+        <v>0.1695315002098256</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9998765245893947</v>
+        <v>0.9994797774650047</v>
       </c>
       <c r="K15" t="n">
-        <v>1438</v>
+        <v>448</v>
       </c>
       <c r="L15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.963700994655056</v>
+        <v>-7.959263001754305</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3787456414393</v>
+        <v>113.3962348205603</v>
       </c>
       <c r="R15" t="n">
-        <v>20.06743474061498</v>
+        <v>201.6980394812829</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,31 +1457,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-8.058921340873448</v>
+        <v>-7.950907011494536</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3482511971719</v>
+        <v>113.3995920884386</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.959489586493329</v>
+        <v>-7.959263001754305</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3854753081178</v>
+        <v>113.3962348205603</v>
       </c>
       <c r="G16" t="n">
-        <v>20.34318262735099</v>
+        <v>201.6980394812829</v>
       </c>
       <c r="H16" t="n">
-        <v>11.79159567167438</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1726018237729497</v>
+        <v>0.1695315002098256</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9998812684985567</v>
+        <v>0.9995078116793321</v>
       </c>
       <c r="K16" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.959489586493329</v>
+        <v>-7.959263001754305</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3854753081178</v>
+        <v>113.3962348205603</v>
       </c>
       <c r="R16" t="n">
-        <v>20.34318262735099</v>
+        <v>201.6980394812829</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-8.063532153704026</v>
+        <v>-7.950907011494536</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3393283151189</v>
+        <v>113.3995920884386</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.961403325694623</v>
+        <v>-7.959263001754305</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3813386283987</v>
+        <v>113.3962348205603</v>
       </c>
       <c r="G17" t="n">
-        <v>22.1655037138142</v>
+        <v>201.6980394812829</v>
       </c>
       <c r="H17" t="n">
-        <v>12.26217073655936</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1726190942842914</v>
+        <v>0.1695315002098256</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9998615556002004</v>
+        <v>0.999490494190392</v>
       </c>
       <c r="K17" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.961403325694623</v>
+        <v>-7.959263001754305</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3813386283987</v>
+        <v>113.3962348205603</v>
       </c>
       <c r="R17" t="n">
-        <v>22.1655037138142</v>
+        <v>201.6980394812829</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-8.061838968193639</v>
+        <v>-7.94977076373936</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3396839744847</v>
+        <v>113.4005490429886</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.957606164997337</v>
+        <v>-7.958355215204417</v>
       </c>
       <c r="F18" t="n">
-        <v>113.381234627831</v>
+        <v>113.3971116679271</v>
       </c>
       <c r="G18" t="n">
-        <v>21.5442432910529</v>
+        <v>201.6313768214382</v>
       </c>
       <c r="H18" t="n">
-        <v>12.46048817679355</v>
+        <v>1.026866339754594</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1726226021853366</v>
+        <v>0.16953335413524</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9998739224991265</v>
+        <v>0.9995760205219847</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.957606164997337</v>
+        <v>-7.958355215204417</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.381234627831</v>
+        <v>113.3971116679271</v>
       </c>
       <c r="R18" t="n">
-        <v>21.5442432910529</v>
+        <v>201.6313768214382</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-8.059854541077739</v>
+        <v>-7.94977076373936</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3427534392312</v>
+        <v>113.4005490429886</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.95765033259031</v>
+        <v>-7.958355215204417</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3837726565298</v>
+        <v>113.3971116679271</v>
       </c>
       <c r="G19" t="n">
-        <v>21.67728117529937</v>
+        <v>201.6313768214382</v>
       </c>
       <c r="H19" t="n">
-        <v>12.22922541155783</v>
+        <v>1.026866339754594</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1726243648276834</v>
+        <v>0.16953335413524</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9999045495419379</v>
+        <v>0.9995689506801857</v>
       </c>
       <c r="K19" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.95765033259031</v>
+        <v>-7.958355215204417</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3837726565298</v>
+        <v>113.3971116679271</v>
       </c>
       <c r="R19" t="n">
-        <v>21.67728117529937</v>
+        <v>201.6313768214382</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-8.062474818097195</v>
+        <v>-7.94977076373936</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3415688419264</v>
+        <v>113.4005490429886</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.95858078020991</v>
+        <v>-7.958355215204417</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3831764448753</v>
+        <v>113.3971116679271</v>
       </c>
       <c r="G20" t="n">
-        <v>21.63486461387023</v>
+        <v>201.6313768214382</v>
       </c>
       <c r="H20" t="n">
-        <v>12.42776492022879</v>
+        <v>1.026866339754594</v>
       </c>
       <c r="I20" t="n">
-        <v>0.172624579090728</v>
+        <v>0.16953335413524</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9999148488104418</v>
+        <v>0.9997266035111343</v>
       </c>
       <c r="K20" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.95858078020991</v>
+        <v>-7.958355215204417</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3831764448753</v>
+        <v>113.3971116679271</v>
       </c>
       <c r="R20" t="n">
-        <v>21.63486461387023</v>
+        <v>201.6313768214382</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-8.064922708311267</v>
+        <v>-7.948783649321465</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3405748436671</v>
+        <v>113.3981975149658</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.959477552114903</v>
+        <v>-7.957277272954132</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3831008161651</v>
+        <v>113.394804052421</v>
       </c>
       <c r="G21" t="n">
-        <v>21.77288681099294</v>
+        <v>201.587868665987</v>
       </c>
       <c r="H21" t="n">
-        <v>12.62540134285114</v>
+        <v>1.015695983026278</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1726264292473598</v>
+        <v>0.1695361061650917</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9999263335758874</v>
+        <v>0.9998616605545286</v>
       </c>
       <c r="K21" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.959477552114903</v>
+        <v>-7.957277272954132</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3831008161651</v>
+        <v>113.394804052421</v>
       </c>
       <c r="R21" t="n">
-        <v>21.77288681099294</v>
+        <v>201.587868665987</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-8.064922708311267</v>
+        <v>-7.947254491394587</v>
       </c>
       <c r="D22" t="n">
-        <v>113.3405748436671</v>
+        <v>113.3977957155772</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.959477552114903</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3831008161651</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="G22" t="n">
-        <v>21.77288681099294</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="H22" t="n">
-        <v>12.62540134285114</v>
+        <v>1.04788630253388</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1726264292473598</v>
+        <v>0.1695365492043995</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857864376357882</v>
+        <v>0.5857864354828364</v>
       </c>
       <c r="K22" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.959477552114903</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3831008161651</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="R22" t="n">
-        <v>21.77288681099294</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-8.062054973168523</v>
+        <v>-7.947254491394587</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3403595296541</v>
+        <v>113.3977957155772</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.959347539034096</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="F23" t="n">
-        <v>113.381880939577</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="G23" t="n">
-        <v>21.82030554376683</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="H23" t="n">
-        <v>12.30167834812455</v>
+        <v>1.04788630253388</v>
       </c>
       <c r="I23" t="n">
-        <v>0.172627142999938</v>
+        <v>0.1695365492043995</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999482802624661</v>
+        <v>0.9999664846974102</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.959347539034096</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.381880939577</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="R23" t="n">
-        <v>21.82030554376683</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-8.062054973168523</v>
+        <v>-7.947254491394587</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3403595296541</v>
+        <v>113.3977957155772</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.959347539034096</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="F24" t="n">
-        <v>113.381880939577</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="G24" t="n">
-        <v>21.82030554376683</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="H24" t="n">
-        <v>12.30167834812455</v>
+        <v>1.04788630253388</v>
       </c>
       <c r="I24" t="n">
-        <v>0.172627142999938</v>
+        <v>0.1695365492043995</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9999472106387636</v>
+        <v>0.9999685335011461</v>
       </c>
       <c r="K24" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.959347539034096</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.381880939577</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="R24" t="n">
-        <v>21.82030554376683</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-8.060658484824932</v>
+        <v>-7.947254491394587</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3416374647604</v>
+        <v>113.3977957155772</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.958667515723249</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3828545544675</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="G25" t="n">
-        <v>21.81329761172898</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="H25" t="n">
-        <v>12.21526830718335</v>
+        <v>1.04788630253388</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1726273907238148</v>
+        <v>0.1695365492043995</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999467846184487</v>
+        <v>0.9999764690136572</v>
       </c>
       <c r="K25" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.958667515723249</v>
+        <v>-7.956018787783186</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3828545544675</v>
+        <v>113.3942985093004</v>
       </c>
       <c r="R25" t="n">
-        <v>21.81329761172898</v>
+        <v>201.5633019054962</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-8.060658484824932</v>
+        <v>-7.947840354508198</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3416374647604</v>
+        <v>113.3989530261183</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.958667515723249</v>
+        <v>-7.956252180330369</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3828545544675</v>
+        <v>113.3956023434042</v>
       </c>
       <c r="G26" t="n">
-        <v>21.81329761172898</v>
+        <v>201.5289904317556</v>
       </c>
       <c r="H26" t="n">
-        <v>12.21526830718335</v>
+        <v>1.005505981779332</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1726273907238148</v>
+        <v>0.1695368880754247</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9999463607635352</v>
+        <v>0.999983703489746</v>
       </c>
       <c r="K26" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.958667515723249</v>
+        <v>-7.956252180330369</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3828545544675</v>
+        <v>113.3956023434042</v>
       </c>
       <c r="R26" t="n">
-        <v>21.81329761172898</v>
+        <v>201.5289904317556</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-8.061341513969014</v>
+        <v>-7.947686705220216</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3408533158868</v>
+        <v>113.3980773668556</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.958614646481205</v>
+        <v>-7.956145392902079</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3823753393074</v>
+        <v>113.3947046630095</v>
       </c>
       <c r="G27" t="n">
-        <v>21.81689263783882</v>
+        <v>201.5484663420931</v>
       </c>
       <c r="H27" t="n">
-        <v>12.30371260583434</v>
+        <v>1.011243279736596</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1726274559640359</v>
+        <v>0.1695370131074387</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999459750304748</v>
+        <v>0.9999899574448144</v>
       </c>
       <c r="K27" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.958614646481205</v>
+        <v>-7.956145392902079</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3823753393074</v>
+        <v>113.3947046630095</v>
       </c>
       <c r="R27" t="n">
-        <v>21.81689263783882</v>
+        <v>201.5484663420931</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-8.061341513969014</v>
+        <v>-7.948056629872416</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3408533158868</v>
+        <v>113.3990593549623</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.958614646481205</v>
+        <v>-7.956655370437868</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3823753393074</v>
+        <v>113.3956310171014</v>
       </c>
       <c r="G28" t="n">
-        <v>21.81689263783882</v>
+        <v>201.5472494699561</v>
       </c>
       <c r="H28" t="n">
-        <v>12.30371260583434</v>
+        <v>1.027978126671472</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1726274559640359</v>
+        <v>0.1695370772295136</v>
       </c>
       <c r="J28" t="n">
-        <v>0.999945844597167</v>
+        <v>0.9999910289216034</v>
       </c>
       <c r="K28" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.958614646481205</v>
+        <v>-7.956655370437868</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3823753393074</v>
+        <v>113.3956310171014</v>
       </c>
       <c r="R28" t="n">
-        <v>21.81689263783882</v>
+        <v>201.5472494699561</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-8.061552061448616</v>
+        <v>-7.947492573581599</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3407094288754</v>
+        <v>113.3987632508614</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.958753217408495</v>
+        <v>-7.956239601477443</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3822534898266</v>
+        <v>113.3952758875022</v>
       </c>
       <c r="G29" t="n">
-        <v>21.81352942719412</v>
+        <v>201.546724359711</v>
       </c>
       <c r="H29" t="n">
-        <v>12.31204393517703</v>
+        <v>1.045702099494519</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1726274723403671</v>
+        <v>0.1695371523123573</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9999492197379297</v>
+        <v>0.9999944197970172</v>
       </c>
       <c r="K29" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.958753217408495</v>
+        <v>-7.956239601477443</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3822534898266</v>
+        <v>113.3952758875022</v>
       </c>
       <c r="R29" t="n">
-        <v>21.81352942719412</v>
+        <v>201.546724359711</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-8.060615052001811</v>
+        <v>-7.947492573581599</v>
       </c>
       <c r="D30" t="n">
-        <v>113.3412921084304</v>
+        <v>113.3987632508614</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.958671554258573</v>
+        <v>-7.956239601477443</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3824907920324</v>
+        <v>113.3952758875022</v>
       </c>
       <c r="G30" t="n">
-        <v>21.81367062205648</v>
+        <v>201.546724359711</v>
       </c>
       <c r="H30" t="n">
-        <v>12.20961467134593</v>
+        <v>1.045702099494519</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1726274769253296</v>
+        <v>0.1695371523123573</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9999489633521461</v>
+        <v>0.9999975073968307</v>
       </c>
       <c r="K30" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.958671554258573</v>
+        <v>-7.956239601477443</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3824907920324</v>
+        <v>113.3952758875022</v>
       </c>
       <c r="R30" t="n">
-        <v>21.81367062205648</v>
+        <v>201.546724359711</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.904362523902446</v>
+        <v>-7.947833529766453</v>
       </c>
       <c r="D31" t="n">
-        <v>113.4043620808579</v>
+        <v>113.3986258952773</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.958555161382233</v>
+        <v>-7.956198148418074</v>
       </c>
       <c r="F31" t="n">
-        <v>113.3824594138636</v>
+        <v>113.395290630395</v>
       </c>
       <c r="G31" t="n">
-        <v>201.8145607201867</v>
+        <v>201.5488682957016</v>
       </c>
       <c r="H31" t="n">
-        <v>6.490807391867424</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1726274845895527</v>
+        <v>0.1695371844790213</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9999541408786627</v>
+        <v>0.9999983201638695</v>
       </c>
       <c r="K31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.958555161382233</v>
+        <v>-7.956198148418074</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.3824594138636</v>
+        <v>113.395290630395</v>
       </c>
       <c r="R31" t="n">
-        <v>201.8145607201867</v>
+        <v>201.5488682957016</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-8.061087579117167</v>
+        <v>-7.947831214773533</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3410358217306</v>
+        <v>113.3986742992364</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.958705787511212</v>
+        <v>-7.956195831741564</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3824132987942</v>
+        <v>113.3953390300682</v>
       </c>
       <c r="G32" t="n">
-        <v>21.81446605006386</v>
+        <v>201.5488974982361</v>
       </c>
       <c r="H32" t="n">
-        <v>12.26217549551867</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1726274908511014</v>
+        <v>0.169537187718597</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5358983867452493</v>
+        <v>0.5857864397726815</v>
       </c>
       <c r="K32" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.958705787511212</v>
+        <v>-7.956195831741564</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3824132987942</v>
+        <v>113.3953390300682</v>
       </c>
       <c r="R32" t="n">
-        <v>21.81446605006386</v>
+        <v>201.5488974982361</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,28 +2562,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.904598259658232</v>
+        <v>-7.947831214773533</v>
       </c>
       <c r="D33" t="n">
-        <v>113.404177336508</v>
+        <v>113.3986742992364</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.958673216816945</v>
+        <v>-7.956195831741564</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3823222964956</v>
+        <v>113.3953390300682</v>
       </c>
       <c r="G33" t="n">
-        <v>201.814496734282</v>
+        <v>201.5488974982361</v>
       </c>
       <c r="H33" t="n">
-        <v>6.476709440632503</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1726274914041381</v>
+        <v>0.169537187718597</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999673015692158</v>
+        <v>0.9999997085855571</v>
       </c>
       <c r="K33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.958673216816945</v>
+        <v>-7.956195831741564</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3823222964956</v>
+        <v>113.3953390300682</v>
       </c>
       <c r="R33" t="n">
-        <v>201.814496734282</v>
+        <v>201.5488974982361</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,28 +2627,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.904598259658232</v>
+        <v>-7.94764392583857</v>
       </c>
       <c r="D34" t="n">
-        <v>113.404177336508</v>
+        <v>113.3988133314962</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.958673216816945</v>
+        <v>-7.956225118889897</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3823222964956</v>
+        <v>113.3953916712824</v>
       </c>
       <c r="G34" t="n">
-        <v>201.814496734282</v>
+        <v>201.5490925831322</v>
       </c>
       <c r="H34" t="n">
-        <v>6.476709440632503</v>
+        <v>1.0258933523843</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1726274914041381</v>
+        <v>0.1695371890952646</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9999742689309731</v>
+        <v>0.8530334251417701</v>
       </c>
       <c r="K34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.958673216816945</v>
+        <v>-7.956225118889897</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3823222964956</v>
+        <v>113.3953916712824</v>
       </c>
       <c r="R34" t="n">
-        <v>201.814496734282</v>
+        <v>201.5490925831322</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,28 +2692,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.904493207279992</v>
+        <v>-7.947691552103633</v>
       </c>
       <c r="D35" t="n">
-        <v>113.4042168183158</v>
+        <v>113.3987859426267</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.958670182761678</v>
+        <v>-7.956176882553048</v>
       </c>
       <c r="F35" t="n">
-        <v>113.3823206482044</v>
+        <v>113.3954025186885</v>
       </c>
       <c r="G35" t="n">
-        <v>201.8144045814301</v>
+        <v>201.54902539015</v>
       </c>
       <c r="H35" t="n">
-        <v>6.488924411776442</v>
+        <v>1.014432359074546</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1726274927663074</v>
+        <v>0.1695371896544744</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9999853063278347</v>
+        <v>0.9784934157929174</v>
       </c>
       <c r="K35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.958670182761678</v>
+        <v>-7.956176882553048</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3823206482044</v>
+        <v>113.3954025186885</v>
       </c>
       <c r="R35" t="n">
-        <v>201.8144045814301</v>
+        <v>201.54902539015</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.904493207279992</v>
+        <v>-7.947691552103633</v>
       </c>
       <c r="D36" t="n">
-        <v>113.4042168183158</v>
+        <v>113.3987859426267</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.958670182761678</v>
+        <v>-7.956176882553048</v>
       </c>
       <c r="F36" t="n">
-        <v>113.3823206482044</v>
+        <v>113.3954025186885</v>
       </c>
       <c r="G36" t="n">
-        <v>201.8144045814301</v>
+        <v>201.54902539015</v>
       </c>
       <c r="H36" t="n">
-        <v>6.488924411776442</v>
+        <v>1.014432359074546</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1726274927663074</v>
+        <v>0.1695371896544744</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9999932994191194</v>
+        <v>0.8736265668676111</v>
       </c>
       <c r="K36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.958670182761678</v>
+        <v>-7.956176882553048</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.3823206482044</v>
+        <v>113.3954025186885</v>
       </c>
       <c r="R36" t="n">
-        <v>201.8144045814301</v>
+        <v>201.54902539015</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,28 +2822,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.904509525705922</v>
+        <v>-7.947604122486936</v>
       </c>
       <c r="D37" t="n">
-        <v>113.4042472303964</v>
+        <v>113.3988110363126</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.958634265706793</v>
+        <v>-7.95618643388037</v>
       </c>
       <c r="F37" t="n">
-        <v>113.3823721996971</v>
+        <v>113.3953889447666</v>
       </c>
       <c r="G37" t="n">
-        <v>201.8143812837272</v>
+        <v>201.5490109467333</v>
       </c>
       <c r="H37" t="n">
-        <v>6.48266690432815</v>
+        <v>1.026026474599693</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1726274931465417</v>
+        <v>0.1695371900441651</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9999950875292951</v>
+        <v>0.9749627489683239</v>
       </c>
       <c r="K37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.958634265706793</v>
+        <v>-7.95618643388037</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.3823721996971</v>
+        <v>113.3953889447666</v>
       </c>
       <c r="R37" t="n">
-        <v>201.8143812837272</v>
+        <v>201.5490109467333</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.904509525705922</v>
+        <v>-7.947622810067872</v>
       </c>
       <c r="D38" t="n">
-        <v>113.4042472303964</v>
+        <v>113.398839437951</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.958634265706793</v>
+        <v>-7.956212328864967</v>
       </c>
       <c r="F38" t="n">
-        <v>113.3823721996971</v>
+        <v>113.3954144768482</v>
       </c>
       <c r="G38" t="n">
-        <v>201.8143812837272</v>
+        <v>201.5489850685552</v>
       </c>
       <c r="H38" t="n">
-        <v>6.48266690432815</v>
+        <v>1.026887947320743</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1726274931465417</v>
+        <v>0.1695371902660881</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9330145036862169</v>
+        <v>0.9937607307822127</v>
       </c>
       <c r="K38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.958634265706793</v>
+        <v>-7.956212328864967</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3823721996971</v>
+        <v>113.3954144768482</v>
       </c>
       <c r="R38" t="n">
-        <v>201.8143812837272</v>
+        <v>201.5489850685552</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,28 +2952,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.904509525705922</v>
+        <v>-7.947672283781669</v>
       </c>
       <c r="D39" t="n">
-        <v>113.4042472303964</v>
+        <v>113.3988000524943</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.958634265706793</v>
+        <v>-7.956206134960988</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3823721996971</v>
+        <v>113.3953972842816</v>
       </c>
       <c r="G39" t="n">
-        <v>201.8143812837272</v>
+        <v>201.5490077895559</v>
       </c>
       <c r="H39" t="n">
-        <v>6.48266690432815</v>
+        <v>1.020232961470545</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1726274931465417</v>
+        <v>0.1695371903634664</v>
       </c>
       <c r="J39" t="n">
-        <v>0.921111599946363</v>
+        <v>0.9962629629969056</v>
       </c>
       <c r="K39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.958634265706793</v>
+        <v>-7.956206134960988</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3823721996971</v>
+        <v>113.3953972842816</v>
       </c>
       <c r="R39" t="n">
-        <v>201.8143812837272</v>
+        <v>201.5490077895559</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,31 +3017,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-8.060626283481596</v>
+        <v>-7.94764408520616</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3411552204863</v>
+        <v>113.3988019907279</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.958640949327056</v>
+        <v>-7.956217330045526</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3823723770843</v>
+        <v>113.3953835166087</v>
       </c>
       <c r="G40" t="n">
-        <v>21.81442309315776</v>
+        <v>201.5489966254698</v>
       </c>
       <c r="H40" t="n">
-        <v>12.21468944171813</v>
+        <v>1.024942453355505</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1726274932659926</v>
+        <v>0.1695371904224287</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9683626670546697</v>
+        <v>0.9986116171256554</v>
       </c>
       <c r="K40" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.958640949327056</v>
+        <v>-7.956217330045526</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3823723770843</v>
+        <v>113.3953835166087</v>
       </c>
       <c r="R40" t="n">
-        <v>21.81442309315776</v>
+        <v>201.5489966254698</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,31 +3082,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-8.060561651614661</v>
+        <v>-7.94764408520616</v>
       </c>
       <c r="D41" t="n">
-        <v>113.3411661325726</v>
+        <v>113.3988019907279</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.958637124424174</v>
+        <v>-7.956217330045526</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3823586731278</v>
+        <v>113.3953835166087</v>
       </c>
       <c r="G41" t="n">
-        <v>21.81440333334779</v>
+        <v>201.5489966254698</v>
       </c>
       <c r="H41" t="n">
-        <v>12.20740511073507</v>
+        <v>1.024942453355505</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1726274935082803</v>
+        <v>0.1695371904224287</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9836688105172422</v>
+        <v>0.9988364875590211</v>
       </c>
       <c r="K41" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.958637124424174</v>
+        <v>-7.956217330045526</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3823586731278</v>
+        <v>113.3953835166087</v>
       </c>
       <c r="R41" t="n">
-        <v>21.81440333334779</v>
+        <v>201.5489966254698</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-8.060622357306507</v>
+        <v>-7.94764408520616</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3411594521408</v>
+        <v>113.3988019907279</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.958656279673325</v>
+        <v>-7.956217330045526</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3823687966077</v>
+        <v>113.3953835166087</v>
       </c>
       <c r="G42" t="n">
-        <v>21.81440805291589</v>
+        <v>201.5489966254698</v>
       </c>
       <c r="H42" t="n">
-        <v>12.21238186939866</v>
+        <v>1.024942453355505</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1726274935519024</v>
+        <v>0.1695371904224287</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5857712416433664</v>
+        <v>0.585786142094663</v>
       </c>
       <c r="K42" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.958656279673325</v>
+        <v>-7.956217330045526</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3823687966077</v>
+        <v>113.3953835166087</v>
       </c>
       <c r="R42" t="n">
-        <v>21.81440805291589</v>
+        <v>201.5489966254698</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-8.060617205259986</v>
+        <v>-7.947758267739696</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3411567748006</v>
+        <v>113.3987726326544</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.958654815447919</v>
+        <v>-7.956222325029492</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3823646229705</v>
+        <v>113.3953976960025</v>
       </c>
       <c r="G43" t="n">
-        <v>21.81440529097791</v>
+        <v>201.5489950630535</v>
       </c>
       <c r="H43" t="n">
-        <v>12.21193995594912</v>
+        <v>1.011888909411788</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1726274935986735</v>
+        <v>0.1695371904618223</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9979339967584213</v>
+        <v>0.9998700973182536</v>
       </c>
       <c r="K43" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.958654815447919</v>
+        <v>-7.956222325029492</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3823646229705</v>
+        <v>113.3953976960025</v>
       </c>
       <c r="R43" t="n">
-        <v>21.81440529097791</v>
+        <v>201.5489950630535</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,31 +3277,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-8.060619567973795</v>
+        <v>-7.947758267739696</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3411549062798</v>
+        <v>113.3987726326544</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.958653656212997</v>
+        <v>-7.956222325029492</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3823641730674</v>
+        <v>113.3953976960025</v>
       </c>
       <c r="G44" t="n">
-        <v>21.81440307366077</v>
+        <v>201.5489950630535</v>
       </c>
       <c r="H44" t="n">
-        <v>12.2123615788233</v>
+        <v>1.011888909411788</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1726274936141486</v>
+        <v>0.1695371904618223</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9994062444669992</v>
+        <v>0.9999222881097654</v>
       </c>
       <c r="K44" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.958653656212997</v>
+        <v>-7.956222325029492</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3823641730674</v>
+        <v>113.3953976960025</v>
       </c>
       <c r="R44" t="n">
-        <v>21.81440307366077</v>
+        <v>201.5489950630535</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,31 +3342,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-8.060619567973795</v>
+        <v>-7.947586321972436</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3411549062798</v>
+        <v>113.3988305021071</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.958653656212997</v>
+        <v>-7.956202251168192</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3823641730674</v>
+        <v>113.3953950082519</v>
       </c>
       <c r="G45" t="n">
-        <v>21.81440307366077</v>
+        <v>201.5489965203318</v>
       </c>
       <c r="H45" t="n">
-        <v>12.2123615788233</v>
+        <v>1.03004543069276</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1726274936141486</v>
+        <v>0.1695371904626989</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9999999972068199</v>
+        <v>0.9999644479702678</v>
       </c>
       <c r="K45" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.958653656212997</v>
+        <v>-7.956202251168192</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3823641730674</v>
+        <v>113.3953950082519</v>
       </c>
       <c r="R45" t="n">
-        <v>21.81440307366077</v>
+        <v>201.5489965203318</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,31 +3407,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-8.060619567973795</v>
+        <v>-7.947612472621267</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3411549062798</v>
+        <v>113.3988309732644</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.958653656212997</v>
+        <v>-7.956217968473983</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3823641730674</v>
+        <v>113.3953996392019</v>
       </c>
       <c r="G46" t="n">
-        <v>21.81440307366077</v>
+        <v>201.5489979313218</v>
       </c>
       <c r="H46" t="n">
-        <v>12.2123615788233</v>
+        <v>1.028798119066468</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1726274936141486</v>
+        <v>0.1695371905170268</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9999999978932603</v>
+        <v>0.9999735880409861</v>
       </c>
       <c r="K46" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.958653656212997</v>
+        <v>-7.956217968473983</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3823641730674</v>
+        <v>113.3953996392019</v>
       </c>
       <c r="R46" t="n">
-        <v>21.81440307366077</v>
+        <v>201.5489979313218</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-8.060586510380341</v>
+        <v>-7.947631769306187</v>
       </c>
       <c r="D47" t="n">
-        <v>113.3411706128098</v>
+        <v>113.398817261629</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.958652321753555</v>
+        <v>-7.956212072248814</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3823670599739</v>
+        <v>113.3953959729726</v>
       </c>
       <c r="G47" t="n">
-        <v>21.81440358330093</v>
+        <v>201.548998033508</v>
       </c>
       <c r="H47" t="n">
-        <v>12.20856224930362</v>
+        <v>1.025786270012412</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1726274936220604</v>
+        <v>0.1695371905191192</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999999978703087</v>
+        <v>0.9999781796389501</v>
       </c>
       <c r="K47" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.958652321753555</v>
+        <v>-7.956212072248814</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3823670599739</v>
+        <v>113.3953959729726</v>
       </c>
       <c r="R47" t="n">
-        <v>21.81440358330093</v>
+        <v>201.548998033508</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,31 +3537,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-8.060586510380341</v>
+        <v>-7.947608093094142</v>
       </c>
       <c r="D48" t="n">
-        <v>113.3411706128098</v>
+        <v>113.3988301730658</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.958652321753555</v>
+        <v>-7.956215518153587</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3823670599739</v>
+        <v>113.3953980697524</v>
       </c>
       <c r="G48" t="n">
-        <v>21.81440358330093</v>
+        <v>201.5489980626197</v>
       </c>
       <c r="H48" t="n">
-        <v>12.20856224930362</v>
+        <v>1.029028759524914</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1726274936220604</v>
+        <v>0.1695371905207228</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999999982128225</v>
+        <v>0.9999904159570252</v>
       </c>
       <c r="K48" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.958652321753555</v>
+        <v>-7.956215518153587</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3823670599739</v>
+        <v>113.3953980697524</v>
       </c>
       <c r="R48" t="n">
-        <v>21.81440358330093</v>
+        <v>201.5489980626197</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,31 +3602,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-8.060586415188473</v>
+        <v>-7.947640575338764</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3411705231763</v>
+        <v>113.3988175022159</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.958654729011141</v>
+        <v>-7.956212255985298</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3823659595946</v>
+        <v>113.3953996516448</v>
       </c>
       <c r="G49" t="n">
-        <v>21.81440375105121</v>
+        <v>201.548997756491</v>
       </c>
       <c r="H49" t="n">
-        <v>12.20826255357767</v>
+        <v>1.024755459772401</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1726274936221907</v>
+        <v>0.16953719052681</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999999982860746</v>
+        <v>0.9999920658576419</v>
       </c>
       <c r="K49" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.958654729011141</v>
+        <v>-7.956212255985298</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3823659595946</v>
+        <v>113.3953996516448</v>
       </c>
       <c r="R49" t="n">
-        <v>21.81440375105121</v>
+        <v>201.548997756491</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,31 +3667,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-8.060587228495759</v>
+        <v>-7.947640575338764</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3411696357523</v>
+        <v>113.3988175022159</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.956212255985298</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3953996516448</v>
       </c>
       <c r="G50" t="n">
-        <v>21.8144036935562</v>
+        <v>201.548997756491</v>
       </c>
       <c r="H50" t="n">
-        <v>12.20854977866646</v>
+        <v>1.024755459772401</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1726274936241491</v>
+        <v>0.16953719052681</v>
       </c>
       <c r="J50" t="n">
-        <v>0.999999998604391</v>
+        <v>0.9999972900049665</v>
       </c>
       <c r="K50" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.956212255985298</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3953996516448</v>
       </c>
       <c r="R50" t="n">
-        <v>21.8144036935562</v>
+        <v>201.548997756491</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-8.060587228495759</v>
+        <v>-7.947639922362594</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3411696357523</v>
+        <v>113.3988183665543</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.956212574881254</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3954001284877</v>
       </c>
       <c r="G51" t="n">
-        <v>21.8144036935562</v>
+        <v>201.5489975866523</v>
       </c>
       <c r="H51" t="n">
-        <v>12.20854977866646</v>
+        <v>1.024871647326176</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1726274936241491</v>
+        <v>0.169537190527194</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9999999987370671</v>
+        <v>0.9999988797826375</v>
       </c>
       <c r="K51" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.956212574881254</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3954001284877</v>
       </c>
       <c r="R51" t="n">
-        <v>21.8144036935562</v>
+        <v>201.5489975866523</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,31 +3797,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-8.060587228495759</v>
+        <v>-7.947640315917958</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3411696357523</v>
+        <v>113.3988170678925</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.956212141304377</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3953991596373</v>
       </c>
       <c r="G52" t="n">
-        <v>21.8144036935562</v>
+        <v>201.5489975944602</v>
       </c>
       <c r="H52" t="n">
-        <v>12.20854977866646</v>
+        <v>1.024772762495816</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1726274936241491</v>
+        <v>0.1695371905273096</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5857864397352656</v>
+        <v>0.585786439773511</v>
       </c>
       <c r="K52" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.956212141304377</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3953991596373</v>
       </c>
       <c r="R52" t="n">
-        <v>21.8144036935562</v>
+        <v>201.5489975944602</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,31 +3862,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-8.060587228495759</v>
+        <v>-7.947639916489395</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3411696357523</v>
+        <v>113.3988178332493</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.95621329469895</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3953993058108</v>
       </c>
       <c r="G53" t="n">
-        <v>21.8144036935562</v>
+        <v>201.5489976167153</v>
       </c>
       <c r="H53" t="n">
-        <v>12.20854977866646</v>
+        <v>1.024958404960697</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1726274936241491</v>
+        <v>0.1695371905281201</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999999993295676</v>
+        <v>0.9999999940560342</v>
       </c>
       <c r="K53" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.958653144071719</v>
+        <v>-7.95621329469895</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3823660411164</v>
+        <v>113.3953993058108</v>
       </c>
       <c r="R53" t="n">
-        <v>21.8144036935562</v>
+        <v>201.5489976167153</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,31 +3927,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-8.060585740626935</v>
+        <v>-7.947639157167387</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3411698353432</v>
+        <v>113.3988180797968</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.958652668189295</v>
+        <v>-7.956213448471776</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3823658316647</v>
+        <v>113.395399188265</v>
       </c>
       <c r="G54" t="n">
-        <v>21.8144036879257</v>
+        <v>201.5489976531294</v>
       </c>
       <c r="H54" t="n">
-        <v>12.20842857599401</v>
+        <v>1.025067567059345</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1726274936242325</v>
+        <v>0.1695371905286417</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999996574165</v>
+        <v>0.9999999954224266</v>
       </c>
       <c r="K54" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.958652668189295</v>
+        <v>-7.956213448471776</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3823658316647</v>
+        <v>113.395399188265</v>
       </c>
       <c r="R54" t="n">
-        <v>21.8144036879257</v>
+        <v>201.5489976531294</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,31 +3992,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-8.060587100631528</v>
+        <v>-7.947639157167387</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3411693644776</v>
+        <v>113.3988180797968</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.958652646535901</v>
+        <v>-7.956213448471776</v>
       </c>
       <c r="F55" t="n">
-        <v>113.3823659191701</v>
+        <v>113.395399188265</v>
       </c>
       <c r="G55" t="n">
-        <v>21.81440368381895</v>
+        <v>201.5489976531294</v>
       </c>
       <c r="H55" t="n">
-        <v>12.20859405217419</v>
+        <v>1.025067567059345</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1726274936242743</v>
+        <v>0.1695371905286417</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999996700724</v>
+        <v>0.9999999957247183</v>
       </c>
       <c r="K55" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.958652646535901</v>
+        <v>-7.956213448471776</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.3823659191701</v>
+        <v>113.395399188265</v>
       </c>
       <c r="R55" t="n">
-        <v>21.81440368381895</v>
+        <v>201.5489976531294</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-8.060587100631528</v>
+        <v>-7.947638635872526</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3411693644776</v>
+        <v>113.3988180183512</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.958652646535901</v>
+        <v>-7.956213353433331</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3823659191701</v>
+        <v>113.3953989568544</v>
       </c>
       <c r="G56" t="n">
-        <v>21.81440368381895</v>
+        <v>201.5489976595895</v>
       </c>
       <c r="H56" t="n">
-        <v>12.20859405217419</v>
+        <v>1.025118526691151</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1726274936242743</v>
+        <v>0.1695371905286555</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999999997513245</v>
+        <v>0.9999999959659696</v>
       </c>
       <c r="K56" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.958652646535901</v>
+        <v>-7.956213353433331</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3823659191701</v>
+        <v>113.3953989568544</v>
       </c>
       <c r="R56" t="n">
-        <v>21.81440368381895</v>
+        <v>201.5489976595895</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,31 +4122,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-8.060587110437133</v>
+        <v>-7.947639436785174</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3411695320496</v>
+        <v>113.3988180643929</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.958652994481755</v>
+        <v>-7.95621345451482</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3823659501199</v>
+        <v>113.3953992819444</v>
       </c>
       <c r="G57" t="n">
-        <v>21.81440368310755</v>
+        <v>201.548997660371</v>
       </c>
       <c r="H57" t="n">
-        <v>12.20855355418263</v>
+        <v>1.025034860844234</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1726274936243011</v>
+        <v>0.1695371905286565</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9999999998455273</v>
+        <v>0.9999999959995827</v>
       </c>
       <c r="K57" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.958652994481755</v>
+        <v>-7.95621345451482</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3823659501199</v>
+        <v>113.3953992819444</v>
       </c>
       <c r="R57" t="n">
-        <v>21.81440368310755</v>
+        <v>201.548997660371</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,31 +4187,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-8.060587110437133</v>
+        <v>-7.947639079772967</v>
       </c>
       <c r="D58" t="n">
-        <v>113.3411695320496</v>
+        <v>113.39881800032</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.958652994481755</v>
+        <v>-7.956213097185757</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3823659501199</v>
+        <v>113.395399218001</v>
       </c>
       <c r="G58" t="n">
-        <v>21.81440368310755</v>
+        <v>201.5489976592591</v>
       </c>
       <c r="H58" t="n">
-        <v>12.20855355418263</v>
+        <v>1.025034822955752</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1726274936243011</v>
+        <v>0.1695371905286634</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9999999998807791</v>
+        <v>0.9999999962252746</v>
       </c>
       <c r="K58" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.958652994481755</v>
+        <v>-7.956213097185757</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3823659501199</v>
+        <v>113.395399218001</v>
       </c>
       <c r="R58" t="n">
-        <v>21.81440368310755</v>
+        <v>201.5489976592591</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,31 +4252,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-8.060587084105935</v>
+        <v>-7.947639231661552</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3411694990144</v>
+        <v>113.3988181366646</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.958652971332723</v>
+        <v>-7.956213535840529</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3823659157964</v>
+        <v>113.3953992399976</v>
       </c>
       <c r="G59" t="n">
-        <v>21.8144036831476</v>
+        <v>201.5489976577762</v>
       </c>
       <c r="H59" t="n">
-        <v>12.20855317306935</v>
+        <v>1.025069106268064</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1726274936243059</v>
+        <v>0.1695371905286855</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999999511355</v>
+        <v>0.9999999964715849</v>
       </c>
       <c r="K59" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.958652971332723</v>
+        <v>-7.956213535840529</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3823659157964</v>
+        <v>113.3953992399976</v>
       </c>
       <c r="R59" t="n">
-        <v>21.8144036831476</v>
+        <v>201.5489976577762</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,31 +4317,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-8.060587193082524</v>
+        <v>-7.947638465844761</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3411692613749</v>
+        <v>113.3988181872019</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.958652998738623</v>
+        <v>-7.956213305190888</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3823657111294</v>
+        <v>113.3953990771453</v>
       </c>
       <c r="G60" t="n">
-        <v>21.81440368499198</v>
+        <v>201.548997657757</v>
       </c>
       <c r="H60" t="n">
-        <v>12.20856294267276</v>
+        <v>1.02513308629406</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1726274936243127</v>
+        <v>0.1695371905286975</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999999590707</v>
+        <v>0.9999999967293702</v>
       </c>
       <c r="K60" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.958652998738623</v>
+        <v>-7.956213305190888</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3823657111294</v>
+        <v>113.3953990771453</v>
       </c>
       <c r="R60" t="n">
-        <v>21.81440368499198</v>
+        <v>201.548997657757</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,31 +4382,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-8.060587230769816</v>
+        <v>-7.947639446266073</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3411693164356</v>
+        <v>113.3988177940193</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.958653004173714</v>
+        <v>-7.956213290827828</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3823657792238</v>
+        <v>113.3953990806213</v>
       </c>
       <c r="G61" t="n">
-        <v>21.8144036843594</v>
+        <v>201.5489976575224</v>
       </c>
       <c r="H61" t="n">
-        <v>12.20856680535645</v>
+        <v>1.025014158346151</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1726274936243231</v>
+        <v>0.1695371905287009</v>
       </c>
       <c r="J61" t="n">
-        <v>0.999999999963102</v>
+        <v>0.9999999968963857</v>
       </c>
       <c r="K61" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.958653004173714</v>
+        <v>-7.956213290827828</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3823657792238</v>
+        <v>113.3953990806213</v>
       </c>
       <c r="R61" t="n">
-        <v>21.8144036843594</v>
+        <v>201.5489976575224</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-8.060587119377441</v>
+        <v>-7.947639446266073</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3411694148225</v>
+        <v>113.3988177940193</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.958652955515679</v>
+        <v>-7.956213290827828</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3823658522515</v>
+        <v>113.3953990806213</v>
       </c>
       <c r="G62" t="n">
-        <v>21.81440368395639</v>
+        <v>201.5489976575224</v>
       </c>
       <c r="H62" t="n">
-        <v>12.20855929184265</v>
+        <v>1.025014158346151</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1726274936243231</v>
+        <v>0.1695371905287009</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857864397352656</v>
+        <v>0.5857864397736966</v>
       </c>
       <c r="K62" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.958652955515679</v>
+        <v>-7.956213290827828</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3823658522515</v>
+        <v>113.3953990806213</v>
       </c>
       <c r="R62" t="n">
-        <v>21.81440368395639</v>
+        <v>201.5489976575224</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,31 +4512,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-8.06058723145237</v>
+        <v>-7.947638911195767</v>
       </c>
       <c r="D63" t="n">
-        <v>113.3411693167726</v>
+        <v>113.398818155368</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.958653034848904</v>
+        <v>-7.956213300897007</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3823657674417</v>
+        <v>113.3953992246021</v>
       </c>
       <c r="G63" t="n">
-        <v>21.81440368394272</v>
+        <v>201.5489976576058</v>
       </c>
       <c r="H63" t="n">
-        <v>12.20856321320266</v>
+        <v>1.025079330580104</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1726274936243249</v>
+        <v>0.1695371905287046</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999999999105</v>
+        <v>0.999999999999809</v>
       </c>
       <c r="K63" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.958653034848904</v>
+        <v>-7.956213300897007</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3823657674417</v>
+        <v>113.3953992246021</v>
       </c>
       <c r="R63" t="n">
-        <v>21.81440368394272</v>
+        <v>201.5489976576058</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,31 +4577,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-8.06058708131965</v>
+        <v>-7.947638896083411</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3411693387599</v>
+        <v>113.3988181743072</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.958652951040516</v>
+        <v>-7.956213302092017</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3823657626167</v>
+        <v>113.3953992370389</v>
       </c>
       <c r="G64" t="n">
-        <v>21.81440368409608</v>
+        <v>201.5489976572711</v>
       </c>
       <c r="H64" t="n">
-        <v>12.20855526977622</v>
+        <v>1.0250812801476</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1726274936243269</v>
+        <v>0.1695371905287065</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9276199366493693</v>
+        <v>0.9326234962840773</v>
       </c>
       <c r="K64" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.958652951040516</v>
+        <v>-7.956213302092017</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3823657626167</v>
+        <v>113.3953992370389</v>
       </c>
       <c r="R64" t="n">
-        <v>21.81440368409608</v>
+        <v>201.5489976572711</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,31 +4642,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-8.060587155971596</v>
+        <v>-7.94763920346506</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3411692903796</v>
+        <v>113.3988179669472</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.958652955827715</v>
+        <v>-7.95621328775155</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3823657424719</v>
+        <v>113.3953991579618</v>
       </c>
       <c r="G65" t="n">
-        <v>21.81440368405764</v>
+        <v>201.5489976573314</v>
       </c>
       <c r="H65" t="n">
-        <v>12.20856363723854</v>
+        <v>1.025042817792229</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1726274936243272</v>
+        <v>0.169537190528707</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9878442305847307</v>
+        <v>0.9722174973021552</v>
       </c>
       <c r="K65" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.958652955827715</v>
+        <v>-7.95621328775155</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3823657424719</v>
+        <v>113.3953991579618</v>
       </c>
       <c r="R65" t="n">
-        <v>21.81440368405764</v>
+        <v>201.5489976573314</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,31 +4707,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-8.060587235550557</v>
+        <v>-7.947639415861759</v>
       </c>
       <c r="D66" t="n">
-        <v>113.3411693032338</v>
+        <v>113.398817962311</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.958652977509895</v>
+        <v>-7.956213335409503</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3823657787266</v>
+        <v>113.3953992190129</v>
       </c>
       <c r="G66" t="n">
-        <v>21.81440368406009</v>
+        <v>201.548997657332</v>
       </c>
       <c r="H66" t="n">
-        <v>12.2085705713407</v>
+        <v>1.025023123031057</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1726274936243276</v>
+        <v>0.1695371905287077</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9935908428645369</v>
+        <v>0.9182855006015086</v>
       </c>
       <c r="K66" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.958652977509895</v>
+        <v>-7.956213335409503</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3823657787266</v>
+        <v>113.3953992190129</v>
       </c>
       <c r="R66" t="n">
-        <v>21.81440368406009</v>
+        <v>201.548997657332</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,31 +4772,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-8.060587235550557</v>
+        <v>-7.947639415861759</v>
       </c>
       <c r="D67" t="n">
-        <v>113.3411693032338</v>
+        <v>113.398817962311</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.958652977509895</v>
+        <v>-7.956213335409503</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3823657787266</v>
+        <v>113.3953992190129</v>
       </c>
       <c r="G67" t="n">
-        <v>21.81440368406009</v>
+        <v>201.548997657332</v>
       </c>
       <c r="H67" t="n">
-        <v>12.2085705713407</v>
+        <v>1.025023123031057</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1726274936243276</v>
+        <v>0.1695371905287077</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9948926343477994</v>
+        <v>0.991744588488605</v>
       </c>
       <c r="K67" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.958652977509895</v>
+        <v>-7.956213335409503</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3823657787266</v>
+        <v>113.3953992190129</v>
       </c>
       <c r="R67" t="n">
-        <v>21.81440368406009</v>
+        <v>201.548997657332</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,31 +4837,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.060587160231828</v>
+        <v>-7.947639217734699</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3411693256967</v>
+        <v>113.3988180019861</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.958652982609677</v>
+        <v>-7.95621331041075</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3823657686898</v>
+        <v>113.3953991896554</v>
       </c>
       <c r="G68" t="n">
-        <v>21.81440368406207</v>
+        <v>201.5489976573548</v>
       </c>
       <c r="H68" t="n">
-        <v>12.20856093988606</v>
+        <v>1.025043820776753</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287082</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9965034137193443</v>
+        <v>0.9944068880720018</v>
       </c>
       <c r="K68" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.958652982609677</v>
+        <v>-7.95621331041075</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3823657686898</v>
+        <v>113.3953991896554</v>
       </c>
       <c r="R68" t="n">
-        <v>21.81440368406207</v>
+        <v>201.5489976573548</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,31 +4902,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639217734699</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988180019861</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.95621331041075</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953991896554</v>
       </c>
       <c r="G69" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573548</v>
       </c>
       <c r="H69" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025043820776753</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287082</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9264510354374216</v>
+        <v>0.9973098814641107</v>
       </c>
       <c r="K69" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.95621331041075</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953991896554</v>
       </c>
       <c r="R69" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573548</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,31 +4967,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639413852502</v>
       </c>
       <c r="D70" t="n">
-        <v>113.3411693293282</v>
+        <v>113.398817944351</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213334210594</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992007298</v>
       </c>
       <c r="G70" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573657</v>
       </c>
       <c r="H70" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025023219909336</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287083</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9785874279911531</v>
+        <v>0.99872257162652</v>
       </c>
       <c r="K70" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213334210594</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992007298</v>
       </c>
       <c r="R70" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573657</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639413852502</v>
       </c>
       <c r="D71" t="n">
-        <v>113.3411693293282</v>
+        <v>113.398817944351</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213334210594</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992007298</v>
       </c>
       <c r="G71" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573657</v>
       </c>
       <c r="H71" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025023219909336</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287083</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9910993383802941</v>
+        <v>0.9993528637664086</v>
       </c>
       <c r="K71" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213334210594</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992007298</v>
       </c>
       <c r="R71" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573657</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,31 +5097,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639413852502</v>
       </c>
       <c r="D72" t="n">
-        <v>113.3411693293282</v>
+        <v>113.398817944351</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213334210594</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992007298</v>
       </c>
       <c r="G72" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573657</v>
       </c>
       <c r="H72" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025023219909336</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287083</v>
       </c>
       <c r="J72" t="n">
-        <v>0.535878960202093</v>
+        <v>0.5857863836227353</v>
       </c>
       <c r="K72" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213334210594</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992007298</v>
       </c>
       <c r="R72" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573657</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,31 +5162,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639407982049</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179530972</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213318511028</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992133953</v>
       </c>
       <c r="G73" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573658</v>
       </c>
       <c r="H73" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022044824369</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9937936419052401</v>
+        <v>0.9998866396898476</v>
       </c>
       <c r="K73" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213318511028</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992133953</v>
       </c>
       <c r="R73" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573658</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,31 +5227,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G74" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H74" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9938258218686054</v>
+        <v>0.9999449135370782</v>
       </c>
       <c r="K74" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R74" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,31 +5292,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G75" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H75" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9965604051090238</v>
+        <v>0.9999801380222642</v>
       </c>
       <c r="K75" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R75" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,31 +5357,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G76" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H76" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9974704303505828</v>
+        <v>0.999988821370928</v>
       </c>
       <c r="K76" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R76" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,31 +5422,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G77" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H77" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9977129937949676</v>
+        <v>0.9999994362404604</v>
       </c>
       <c r="K77" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R77" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,31 +5487,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G78" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H78" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9980001379602316</v>
+        <v>0.9999997689161783</v>
       </c>
       <c r="K78" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R78" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G79" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H79" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9989476387202305</v>
+        <v>0.999999872235514</v>
       </c>
       <c r="K79" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R79" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,31 +5617,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G80" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H80" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9996627057619057</v>
+        <v>0.9999999767404885</v>
       </c>
       <c r="K80" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R80" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,31 +5682,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G81" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H81" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J81" t="n">
-        <v>0.999783639677524</v>
+        <v>0.9493732421534433</v>
       </c>
       <c r="K81" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R81" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,31 +5747,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G82" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H82" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857864397352656</v>
+        <v>0.5854275450226638</v>
       </c>
       <c r="K82" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R82" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,31 +5812,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G83" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H83" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999999999738</v>
+        <v>0.9999999999999452</v>
       </c>
       <c r="K83" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R83" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,31 +5877,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G84" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H84" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999999738</v>
+        <v>0.9999999999999498</v>
       </c>
       <c r="K84" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R84" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,31 +5942,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G85" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H85" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999999736</v>
+        <v>0.9999999999999498</v>
       </c>
       <c r="K85" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R85" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G86" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H86" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999999999999736</v>
+        <v>0.999999999999956</v>
       </c>
       <c r="K86" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R86" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,31 +6072,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G87" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H87" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999999999999736</v>
+        <v>0.9999999999999696</v>
       </c>
       <c r="K87" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R87" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,31 +6137,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G88" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H88" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999999999999736</v>
+        <v>0.9999999999999765</v>
       </c>
       <c r="K88" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R88" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,31 +6202,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G89" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H89" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9999999999999736</v>
+        <v>0.9999999999999765</v>
       </c>
       <c r="K89" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R89" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,31 +6267,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G90" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H90" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9999999999999734</v>
+        <v>0.999999999999978</v>
       </c>
       <c r="K90" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R90" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,31 +6332,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G91" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H91" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9999999999999734</v>
+        <v>0.9999999999999885</v>
       </c>
       <c r="K91" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R91" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,31 +6397,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G92" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H92" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5857864397352656</v>
+        <v>0.5857864397736966</v>
       </c>
       <c r="K92" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R92" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,31 +6462,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G93" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H93" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9999999999999987</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R93" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,31 +6527,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G94" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H94" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9141547975213861</v>
+        <v>0.9086001209088197</v>
       </c>
       <c r="K94" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R94" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,31 +6592,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G95" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H95" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9815054459273047</v>
+        <v>0.9820064438602405</v>
       </c>
       <c r="K95" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R95" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,31 +6657,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G96" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H96" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9907038433819619</v>
+        <v>0.8754730738273039</v>
       </c>
       <c r="K96" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R96" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,31 +6722,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G97" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H97" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9967217073627571</v>
+        <v>0.971293993302515</v>
       </c>
       <c r="K97" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R97" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,31 +6787,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G98" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H98" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9979842987798817</v>
+        <v>0.983947528783786</v>
       </c>
       <c r="K98" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R98" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,31 +6852,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G99" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H99" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9035263664577083</v>
+        <v>0.9862543251369094</v>
       </c>
       <c r="K99" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R99" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,31 +6917,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G100" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H100" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9833374049075508</v>
+        <v>0.9939487972356729</v>
       </c>
       <c r="K100" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R100" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,31 +6982,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G101" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H101" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J101" t="n">
-        <v>0.991667856995898</v>
+        <v>0.9966823795891645</v>
       </c>
       <c r="K101" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R101" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,31 +7047,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G102" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H102" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5358883682353043</v>
+        <v>0.5857823546937331</v>
       </c>
       <c r="K102" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R102" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,31 +7112,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G103" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H103" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9963042156199449</v>
+        <v>0.9999634286141803</v>
       </c>
       <c r="K103" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R103" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,31 +7177,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G104" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H104" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9972115956976858</v>
+        <v>0.9999880548484925</v>
       </c>
       <c r="K104" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R104" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,31 +7242,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G105" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H105" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9986172496189454</v>
+        <v>0.9999951691061558</v>
       </c>
       <c r="K105" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R105" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,31 +7307,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G106" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H106" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9986259937925681</v>
+        <v>0.9999958064887428</v>
       </c>
       <c r="K106" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R106" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,31 +7372,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G107" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H107" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9992534587937837</v>
+        <v>0.9999987359059438</v>
       </c>
       <c r="K107" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R107" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,31 +7437,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G108" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H108" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9993865396928029</v>
+        <v>0.9999993430781365</v>
       </c>
       <c r="K108" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R108" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G109" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H109" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9994481697003974</v>
+        <v>0.9999995833284396</v>
       </c>
       <c r="K109" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R109" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,31 +7567,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G110" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H110" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9997988650587409</v>
+        <v>0.999999760980041</v>
       </c>
       <c r="K110" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R110" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,31 +7632,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G111" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H111" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9999753441792408</v>
+        <v>0.9177808655512067</v>
       </c>
       <c r="K111" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R111" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,31 +7697,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G112" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H112" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5857864397352638</v>
+        <v>0.5857168279982921</v>
       </c>
       <c r="K112" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R112" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,31 +7762,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G113" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H113" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999863388491</v>
       </c>
       <c r="K113" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R113" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,31 +7827,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G114" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H114" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999933967803</v>
       </c>
       <c r="K114" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R114" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,31 +7892,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G115" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H115" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999989557551</v>
       </c>
       <c r="K115" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R115" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,31 +7957,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D116" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G116" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H116" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999991</v>
       </c>
       <c r="K116" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R116" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G117" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H117" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R117" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,31 +8087,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G118" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H118" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R118" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,31 +8152,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G119" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H119" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R119" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,31 +8217,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G120" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H120" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R120" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,31 +8282,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639411281891</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179391084</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="G121" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="H121" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025021230944155</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287084</v>
       </c>
       <c r="J121" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213315003089</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992021211</v>
       </c>
       <c r="R121" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573655</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,31 +8347,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G122" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H122" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857864397352656</v>
+        <v>0.5857864397736966</v>
       </c>
       <c r="K122" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R122" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,31 +8412,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G123" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H123" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J123" t="n">
         <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R123" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,31 +8477,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G124" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H124" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9261776022764491</v>
+        <v>0.8550773799756022</v>
       </c>
       <c r="K124" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R124" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,31 +8542,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G125" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H125" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J125" t="n">
-        <v>0.981869612415996</v>
+        <v>0.9662654968845387</v>
       </c>
       <c r="K125" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R125" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,31 +8607,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G126" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H126" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9933728063118151</v>
+        <v>0.9915725541349829</v>
       </c>
       <c r="K126" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R126" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,31 +8672,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G127" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H127" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9940949597417921</v>
+        <v>0.9117151042237767</v>
       </c>
       <c r="K127" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R127" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,31 +8737,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G128" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H128" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9953414224164435</v>
+        <v>0.9826505684313107</v>
       </c>
       <c r="K128" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R128" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,31 +8802,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G129" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H129" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J129" t="n">
-        <v>0.8957536511648081</v>
+        <v>0.9965598155465272</v>
       </c>
       <c r="K129" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R129" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G130" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H130" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9748601096777615</v>
+        <v>0.9982248651925838</v>
       </c>
       <c r="K130" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R130" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,31 +8932,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G131" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H131" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9951341657187575</v>
+        <v>0.9989820295679913</v>
       </c>
       <c r="K131" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R131" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G132" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H132" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5358948459504742</v>
+        <v>0.5857862934277519</v>
       </c>
       <c r="K132" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R132" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,31 +9062,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D133" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G133" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H133" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9975065537351386</v>
+        <v>0.9997055375226472</v>
       </c>
       <c r="K133" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R133" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,31 +9127,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D134" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G134" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H134" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9974821947336754</v>
+        <v>0.9997319207326829</v>
       </c>
       <c r="K134" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R134" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,31 +9192,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D135" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G135" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H135" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9978773826364659</v>
+        <v>0.9998241296833204</v>
       </c>
       <c r="K135" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R135" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,31 +9257,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D136" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G136" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H136" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9984349473875361</v>
+        <v>0.9998848873072776</v>
       </c>
       <c r="K136" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R136" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,31 +9322,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D137" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G137" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H137" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9984667121472744</v>
+        <v>0.9999228288246657</v>
       </c>
       <c r="K137" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R137" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D138" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G138" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H138" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9986021745672522</v>
+        <v>0.999960021041725</v>
       </c>
       <c r="K138" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R138" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,31 +9452,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D139" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G139" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H139" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9986929663404566</v>
+        <v>0.9999716998665977</v>
       </c>
       <c r="K139" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R139" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,31 +9517,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D140" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G140" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H140" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9988881322025019</v>
+        <v>0.9999975554870202</v>
       </c>
       <c r="K140" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R140" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,31 +9582,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D141" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G141" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H141" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9996280488982814</v>
+        <v>0.9237927592731633</v>
       </c>
       <c r="K141" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R141" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,31 +9647,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D142" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G142" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H142" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857864378914066</v>
+        <v>0.5857208380447377</v>
       </c>
       <c r="K142" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R142" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D143" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G143" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H143" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K143" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R143" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,31 +9777,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D144" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G144" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H144" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K144" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R144" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,31 +9842,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D145" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G145" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H145" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R145" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,31 +9907,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D146" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G146" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H146" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J146" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K146" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R146" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,31 +9972,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D147" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G147" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H147" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J147" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R147" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,31 +10037,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D148" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G148" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H148" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J148" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K148" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R148" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,31 +10102,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G149" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H149" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J149" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R149" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,31 +10167,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G150" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H150" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R150" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,31 +10232,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-8.060587153218956</v>
+        <v>-7.947639408073386</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3411693293282</v>
+        <v>113.3988179409098</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="G151" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="H151" t="n">
-        <v>12.20856082819068</v>
+        <v>1.025022308690701</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1726274936243277</v>
+        <v>0.1695371905287085</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="L151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.958652976529417</v>
+        <v>-7.956213320809501</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3823657719438</v>
+        <v>113.3953992003278</v>
       </c>
       <c r="R151" t="n">
-        <v>21.81440368406435</v>
+        <v>201.5489976573651</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -565,10 +565,10 @@
         <v>23.8222295006408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1671673548520525</v>
+        <v>0.1652105795513159</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8922371708293431</v>
+        <v>0.8932631420715178</v>
       </c>
       <c r="K2" t="n">
         <v>1965</v>
@@ -630,10 +630,10 @@
         <v>23.8222295006408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1671673548520525</v>
+        <v>0.1652105795513159</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9603030880641853</v>
+        <v>0.9607661449415719</v>
       </c>
       <c r="K3" t="n">
         <v>1965</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.963264109685748</v>
+        <v>-7.681342702896329</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4064375270518</v>
+        <v>114.0012689895788</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.966625587708326</v>
+        <v>-7.98794731152359</v>
       </c>
       <c r="F4" t="n">
-        <v>113.4148601466131</v>
+        <v>113.3798956517236</v>
       </c>
       <c r="G4" t="n">
-        <v>111.9494698432437</v>
+        <v>243.480928745101</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>76.46910851235259</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1682221770288521</v>
+        <v>0.1671024779674173</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9774849780836027</v>
+        <v>0.978633083904394</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>1342</v>
       </c>
       <c r="L4" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O4" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.966625587708326</v>
+        <v>-7.98794731152359</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.4148601466131</v>
+        <v>113.3798956517236</v>
       </c>
       <c r="R4" t="n">
-        <v>111.9494698432437</v>
+        <v>243.480928745101</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -739,55 +739,55 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.958700702975671</v>
+        <v>-7.681342702896329</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3984403084908</v>
+        <v>114.0012689895788</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.968030485669297</v>
+        <v>-7.98794731152359</v>
       </c>
       <c r="F5" t="n">
-        <v>113.4159133833603</v>
+        <v>113.3798956517236</v>
       </c>
       <c r="G5" t="n">
-        <v>118.3325847337771</v>
+        <v>243.480928745101</v>
       </c>
       <c r="H5" t="n">
-        <v>2.186029232032917</v>
+        <v>76.46910851235259</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1682871435082686</v>
+        <v>0.1671024779674173</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9939403160332684</v>
+        <v>0.989046581212189</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>1342</v>
       </c>
       <c r="L5" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O5" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.968030485669297</v>
+        <v>-7.98794731152359</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.4159133833603</v>
+        <v>113.3798956517236</v>
       </c>
       <c r="R5" t="n">
-        <v>118.3325847337771</v>
+        <v>243.480928745101</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -807,31 +807,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.949860007626683</v>
+        <v>-7.964519385897233</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3538712550597</v>
+        <v>113.4106735218183</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.946513023815009</v>
+        <v>-7.971452281958121</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3622994131996</v>
+        <v>113.4048894268719</v>
       </c>
       <c r="G6" t="n">
-        <v>68.15122051178177</v>
+        <v>219.56456410293</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1685502676131463</v>
+        <v>0.1672186874259055</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9958600420628068</v>
+        <v>0.9957192043005308</v>
       </c>
       <c r="K6" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
         <v>448</v>
@@ -846,13 +846,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.946513023815009</v>
+        <v>-7.971452281958121</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3622994131996</v>
+        <v>113.4048894268719</v>
       </c>
       <c r="R6" t="n">
-        <v>68.15122051178177</v>
+        <v>219.56456410293</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -872,31 +872,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.778411924554954</v>
+        <v>-7.964519385897233</v>
       </c>
       <c r="D7" t="n">
-        <v>113.3255315235373</v>
+        <v>113.4106735218183</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.960514775216507</v>
+        <v>-7.971452281958121</v>
       </c>
       <c r="F7" t="n">
-        <v>113.4121969375984</v>
+        <v>113.4048894268719</v>
       </c>
       <c r="G7" t="n">
-        <v>154.7651939515681</v>
+        <v>219.56456410293</v>
       </c>
       <c r="H7" t="n">
-        <v>22.38625773496128</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1688952712594764</v>
+        <v>0.1672186874259055</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9975888412332371</v>
+        <v>0.9977514103732356</v>
       </c>
       <c r="K7" t="n">
-        <v>1909</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
         <v>448</v>
@@ -911,13 +911,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.960514775216507</v>
+        <v>-7.971452281958121</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.4121969375984</v>
+        <v>113.4048894268719</v>
       </c>
       <c r="R7" t="n">
-        <v>154.7651939515681</v>
+        <v>219.56456410293</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.778411924554954</v>
+        <v>-7.880359410435489</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3255315235373</v>
+        <v>113.4591383253542</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.960514775216507</v>
+        <v>-7.965741615394557</v>
       </c>
       <c r="F8" t="n">
-        <v>113.4121969375984</v>
+        <v>113.4110304351739</v>
       </c>
       <c r="G8" t="n">
-        <v>154.7651939515681</v>
+        <v>209.1609613537134</v>
       </c>
       <c r="H8" t="n">
-        <v>22.38625773496128</v>
+        <v>10.87240483407599</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1688952712594764</v>
+        <v>0.1673425146695476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9984667530564295</v>
+        <v>0.9982314323208495</v>
       </c>
       <c r="K8" t="n">
-        <v>1909</v>
+        <v>1426</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.960514775216507</v>
+        <v>-7.965741615394557</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.4121969375984</v>
+        <v>113.4110304351739</v>
       </c>
       <c r="R8" t="n">
-        <v>154.7651939515681</v>
+        <v>209.1609613537134</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.919697559386807</v>
+        <v>-7.737094606115738</v>
       </c>
       <c r="D9" t="n">
-        <v>113.3863659928242</v>
+        <v>113.5948209979297</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.92819530240732</v>
+        <v>-7.975041791809903</v>
       </c>
       <c r="F9" t="n">
-        <v>113.389338229728</v>
+        <v>113.3768457620663</v>
       </c>
       <c r="G9" t="n">
-        <v>160.8926769137976</v>
+        <v>222.2078929740074</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>35.72876846015237</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1691810546819559</v>
+        <v>0.1675073423571009</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9985874748239016</v>
+        <v>0.9985717945557602</v>
       </c>
       <c r="K9" t="n">
-        <v>448</v>
+        <v>37</v>
       </c>
       <c r="L9" t="n">
         <v>448</v>
@@ -1041,13 +1041,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.92819530240732</v>
+        <v>-7.975041791809903</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.389338229728</v>
+        <v>113.3768457620663</v>
       </c>
       <c r="R9" t="n">
-        <v>160.8926769137976</v>
+        <v>222.2078929740074</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,28 +1067,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.927574870414333</v>
+        <v>-7.935767318647319</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3860729544726</v>
+        <v>113.3885245192334</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.936395861962063</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3878414575412</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="G10" t="n">
-        <v>168.7690005667855</v>
+        <v>191.728539425681</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>1.005033039094724</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1693107374601433</v>
+        <v>0.1676643490030086</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9982587934176675</v>
+        <v>0.998313470363861</v>
       </c>
       <c r="K10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.936395861962063</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3878414575412</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="R10" t="n">
-        <v>168.7690005667855</v>
+        <v>191.728539425681</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,28 +1132,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.927574870414333</v>
+        <v>-7.935767318647319</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3860729544726</v>
+        <v>113.3885245192334</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.936395861962063</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3878414575412</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="G11" t="n">
-        <v>168.7690005667855</v>
+        <v>191.728539425681</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>1.005033039094724</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1693107374601433</v>
+        <v>0.1676643490030086</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9983725603364841</v>
+        <v>0.998164544411142</v>
       </c>
       <c r="K11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.936395861962063</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3878414575412</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="R11" t="n">
-        <v>168.7690005667855</v>
+        <v>191.728539425681</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.851691490845276</v>
+        <v>-7.935767318647319</v>
       </c>
       <c r="D12" t="n">
-        <v>113.4589139680096</v>
+        <v>113.3885245192334</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.974148199168034</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="F12" t="n">
-        <v>113.393801561749</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="G12" t="n">
-        <v>207.7692819605994</v>
+        <v>191.728539425681</v>
       </c>
       <c r="H12" t="n">
-        <v>15.38952161731767</v>
+        <v>1.005033039094724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1693338216791876</v>
+        <v>0.1676643490030086</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857853518158063</v>
+        <v>0.5857851399430662</v>
       </c>
       <c r="K12" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.974148199168034</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.393801561749</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="R12" t="n">
-        <v>207.7692819605994</v>
+        <v>191.728539425681</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,28 +1262,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.883387947947598</v>
+        <v>-7.935767318647319</v>
       </c>
       <c r="D13" t="n">
-        <v>113.4173405482411</v>
+        <v>113.3885245192334</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.949109876521227</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3882337145641</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="G13" t="n">
-        <v>203.683046913467</v>
+        <v>191.728539425681</v>
       </c>
       <c r="H13" t="n">
-        <v>7.98013186790247</v>
+        <v>1.005033039094724</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1694988756166519</v>
+        <v>0.1676643490030086</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9993684200314595</v>
+        <v>0.9995600914473736</v>
       </c>
       <c r="K13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.949109876521227</v>
+        <v>-7.944617085538523</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3882337145641</v>
+        <v>113.3866694170918</v>
       </c>
       <c r="R13" t="n">
-        <v>203.683046913467</v>
+        <v>191.728539425681</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,28 +1327,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.883387947947598</v>
+        <v>-7.953129251333727</v>
       </c>
       <c r="D14" t="n">
-        <v>113.4173405482411</v>
+        <v>113.3844340566845</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.949109876521227</v>
+        <v>-7.96159401390791</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3882337145641</v>
+        <v>113.3813671378137</v>
       </c>
       <c r="G14" t="n">
-        <v>203.683046913467</v>
+        <v>199.7391643242391</v>
       </c>
       <c r="H14" t="n">
-        <v>7.98013186790247</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1694988756166519</v>
+        <v>0.1676799872556706</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9993610188615443</v>
+        <v>0.9995501825280527</v>
       </c>
       <c r="K14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.949109876521227</v>
+        <v>-7.96159401390791</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3882337145641</v>
+        <v>113.3813671378137</v>
       </c>
       <c r="R14" t="n">
-        <v>203.683046913467</v>
+        <v>199.7391643242391</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,28 +1392,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.950907011494536</v>
+        <v>-7.939009198131833</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3995920884386</v>
+        <v>113.3945681619559</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.959263001754305</v>
+        <v>-7.947788669372045</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3962348205603</v>
+        <v>113.3926002235871</v>
       </c>
       <c r="G15" t="n">
-        <v>201.6980394812829</v>
+        <v>192.5166220666887</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1695315002098256</v>
+        <v>0.1677222563889116</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9994797774650047</v>
+        <v>0.9995005090545971</v>
       </c>
       <c r="K15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.959263001754305</v>
+        <v>-7.947788669372045</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3962348205603</v>
+        <v>113.3926002235871</v>
       </c>
       <c r="R15" t="n">
-        <v>201.6980394812829</v>
+        <v>192.5166220666887</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,28 +1457,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.950907011494536</v>
+        <v>-7.939009198131833</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3995920884386</v>
+        <v>113.3945681619559</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.959263001754305</v>
+        <v>-7.947788669372045</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3962348205603</v>
+        <v>113.3926002235871</v>
       </c>
       <c r="G16" t="n">
-        <v>201.6980394812829</v>
+        <v>192.5166220666887</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1695315002098256</v>
+        <v>0.1677222563889116</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9995078116793321</v>
+        <v>0.9994856794333369</v>
       </c>
       <c r="K16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.959263001754305</v>
+        <v>-7.947788669372045</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3962348205603</v>
+        <v>113.3926002235871</v>
       </c>
       <c r="R16" t="n">
-        <v>201.6980394812829</v>
+        <v>192.5166220666887</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.950907011494536</v>
+        <v>-7.820171431912287</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3995920884386</v>
+        <v>113.4790980232159</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.959263001754305</v>
+        <v>-7.956391403530851</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3962348205603</v>
+        <v>113.3901874188384</v>
       </c>
       <c r="G17" t="n">
-        <v>201.6980394812829</v>
+        <v>212.877492365585</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>18.03692664051356</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1695315002098256</v>
+        <v>0.1677279243548565</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999490494190392</v>
+        <v>0.9994707231730851</v>
       </c>
       <c r="K17" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.959263001754305</v>
+        <v>-7.956391403530851</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3962348205603</v>
+        <v>113.3901874188384</v>
       </c>
       <c r="R17" t="n">
-        <v>201.6980394812829</v>
+        <v>212.877492365585</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.94977076373936</v>
+        <v>-7.821685434947646</v>
       </c>
       <c r="D18" t="n">
-        <v>113.4005490429886</v>
+        <v>113.4795564308879</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.958355215204417</v>
+        <v>-7.957087439487255</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3971116679271</v>
+        <v>113.3939742751187</v>
       </c>
       <c r="G18" t="n">
-        <v>201.6313768214382</v>
+        <v>212.0438826290271</v>
       </c>
       <c r="H18" t="n">
-        <v>1.026866339754594</v>
+        <v>17.76337138499295</v>
       </c>
       <c r="I18" t="n">
-        <v>0.16953335413524</v>
+        <v>0.1677361197601187</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9995760205219847</v>
+        <v>0.9996296794386703</v>
       </c>
       <c r="K18" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.958355215204417</v>
+        <v>-7.957087439487255</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3971116679271</v>
+        <v>113.3939742751187</v>
       </c>
       <c r="R18" t="n">
-        <v>201.6313768214382</v>
+        <v>212.0438826290271</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.94977076373936</v>
+        <v>-7.820857115488852</v>
       </c>
       <c r="D19" t="n">
-        <v>113.4005490429886</v>
+        <v>113.4758829518708</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.958355215204417</v>
+        <v>-7.959677961276572</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3971116679271</v>
+        <v>113.3915304599795</v>
       </c>
       <c r="G19" t="n">
-        <v>201.6313768214382</v>
+        <v>211.0372417285053</v>
       </c>
       <c r="H19" t="n">
-        <v>1.026866339754594</v>
+        <v>18.01648796335714</v>
       </c>
       <c r="I19" t="n">
-        <v>0.16953335413524</v>
+        <v>0.1677422929531031</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9995689506801857</v>
+        <v>0.9997896480607104</v>
       </c>
       <c r="K19" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.958355215204417</v>
+        <v>-7.959677961276572</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3971116679271</v>
+        <v>113.3915304599795</v>
       </c>
       <c r="R19" t="n">
-        <v>201.6313768214382</v>
+        <v>211.0372417285053</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.94977076373936</v>
+        <v>-7.821778634334938</v>
       </c>
       <c r="D20" t="n">
-        <v>113.4005490429886</v>
+        <v>113.473417575924</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.958355215204417</v>
+        <v>-7.957703258910239</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3971116679271</v>
+        <v>113.3901439197127</v>
       </c>
       <c r="G20" t="n">
-        <v>201.6313768214382</v>
+        <v>211.2456215164036</v>
       </c>
       <c r="H20" t="n">
-        <v>1.026866339754594</v>
+        <v>17.67941292946428</v>
       </c>
       <c r="I20" t="n">
-        <v>0.16953335413524</v>
+        <v>0.1677488536594211</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9997266035111343</v>
+        <v>0.9999048919404552</v>
       </c>
       <c r="K20" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.958355215204417</v>
+        <v>-7.957703258910239</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3971116679271</v>
+        <v>113.3901439197127</v>
       </c>
       <c r="R20" t="n">
-        <v>201.6313768214382</v>
+        <v>211.2456215164036</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.948783649321465</v>
+        <v>-7.821778634334938</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3981975149658</v>
+        <v>113.473417575924</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.957277272954132</v>
+        <v>-7.957703258910239</v>
       </c>
       <c r="F21" t="n">
-        <v>113.394804052421</v>
+        <v>113.3901439197127</v>
       </c>
       <c r="G21" t="n">
-        <v>201.587868665987</v>
+        <v>211.2456215164036</v>
       </c>
       <c r="H21" t="n">
-        <v>1.015695983026278</v>
+        <v>17.67941292946428</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1695361061650917</v>
+        <v>0.1677488536594211</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9998616605545286</v>
+        <v>0.9999159316745828</v>
       </c>
       <c r="K21" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.957277272954132</v>
+        <v>-7.957703258910239</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.394804052421</v>
+        <v>113.3901439197127</v>
       </c>
       <c r="R21" t="n">
-        <v>201.587868665987</v>
+        <v>211.2456215164036</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.947254491394587</v>
+        <v>-7.821778634334938</v>
       </c>
       <c r="D22" t="n">
-        <v>113.3977957155772</v>
+        <v>113.473417575924</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.957703258910239</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3901439197127</v>
       </c>
       <c r="G22" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2456215164036</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04788630253388</v>
+        <v>17.67941292946428</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1695365492043995</v>
+        <v>0.1677488536594211</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857864354828364</v>
+        <v>0.5857864377555499</v>
       </c>
       <c r="K22" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.957703258910239</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3901439197127</v>
       </c>
       <c r="R22" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2456215164036</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.947254491394587</v>
+        <v>-7.820292288014121</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3977957155772</v>
+        <v>113.4748523605862</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.956560107230088</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3912027264869</v>
       </c>
       <c r="G23" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2960943850779</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04788630253388</v>
+        <v>17.73354305262774</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1695365492043995</v>
+        <v>0.1677502247827846</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999664846974102</v>
+        <v>0.9999517528933224</v>
       </c>
       <c r="K23" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.956560107230088</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3912027264869</v>
       </c>
       <c r="R23" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2960943850779</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.947254491394587</v>
+        <v>-7.820292288014121</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3977957155772</v>
+        <v>113.4748523605862</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.956560107230088</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3912027264869</v>
       </c>
       <c r="G24" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2960943850779</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04788630253388</v>
+        <v>17.73354305262774</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1695365492043995</v>
+        <v>0.1677502247827846</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9999685335011461</v>
+        <v>0.9999542111806111</v>
       </c>
       <c r="K24" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.956560107230088</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3912027264869</v>
       </c>
       <c r="R24" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2960943850779</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.947254491394587</v>
+        <v>-7.820292288014121</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3977957155772</v>
+        <v>113.4748523605862</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.956560107230088</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3912027264869</v>
       </c>
       <c r="G25" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2960943850779</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04788630253388</v>
+        <v>17.73354305262774</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1695365492043995</v>
+        <v>0.1677502247827846</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999764690136572</v>
+        <v>0.9999577965821367</v>
       </c>
       <c r="K25" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.956018787783186</v>
+        <v>-7.956560107230088</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3942985093004</v>
+        <v>113.3912027264869</v>
       </c>
       <c r="R25" t="n">
-        <v>201.5633019054962</v>
+        <v>211.2960943850779</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.947840354508198</v>
+        <v>-7.819940871900245</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3989530261183</v>
+        <v>113.4749863433088</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.956252180330369</v>
+        <v>-7.9563831988085</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3956023434042</v>
+        <v>113.3912870782043</v>
       </c>
       <c r="G26" t="n">
-        <v>201.5289904317556</v>
+        <v>211.2786450903438</v>
       </c>
       <c r="H26" t="n">
-        <v>1.005505981779332</v>
+        <v>17.75296694298588</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1695368880754247</v>
+        <v>0.1677503366083224</v>
       </c>
       <c r="J26" t="n">
-        <v>0.999983703489746</v>
+        <v>0.9999599513596702</v>
       </c>
       <c r="K26" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.956252180330369</v>
+        <v>-7.9563831988085</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3956023434042</v>
+        <v>113.3912870782043</v>
       </c>
       <c r="R26" t="n">
-        <v>201.5289904317556</v>
+        <v>211.2786450903438</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.947686705220216</v>
+        <v>-7.820491154441903</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3980773668556</v>
+        <v>113.4743227068649</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.956145392902079</v>
+        <v>-7.956579237347988</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3947046630095</v>
+        <v>113.3908250107408</v>
       </c>
       <c r="G27" t="n">
-        <v>201.5484663420931</v>
+        <v>211.2834290798496</v>
       </c>
       <c r="H27" t="n">
-        <v>1.011243279736596</v>
+        <v>17.70777101363248</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1695370131074387</v>
+        <v>0.1677504109867626</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999899574448144</v>
+        <v>0.9999628098953455</v>
       </c>
       <c r="K27" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.956145392902079</v>
+        <v>-7.956579237347988</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3947046630095</v>
+        <v>113.3908250107408</v>
       </c>
       <c r="R27" t="n">
-        <v>201.5484663420931</v>
+        <v>211.2834290798496</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.948056629872416</v>
+        <v>-7.819755694371882</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3990593549623</v>
+        <v>113.4744042251574</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.956655370437868</v>
+        <v>-7.956219313107773</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3956310171014</v>
+        <v>113.3906672266203</v>
       </c>
       <c r="G28" t="n">
-        <v>201.5472494699561</v>
+        <v>211.2861467123135</v>
       </c>
       <c r="H28" t="n">
-        <v>1.027978126671472</v>
+        <v>17.7571506059177</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1695370772295136</v>
+        <v>0.1677504796626317</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9999910289216034</v>
+        <v>0.9999667117543988</v>
       </c>
       <c r="K28" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.956655370437868</v>
+        <v>-7.956219313107773</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3956310171014</v>
+        <v>113.3906672266203</v>
       </c>
       <c r="R28" t="n">
-        <v>201.5472494699561</v>
+        <v>211.2861467123135</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.947492573581599</v>
+        <v>-7.819913010741498</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3987632508614</v>
+        <v>113.4742715653347</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.956239601477443</v>
+        <v>-7.955881672323675</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3952758875022</v>
+        <v>113.3908429298032</v>
       </c>
       <c r="G29" t="n">
-        <v>201.546724359711</v>
+        <v>211.2847570783266</v>
       </c>
       <c r="H29" t="n">
-        <v>1.045702099494519</v>
+        <v>17.69248017771793</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1695371523123573</v>
+        <v>0.1677505114083017</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9999944197970172</v>
+        <v>0.9999686749192888</v>
       </c>
       <c r="K29" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.956239601477443</v>
+        <v>-7.955881672323675</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3952758875022</v>
+        <v>113.3908429298032</v>
       </c>
       <c r="R29" t="n">
-        <v>201.546724359711</v>
+        <v>211.2847570783266</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.947492573581599</v>
+        <v>-7.819913010741498</v>
       </c>
       <c r="D30" t="n">
-        <v>113.3987632508614</v>
+        <v>113.4742715653347</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.956239601477443</v>
+        <v>-7.955881672323675</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3952758875022</v>
+        <v>113.3908429298032</v>
       </c>
       <c r="G30" t="n">
-        <v>201.546724359711</v>
+        <v>211.2847570783266</v>
       </c>
       <c r="H30" t="n">
-        <v>1.045702099494519</v>
+        <v>17.69248017771793</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1695371523123573</v>
+        <v>0.1677505114083017</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9999975073968307</v>
+        <v>0.9999705206033859</v>
       </c>
       <c r="K30" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.956239601477443</v>
+        <v>-7.955881672323675</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3952758875022</v>
+        <v>113.3908429298032</v>
       </c>
       <c r="R30" t="n">
-        <v>201.546724359711</v>
+        <v>211.2847570783266</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,31 +2432,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.947833529766453</v>
+        <v>-7.819913010741498</v>
       </c>
       <c r="D31" t="n">
-        <v>113.3986258952773</v>
+        <v>113.4742715653347</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.956198148418074</v>
+        <v>-7.955881672323675</v>
       </c>
       <c r="F31" t="n">
-        <v>113.395290630395</v>
+        <v>113.3908429298032</v>
       </c>
       <c r="G31" t="n">
-        <v>201.5488682957016</v>
+        <v>211.2847570783266</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>17.69248017771793</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1695371844790213</v>
+        <v>0.1677505114083017</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9999983201638695</v>
+        <v>0.9999732440696784</v>
       </c>
       <c r="K31" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.956198148418074</v>
+        <v>-7.955881672323675</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.395290630395</v>
+        <v>113.3908429298032</v>
       </c>
       <c r="R31" t="n">
-        <v>201.5488682957016</v>
+        <v>211.2847570783266</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.947831214773533</v>
+        <v>-7.820049379604276</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3986742992364</v>
+        <v>113.4743753780785</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.956195831741564</v>
+        <v>-7.956160745713864</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3953390300682</v>
+        <v>113.3908594294204</v>
       </c>
       <c r="G32" t="n">
-        <v>201.5488974982361</v>
+        <v>211.2846625053665</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>17.71103251982715</v>
       </c>
       <c r="I32" t="n">
-        <v>0.169537187718597</v>
+        <v>0.1677505171536066</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5857864397726815</v>
+        <v>0.5358983873027017</v>
       </c>
       <c r="K32" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.956195831741564</v>
+        <v>-7.956160745713864</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3953390300682</v>
+        <v>113.3908594294204</v>
       </c>
       <c r="R32" t="n">
-        <v>201.5488974982361</v>
+        <v>211.2846625053665</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,31 +2562,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.947831214773533</v>
+        <v>-7.819945106915402</v>
       </c>
       <c r="D33" t="n">
-        <v>113.3986742992364</v>
+        <v>113.4743430371565</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.956195831741564</v>
+        <v>-7.956057449920416</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3953390300682</v>
+        <v>113.3908264775511</v>
       </c>
       <c r="G33" t="n">
-        <v>201.5488974982361</v>
+        <v>211.2846724337639</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>17.71116149410992</v>
       </c>
       <c r="I33" t="n">
-        <v>0.169537187718597</v>
+        <v>0.1677505216314751</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999997085855571</v>
+        <v>0.9999790791216217</v>
       </c>
       <c r="K33" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.956195831741564</v>
+        <v>-7.956057449920416</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3953390300682</v>
+        <v>113.3908264775511</v>
       </c>
       <c r="R33" t="n">
-        <v>201.5488974982361</v>
+        <v>211.2846724337639</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,31 +2627,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.94764392583857</v>
+        <v>-7.819780433130916</v>
       </c>
       <c r="D34" t="n">
-        <v>113.3988133314962</v>
+        <v>113.4744679037979</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.956225118889897</v>
+        <v>-7.955989486242112</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3953916712824</v>
+        <v>113.3908925754403</v>
       </c>
       <c r="G34" t="n">
-        <v>201.5490925831322</v>
+        <v>211.284501863603</v>
       </c>
       <c r="H34" t="n">
-        <v>1.0258933523843</v>
+        <v>17.72371424113769</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1695371890952646</v>
+        <v>0.1677505223748074</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8530334251417701</v>
+        <v>0.8984711064098582</v>
       </c>
       <c r="K34" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.956225118889897</v>
+        <v>-7.955989486242112</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3953916712824</v>
+        <v>113.3908925754403</v>
       </c>
       <c r="R34" t="n">
-        <v>201.5490925831322</v>
+        <v>211.284501863603</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,31 +2692,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.947691552103633</v>
+        <v>-7.819826381280532</v>
       </c>
       <c r="D35" t="n">
-        <v>113.3987859426267</v>
+        <v>113.4744270578765</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.956176882553048</v>
+        <v>-7.955996867090533</v>
       </c>
       <c r="F35" t="n">
-        <v>113.3954025186885</v>
+        <v>113.3908755155571</v>
       </c>
       <c r="G35" t="n">
-        <v>201.54902539015</v>
+        <v>211.2844647409294</v>
       </c>
       <c r="H35" t="n">
-        <v>1.014432359074546</v>
+        <v>17.71868853075931</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1695371896544744</v>
+        <v>0.1677505236183363</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9784934157929174</v>
+        <v>0.9827224821228089</v>
       </c>
       <c r="K35" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.956176882553048</v>
+        <v>-7.955996867090533</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3954025186885</v>
+        <v>113.3908755155571</v>
       </c>
       <c r="R35" t="n">
-        <v>201.54902539015</v>
+        <v>211.2844647409294</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,31 +2757,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.947691552103633</v>
+        <v>-7.819916678768252</v>
       </c>
       <c r="D36" t="n">
-        <v>113.3987859426267</v>
+        <v>113.4743374901814</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.956176882553048</v>
+        <v>-7.956024636507529</v>
       </c>
       <c r="F36" t="n">
-        <v>113.3954025186885</v>
+        <v>113.3908242854094</v>
       </c>
       <c r="G36" t="n">
-        <v>201.54902539015</v>
+        <v>211.2844723528091</v>
       </c>
       <c r="H36" t="n">
-        <v>1.014432359074546</v>
+        <v>17.71055324001068</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1695371896544744</v>
+        <v>0.1677505243429521</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8736265668676111</v>
+        <v>0.9907859383888362</v>
       </c>
       <c r="K36" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.956176882553048</v>
+        <v>-7.956024636507529</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.3954025186885</v>
+        <v>113.3908242854094</v>
       </c>
       <c r="R36" t="n">
-        <v>201.54902539015</v>
+        <v>211.2844723528091</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,31 +2822,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.947604122486936</v>
+        <v>-7.819916678768252</v>
       </c>
       <c r="D37" t="n">
-        <v>113.3988110363126</v>
+        <v>113.4743374901814</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.95618643388037</v>
+        <v>-7.956024636507529</v>
       </c>
       <c r="F37" t="n">
-        <v>113.3953889447666</v>
+        <v>113.3908242854094</v>
       </c>
       <c r="G37" t="n">
-        <v>201.5490109467333</v>
+        <v>211.2844723528091</v>
       </c>
       <c r="H37" t="n">
-        <v>1.026026474599693</v>
+        <v>17.71055324001068</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1695371900441651</v>
+        <v>0.1677505243429521</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9749627489683239</v>
+        <v>0.9922082670921955</v>
       </c>
       <c r="K37" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.95618643388037</v>
+        <v>-7.956024636507529</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.3953889447666</v>
+        <v>113.3908242854094</v>
       </c>
       <c r="R37" t="n">
-        <v>201.5490109467333</v>
+        <v>211.2844723528091</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,31 +2887,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.947622810067872</v>
+        <v>-7.819913542706947</v>
       </c>
       <c r="D38" t="n">
-        <v>113.398839437951</v>
+        <v>113.4743358276042</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.956212328864967</v>
+        <v>-7.956018156641701</v>
       </c>
       <c r="F38" t="n">
-        <v>113.3954144768482</v>
+        <v>113.390824765675</v>
       </c>
       <c r="G38" t="n">
-        <v>201.5489850685552</v>
+        <v>211.2844450430931</v>
       </c>
       <c r="H38" t="n">
-        <v>1.026887947320743</v>
+        <v>17.71011298100021</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1695371902660881</v>
+        <v>0.1677505245925004</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9937607307822127</v>
+        <v>0.9964803482636542</v>
       </c>
       <c r="K38" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.956212328864967</v>
+        <v>-7.956018156641701</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3954144768482</v>
+        <v>113.390824765675</v>
       </c>
       <c r="R38" t="n">
-        <v>201.5489850685552</v>
+        <v>211.2844450430931</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,31 +2952,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.947672283781669</v>
+        <v>-7.819919016625466</v>
       </c>
       <c r="D39" t="n">
-        <v>113.3988000524943</v>
+        <v>113.4743501856611</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.956206134960988</v>
+        <v>-7.956029453661562</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3953972842816</v>
+        <v>113.3908355421293</v>
       </c>
       <c r="G39" t="n">
-        <v>201.5490077895559</v>
+        <v>211.2844469147554</v>
       </c>
       <c r="H39" t="n">
-        <v>1.020232961470545</v>
+        <v>17.71087108934304</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1695371903634664</v>
+        <v>0.167750524872109</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9962629629969056</v>
+        <v>0.9987209083506134</v>
       </c>
       <c r="K39" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.956206134960988</v>
+        <v>-7.956029453661562</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3953972842816</v>
+        <v>113.3908355421293</v>
       </c>
       <c r="R39" t="n">
-        <v>201.5490077895559</v>
+        <v>211.2844469147554</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,31 +3017,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.94764408520616</v>
+        <v>-7.819919019040989</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3988019907279</v>
+        <v>113.4743573941038</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.956217330045526</v>
+        <v>-7.956041518281994</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3953835166087</v>
+        <v>113.390835334806</v>
       </c>
       <c r="G40" t="n">
-        <v>201.5489966254698</v>
+        <v>211.2844504892403</v>
       </c>
       <c r="H40" t="n">
-        <v>1.024942453355505</v>
+        <v>17.71244140695482</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1695371904224287</v>
+        <v>0.167750524894677</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9986116171256554</v>
+        <v>0.9988379271429599</v>
       </c>
       <c r="K40" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.956217330045526</v>
+        <v>-7.956041518281994</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3953835166087</v>
+        <v>113.390835334806</v>
       </c>
       <c r="R40" t="n">
-        <v>201.5489966254698</v>
+        <v>211.2844504892403</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,31 +3082,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.94764408520616</v>
+        <v>-7.819949840696204</v>
       </c>
       <c r="D41" t="n">
-        <v>113.3988019907279</v>
+        <v>113.4743499531854</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.956217330045526</v>
+        <v>-7.956050320027701</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3953835166087</v>
+        <v>113.3908414188745</v>
       </c>
       <c r="G41" t="n">
-        <v>201.5489966254698</v>
+        <v>211.2844459156414</v>
       </c>
       <c r="H41" t="n">
-        <v>1.024942453355505</v>
+        <v>17.70957511710337</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1695371904224287</v>
+        <v>0.1677505249619608</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9988364875590211</v>
+        <v>0.9189120494874442</v>
       </c>
       <c r="K41" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.956217330045526</v>
+        <v>-7.956050320027701</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3953835166087</v>
+        <v>113.3908414188745</v>
       </c>
       <c r="R41" t="n">
-        <v>201.5489966254698</v>
+        <v>211.2844459156414</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.94764408520616</v>
+        <v>-7.819949840696204</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3988019907279</v>
+        <v>113.4743499531854</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.956217330045526</v>
+        <v>-7.956050320027701</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3953835166087</v>
+        <v>113.3908414188745</v>
       </c>
       <c r="G42" t="n">
-        <v>201.5489966254698</v>
+        <v>211.2844459156414</v>
       </c>
       <c r="H42" t="n">
-        <v>1.024942453355505</v>
+        <v>17.70957511710337</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1695371904224287</v>
+        <v>0.1677505249619608</v>
       </c>
       <c r="J42" t="n">
-        <v>0.585786142094663</v>
+        <v>0.5856903107367535</v>
       </c>
       <c r="K42" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.956217330045526</v>
+        <v>-7.956050320027701</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3953835166087</v>
+        <v>113.3908414188745</v>
       </c>
       <c r="R42" t="n">
-        <v>201.5489966254698</v>
+        <v>211.2844459156414</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.947758267739696</v>
+        <v>-7.819948821360185</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3987726326544</v>
+        <v>113.4743526749209</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.956222325029492</v>
+        <v>-7.956049887466011</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3953976960025</v>
+        <v>113.3908437807214</v>
       </c>
       <c r="G43" t="n">
-        <v>201.5489950630535</v>
+        <v>211.2844458922354</v>
       </c>
       <c r="H43" t="n">
-        <v>1.011888909411788</v>
+        <v>17.70965146907468</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1695371904618223</v>
+        <v>0.1677505249667006</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9998700973182536</v>
+        <v>0.9995315524768775</v>
       </c>
       <c r="K43" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.956222325029492</v>
+        <v>-7.956049887466011</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3953976960025</v>
+        <v>113.3908437807214</v>
       </c>
       <c r="R43" t="n">
-        <v>201.5489950630535</v>
+        <v>211.2844458922354</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,31 +3277,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.947758267739696</v>
+        <v>-7.819946780467791</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3987726326544</v>
+        <v>113.4743536383168</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.956222325029492</v>
+        <v>-7.956048865670478</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3953976960025</v>
+        <v>113.3908441170957</v>
       </c>
       <c r="G44" t="n">
-        <v>201.5489950630535</v>
+        <v>211.284446469655</v>
       </c>
       <c r="H44" t="n">
-        <v>1.011888909411788</v>
+        <v>17.70978419161298</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1695371904618223</v>
+        <v>0.1677505249763809</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9999222881097654</v>
+        <v>0.9995314812394315</v>
       </c>
       <c r="K44" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.956222325029492</v>
+        <v>-7.956048865670478</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3953976960025</v>
+        <v>113.3908441170957</v>
       </c>
       <c r="R44" t="n">
-        <v>201.5489950630535</v>
+        <v>211.284446469655</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,31 +3342,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.947586321972436</v>
+        <v>-7.819945685632129</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3988305021071</v>
+        <v>113.4743544337349</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.956202251168192</v>
+        <v>-7.956044577328535</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3953950082519</v>
+        <v>113.3908468733896</v>
       </c>
       <c r="G45" t="n">
-        <v>201.5489965203318</v>
+        <v>211.2844463435698</v>
       </c>
       <c r="H45" t="n">
-        <v>1.03004543069276</v>
+        <v>17.70936859915307</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1695371904626989</v>
+        <v>0.1677505249824123</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9999644479702678</v>
+        <v>0.9998796960920875</v>
       </c>
       <c r="K45" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.956202251168192</v>
+        <v>-7.956044577328535</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3953950082519</v>
+        <v>113.3908468733896</v>
       </c>
       <c r="R45" t="n">
-        <v>201.5489965203318</v>
+        <v>211.2844463435698</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,31 +3407,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.947612472621267</v>
+        <v>-7.819945685632129</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3988309732644</v>
+        <v>113.4743544337349</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.956217968473983</v>
+        <v>-7.956044577328535</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3953996392019</v>
+        <v>113.3908468733896</v>
       </c>
       <c r="G46" t="n">
-        <v>201.5489979313218</v>
+        <v>211.2844463435698</v>
       </c>
       <c r="H46" t="n">
-        <v>1.028798119066468</v>
+        <v>17.70936859915307</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1695371905170268</v>
+        <v>0.1677505249824123</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9999735880409861</v>
+        <v>0.9998978592328058</v>
       </c>
       <c r="K46" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.956217968473983</v>
+        <v>-7.956044577328535</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3953996392019</v>
+        <v>113.3908468733896</v>
       </c>
       <c r="R46" t="n">
-        <v>201.5489979313218</v>
+        <v>211.2844463435698</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.947631769306187</v>
+        <v>-7.819938185657015</v>
       </c>
       <c r="D47" t="n">
-        <v>113.398817261629</v>
+        <v>113.4743562717908</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.956212072248814</v>
+        <v>-7.956044011649417</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3953959729726</v>
+        <v>113.3908444563121</v>
       </c>
       <c r="G47" t="n">
-        <v>201.548998033508</v>
+        <v>211.28444642171</v>
       </c>
       <c r="H47" t="n">
-        <v>1.025786270012412</v>
+        <v>17.71027096762408</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1695371905191192</v>
+        <v>0.1677505249842974</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999781796389501</v>
+        <v>0.9999150699891597</v>
       </c>
       <c r="K47" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.956212072248814</v>
+        <v>-7.956044011649417</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3953959729726</v>
+        <v>113.3908444563121</v>
       </c>
       <c r="R47" t="n">
-        <v>201.548998033508</v>
+        <v>211.28444642171</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,31 +3537,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.947608093094142</v>
+        <v>-7.819938185657015</v>
       </c>
       <c r="D48" t="n">
-        <v>113.3988301730658</v>
+        <v>113.4743562717908</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.956215518153587</v>
+        <v>-7.956044011649417</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3953980697524</v>
+        <v>113.3908444563121</v>
       </c>
       <c r="G48" t="n">
-        <v>201.5489980626197</v>
+        <v>211.28444642171</v>
       </c>
       <c r="H48" t="n">
-        <v>1.029028759524914</v>
+        <v>17.71027096762408</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1695371905207228</v>
+        <v>0.1677505249842974</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999904159570252</v>
+        <v>0.9999417435580474</v>
       </c>
       <c r="K48" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.956215518153587</v>
+        <v>-7.956044011649417</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3953980697524</v>
+        <v>113.3908444563121</v>
       </c>
       <c r="R48" t="n">
-        <v>201.5489980626197</v>
+        <v>211.28444642171</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,31 +3602,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.947640575338764</v>
+        <v>-7.819938185657015</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3988175022159</v>
+        <v>113.4743562717908</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.956212255985298</v>
+        <v>-7.956044011649417</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3953996516448</v>
+        <v>113.3908444563121</v>
       </c>
       <c r="G49" t="n">
-        <v>201.548997756491</v>
+        <v>211.28444642171</v>
       </c>
       <c r="H49" t="n">
-        <v>1.024755459772401</v>
+        <v>17.71027096762408</v>
       </c>
       <c r="I49" t="n">
-        <v>0.16953719052681</v>
+        <v>0.1677505249842974</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999920658576419</v>
+        <v>0.9999775136166025</v>
       </c>
       <c r="K49" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.956212255985298</v>
+        <v>-7.956044011649417</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3953996516448</v>
+        <v>113.3908444563121</v>
       </c>
       <c r="R49" t="n">
-        <v>201.548997756491</v>
+        <v>211.28444642171</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,31 +3667,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.947640575338764</v>
+        <v>-7.819944203733251</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3988175022159</v>
+        <v>113.4743529459396</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.956212255985298</v>
+        <v>-7.956043971005837</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3953996516448</v>
+        <v>113.3908448482526</v>
       </c>
       <c r="G50" t="n">
-        <v>201.548997756491</v>
+        <v>211.2844464039892</v>
       </c>
       <c r="H50" t="n">
-        <v>1.024755459772401</v>
+        <v>17.7094825483836</v>
       </c>
       <c r="I50" t="n">
-        <v>0.16953719052681</v>
+        <v>0.1677505249845407</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9999972900049665</v>
+        <v>0.9999889369149186</v>
       </c>
       <c r="K50" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.956212255985298</v>
+        <v>-7.956043971005837</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3953996516448</v>
+        <v>113.3908448482526</v>
       </c>
       <c r="R50" t="n">
-        <v>201.548997756491</v>
+        <v>211.2844464039892</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.947639922362594</v>
+        <v>-7.819943070603043</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3988183665543</v>
+        <v>113.474352976476</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.956212574881254</v>
+        <v>-7.956043995268858</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3954001284877</v>
+        <v>113.3908441686194</v>
       </c>
       <c r="G51" t="n">
-        <v>201.5489975866523</v>
+        <v>211.2844463948512</v>
       </c>
       <c r="H51" t="n">
-        <v>1.024871647326176</v>
+        <v>17.709633157237</v>
       </c>
       <c r="I51" t="n">
-        <v>0.169537190527194</v>
+        <v>0.1677505249846025</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9999988797826375</v>
+        <v>0.999988850033582</v>
       </c>
       <c r="K51" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.956212574881254</v>
+        <v>-7.956043995268858</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3954001284877</v>
+        <v>113.3908441686194</v>
       </c>
       <c r="R51" t="n">
-        <v>201.5489975866523</v>
+        <v>211.2844463948512</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,31 +3797,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.947640315917958</v>
+        <v>-7.819943070603043</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3988170678925</v>
+        <v>113.474352976476</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.956212141304377</v>
+        <v>-7.956043995268858</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3953991596373</v>
+        <v>113.3908441686194</v>
       </c>
       <c r="G52" t="n">
-        <v>201.5489975944602</v>
+        <v>211.2844463948512</v>
       </c>
       <c r="H52" t="n">
-        <v>1.024772762495816</v>
+        <v>17.709633157237</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1695371905273096</v>
+        <v>0.1677505249846025</v>
       </c>
       <c r="J52" t="n">
-        <v>0.585786439773511</v>
+        <v>0.585786439751984</v>
       </c>
       <c r="K52" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.956212141304377</v>
+        <v>-7.956043995268858</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3953991596373</v>
+        <v>113.3908441686194</v>
       </c>
       <c r="R52" t="n">
-        <v>201.5489975944602</v>
+        <v>211.2844463948512</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,31 +3862,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.947639916489395</v>
+        <v>-7.819943495446293</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3988178332493</v>
+        <v>113.4743529723037</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.95621329469895</v>
+        <v>-7.956044207630407</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3953993058108</v>
+        <v>113.3908442947878</v>
       </c>
       <c r="G53" t="n">
-        <v>201.5489976167153</v>
+        <v>211.2844463942482</v>
       </c>
       <c r="H53" t="n">
-        <v>1.024958404960697</v>
+        <v>17.70960550709533</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1695371905281201</v>
+        <v>0.1677505249846807</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999999940560342</v>
+        <v>0.9999999889151442</v>
       </c>
       <c r="K53" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.95621329469895</v>
+        <v>-7.956044207630407</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3953993058108</v>
+        <v>113.3908442947878</v>
       </c>
       <c r="R53" t="n">
-        <v>201.5489976167153</v>
+        <v>211.2844463942482</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,31 +3927,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.947639157167387</v>
+        <v>-7.819944352668565</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3988180797968</v>
+        <v>113.4743529865742</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.956213448471776</v>
+        <v>-7.956044512263761</v>
       </c>
       <c r="F54" t="n">
-        <v>113.395399188265</v>
+        <v>113.3908446480681</v>
       </c>
       <c r="G54" t="n">
-        <v>201.5489976531294</v>
+        <v>211.2844463958338</v>
       </c>
       <c r="H54" t="n">
-        <v>1.025067567059345</v>
+        <v>17.7095335995234</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1695371905286417</v>
+        <v>0.1677505249846966</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999954224266</v>
+        <v>0.9999999938024662</v>
       </c>
       <c r="K54" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.956213448471776</v>
+        <v>-7.956044512263761</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.395399188265</v>
+        <v>113.3908446480681</v>
       </c>
       <c r="R54" t="n">
-        <v>201.5489976531294</v>
+        <v>211.2844463958338</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,31 +3992,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.947639157167387</v>
+        <v>-7.819944195405501</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3988180797968</v>
+        <v>113.4743529457748</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.956213448471776</v>
+        <v>-7.956044442051195</v>
       </c>
       <c r="F55" t="n">
-        <v>113.395399188265</v>
+        <v>113.3908445538828</v>
       </c>
       <c r="G55" t="n">
-        <v>201.5489976531294</v>
+        <v>211.28444639115</v>
       </c>
       <c r="H55" t="n">
-        <v>1.025067567059345</v>
+        <v>17.70954492643879</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1695371905286417</v>
+        <v>0.1677505249847603</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999957247183</v>
+        <v>0.9999999938023501</v>
       </c>
       <c r="K55" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.956213448471776</v>
+        <v>-7.956044442051195</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.395399188265</v>
+        <v>113.3908445538828</v>
       </c>
       <c r="R55" t="n">
-        <v>201.5489976531294</v>
+        <v>211.28444639115</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.947638635872526</v>
+        <v>-7.819944266382667</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3988180183512</v>
+        <v>113.4743529731912</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.956213353433331</v>
+        <v>-7.956044371740403</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3953989568544</v>
+        <v>113.3908446680085</v>
       </c>
       <c r="G56" t="n">
-        <v>201.5489976595895</v>
+        <v>211.2844463916369</v>
       </c>
       <c r="H56" t="n">
-        <v>1.025118526691151</v>
+        <v>17.70952654084209</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1695371905286555</v>
+        <v>0.1677505249847676</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999999959659696</v>
+        <v>0.9999999938022939</v>
       </c>
       <c r="K56" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.956213353433331</v>
+        <v>-7.956044371740403</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3953989568544</v>
+        <v>113.3908446680085</v>
       </c>
       <c r="R56" t="n">
-        <v>201.5489976595895</v>
+        <v>211.2844463916369</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,31 +4122,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.947639436785174</v>
+        <v>-7.819944321986247</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3988180643929</v>
+        <v>113.4743529739594</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.95621345451482</v>
+        <v>-7.956044325521568</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3953992819444</v>
+        <v>113.3908447312662</v>
       </c>
       <c r="G57" t="n">
-        <v>201.548997660371</v>
+        <v>211.284446391559</v>
       </c>
       <c r="H57" t="n">
-        <v>1.025034860844234</v>
+        <v>17.70951329075982</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1695371905286565</v>
+        <v>0.1677505249847681</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9999999959995827</v>
+        <v>0.9999999938022623</v>
       </c>
       <c r="K57" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.95621345451482</v>
+        <v>-7.956044325521568</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3953992819444</v>
+        <v>113.3908447312662</v>
       </c>
       <c r="R57" t="n">
-        <v>201.548997660371</v>
+        <v>211.284446391559</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,31 +4187,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.947639079772967</v>
+        <v>-7.819944163350533</v>
       </c>
       <c r="D58" t="n">
-        <v>113.39881800032</v>
+        <v>113.4743529767491</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.956213097185757</v>
+        <v>-7.956044312580332</v>
       </c>
       <c r="F58" t="n">
-        <v>113.395399218001</v>
+        <v>113.3908446446582</v>
       </c>
       <c r="G58" t="n">
-        <v>201.5489976592591</v>
+        <v>211.2844463915374</v>
       </c>
       <c r="H58" t="n">
-        <v>1.025034822955752</v>
+        <v>17.70953224984867</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1695371905286634</v>
+        <v>0.1677505249847698</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9999999962252746</v>
+        <v>0.999999993802243</v>
       </c>
       <c r="K58" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.956213097185757</v>
+        <v>-7.956044312580332</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.395399218001</v>
+        <v>113.3908446446582</v>
       </c>
       <c r="R58" t="n">
-        <v>201.5489976592591</v>
+        <v>211.2844463915374</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,31 +4252,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.947639231661552</v>
+        <v>-7.819944053686148</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3988181366646</v>
+        <v>113.4743530552664</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.956213535840529</v>
+        <v>-7.956044365346544</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3953992399976</v>
+        <v>113.3908446234953</v>
       </c>
       <c r="G59" t="n">
-        <v>201.5489976577762</v>
+        <v>211.2844463913872</v>
       </c>
       <c r="H59" t="n">
-        <v>1.025069106268064</v>
+        <v>17.70955338677888</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1695371905286855</v>
+        <v>0.1677505249847707</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999964715849</v>
+        <v>0.9999999938006712</v>
       </c>
       <c r="K59" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.956213535840529</v>
+        <v>-7.956044365346544</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3953992399976</v>
+        <v>113.3908446234953</v>
       </c>
       <c r="R59" t="n">
-        <v>201.5489976577762</v>
+        <v>211.2844463913872</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,31 +4317,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.947638465844761</v>
+        <v>-7.819944142953561</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3988181872019</v>
+        <v>113.4743529769748</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.956213305190888</v>
+        <v>-7.956044285201317</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3953990771453</v>
+        <v>113.3908446491746</v>
       </c>
       <c r="G60" t="n">
-        <v>201.548997657757</v>
+        <v>211.2844463913173</v>
       </c>
       <c r="H60" t="n">
-        <v>1.02513308629406</v>
+        <v>17.7095313412363</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1695371905286975</v>
+        <v>0.1677505249847714</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999967293702</v>
+        <v>0.9999999938003254</v>
       </c>
       <c r="K60" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.956213305190888</v>
+        <v>-7.956044285201317</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3953990771453</v>
+        <v>113.3908446491746</v>
       </c>
       <c r="R60" t="n">
-        <v>201.548997657757</v>
+        <v>211.2844463913173</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,31 +4382,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.947639446266073</v>
+        <v>-7.819944246055138</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3988177940193</v>
+        <v>113.4743529444117</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.956213290827828</v>
+        <v>-7.95604433340637</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3953990806213</v>
+        <v>113.3908446502868</v>
       </c>
       <c r="G61" t="n">
-        <v>201.5489976575224</v>
+        <v>211.2844463913569</v>
       </c>
       <c r="H61" t="n">
-        <v>1.025014158346151</v>
+        <v>17.70952419761396</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1695371905287009</v>
+        <v>0.1677505249847723</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9999999968963857</v>
+        <v>0.9999999938003128</v>
       </c>
       <c r="K61" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.956213290827828</v>
+        <v>-7.95604433340637</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3953990806213</v>
+        <v>113.3908446502868</v>
       </c>
       <c r="R61" t="n">
-        <v>201.5489976575224</v>
+        <v>211.2844463913569</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.947639446266073</v>
+        <v>-7.819944246055138</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3988177940193</v>
+        <v>113.4743529444117</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.956213290827828</v>
+        <v>-7.95604433340637</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3953990806213</v>
+        <v>113.3908446502868</v>
       </c>
       <c r="G62" t="n">
-        <v>201.5489976575224</v>
+        <v>211.2844463913569</v>
       </c>
       <c r="H62" t="n">
-        <v>1.025014158346151</v>
+        <v>17.70952419761396</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1695371905287009</v>
+        <v>0.1677505249847723</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857864397736966</v>
+        <v>0.535898387456841</v>
       </c>
       <c r="K62" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.956213290827828</v>
+        <v>-7.95604433340637</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3953990806213</v>
+        <v>113.3908446502868</v>
       </c>
       <c r="R62" t="n">
-        <v>201.5489976575224</v>
+        <v>211.2844463913569</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,31 +4512,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.947638911195767</v>
+        <v>-7.819944247351022</v>
       </c>
       <c r="D63" t="n">
-        <v>113.398818155368</v>
+        <v>113.4743529600179</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.956213300897007</v>
+        <v>-7.956044317196787</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3953992246021</v>
+        <v>113.3908446766379</v>
       </c>
       <c r="G63" t="n">
-        <v>201.5489976576058</v>
+        <v>211.2844463913557</v>
       </c>
       <c r="H63" t="n">
-        <v>1.025079330580104</v>
+        <v>17.70952191964032</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1695371905287046</v>
+        <v>0.1677505249847724</v>
       </c>
       <c r="J63" t="n">
-        <v>0.999999999999809</v>
+        <v>0.9999999999969691</v>
       </c>
       <c r="K63" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.956213300897007</v>
+        <v>-7.956044317196787</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3953992246021</v>
+        <v>113.3908446766379</v>
       </c>
       <c r="R63" t="n">
-        <v>201.5489976576058</v>
+        <v>211.2844463913557</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,31 +4577,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.947638896083411</v>
+        <v>-7.819944247351022</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3988181743072</v>
+        <v>113.4743529600179</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.956213302092017</v>
+        <v>-7.956044317196787</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3953992370389</v>
+        <v>113.3908446766379</v>
       </c>
       <c r="G64" t="n">
-        <v>201.5489976572711</v>
+        <v>211.2844463913557</v>
       </c>
       <c r="H64" t="n">
-        <v>1.0250812801476</v>
+        <v>17.70952191964032</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1695371905287065</v>
+        <v>0.1677505249847724</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9326234962840773</v>
+        <v>0.9999999999995151</v>
       </c>
       <c r="K64" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.956213302092017</v>
+        <v>-7.956044317196787</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3953992370389</v>
+        <v>113.3908446766379</v>
       </c>
       <c r="R64" t="n">
-        <v>201.5489976572711</v>
+        <v>211.2844463913557</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,31 +4642,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.94763920346506</v>
+        <v>-7.819944200915216</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3988179669472</v>
+        <v>113.4743529857817</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.95621328775155</v>
+        <v>-7.956044321400469</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3953991579618</v>
+        <v>113.3908446713277</v>
       </c>
       <c r="G65" t="n">
-        <v>201.5489976573314</v>
+        <v>211.2844463913578</v>
       </c>
       <c r="H65" t="n">
-        <v>1.025042817792229</v>
+        <v>17.70952850931348</v>
       </c>
       <c r="I65" t="n">
-        <v>0.169537190528707</v>
+        <v>0.1677505249847724</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9722174973021552</v>
+        <v>0.9656026401515507</v>
       </c>
       <c r="K65" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.95621328775155</v>
+        <v>-7.956044321400469</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3953991579618</v>
+        <v>113.3908446713277</v>
       </c>
       <c r="R65" t="n">
-        <v>201.5489976573314</v>
+        <v>211.2844463913578</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,31 +4707,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.947639415861759</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D66" t="n">
-        <v>113.398817962311</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.956213335409503</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3953992190129</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G66" t="n">
-        <v>201.548997657332</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H66" t="n">
-        <v>1.025023123031057</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1695371905287077</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9182855006015086</v>
+        <v>0.9885861949992065</v>
       </c>
       <c r="K66" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.956213335409503</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3953992190129</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R66" t="n">
-        <v>201.548997657332</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,31 +4772,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.947639415861759</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D67" t="n">
-        <v>113.398817962311</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.956213335409503</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3953992190129</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G67" t="n">
-        <v>201.548997657332</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H67" t="n">
-        <v>1.025023123031057</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1695371905287077</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J67" t="n">
-        <v>0.991744588488605</v>
+        <v>0.9931709810805889</v>
       </c>
       <c r="K67" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.956213335409503</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3953992190129</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R67" t="n">
-        <v>201.548997657332</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,31 +4837,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.947639217734699</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3988180019861</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.95621331041075</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3953991896554</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G68" t="n">
-        <v>201.5489976573548</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H68" t="n">
-        <v>1.025043820776753</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1695371905287082</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9944068880720018</v>
+        <v>0.9971907282941895</v>
       </c>
       <c r="K68" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.95621331041075</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3953991896554</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R68" t="n">
-        <v>201.5489976573548</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,31 +4902,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.947639217734699</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3988180019861</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.95621331041075</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3953991896554</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G69" t="n">
-        <v>201.5489976573548</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H69" t="n">
-        <v>1.025043820776753</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1695371905287082</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9973098814641107</v>
+        <v>0.9978288384625245</v>
       </c>
       <c r="K69" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.95621331041075</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3953991896554</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R69" t="n">
-        <v>201.5489976573548</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,31 +4967,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.947639413852502</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D70" t="n">
-        <v>113.398817944351</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.956213334210594</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3953992007298</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G70" t="n">
-        <v>201.5489976573657</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H70" t="n">
-        <v>1.025023219909336</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1695371905287083</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J70" t="n">
-        <v>0.99872257162652</v>
+        <v>0.9985881288505732</v>
       </c>
       <c r="K70" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.956213334210594</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3953992007298</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R70" t="n">
-        <v>201.5489976573657</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.947639413852502</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D71" t="n">
-        <v>113.398817944351</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.956213334210594</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3953992007298</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G71" t="n">
-        <v>201.5489976573657</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H71" t="n">
-        <v>1.025023219909336</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1695371905287083</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9993528637664086</v>
+        <v>0.8656475494297885</v>
       </c>
       <c r="K71" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.956213334210594</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3953992007298</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R71" t="n">
-        <v>201.5489976573657</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,31 +5097,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.947639413852502</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D72" t="n">
-        <v>113.398817944351</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.956213334210594</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3953992007298</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G72" t="n">
-        <v>201.5489976573657</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H72" t="n">
-        <v>1.025023219909336</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1695371905287083</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5857863836227353</v>
+        <v>0.5355869819050061</v>
       </c>
       <c r="K72" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.956213334210594</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3953992007298</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R72" t="n">
-        <v>201.5489976573657</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,31 +5162,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.947639407982049</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3988179530972</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.956213318511028</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3953992133953</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G73" t="n">
-        <v>201.5489976573658</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H73" t="n">
-        <v>1.025022044824369</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9998866396898476</v>
+        <v>0.9997492092380647</v>
       </c>
       <c r="K73" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.956213318511028</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3953992133953</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R73" t="n">
-        <v>201.5489976573658</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,31 +5227,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G74" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H74" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9999449135370782</v>
+        <v>0.999793013708785</v>
       </c>
       <c r="K74" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R74" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,31 +5292,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G75" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H75" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9999801380222642</v>
+        <v>0.9999097936794814</v>
       </c>
       <c r="K75" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R75" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,31 +5357,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G76" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H76" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J76" t="n">
-        <v>0.999988821370928</v>
+        <v>0.9999513807651238</v>
       </c>
       <c r="K76" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R76" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,31 +5422,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G77" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H77" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9999994362404604</v>
+        <v>0.9999999999996565</v>
       </c>
       <c r="K77" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R77" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,31 +5487,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G78" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H78" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9999997689161783</v>
+        <v>0.9999999999996696</v>
       </c>
       <c r="K78" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R78" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G79" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H79" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J79" t="n">
-        <v>0.999999872235514</v>
+        <v>0.9999999999997684</v>
       </c>
       <c r="K79" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R79" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,31 +5617,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G80" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H80" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9999999767404885</v>
+        <v>0.9999999999998301</v>
       </c>
       <c r="K80" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R80" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,31 +5682,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G81" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H81" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9493732421534433</v>
+        <v>0.9999999999998515</v>
       </c>
       <c r="K81" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R81" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,31 +5747,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G82" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H82" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5854275450226638</v>
+        <v>0.5857864397965615</v>
       </c>
       <c r="K82" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R82" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,31 +5812,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G83" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H83" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999999999452</v>
+        <v>0.999999999999996</v>
       </c>
       <c r="K83" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R83" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,31 +5877,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G84" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H84" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999999498</v>
+        <v>0.9999999999999964</v>
       </c>
       <c r="K84" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R84" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,31 +5942,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G85" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H85" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999999498</v>
+        <v>0.9999999999999973</v>
       </c>
       <c r="K85" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R85" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G86" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H86" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J86" t="n">
-        <v>0.999999999999956</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="K86" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R86" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,31 +6072,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G87" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H87" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999999999999696</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="K87" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R87" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,31 +6137,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G88" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H88" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999999999999765</v>
+        <v>0.9999999999999991</v>
       </c>
       <c r="K88" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R88" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,31 +6202,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G89" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H89" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9999999999999765</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K89" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R89" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,31 +6267,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G90" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H90" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J90" t="n">
-        <v>0.999999999999978</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K90" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R90" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,31 +6332,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G91" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H91" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9999999999999885</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K91" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R91" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,31 +6397,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G92" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H92" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5857864397736966</v>
+        <v>0.535898387456841</v>
       </c>
       <c r="K92" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R92" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,31 +6462,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G93" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H93" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K93" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R93" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,31 +6527,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G94" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H94" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9086001209088197</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R94" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,31 +6592,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G95" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H95" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9820064438602405</v>
+        <v>0.9227085194931993</v>
       </c>
       <c r="K95" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R95" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,31 +6657,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G96" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H96" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J96" t="n">
-        <v>0.8754730738273039</v>
+        <v>0.9799563927419309</v>
       </c>
       <c r="K96" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R96" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,31 +6722,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G97" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H97" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J97" t="n">
-        <v>0.971293993302515</v>
+        <v>0.9878913385842291</v>
       </c>
       <c r="K97" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R97" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,31 +6787,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G98" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H98" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J98" t="n">
-        <v>0.983947528783786</v>
+        <v>0.9978436043673472</v>
       </c>
       <c r="K98" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R98" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,31 +6852,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G99" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H99" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9862543251369094</v>
+        <v>0.9983833698819292</v>
       </c>
       <c r="K99" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R99" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,31 +6917,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G100" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H100" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9939487972356729</v>
+        <v>0.9985145402083293</v>
       </c>
       <c r="K100" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R100" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,31 +6982,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G101" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H101" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9966823795891645</v>
+        <v>0.9445522083896909</v>
       </c>
       <c r="K101" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R101" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,31 +7047,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G102" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H102" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5857823546937331</v>
+        <v>0.5358944022548114</v>
       </c>
       <c r="K102" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R102" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,31 +7112,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G103" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H103" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9999634286141803</v>
+        <v>0.9995750705632197</v>
       </c>
       <c r="K103" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R103" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,31 +7177,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G104" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H104" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9999880548484925</v>
+        <v>0.9997482369213039</v>
       </c>
       <c r="K104" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R104" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,31 +7242,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G105" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H105" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9999951691061558</v>
+        <v>0.9999439471119329</v>
       </c>
       <c r="K105" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R105" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,31 +7307,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G106" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H106" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9999958064887428</v>
+        <v>0.999972593527977</v>
       </c>
       <c r="K106" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R106" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,31 +7372,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G107" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H107" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9999987359059438</v>
+        <v>0.9999827715042801</v>
       </c>
       <c r="K107" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R107" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,31 +7437,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G108" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H108" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9999993430781365</v>
+        <v>0.9999986301489012</v>
       </c>
       <c r="K108" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R108" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G109" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H109" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9999995833284396</v>
+        <v>0.9999996333715658</v>
       </c>
       <c r="K109" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R109" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,31 +7567,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G110" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H110" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J110" t="n">
-        <v>0.999999760980041</v>
+        <v>0.9999996702934192</v>
       </c>
       <c r="K110" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R110" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,31 +7632,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G111" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H111" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9177808655512067</v>
+        <v>0.9999997036332046</v>
       </c>
       <c r="K111" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R111" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,31 +7697,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G112" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H112" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5857168279982921</v>
+        <v>0.585786439796559</v>
       </c>
       <c r="K112" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R112" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,31 +7762,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G113" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H113" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9999999863388491</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K113" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R113" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,31 +7827,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G114" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H114" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9999999933967803</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K114" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R114" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,31 +7892,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G115" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H115" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9999999989557551</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K115" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R115" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,31 +7957,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D116" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G116" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H116" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9999999999999991</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K116" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R116" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G117" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H117" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K117" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R117" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,31 +8087,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G118" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H118" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K118" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R118" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,31 +8152,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G119" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H119" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K119" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R119" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,31 +8217,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G120" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H120" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K120" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R120" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,31 +8282,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.947639411281891</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3988179391084</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G121" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H121" t="n">
-        <v>1.025021230944155</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1695371905287084</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K121" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.956213315003089</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3953992021211</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R121" t="n">
-        <v>201.5489976573655</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,31 +8347,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G122" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H122" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857864397736966</v>
+        <v>0.535898387456841</v>
       </c>
       <c r="K122" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R122" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,31 +8412,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G123" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H123" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K123" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R123" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,31 +8477,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G124" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H124" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J124" t="n">
-        <v>0.8550773799756022</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R124" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,31 +8542,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G125" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H125" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9662654968845387</v>
+        <v>0.9256966345004899</v>
       </c>
       <c r="K125" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R125" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,31 +8607,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G126" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H126" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9915725541349829</v>
+        <v>0.9656855632977244</v>
       </c>
       <c r="K126" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R126" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,31 +8672,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G127" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H127" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9117151042237767</v>
+        <v>0.9843340874897724</v>
       </c>
       <c r="K127" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R127" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,31 +8737,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G128" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H128" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9826505684313107</v>
+        <v>0.9924194168932914</v>
       </c>
       <c r="K128" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R128" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,31 +8802,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G129" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H129" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9965598155465272</v>
+        <v>0.992814791634261</v>
       </c>
       <c r="K129" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R129" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G130" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H130" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9982248651925838</v>
+        <v>0.9979573820217965</v>
       </c>
       <c r="K130" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R130" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,31 +8932,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G131" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H131" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9989820295679913</v>
+        <v>0.9461242876202979</v>
       </c>
       <c r="K131" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R131" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G132" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H132" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5857862934277519</v>
+        <v>0.5358191361502194</v>
       </c>
       <c r="K132" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R132" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,31 +9062,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D133" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G133" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H133" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9997055375226472</v>
+        <v>0.9989885268098306</v>
       </c>
       <c r="K133" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R133" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,31 +9127,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D134" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G134" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H134" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9997319207326829</v>
+        <v>0.9992879136034222</v>
       </c>
       <c r="K134" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R134" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,31 +9192,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D135" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G135" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H135" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9998241296833204</v>
+        <v>0.9994887975722302</v>
       </c>
       <c r="K135" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R135" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,31 +9257,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D136" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G136" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H136" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9998848873072776</v>
+        <v>0.9995485182102001</v>
       </c>
       <c r="K136" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R136" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,31 +9322,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D137" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G137" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H137" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9999228288246657</v>
+        <v>0.9997356374062648</v>
       </c>
       <c r="K137" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R137" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D138" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G138" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H138" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J138" t="n">
-        <v>0.999960021041725</v>
+        <v>0.9999081856025579</v>
       </c>
       <c r="K138" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R138" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,31 +9452,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D139" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G139" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H139" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9999716998665977</v>
+        <v>0.9999552086564912</v>
       </c>
       <c r="K139" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R139" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,31 +9517,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D140" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G140" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H140" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9999975554870202</v>
+        <v>0.9999632223915842</v>
       </c>
       <c r="K140" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R140" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,31 +9582,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D141" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G141" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H141" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9237927592731633</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K141" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R141" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,31 +9647,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D142" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G142" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H142" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857208380447377</v>
+        <v>0.5857864397965615</v>
       </c>
       <c r="K142" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R142" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D143" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G143" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H143" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K143" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R143" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,31 +9777,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D144" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G144" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H144" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K144" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R144" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,31 +9842,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D145" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G145" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H145" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K145" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R145" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,31 +9907,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D146" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G146" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H146" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K146" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R146" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,31 +9972,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D147" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G147" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H147" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K147" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R147" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,31 +10037,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D148" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G148" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H148" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K148" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R148" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,31 +10102,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G149" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H149" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K149" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R149" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,31 +10167,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G150" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H150" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K150" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R150" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,31 +10232,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.947639408073386</v>
+        <v>-7.819944230538701</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3988179409098</v>
+        <v>113.4743529585126</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="G151" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="H151" t="n">
-        <v>1.025022308690701</v>
+        <v>17.70952384775023</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1695371905287085</v>
+        <v>0.1677505249847725</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K151" t="n">
-        <v>448</v>
+        <v>1426</v>
       </c>
       <c r="L151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.956213320809501</v>
+        <v>-7.956044315201369</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3953992003278</v>
+        <v>113.3908446660412</v>
       </c>
       <c r="R151" t="n">
-        <v>201.5489976573651</v>
+        <v>211.2844463913545</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.153593526264119</v>
+        <v>-7.546622452827696</v>
       </c>
       <c r="D2" t="n">
-        <v>113.3311362201217</v>
+        <v>113.0387077883158</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.927170613095884</v>
       </c>
       <c r="F2" t="n">
-        <v>113.4647183977525</v>
+        <v>113.3287864261403</v>
       </c>
       <c r="G2" t="n">
-        <v>38.13208364715861</v>
+        <v>142.9547122220439</v>
       </c>
       <c r="H2" t="n">
-        <v>23.8222295006408</v>
+        <v>53.02927486634655</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1652105795513159</v>
+        <v>0.1708192615186635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8932631420715178</v>
+        <v>0.9010754493705263</v>
       </c>
       <c r="K2" t="n">
-        <v>1965</v>
+        <v>122</v>
       </c>
       <c r="L2" t="n">
-        <v>1797</v>
+        <v>640</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O2" t="n">
-        <v>113.491685257373</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.927170613095884</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.4647183977525</v>
+        <v>113.3287864261403</v>
       </c>
       <c r="R2" t="n">
-        <v>38.13208364715861</v>
+        <v>142.9547122220439</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.153593526264119</v>
+        <v>-7.546622452827696</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3311362201217</v>
+        <v>113.0387077883158</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.927170613095884</v>
       </c>
       <c r="F3" t="n">
-        <v>113.4647183977525</v>
+        <v>113.3287864261403</v>
       </c>
       <c r="G3" t="n">
-        <v>38.13208364715861</v>
+        <v>142.9547122220439</v>
       </c>
       <c r="H3" t="n">
-        <v>23.8222295006408</v>
+        <v>53.02927486634655</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1652105795513159</v>
+        <v>0.1708192615186635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9607661449415719</v>
+        <v>0.9668106035690233</v>
       </c>
       <c r="K3" t="n">
-        <v>1965</v>
+        <v>122</v>
       </c>
       <c r="L3" t="n">
-        <v>1797</v>
+        <v>640</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O3" t="n">
-        <v>113.491685257373</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.927170613095884</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.4647183977525</v>
+        <v>113.3287864261403</v>
       </c>
       <c r="R3" t="n">
-        <v>38.13208364715861</v>
+        <v>142.9547122220439</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -677,31 +677,31 @@
         <v>44877.10347222222</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.681342702896329</v>
+        <v>-7.546622452827696</v>
       </c>
       <c r="D4" t="n">
-        <v>114.0012689895788</v>
+        <v>113.0387077883158</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.98794731152359</v>
+        <v>-7.927170613095884</v>
       </c>
       <c r="F4" t="n">
-        <v>113.3798956517236</v>
+        <v>113.3287864261403</v>
       </c>
       <c r="G4" t="n">
-        <v>243.480928745101</v>
+        <v>142.9547122220439</v>
       </c>
       <c r="H4" t="n">
-        <v>76.46910851235259</v>
+        <v>53.02927486634655</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1671024779674173</v>
+        <v>0.1708192615186635</v>
       </c>
       <c r="J4" t="n">
-        <v>0.978633083904394</v>
+        <v>0.9836961483388372</v>
       </c>
       <c r="K4" t="n">
-        <v>1342</v>
+        <v>122</v>
       </c>
       <c r="L4" t="n">
         <v>640</v>
@@ -716,13 +716,13 @@
         <v>113.300380121246</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.98794731152359</v>
+        <v>-7.927170613095884</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.3798956517236</v>
+        <v>113.3287864261403</v>
       </c>
       <c r="R4" t="n">
-        <v>243.480928745101</v>
+        <v>142.9547122220439</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -739,55 +739,55 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.681342702896329</v>
+        <v>-7.935851975517988</v>
       </c>
       <c r="D5" t="n">
-        <v>114.0012689895788</v>
+        <v>113.3942293442498</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.98794731152359</v>
+        <v>-7.941387678881207</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3798956517236</v>
+        <v>113.3870731743803</v>
       </c>
       <c r="G5" t="n">
-        <v>243.480928745101</v>
+        <v>232.0081829376357</v>
       </c>
       <c r="H5" t="n">
-        <v>76.46910851235259</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1671024779674173</v>
+        <v>0.1721819325204474</v>
       </c>
       <c r="J5" t="n">
-        <v>0.989046581212189</v>
+        <v>0.9880621742921812</v>
       </c>
       <c r="K5" t="n">
-        <v>1342</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O5" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.98794731152359</v>
+        <v>-7.941387678881207</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3798956517236</v>
+        <v>113.3870731743803</v>
       </c>
       <c r="R5" t="n">
-        <v>243.480928745101</v>
+        <v>232.0081829376357</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -807,28 +807,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.964519385897233</v>
+        <v>-7.961704554939073</v>
       </c>
       <c r="D6" t="n">
-        <v>113.4106735218183</v>
+        <v>113.3982534350317</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.971452281958121</v>
+        <v>-7.968892890147505</v>
       </c>
       <c r="F6" t="n">
-        <v>113.4048894268719</v>
+        <v>113.3927965514963</v>
       </c>
       <c r="G6" t="n">
-        <v>219.56456410293</v>
+        <v>216.93570199387</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1672186874259055</v>
+        <v>0.1725901599184316</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9957192043005308</v>
+        <v>0.9963727598665285</v>
       </c>
       <c r="K6" t="n">
         <v>448</v>
@@ -846,13 +846,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.971452281958121</v>
+        <v>-7.968892890147505</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.4048894268719</v>
+        <v>113.3927965514963</v>
       </c>
       <c r="R6" t="n">
-        <v>219.56456410293</v>
+        <v>216.93570199387</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -872,28 +872,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.964519385897233</v>
+        <v>-7.93658956687915</v>
       </c>
       <c r="D7" t="n">
-        <v>113.4106735218183</v>
+        <v>113.3870702583051</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.971452281958121</v>
+        <v>-7.945029933410848</v>
       </c>
       <c r="F7" t="n">
-        <v>113.4048894268719</v>
+        <v>113.3839356650109</v>
       </c>
       <c r="G7" t="n">
-        <v>219.56456410293</v>
+        <v>200.1943212494579</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1672186874259055</v>
+        <v>0.1728114456828493</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9977514103732356</v>
+        <v>0.9968824388236475</v>
       </c>
       <c r="K7" t="n">
         <v>448</v>
@@ -911,13 +911,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.971452281958121</v>
+        <v>-7.945029933410848</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.4048894268719</v>
+        <v>113.3839356650109</v>
       </c>
       <c r="R7" t="n">
-        <v>219.56456410293</v>
+        <v>200.1943212494579</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.880359410435489</v>
+        <v>-7.948416380319064</v>
       </c>
       <c r="D8" t="n">
-        <v>113.4591383253542</v>
+        <v>113.3947727832923</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.965741615394557</v>
+        <v>-7.956285590732064</v>
       </c>
       <c r="F8" t="n">
-        <v>113.4110304351739</v>
+        <v>113.3903769531832</v>
       </c>
       <c r="G8" t="n">
-        <v>209.1609613537134</v>
+        <v>208.9527941880396</v>
       </c>
       <c r="H8" t="n">
-        <v>10.87240483407599</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1673425146695476</v>
+        <v>0.1728871124503115</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9982314323208495</v>
+        <v>0.9970070712850319</v>
       </c>
       <c r="K8" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.965741615394557</v>
+        <v>-7.956285590732064</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.4110304351739</v>
+        <v>113.3903769531832</v>
       </c>
       <c r="R8" t="n">
-        <v>209.1609613537134</v>
+        <v>208.9527941880396</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.737094606115738</v>
+        <v>-7.93434578483743</v>
       </c>
       <c r="D9" t="n">
-        <v>113.5948209979297</v>
+        <v>113.3899832504918</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.975041791809903</v>
+        <v>-7.943072822438574</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3768457620663</v>
+        <v>113.3877904273481</v>
       </c>
       <c r="G9" t="n">
-        <v>222.2078929740074</v>
+        <v>193.9745843851332</v>
       </c>
       <c r="H9" t="n">
-        <v>35.72876846015237</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1675073423571009</v>
+        <v>0.1728961702570467</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9985717945557602</v>
+        <v>0.9975328296956665</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>448</v>
       </c>
       <c r="L9" t="n">
         <v>448</v>
@@ -1041,13 +1041,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.975041791809903</v>
+        <v>-7.943072822438574</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3768457620663</v>
+        <v>113.3877904273481</v>
       </c>
       <c r="R9" t="n">
-        <v>222.2078929740074</v>
+        <v>193.9745843851332</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,28 +1067,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.935767318647319</v>
+        <v>-7.93434578483743</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3885245192334</v>
+        <v>113.3899832504918</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.943072822438574</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3866694170918</v>
+        <v>113.3877904273481</v>
       </c>
       <c r="G10" t="n">
-        <v>191.728539425681</v>
+        <v>193.9745843851332</v>
       </c>
       <c r="H10" t="n">
-        <v>1.005033039094724</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1676643490030086</v>
+        <v>0.1728961702570467</v>
       </c>
       <c r="J10" t="n">
-        <v>0.998313470363861</v>
+        <v>0.9985079052392184</v>
       </c>
       <c r="K10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.943072822438574</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3866694170918</v>
+        <v>113.3877904273481</v>
       </c>
       <c r="R10" t="n">
-        <v>191.728539425681</v>
+        <v>193.9745843851332</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,28 +1132,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.935767318647319</v>
+        <v>-7.946004835280128</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3885245192334</v>
+        <v>113.3870632100484</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.953730407035009</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3866694170918</v>
+        <v>113.3824149000138</v>
       </c>
       <c r="G11" t="n">
-        <v>191.728539425681</v>
+        <v>210.7902234313149</v>
       </c>
       <c r="H11" t="n">
-        <v>1.005033039094724</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1676643490030086</v>
+        <v>0.1729028126082959</v>
       </c>
       <c r="J11" t="n">
-        <v>0.998164544411142</v>
+        <v>0.9985390735139615</v>
       </c>
       <c r="K11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.953730407035009</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3866694170918</v>
+        <v>113.3824149000138</v>
       </c>
       <c r="R11" t="n">
-        <v>191.728539425681</v>
+        <v>210.7902234313149</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,28 +1197,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.935767318647319</v>
+        <v>-7.941147373148163</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3885245192334</v>
+        <v>113.3905914296667</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.949452260563246</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3866694170918</v>
+        <v>113.3871073640762</v>
       </c>
       <c r="G12" t="n">
-        <v>191.728539425681</v>
+        <v>202.5622880881011</v>
       </c>
       <c r="H12" t="n">
-        <v>1.005033039094724</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1676643490030086</v>
+        <v>0.1729058436499597</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857851399430662</v>
+        <v>0.585785671207193</v>
       </c>
       <c r="K12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.949452260563246</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3866694170918</v>
+        <v>113.3871073640762</v>
       </c>
       <c r="R12" t="n">
-        <v>191.728539425681</v>
+        <v>202.5622880881011</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,28 +1262,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.935767318647319</v>
+        <v>-7.942247698770834</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3885245192334</v>
+        <v>113.3913374779526</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.950390375560152</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3866694170918</v>
+        <v>113.387482776141</v>
       </c>
       <c r="G13" t="n">
-        <v>191.728539425681</v>
+        <v>205.1192371889614</v>
       </c>
       <c r="H13" t="n">
-        <v>1.005033039094724</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1676643490030086</v>
+        <v>0.1729082741409874</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9995600914473736</v>
+        <v>0.9998279464302917</v>
       </c>
       <c r="K13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.944617085538523</v>
+        <v>-7.950390375560152</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3866694170918</v>
+        <v>113.387482776141</v>
       </c>
       <c r="R13" t="n">
-        <v>191.728539425681</v>
+        <v>205.1192371889614</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,28 +1327,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.953129251333727</v>
+        <v>-7.93497743739591</v>
       </c>
       <c r="D14" t="n">
-        <v>113.3844340566845</v>
+        <v>113.4025459960516</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.96159401390791</v>
+        <v>-7.954294895968587</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3813671378137</v>
+        <v>113.3909535689302</v>
       </c>
       <c r="G14" t="n">
-        <v>199.7391643242391</v>
+        <v>210.7239648155063</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2.498749005082724</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1676799872556706</v>
+        <v>0.1729180726070106</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9995501825280527</v>
+        <v>0.999831281509041</v>
       </c>
       <c r="K14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.96159401390791</v>
+        <v>-7.954294895968587</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3813671378137</v>
+        <v>113.3909535689302</v>
       </c>
       <c r="R14" t="n">
-        <v>199.7391643242391</v>
+        <v>210.7239648155063</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,28 +1392,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.939009198131833</v>
+        <v>-7.92568893273445</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3945681619559</v>
+        <v>113.3966282047625</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.947788669372045</v>
+        <v>-7.951653689720641</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3926002235871</v>
+        <v>113.3851509586955</v>
       </c>
       <c r="G15" t="n">
-        <v>192.5166220666887</v>
+        <v>203.6427942988933</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3.151710413276432</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1677222563889116</v>
+        <v>0.1729194714748303</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9995005090545971</v>
+        <v>0.9999008213182147</v>
       </c>
       <c r="K15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.947788669372045</v>
+        <v>-7.951653689720641</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3926002235871</v>
+        <v>113.3851509586955</v>
       </c>
       <c r="R15" t="n">
-        <v>192.5166220666887</v>
+        <v>203.6427942988933</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,28 +1457,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.939009198131833</v>
+        <v>-7.942136817407444</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3945681619559</v>
+        <v>113.3898792570441</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.947788669372045</v>
+        <v>-7.950380890131098</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3926002235871</v>
+        <v>113.3862509242902</v>
       </c>
       <c r="G16" t="n">
-        <v>192.5166220666887</v>
+        <v>203.5515688352019</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1677222563889116</v>
+        <v>0.1729202711171086</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9994856794333369</v>
+        <v>0.9999365962737594</v>
       </c>
       <c r="K16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.947788669372045</v>
+        <v>-7.950380890131098</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3926002235871</v>
+        <v>113.3862509242902</v>
       </c>
       <c r="R16" t="n">
-        <v>192.5166220666887</v>
+        <v>203.5515688352019</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.820171431912287</v>
+        <v>-7.939918081870034</v>
       </c>
       <c r="D17" t="n">
-        <v>113.4790980232159</v>
+        <v>113.3906717879645</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.956391403530851</v>
+        <v>-7.948635914067584</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3901874188384</v>
+        <v>113.3884419184518</v>
       </c>
       <c r="G17" t="n">
-        <v>212.877492365585</v>
+        <v>194.2154020888845</v>
       </c>
       <c r="H17" t="n">
-        <v>18.03692664051356</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1677279243548565</v>
+        <v>0.1729249322885775</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9994707231730851</v>
+        <v>0.9999307697167897</v>
       </c>
       <c r="K17" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.956391403530851</v>
+        <v>-7.948635914067584</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3901874188384</v>
+        <v>113.3884419184518</v>
       </c>
       <c r="R17" t="n">
-        <v>212.877492365585</v>
+        <v>194.2154020888845</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.821685434947646</v>
+        <v>-7.939918081870034</v>
       </c>
       <c r="D18" t="n">
-        <v>113.4795564308879</v>
+        <v>113.3906717879645</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.957087439487255</v>
+        <v>-7.948635914067584</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3939742751187</v>
+        <v>113.3884419184518</v>
       </c>
       <c r="G18" t="n">
-        <v>212.0438826290271</v>
+        <v>194.2154020888845</v>
       </c>
       <c r="H18" t="n">
-        <v>17.76337138499295</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1677361197601187</v>
+        <v>0.1729249322885775</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9996296794386703</v>
+        <v>0.99992934721306</v>
       </c>
       <c r="K18" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.957087439487255</v>
+        <v>-7.948635914067584</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3939742751187</v>
+        <v>113.3884419184518</v>
       </c>
       <c r="R18" t="n">
-        <v>212.0438826290271</v>
+        <v>194.2154020888845</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.820857115488852</v>
+        <v>-7.930349921008439</v>
       </c>
       <c r="D19" t="n">
-        <v>113.4758829518708</v>
+        <v>113.3992681218296</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.959677961276572</v>
+        <v>-7.950498956513697</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3915304599795</v>
+        <v>113.3902894328216</v>
       </c>
       <c r="G19" t="n">
-        <v>211.0372417285053</v>
+        <v>203.813233148642</v>
       </c>
       <c r="H19" t="n">
-        <v>18.01648796335714</v>
+        <v>2.448970828607757</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1677422929531031</v>
+        <v>0.1729277700858524</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9997896480607104</v>
+        <v>0.9999320823123063</v>
       </c>
       <c r="K19" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.959677961276572</v>
+        <v>-7.950498956513697</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3915304599795</v>
+        <v>113.3902894328216</v>
       </c>
       <c r="R19" t="n">
-        <v>211.0372417285053</v>
+        <v>203.813233148642</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.821778634334938</v>
+        <v>-7.930349921008439</v>
       </c>
       <c r="D20" t="n">
-        <v>113.473417575924</v>
+        <v>113.3992681218296</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.957703258910239</v>
+        <v>-7.950498956513697</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3901439197127</v>
+        <v>113.3902894328216</v>
       </c>
       <c r="G20" t="n">
-        <v>211.2456215164036</v>
+        <v>203.813233148642</v>
       </c>
       <c r="H20" t="n">
-        <v>17.67941292946428</v>
+        <v>2.448970828607757</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1677488536594211</v>
+        <v>0.1729277700858524</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9999048919404552</v>
+        <v>0.9999381496048059</v>
       </c>
       <c r="K20" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.957703258910239</v>
+        <v>-7.950498956513697</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3901439197127</v>
+        <v>113.3902894328216</v>
       </c>
       <c r="R20" t="n">
-        <v>211.2456215164036</v>
+        <v>203.813233148642</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.821778634334938</v>
+        <v>-7.930784964873674</v>
       </c>
       <c r="D21" t="n">
-        <v>113.473417575924</v>
+        <v>113.3984703493835</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.957703258910239</v>
+        <v>-7.952594025126735</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3901439197127</v>
+        <v>113.3887041865112</v>
       </c>
       <c r="G21" t="n">
-        <v>211.2456215164036</v>
+        <v>203.9170053381945</v>
       </c>
       <c r="H21" t="n">
-        <v>17.67941292946428</v>
+        <v>2.652860949177557</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1677488536594211</v>
+        <v>0.1729281109008081</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9999159316745828</v>
+        <v>0.9999587574651947</v>
       </c>
       <c r="K21" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.957703258910239</v>
+        <v>-7.952594025126735</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3901439197127</v>
+        <v>113.3887041865112</v>
       </c>
       <c r="R21" t="n">
-        <v>211.2456215164036</v>
+        <v>203.9170053381945</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.821778634334938</v>
+        <v>-7.932008453917532</v>
       </c>
       <c r="D22" t="n">
-        <v>113.473417575924</v>
+        <v>113.3988740343873</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.957703258910239</v>
+        <v>-7.951938814901519</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3901439197127</v>
+        <v>113.3899690407818</v>
       </c>
       <c r="G22" t="n">
-        <v>211.2456215164036</v>
+        <v>203.8697286998925</v>
       </c>
       <c r="H22" t="n">
-        <v>17.67941292946428</v>
+        <v>2.423448222911395</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1677488536594211</v>
+        <v>0.1729291017264576</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857864377555499</v>
+        <v>0.5857864391808946</v>
       </c>
       <c r="K22" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.957703258910239</v>
+        <v>-7.951938814901519</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3901439197127</v>
+        <v>113.3899690407818</v>
       </c>
       <c r="R22" t="n">
-        <v>211.2456215164036</v>
+        <v>203.8697286998925</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.820292288014121</v>
+        <v>-7.932008453917532</v>
       </c>
       <c r="D23" t="n">
-        <v>113.4748523605862</v>
+        <v>113.3988740343873</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.956560107230088</v>
+        <v>-7.951938814901519</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3912027264869</v>
+        <v>113.3899690407818</v>
       </c>
       <c r="G23" t="n">
-        <v>211.2960943850779</v>
+        <v>203.8697286998925</v>
       </c>
       <c r="H23" t="n">
-        <v>17.73354305262774</v>
+        <v>2.423448222911395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1677502247827846</v>
+        <v>0.1729291017264576</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999517528933224</v>
+        <v>0.9999927894612668</v>
       </c>
       <c r="K23" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.956560107230088</v>
+        <v>-7.951938814901519</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3912027264869</v>
+        <v>113.3899690407818</v>
       </c>
       <c r="R23" t="n">
-        <v>211.2960943850779</v>
+        <v>203.8697286998925</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.820292288014121</v>
+        <v>-7.930577736145901</v>
       </c>
       <c r="D24" t="n">
-        <v>113.4748523605862</v>
+        <v>113.3992551153185</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.956560107230088</v>
+        <v>-7.95205298962433</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3912027264869</v>
+        <v>113.3896597636311</v>
       </c>
       <c r="G24" t="n">
-        <v>211.2960943850779</v>
+        <v>203.8699177381165</v>
       </c>
       <c r="H24" t="n">
-        <v>17.73354305262774</v>
+        <v>2.611305436908566</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1677502247827846</v>
+        <v>0.17292917205435</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9999542111806111</v>
+        <v>0.999990885061856</v>
       </c>
       <c r="K24" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.956560107230088</v>
+        <v>-7.95205298962433</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3912027264869</v>
+        <v>113.3896597636311</v>
       </c>
       <c r="R24" t="n">
-        <v>211.2960943850779</v>
+        <v>203.8699177381165</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.820292288014121</v>
+        <v>-7.932107078777994</v>
       </c>
       <c r="D25" t="n">
-        <v>113.4748523605862</v>
+        <v>113.3981905387637</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.956560107230088</v>
+        <v>-7.951416616657495</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3912027264869</v>
+        <v>113.3895673430743</v>
       </c>
       <c r="G25" t="n">
-        <v>211.2960943850779</v>
+        <v>203.8589185981129</v>
       </c>
       <c r="H25" t="n">
-        <v>17.73354305262774</v>
+        <v>2.347762411552878</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1677502247827846</v>
+        <v>0.1729292708802717</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999577965821367</v>
+        <v>0.9999904764196226</v>
       </c>
       <c r="K25" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.956560107230088</v>
+        <v>-7.951416616657495</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3912027264869</v>
+        <v>113.3895673430743</v>
       </c>
       <c r="R25" t="n">
-        <v>211.2960943850779</v>
+        <v>203.8589185981129</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.819940871900245</v>
+        <v>-7.932107078777994</v>
       </c>
       <c r="D26" t="n">
-        <v>113.4749863433088</v>
+        <v>113.3981905387637</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.9563831988085</v>
+        <v>-7.951416616657495</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3912870782043</v>
+        <v>113.3895673430743</v>
       </c>
       <c r="G26" t="n">
-        <v>211.2786450903438</v>
+        <v>203.8589185981129</v>
       </c>
       <c r="H26" t="n">
-        <v>17.75296694298588</v>
+        <v>2.347762411552878</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1677503366083224</v>
+        <v>0.1729292708802717</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9999599513596702</v>
+        <v>0.9999904320720423</v>
       </c>
       <c r="K26" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.9563831988085</v>
+        <v>-7.951416616657495</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3912870782043</v>
+        <v>113.3895673430743</v>
       </c>
       <c r="R26" t="n">
-        <v>211.2786450903438</v>
+        <v>203.8589185981129</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.820491154441903</v>
+        <v>-7.931647608770078</v>
       </c>
       <c r="D27" t="n">
-        <v>113.4743227068649</v>
+        <v>113.3984024602745</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.956579237347988</v>
+        <v>-7.951588459052373</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3908250107408</v>
+        <v>113.3894976567213</v>
       </c>
       <c r="G27" t="n">
-        <v>211.2834290798496</v>
+        <v>203.858140797816</v>
       </c>
       <c r="H27" t="n">
-        <v>17.70777101363248</v>
+        <v>2.424506737041943</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1677504109867626</v>
+        <v>0.1729293367946654</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999628098953455</v>
+        <v>0.9999902991749878</v>
       </c>
       <c r="K27" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.956579237347988</v>
+        <v>-7.951588459052373</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3908250107408</v>
+        <v>113.3894976567213</v>
       </c>
       <c r="R27" t="n">
-        <v>211.2834290798496</v>
+        <v>203.858140797816</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.819755694371882</v>
+        <v>-7.93121009264768</v>
       </c>
       <c r="D28" t="n">
-        <v>113.4744042251574</v>
+        <v>113.3985207687868</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.956219313107773</v>
+        <v>-7.951969419520295</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3906672266203</v>
+        <v>113.3892506956288</v>
       </c>
       <c r="G28" t="n">
-        <v>211.2861467123135</v>
+        <v>203.8575911452319</v>
       </c>
       <c r="H28" t="n">
-        <v>17.7571506059177</v>
+        <v>2.524010932063897</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1677504796626317</v>
+        <v>0.1729293645839448</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9999667117543988</v>
+        <v>0.9999900946689858</v>
       </c>
       <c r="K28" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.956219313107773</v>
+        <v>-7.951969419520295</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3906672266203</v>
+        <v>113.3892506956288</v>
       </c>
       <c r="R28" t="n">
-        <v>211.2861467123135</v>
+        <v>203.8575911452319</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.819913010741498</v>
+        <v>-7.931757624372517</v>
       </c>
       <c r="D29" t="n">
-        <v>113.4742715653347</v>
+        <v>113.3982389282071</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.955881672323675</v>
+        <v>-7.951738748625412</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3908429298032</v>
+        <v>113.3893168277212</v>
       </c>
       <c r="G29" t="n">
-        <v>211.2847570783266</v>
+        <v>203.8564989784691</v>
       </c>
       <c r="H29" t="n">
-        <v>17.69248017771793</v>
+        <v>2.429372679444343</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1677505114083017</v>
+        <v>0.1729293790105</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9999686749192888</v>
+        <v>0.9999900821510528</v>
       </c>
       <c r="K29" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.955881672323675</v>
+        <v>-7.951738748625412</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3908429298032</v>
+        <v>113.3893168277212</v>
       </c>
       <c r="R29" t="n">
-        <v>211.2847570783266</v>
+        <v>203.8564989784691</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.819913010741498</v>
+        <v>-7.931793524103727</v>
       </c>
       <c r="D30" t="n">
-        <v>113.4742715653347</v>
+        <v>113.398524857622</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.955881672323675</v>
+        <v>-7.951960348478597</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3908429298032</v>
+        <v>113.3895201305768</v>
       </c>
       <c r="G30" t="n">
-        <v>211.2847570783266</v>
+        <v>203.8557959535809</v>
       </c>
       <c r="H30" t="n">
-        <v>17.69248017771793</v>
+        <v>2.451937531638806</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1677505114083017</v>
+        <v>0.1729293811710772</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9999705206033859</v>
+        <v>0.9999900865518883</v>
       </c>
       <c r="K30" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.955881672323675</v>
+        <v>-7.951960348478597</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3908429298032</v>
+        <v>113.3895201305768</v>
       </c>
       <c r="R30" t="n">
-        <v>211.2847570783266</v>
+        <v>203.8557959535809</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,31 +2432,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.819913010741498</v>
+        <v>-7.931940464439733</v>
       </c>
       <c r="D31" t="n">
-        <v>113.4742715653347</v>
+        <v>113.398504731382</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.955881672323675</v>
+        <v>-7.951925328827847</v>
       </c>
       <c r="F31" t="n">
-        <v>113.3908429298032</v>
+        <v>113.3895809364715</v>
       </c>
       <c r="G31" t="n">
-        <v>211.2847570783266</v>
+        <v>203.8565471586225</v>
       </c>
       <c r="H31" t="n">
-        <v>17.69248017771793</v>
+        <v>2.429828323811683</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1677505114083017</v>
+        <v>0.1729293892000711</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9999732440696784</v>
+        <v>0.9999900457593704</v>
       </c>
       <c r="K31" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.955881672323675</v>
+        <v>-7.951925328827847</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.3908429298032</v>
+        <v>113.3895809364715</v>
       </c>
       <c r="R31" t="n">
-        <v>211.2847570783266</v>
+        <v>203.8565471586225</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.820049379604276</v>
+        <v>-7.931773990225187</v>
       </c>
       <c r="D32" t="n">
-        <v>113.4743753780785</v>
+        <v>113.3984977788391</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.956160745713864</v>
+        <v>-7.951839282531324</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3908594294204</v>
+        <v>113.3895380931881</v>
       </c>
       <c r="G32" t="n">
-        <v>211.2846625053665</v>
+        <v>203.8564978641921</v>
       </c>
       <c r="H32" t="n">
-        <v>17.71103251982715</v>
+        <v>2.439606144037621</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1677505171536066</v>
+        <v>0.1729293908671587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5358983873027017</v>
+        <v>0.5358983873522942</v>
       </c>
       <c r="K32" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.956160745713864</v>
+        <v>-7.951839282531324</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3908594294204</v>
+        <v>113.3895380931881</v>
       </c>
       <c r="R32" t="n">
-        <v>211.2846625053665</v>
+        <v>203.8564978641921</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,31 +2562,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.819945106915402</v>
+        <v>-7.931789066852779</v>
       </c>
       <c r="D33" t="n">
-        <v>113.4743430371565</v>
+        <v>113.3984218638553</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.956057449920416</v>
+        <v>-7.951908587253786</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3908264775511</v>
+        <v>113.3894379550741</v>
       </c>
       <c r="G33" t="n">
-        <v>211.2846724337639</v>
+        <v>203.8565148803516</v>
       </c>
       <c r="H33" t="n">
-        <v>17.71116149410992</v>
+        <v>2.446199732249556</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1677505216314751</v>
+        <v>0.1729293949969323</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999790791216217</v>
+        <v>0.9999914021220341</v>
       </c>
       <c r="K33" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.956057449920416</v>
+        <v>-7.951908587253786</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3908264775511</v>
+        <v>113.3894379550741</v>
       </c>
       <c r="R33" t="n">
-        <v>211.2846724337639</v>
+        <v>203.8565148803516</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,31 +2627,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.819780433130916</v>
+        <v>-7.931855915499844</v>
       </c>
       <c r="D34" t="n">
-        <v>113.4744679037979</v>
+        <v>113.3983530695536</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.955989486242112</v>
+        <v>-7.951882134917201</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3908925754403</v>
+        <v>113.389410781965</v>
       </c>
       <c r="G34" t="n">
-        <v>211.284501863603</v>
+        <v>203.8566120206795</v>
       </c>
       <c r="H34" t="n">
-        <v>17.72371424113769</v>
+        <v>2.434857652939851</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1677505223748074</v>
+        <v>0.1729293950462735</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8984711064098582</v>
+        <v>0.9999913954557782</v>
       </c>
       <c r="K34" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.955989486242112</v>
+        <v>-7.951882134917201</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3908925754403</v>
+        <v>113.389410781965</v>
       </c>
       <c r="R34" t="n">
-        <v>211.284501863603</v>
+        <v>203.8566120206795</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,31 +2692,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.819826381280532</v>
+        <v>-7.931801750585626</v>
       </c>
       <c r="D35" t="n">
-        <v>113.4744270578765</v>
+        <v>113.3984319364823</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.955996867090533</v>
+        <v>-7.951922779719037</v>
       </c>
       <c r="F35" t="n">
-        <v>113.3908755155571</v>
+        <v>113.389447326493</v>
       </c>
       <c r="G35" t="n">
-        <v>211.2844647409294</v>
+        <v>203.8565790502952</v>
       </c>
       <c r="H35" t="n">
-        <v>17.71868853075931</v>
+        <v>2.446384381705311</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1677505236183363</v>
+        <v>0.1729293958230111</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9827224821228089</v>
+        <v>0.9999913915138996</v>
       </c>
       <c r="K35" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.955996867090533</v>
+        <v>-7.951922779719037</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3908755155571</v>
+        <v>113.389447326493</v>
       </c>
       <c r="R35" t="n">
-        <v>211.2844647409294</v>
+        <v>203.8565790502952</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,31 +2757,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.819916678768252</v>
+        <v>-7.931783019260528</v>
       </c>
       <c r="D36" t="n">
-        <v>113.4743374901814</v>
+        <v>113.3984266810594</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.956024636507529</v>
+        <v>-7.951887660736961</v>
       </c>
       <c r="F36" t="n">
-        <v>113.3908242854094</v>
+        <v>113.389449388178</v>
       </c>
       <c r="G36" t="n">
-        <v>211.2844723528091</v>
+        <v>203.8565819990369</v>
       </c>
       <c r="H36" t="n">
-        <v>17.71055324001068</v>
+        <v>2.444391959701624</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1677505243429521</v>
+        <v>0.1729293960742822</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9907859383888362</v>
+        <v>0.9999913880388721</v>
       </c>
       <c r="K36" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.956024636507529</v>
+        <v>-7.951887660736961</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.3908242854094</v>
+        <v>113.389449388178</v>
       </c>
       <c r="R36" t="n">
-        <v>211.2844723528091</v>
+        <v>203.8565819990369</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,31 +2822,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.819916678768252</v>
+        <v>-7.93177280134961</v>
       </c>
       <c r="D37" t="n">
-        <v>113.4743374901814</v>
+        <v>113.3984380256375</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.956024636507529</v>
+        <v>-7.951892182829148</v>
       </c>
       <c r="F37" t="n">
-        <v>113.3908242854094</v>
+        <v>113.3894541507235</v>
       </c>
       <c r="G37" t="n">
-        <v>211.2844723528091</v>
+        <v>203.8565821704696</v>
       </c>
       <c r="H37" t="n">
-        <v>17.71055324001068</v>
+        <v>2.446184112153949</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1677505243429521</v>
+        <v>0.1729293961000195</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9922082670921955</v>
+        <v>0.9999907812591602</v>
       </c>
       <c r="K37" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.956024636507529</v>
+        <v>-7.951892182829148</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.3908242854094</v>
+        <v>113.3894541507235</v>
       </c>
       <c r="R37" t="n">
-        <v>211.2844723528091</v>
+        <v>203.8565821704696</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,31 +2887,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.819913542706947</v>
+        <v>-7.93177280134961</v>
       </c>
       <c r="D38" t="n">
-        <v>113.4743358276042</v>
+        <v>113.3984380256375</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.956018156641701</v>
+        <v>-7.951892182829148</v>
       </c>
       <c r="F38" t="n">
-        <v>113.390824765675</v>
+        <v>113.3894541507235</v>
       </c>
       <c r="G38" t="n">
-        <v>211.2844450430931</v>
+        <v>203.8565821704696</v>
       </c>
       <c r="H38" t="n">
-        <v>17.71011298100021</v>
+        <v>2.446184112153949</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1677505245925004</v>
+        <v>0.1729293961000195</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9964803482636542</v>
+        <v>0.9267566683981214</v>
       </c>
       <c r="K38" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.956018156641701</v>
+        <v>-7.951892182829148</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.390824765675</v>
+        <v>113.3894541507235</v>
       </c>
       <c r="R38" t="n">
-        <v>211.2844450430931</v>
+        <v>203.8565821704696</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,31 +2952,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.819919016625466</v>
+        <v>-7.93176915869884</v>
       </c>
       <c r="D39" t="n">
-        <v>113.4743501856611</v>
+        <v>113.3984412055428</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.956029453661562</v>
+        <v>-7.951891194217459</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3908355421293</v>
+        <v>113.3894561445736</v>
       </c>
       <c r="G39" t="n">
-        <v>211.2844469147554</v>
+        <v>203.8565844521218</v>
       </c>
       <c r="H39" t="n">
-        <v>17.71087108934304</v>
+        <v>2.446506844050216</v>
       </c>
       <c r="I39" t="n">
-        <v>0.167750524872109</v>
+        <v>0.1729293961150859</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9987209083506134</v>
+        <v>0.9778149966403997</v>
       </c>
       <c r="K39" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.956029453661562</v>
+        <v>-7.951891194217459</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3908355421293</v>
+        <v>113.3894561445736</v>
       </c>
       <c r="R39" t="n">
-        <v>211.2844469147554</v>
+        <v>203.8565844521218</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,31 +3017,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.819919019040989</v>
+        <v>-7.931770970907572</v>
       </c>
       <c r="D40" t="n">
-        <v>113.4743573941038</v>
+        <v>113.3984438261265</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.956041518281994</v>
+        <v>-7.951899314486158</v>
       </c>
       <c r="F40" t="n">
-        <v>113.390835334806</v>
+        <v>113.3894559481714</v>
       </c>
       <c r="G40" t="n">
-        <v>211.2844504892403</v>
+        <v>203.8565846090159</v>
       </c>
       <c r="H40" t="n">
-        <v>17.71244140695482</v>
+        <v>2.447273806495648</v>
       </c>
       <c r="I40" t="n">
-        <v>0.167750524894677</v>
+        <v>0.1729293961263566</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9988379271429599</v>
+        <v>0.9906685468469046</v>
       </c>
       <c r="K40" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.956041518281994</v>
+        <v>-7.951899314486158</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.390835334806</v>
+        <v>113.3894559481714</v>
       </c>
       <c r="R40" t="n">
-        <v>211.2844504892403</v>
+        <v>203.8565846090159</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,31 +3082,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.819949840696204</v>
+        <v>-7.931769075076756</v>
       </c>
       <c r="D41" t="n">
-        <v>113.4743499531854</v>
+        <v>113.3984405176029</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.956050320027701</v>
+        <v>-7.951894521287291</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3908414188745</v>
+        <v>113.3894539338488</v>
       </c>
       <c r="G41" t="n">
-        <v>211.2844459156414</v>
+        <v>203.8565838245593</v>
       </c>
       <c r="H41" t="n">
-        <v>17.70957511710337</v>
+        <v>2.446921517933479</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1677505249619608</v>
+        <v>0.1729293961322074</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9189120494874442</v>
+        <v>0.9982179926395743</v>
       </c>
       <c r="K41" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.956050320027701</v>
+        <v>-7.951894521287291</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3908414188745</v>
+        <v>113.3894539338488</v>
       </c>
       <c r="R41" t="n">
-        <v>211.2844459156414</v>
+        <v>203.8565838245593</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.819949840696204</v>
+        <v>-7.931771020923305</v>
       </c>
       <c r="D42" t="n">
-        <v>113.4743499531854</v>
+        <v>113.3984407375584</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.956050320027701</v>
+        <v>-7.951899667095491</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3908414188745</v>
+        <v>113.3894527248125</v>
       </c>
       <c r="G42" t="n">
-        <v>211.2844459156414</v>
+        <v>203.8565838210217</v>
       </c>
       <c r="H42" t="n">
-        <v>17.70957511710337</v>
+        <v>2.447310582165722</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1677505249619608</v>
+        <v>0.1729293961351877</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5856903107367535</v>
+        <v>0.5835171694214609</v>
       </c>
       <c r="K42" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.956050320027701</v>
+        <v>-7.951899667095491</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3908414188745</v>
+        <v>113.3894527248125</v>
       </c>
       <c r="R42" t="n">
-        <v>211.2844459156414</v>
+        <v>203.8565838210217</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.819948821360185</v>
+        <v>-7.931770601047662</v>
       </c>
       <c r="D43" t="n">
-        <v>113.4743526749209</v>
+        <v>113.3984406295844</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.956049887466011</v>
+        <v>-7.951897814263927</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3908437807214</v>
+        <v>113.3894532566198</v>
       </c>
       <c r="G43" t="n">
-        <v>211.2844458922354</v>
+        <v>203.8565840990742</v>
       </c>
       <c r="H43" t="n">
-        <v>17.70965146907468</v>
+        <v>2.447136362833599</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1677505249667006</v>
+        <v>0.1729293961404928</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9995315524768775</v>
+        <v>0.9995982112534746</v>
       </c>
       <c r="K43" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.956049887466011</v>
+        <v>-7.951897814263927</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3908437807214</v>
+        <v>113.3894532566198</v>
       </c>
       <c r="R43" t="n">
-        <v>211.2844458922354</v>
+        <v>203.8565840990742</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,31 +3277,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.819946780467791</v>
+        <v>-7.931770601047662</v>
       </c>
       <c r="D44" t="n">
-        <v>113.4743536383168</v>
+        <v>113.3984406295844</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.956048865670478</v>
+        <v>-7.951897814263927</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3908441170957</v>
+        <v>113.3894532566198</v>
       </c>
       <c r="G44" t="n">
-        <v>211.284446469655</v>
+        <v>203.8565840990742</v>
       </c>
       <c r="H44" t="n">
-        <v>17.70978419161298</v>
+        <v>2.447136362833599</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1677505249763809</v>
+        <v>0.1729293961404928</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9995314812394315</v>
+        <v>0.9995982112117378</v>
       </c>
       <c r="K44" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.956048865670478</v>
+        <v>-7.951897814263927</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3908441170957</v>
+        <v>113.3894532566198</v>
       </c>
       <c r="R44" t="n">
-        <v>211.284446469655</v>
+        <v>203.8565840990742</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,31 +3342,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.819945685632129</v>
+        <v>-7.931770601047662</v>
       </c>
       <c r="D45" t="n">
-        <v>113.4743544337349</v>
+        <v>113.3984406295844</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.956044577328535</v>
+        <v>-7.951897814263927</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3908468733896</v>
+        <v>113.3894532566198</v>
       </c>
       <c r="G45" t="n">
-        <v>211.2844463435698</v>
+        <v>203.8565840990742</v>
       </c>
       <c r="H45" t="n">
-        <v>17.70936859915307</v>
+        <v>2.447136362833599</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1677505249824123</v>
+        <v>0.1729293961404928</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9998796960920875</v>
+        <v>0.9999920456881926</v>
       </c>
       <c r="K45" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.956044577328535</v>
+        <v>-7.951897814263927</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3908468733896</v>
+        <v>113.3894532566198</v>
       </c>
       <c r="R45" t="n">
-        <v>211.2844463435698</v>
+        <v>203.8565840990742</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,31 +3407,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.819945685632129</v>
+        <v>-7.931770536240147</v>
       </c>
       <c r="D46" t="n">
-        <v>113.4743544337349</v>
+        <v>113.3984385941497</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.956044577328535</v>
+        <v>-7.951897683772569</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3908468733896</v>
+        <v>113.3894512504833</v>
       </c>
       <c r="G46" t="n">
-        <v>211.2844463435698</v>
+        <v>203.8565841803976</v>
       </c>
       <c r="H46" t="n">
-        <v>17.70936859915307</v>
+        <v>2.447128378261846</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1677505249824123</v>
+        <v>0.1729293961421506</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9998978592328058</v>
+        <v>0.9999920457872538</v>
       </c>
       <c r="K46" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.956044577328535</v>
+        <v>-7.951897683772569</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3908468733896</v>
+        <v>113.3894512504833</v>
       </c>
       <c r="R46" t="n">
-        <v>211.2844463435698</v>
+        <v>203.8565841803976</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.819938185657015</v>
+        <v>-7.931770382945968</v>
       </c>
       <c r="D47" t="n">
-        <v>113.4743562717908</v>
+        <v>113.3984388208919</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.956044011649417</v>
+        <v>-7.95189825011831</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3908444563121</v>
+        <v>113.3894511558943</v>
       </c>
       <c r="G47" t="n">
-        <v>211.28444642171</v>
+        <v>203.8565841274296</v>
       </c>
       <c r="H47" t="n">
-        <v>17.71027096762408</v>
+        <v>2.447215873997075</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1677505249842974</v>
+        <v>0.1729293961422012</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999150699891597</v>
+        <v>0.9999920459265104</v>
       </c>
       <c r="K47" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.956044011649417</v>
+        <v>-7.95189825011831</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3908444563121</v>
+        <v>113.3894511558943</v>
       </c>
       <c r="R47" t="n">
-        <v>211.28444642171</v>
+        <v>203.8565841274296</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,31 +3537,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.819938185657015</v>
+        <v>-7.931770140189308</v>
       </c>
       <c r="D48" t="n">
-        <v>113.4743562717908</v>
+        <v>113.39843876043</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.956044011649417</v>
+        <v>-7.951897887678641</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3908444563121</v>
+        <v>113.3894511488771</v>
       </c>
       <c r="G48" t="n">
-        <v>211.28444642171</v>
+        <v>203.8565841401505</v>
       </c>
       <c r="H48" t="n">
-        <v>17.71027096762408</v>
+        <v>2.447201322691989</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1677505249842974</v>
+        <v>0.1729293961425682</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999417435580474</v>
+        <v>0.9999920459690085</v>
       </c>
       <c r="K48" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.956044011649417</v>
+        <v>-7.951897887678641</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3908444563121</v>
+        <v>113.3894511488771</v>
       </c>
       <c r="R48" t="n">
-        <v>211.28444642171</v>
+        <v>203.8565841401505</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,31 +3602,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.819938185657015</v>
+        <v>-7.931769919655502</v>
       </c>
       <c r="D49" t="n">
-        <v>113.4743562717908</v>
+        <v>113.3984388319867</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.956044011649417</v>
+        <v>-7.951897569154091</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3908444563121</v>
+        <v>113.3894512641988</v>
       </c>
       <c r="G49" t="n">
-        <v>211.28444642171</v>
+        <v>203.8565841349952</v>
       </c>
       <c r="H49" t="n">
-        <v>17.71027096762408</v>
+        <v>2.447189408482767</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1677505249842974</v>
+        <v>0.1729293961425687</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999775136166025</v>
+        <v>0.9999920460007939</v>
       </c>
       <c r="K49" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.956044011649417</v>
+        <v>-7.951897569154091</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3908444563121</v>
+        <v>113.3894512641988</v>
       </c>
       <c r="R49" t="n">
-        <v>211.28444642171</v>
+        <v>203.8565841349952</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,31 +3667,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.819944203733251</v>
+        <v>-7.931770067374679</v>
       </c>
       <c r="D50" t="n">
-        <v>113.4743529459396</v>
+        <v>113.3984386697434</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.956043971005837</v>
+        <v>-7.951897724068272</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3908448482526</v>
+        <v>113.3894510987346</v>
       </c>
       <c r="G50" t="n">
-        <v>211.2844464039892</v>
+        <v>203.8565841461113</v>
       </c>
       <c r="H50" t="n">
-        <v>17.7094825483836</v>
+        <v>2.447190283490409</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1677505249845407</v>
+        <v>0.1729293961426482</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9999889369149186</v>
+        <v>0.999992046033455</v>
       </c>
       <c r="K50" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.956043971005837</v>
+        <v>-7.951897724068272</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3908448482526</v>
+        <v>113.3894510987346</v>
       </c>
       <c r="R50" t="n">
-        <v>211.2844464039892</v>
+        <v>203.8565841461113</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.819943070603043</v>
+        <v>-7.931770544234709</v>
       </c>
       <c r="D51" t="n">
-        <v>113.474352976476</v>
+        <v>113.3984384606746</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.956043995268858</v>
+        <v>-7.951897269151391</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3908441686194</v>
+        <v>113.3894513057434</v>
       </c>
       <c r="G51" t="n">
-        <v>211.2844463948512</v>
+        <v>203.8565841443645</v>
       </c>
       <c r="H51" t="n">
-        <v>17.709633157237</v>
+        <v>2.447076994247902</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1677505249846025</v>
+        <v>0.1729293961427085</v>
       </c>
       <c r="J51" t="n">
-        <v>0.999988850033582</v>
+        <v>0.9999920460648686</v>
       </c>
       <c r="K51" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.956043995268858</v>
+        <v>-7.951897269151391</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3908441686194</v>
+        <v>113.3894513057434</v>
       </c>
       <c r="R51" t="n">
-        <v>211.2844463948512</v>
+        <v>203.8565841443645</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,31 +3797,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.819943070603043</v>
+        <v>-7.931770544234709</v>
       </c>
       <c r="D52" t="n">
-        <v>113.474352976476</v>
+        <v>113.3984384606746</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.956043995268858</v>
+        <v>-7.951897269151391</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3908441686194</v>
+        <v>113.3894513057434</v>
       </c>
       <c r="G52" t="n">
-        <v>211.2844463948512</v>
+        <v>203.8565841443645</v>
       </c>
       <c r="H52" t="n">
-        <v>17.709633157237</v>
+        <v>2.447076994247902</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1677505249846025</v>
+        <v>0.1729293961427085</v>
       </c>
       <c r="J52" t="n">
-        <v>0.585786439751984</v>
+        <v>0.5857864397085671</v>
       </c>
       <c r="K52" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.956043995268858</v>
+        <v>-7.951897269151391</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3908441686194</v>
+        <v>113.3894513057434</v>
       </c>
       <c r="R52" t="n">
-        <v>211.2844463948512</v>
+        <v>203.8565841443645</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,31 +3862,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.819943495446293</v>
+        <v>-7.931770544234709</v>
       </c>
       <c r="D53" t="n">
-        <v>113.4743529723037</v>
+        <v>113.3984384606746</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.956044207630407</v>
+        <v>-7.951897269151391</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3908442947878</v>
+        <v>113.3894513057434</v>
       </c>
       <c r="G53" t="n">
-        <v>211.2844463942482</v>
+        <v>203.8565841443645</v>
       </c>
       <c r="H53" t="n">
-        <v>17.70960550709533</v>
+        <v>2.447076994247902</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1677505249846807</v>
+        <v>0.1729293961427085</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999999889151442</v>
+        <v>0.9999999967629889</v>
       </c>
       <c r="K53" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.956044207630407</v>
+        <v>-7.951897269151391</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3908442947878</v>
+        <v>113.3894513057434</v>
       </c>
       <c r="R53" t="n">
-        <v>211.2844463942482</v>
+        <v>203.8565841443645</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,31 +3927,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.819944352668565</v>
+        <v>-7.931769945111932</v>
       </c>
       <c r="D54" t="n">
-        <v>113.4743529865742</v>
+        <v>113.3984388217543</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.956044512263761</v>
+        <v>-7.951897458253595</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3908446480681</v>
+        <v>113.3894513148524</v>
       </c>
       <c r="G54" t="n">
-        <v>211.2844463958338</v>
+        <v>203.8565841442734</v>
       </c>
       <c r="H54" t="n">
-        <v>17.7095335995234</v>
+        <v>2.44717282983071</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1677505249846966</v>
+        <v>0.1729293961427139</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999938024662</v>
+        <v>0.9999999967629731</v>
       </c>
       <c r="K54" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.956044512263761</v>
+        <v>-7.951897458253595</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3908446480681</v>
+        <v>113.3894513148524</v>
       </c>
       <c r="R54" t="n">
-        <v>211.2844463958338</v>
+        <v>203.8565841442734</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,31 +3992,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.819944195405501</v>
+        <v>-7.931769846970921</v>
       </c>
       <c r="D55" t="n">
-        <v>113.4743529457748</v>
+        <v>113.3984387805286</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.956044442051195</v>
+        <v>-7.951897350655975</v>
       </c>
       <c r="F55" t="n">
-        <v>113.3908445538828</v>
+        <v>113.3894512778517</v>
       </c>
       <c r="G55" t="n">
-        <v>211.28444639115</v>
+        <v>203.8565841444265</v>
       </c>
       <c r="H55" t="n">
-        <v>17.70954492643879</v>
+        <v>2.447171680060709</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1677505249847603</v>
+        <v>0.1729293961427147</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999938023501</v>
+        <v>0.9999999967629609</v>
       </c>
       <c r="K55" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.956044442051195</v>
+        <v>-7.951897350655975</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.3908445538828</v>
+        <v>113.3894512778517</v>
       </c>
       <c r="R55" t="n">
-        <v>211.28444639115</v>
+        <v>203.8565841444265</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.819944266382667</v>
+        <v>-7.931769781383726</v>
       </c>
       <c r="D56" t="n">
-        <v>113.4743529731912</v>
+        <v>113.3984387893124</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.956044371740403</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3908446680085</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="G56" t="n">
-        <v>211.2844463916369</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="H56" t="n">
-        <v>17.70952654084209</v>
+        <v>2.447187730139071</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1677505249847676</v>
+        <v>0.1729293961427181</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999999938022939</v>
+        <v>0.9999999967628259</v>
       </c>
       <c r="K56" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.956044371740403</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3908446680085</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="R56" t="n">
-        <v>211.2844463916369</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,31 +4122,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.819944321986247</v>
+        <v>-7.931769781383726</v>
       </c>
       <c r="D57" t="n">
-        <v>113.4743529739594</v>
+        <v>113.3984387893124</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.956044325521568</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3908447312662</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="G57" t="n">
-        <v>211.284446391559</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="H57" t="n">
-        <v>17.70951329075982</v>
+        <v>2.447187730139071</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1677505249847681</v>
+        <v>0.1729293961427181</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9999999938022623</v>
+        <v>0.9999999967621713</v>
       </c>
       <c r="K57" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.956044325521568</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3908447312662</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="R57" t="n">
-        <v>211.284446391559</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,31 +4187,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.819944163350533</v>
+        <v>-7.931769781383726</v>
       </c>
       <c r="D58" t="n">
-        <v>113.4743529767491</v>
+        <v>113.3984387893124</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.956044312580332</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3908446446582</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="G58" t="n">
-        <v>211.2844463915374</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="H58" t="n">
-        <v>17.70953224984867</v>
+        <v>2.447187730139071</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1677505249847698</v>
+        <v>0.1729293961427181</v>
       </c>
       <c r="J58" t="n">
-        <v>0.999999993802243</v>
+        <v>0.9999999967615834</v>
       </c>
       <c r="K58" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.956044312580332</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3908446446582</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="R58" t="n">
-        <v>211.2844463915374</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,31 +4252,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.819944053686148</v>
+        <v>-7.931769781383726</v>
       </c>
       <c r="D59" t="n">
-        <v>113.4743530552664</v>
+        <v>113.3984387893124</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.956044365346544</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3908446234953</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="G59" t="n">
-        <v>211.2844463913872</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="H59" t="n">
-        <v>17.70955338677888</v>
+        <v>2.447187730139071</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1677505249847707</v>
+        <v>0.1729293961427181</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999938006712</v>
+        <v>0.9999999970169255</v>
       </c>
       <c r="K59" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.956044365346544</v>
+        <v>-7.951897417076888</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3908446234953</v>
+        <v>113.3894512276884</v>
       </c>
       <c r="R59" t="n">
-        <v>211.2844463913872</v>
+        <v>203.8565841443224</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,31 +4317,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.819944142953561</v>
+        <v>-7.93176975695541</v>
       </c>
       <c r="D60" t="n">
-        <v>113.4743529769748</v>
+        <v>113.3984388058608</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.956044285201317</v>
+        <v>-7.951897401119436</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3908446491746</v>
+        <v>113.3894512404547</v>
       </c>
       <c r="G60" t="n">
-        <v>211.2844463913173</v>
+        <v>203.8565841443246</v>
       </c>
       <c r="H60" t="n">
-        <v>17.7095313412363</v>
+        <v>2.447188760060922</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1677505249847714</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999938003254</v>
+        <v>0.9999999970593454</v>
       </c>
       <c r="K60" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.956044285201317</v>
+        <v>-7.951897401119436</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3908446491746</v>
+        <v>113.3894512404547</v>
       </c>
       <c r="R60" t="n">
-        <v>211.2844463913173</v>
+        <v>203.8565841443246</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,31 +4382,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.819944246055138</v>
+        <v>-7.93176975695541</v>
       </c>
       <c r="D61" t="n">
-        <v>113.4743529444117</v>
+        <v>113.3984388058608</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.95604433340637</v>
+        <v>-7.951897401119436</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3908446502868</v>
+        <v>113.3894512404547</v>
       </c>
       <c r="G61" t="n">
-        <v>211.2844463913569</v>
+        <v>203.8565841443246</v>
       </c>
       <c r="H61" t="n">
-        <v>17.70952419761396</v>
+        <v>2.447188760060922</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1677505249847723</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9999999938003128</v>
+        <v>0.999999997645393</v>
       </c>
       <c r="K61" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.95604433340637</v>
+        <v>-7.951897401119436</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3908446502868</v>
+        <v>113.3894512404547</v>
       </c>
       <c r="R61" t="n">
-        <v>211.2844463913569</v>
+        <v>203.8565841443246</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.819944246055138</v>
+        <v>-7.931769756509338</v>
       </c>
       <c r="D62" t="n">
-        <v>113.4743529444117</v>
+        <v>113.3984388068378</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.95604433340637</v>
+        <v>-7.951897404962925</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3908446502868</v>
+        <v>113.3894512395162</v>
       </c>
       <c r="G62" t="n">
-        <v>211.2844463913569</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H62" t="n">
-        <v>17.70952419761396</v>
+        <v>2.447189281603321</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1677505249847723</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J62" t="n">
-        <v>0.535898387456841</v>
+        <v>0.5358983873791384</v>
       </c>
       <c r="K62" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.95604433340637</v>
+        <v>-7.951897404962925</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3908446502868</v>
+        <v>113.3894512395162</v>
       </c>
       <c r="R62" t="n">
-        <v>211.2844463913569</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,31 +4512,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.819944247351022</v>
+        <v>-7.931769707437919</v>
       </c>
       <c r="D63" t="n">
-        <v>113.4743529600179</v>
+        <v>113.3984388192308</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.956044317196787</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3908446766379</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="G63" t="n">
-        <v>211.2844463913557</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="H63" t="n">
-        <v>17.70952191964032</v>
+        <v>2.447195532622743</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1677505249847724</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999999969691</v>
+        <v>0.9999999999985159</v>
       </c>
       <c r="K63" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.956044317196787</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3908446766379</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="R63" t="n">
-        <v>211.2844463913557</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,31 +4577,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.819944247351022</v>
+        <v>-7.931769707437919</v>
       </c>
       <c r="D64" t="n">
-        <v>113.4743529600179</v>
+        <v>113.3984388192308</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.956044317196787</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3908446766379</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="G64" t="n">
-        <v>211.2844463913557</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="H64" t="n">
-        <v>17.70952191964032</v>
+        <v>2.447195532622743</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1677505249847724</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9999999999995151</v>
+        <v>0.9999999999987752</v>
       </c>
       <c r="K64" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.956044317196787</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3908446766379</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="R64" t="n">
-        <v>211.2844463913557</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,31 +4642,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.819944200915216</v>
+        <v>-7.931769707437919</v>
       </c>
       <c r="D65" t="n">
-        <v>113.4743529857817</v>
+        <v>113.3984388192308</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.956044321400469</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3908446713277</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="G65" t="n">
-        <v>211.2844463913578</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="H65" t="n">
-        <v>17.70952850931348</v>
+        <v>2.447195532622743</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1677505249847724</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9656026401515507</v>
+        <v>0.9999999999991969</v>
       </c>
       <c r="K65" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.956044321400469</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3908446713277</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="R65" t="n">
-        <v>211.2844463913578</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,31 +4707,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769707437919</v>
       </c>
       <c r="D66" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388192308</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="G66" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="H66" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195532622743</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9885861949992065</v>
+        <v>0.9999999999994553</v>
       </c>
       <c r="K66" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="R66" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,31 +4772,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769707437919</v>
       </c>
       <c r="D67" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388192308</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="G67" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="H67" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195532622743</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9931709810805889</v>
+        <v>0.9999999999997269</v>
       </c>
       <c r="K67" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="R67" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,31 +4837,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769707437919</v>
       </c>
       <c r="D68" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388192308</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="G68" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="H68" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195532622743</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9971907282941895</v>
+        <v>0.939871680184484</v>
       </c>
       <c r="K68" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407304661</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512289516</v>
       </c>
       <c r="R68" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443252</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,31 +4902,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D69" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G69" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H69" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9978288384625245</v>
+        <v>0.9913568667483076</v>
       </c>
       <c r="K69" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R69" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,31 +4967,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D70" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G70" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H70" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9985881288505732</v>
+        <v>0.9927474317061159</v>
       </c>
       <c r="K70" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R70" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D71" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G71" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H71" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8656475494297885</v>
+        <v>0.9986420690253316</v>
       </c>
       <c r="K71" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R71" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,31 +5097,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D72" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G72" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H72" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5355869819050061</v>
+        <v>0.5831627019320869</v>
       </c>
       <c r="K72" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R72" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,31 +5162,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D73" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G73" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H73" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9997492092380647</v>
+        <v>0.9998909867927007</v>
       </c>
       <c r="K73" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R73" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,31 +5227,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D74" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G74" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H74" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J74" t="n">
-        <v>0.999793013708785</v>
+        <v>0.9999127643830191</v>
       </c>
       <c r="K74" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R74" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,31 +5292,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D75" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G75" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H75" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9999097936794814</v>
+        <v>0.9999999999999889</v>
       </c>
       <c r="K75" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R75" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,31 +5357,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D76" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G76" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H76" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9999513807651238</v>
+        <v>0.9999999999999902</v>
       </c>
       <c r="K76" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R76" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,31 +5422,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D77" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G77" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H77" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9999999999996565</v>
+        <v>0.9999999999999902</v>
       </c>
       <c r="K77" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R77" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,31 +5487,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D78" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G78" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H78" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9999999999996696</v>
+        <v>0.9999999999999944</v>
       </c>
       <c r="K78" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R78" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D79" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G79" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H79" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9999999999997684</v>
+        <v>0.999999999999996</v>
       </c>
       <c r="K79" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R79" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,31 +5617,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D80" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G80" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H80" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9999999999998301</v>
+        <v>0.9999999999999964</v>
       </c>
       <c r="K80" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R80" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,31 +5682,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D81" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G81" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H81" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9999999999998515</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="K81" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R81" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,31 +5747,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D82" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G82" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H82" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857864397965615</v>
+        <v>0.585786439731585</v>
       </c>
       <c r="K82" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R82" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,31 +5812,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D83" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G83" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H83" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J83" t="n">
-        <v>0.999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K83" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R83" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,31 +5877,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D84" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G84" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H84" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999999964</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K84" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R84" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,31 +5942,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D85" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G85" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H85" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999999973</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K85" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R85" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D86" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G86" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H86" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J86" t="n">
-        <v>0.999999999999998</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K86" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R86" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,31 +6072,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D87" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G87" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H87" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999999999999982</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K87" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R87" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,31 +6137,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D88" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G88" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H88" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999999999999991</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K88" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R88" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,31 +6202,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D89" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G89" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H89" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J89" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K89" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R89" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,31 +6267,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D90" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G90" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H90" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J90" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K90" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R90" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,31 +6332,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D91" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G91" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H91" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J91" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K91" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R91" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,31 +6397,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D92" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G92" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H92" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J92" t="n">
-        <v>0.535898387456841</v>
+        <v>0.5358983873791384</v>
       </c>
       <c r="K92" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R92" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,31 +6462,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D93" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G93" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H93" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J93" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K93" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R93" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,31 +6527,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D94" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G94" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H94" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K94" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R94" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,31 +6592,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D95" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G95" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H95" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9227085194931993</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K95" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R95" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,31 +6657,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D96" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G96" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H96" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9799563927419309</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K96" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R96" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,31 +6722,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D97" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G97" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H97" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9878913385842291</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R97" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,31 +6787,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D98" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G98" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H98" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9978436043673472</v>
+        <v>0.9222914849436987</v>
       </c>
       <c r="K98" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R98" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,31 +6852,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D99" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G99" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H99" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9983833698819292</v>
+        <v>0.9661791264503056</v>
       </c>
       <c r="K99" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R99" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,31 +6917,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D100" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G100" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H100" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9985145402083293</v>
+        <v>0.9950786913872675</v>
       </c>
       <c r="K100" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R100" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,31 +6982,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D101" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G101" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H101" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9445522083896909</v>
+        <v>0.9966897544142149</v>
       </c>
       <c r="K101" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R101" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,31 +7047,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D102" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G102" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H102" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5358944022548114</v>
+        <v>0.5820763861834198</v>
       </c>
       <c r="K102" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R102" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,31 +7112,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D103" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G103" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H103" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9995750705632197</v>
+        <v>0.998568392045567</v>
       </c>
       <c r="K103" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R103" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,31 +7177,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D104" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G104" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H104" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9997482369213039</v>
+        <v>0.9991590862259849</v>
       </c>
       <c r="K104" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R104" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,31 +7242,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D105" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G105" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H105" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9999439471119329</v>
+        <v>0.9996820743634227</v>
       </c>
       <c r="K105" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R105" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,31 +7307,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D106" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G106" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H106" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J106" t="n">
-        <v>0.999972593527977</v>
+        <v>0.9998361436415479</v>
       </c>
       <c r="K106" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R106" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,31 +7372,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D107" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G107" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H107" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9999827715042801</v>
+        <v>0.9999539973450399</v>
       </c>
       <c r="K107" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R107" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,31 +7437,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D108" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G108" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H108" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9999986301489012</v>
+        <v>0.9999797124347192</v>
       </c>
       <c r="K108" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R108" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D109" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G109" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H109" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9999996333715658</v>
+        <v>0.9999937884144272</v>
       </c>
       <c r="K109" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R109" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,31 +7567,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D110" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G110" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H110" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9999996702934192</v>
+        <v>0.9999996483312046</v>
       </c>
       <c r="K110" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R110" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,31 +7632,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D111" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G111" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H111" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9999997036332046</v>
+        <v>0.9999996483312046</v>
       </c>
       <c r="K111" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R111" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,31 +7697,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D112" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G112" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H112" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J112" t="n">
-        <v>0.585786439796559</v>
+        <v>0.585786439731585</v>
       </c>
       <c r="K112" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R112" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,31 +7762,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D113" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G113" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H113" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J113" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K113" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R113" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,31 +7827,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D114" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G114" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H114" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J114" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K114" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R114" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,31 +7892,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D115" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G115" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H115" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J115" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K115" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R115" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,31 +7957,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D116" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G116" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H116" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J116" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K116" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R116" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D117" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G117" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H117" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J117" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K117" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R117" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,31 +8087,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D118" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G118" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H118" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J118" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K118" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R118" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,31 +8152,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D119" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G119" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H119" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J119" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K119" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R119" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,31 +8217,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D120" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G120" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H120" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J120" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K120" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R120" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,31 +8282,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D121" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G121" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H121" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J121" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K121" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R121" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,31 +8347,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D122" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G122" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H122" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J122" t="n">
-        <v>0.535898387456841</v>
+        <v>0.5358983873791384</v>
       </c>
       <c r="K122" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R122" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,31 +8412,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D123" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G123" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H123" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J123" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K123" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R123" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,31 +8477,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D124" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G124" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H124" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K124" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R124" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,31 +8542,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D125" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G125" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H125" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9256966345004899</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K125" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R125" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,31 +8607,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D126" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G126" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H126" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9656855632977244</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K126" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R126" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,31 +8672,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D127" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G127" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H127" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9843340874897724</v>
+        <v>1</v>
       </c>
       <c r="K127" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R127" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,31 +8737,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D128" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G128" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H128" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9924194168932914</v>
+        <v>0.8577194931596667</v>
       </c>
       <c r="K128" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R128" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,31 +8802,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D129" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G129" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H129" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J129" t="n">
-        <v>0.992814791634261</v>
+        <v>0.9598513398742358</v>
       </c>
       <c r="K129" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R129" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D130" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G130" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H130" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9979573820217965</v>
+        <v>0.9865042634185822</v>
       </c>
       <c r="K130" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R130" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,31 +8932,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D131" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G131" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H131" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9461242876202979</v>
+        <v>0.9945503266705301</v>
       </c>
       <c r="K131" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R131" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D132" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G132" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H132" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5358191361502194</v>
+        <v>0.5810862854775244</v>
       </c>
       <c r="K132" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R132" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,31 +9062,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D133" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G133" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H133" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9989885268098306</v>
+        <v>0.9974909629920715</v>
       </c>
       <c r="K133" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R133" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,31 +9127,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D134" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G134" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H134" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9992879136034222</v>
+        <v>0.9980994178405708</v>
       </c>
       <c r="K134" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R134" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,31 +9192,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D135" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G135" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H135" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9994887975722302</v>
+        <v>0.9987128386050378</v>
       </c>
       <c r="K135" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R135" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,31 +9257,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D136" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G136" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H136" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9995485182102001</v>
+        <v>0.9995293078785104</v>
       </c>
       <c r="K136" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R136" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,31 +9322,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D137" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G137" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H137" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9997356374062648</v>
+        <v>0.9999402979262164</v>
       </c>
       <c r="K137" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R137" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D138" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G138" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H138" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9999081856025579</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K138" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R138" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,31 +9452,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D139" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G139" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H139" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9999552086564912</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K139" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R139" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,31 +9517,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D140" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G140" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H140" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9999632223915842</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K140" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R140" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,31 +9582,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D141" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G141" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H141" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J141" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K141" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R141" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,31 +9647,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D142" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G142" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H142" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857864397965615</v>
+        <v>0.585786439731585</v>
       </c>
       <c r="K142" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R142" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D143" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G143" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H143" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J143" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K143" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R143" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,31 +9777,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D144" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G144" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H144" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J144" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K144" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R144" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,31 +9842,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D145" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G145" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H145" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J145" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K145" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R145" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,31 +9907,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D146" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G146" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H146" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J146" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K146" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R146" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,31 +9972,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D147" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G147" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H147" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J147" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K147" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R147" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,31 +10037,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D148" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G148" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H148" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J148" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K148" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R148" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,31 +10102,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D149" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G149" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H149" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J149" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K149" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R149" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,31 +10167,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D150" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G150" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H150" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J150" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K150" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R150" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,31 +10232,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.819944230538701</v>
+        <v>-7.931769705836016</v>
       </c>
       <c r="D151" t="n">
-        <v>113.4743529585126</v>
+        <v>113.3984388182181</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="G151" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="H151" t="n">
-        <v>17.70952384775023</v>
+        <v>2.447195776211807</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1677505249847725</v>
+        <v>0.1729293961427182</v>
       </c>
       <c r="J151" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="K151" t="n">
-        <v>1426</v>
+        <v>448</v>
       </c>
       <c r="L151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.956044315201369</v>
+        <v>-7.951897407706222</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3908446660412</v>
+        <v>113.3894512270442</v>
       </c>
       <c r="R151" t="n">
-        <v>211.2844463913545</v>
+        <v>203.8565841443273</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44644.05902777778</v>
       </c>
       <c r="C2" t="n">
-        <v>-7.546622452827696</v>
+        <v>-7.947867928369328</v>
       </c>
       <c r="D2" t="n">
-        <v>113.0387077883158</v>
+        <v>113.3074755112753</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.927170613095884</v>
+        <v>-7.839189875639692</v>
       </c>
       <c r="F2" t="n">
-        <v>113.3287864261403</v>
+        <v>113.378025580751</v>
       </c>
       <c r="G2" t="n">
-        <v>142.9547122220439</v>
+        <v>32.74647274213618</v>
       </c>
       <c r="H2" t="n">
-        <v>53.02927486634655</v>
+        <v>14.36712313457345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1708192615186635</v>
+        <v>0.1641927143608508</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9010754493705263</v>
+        <v>0.9187573774091462</v>
       </c>
       <c r="K2" t="n">
-        <v>122</v>
+        <v>640</v>
       </c>
       <c r="L2" t="n">
-        <v>640</v>
+        <v>177</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44644.05902777778</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.79336507804223</v>
       </c>
       <c r="O2" t="n">
-        <v>113.300380121246</v>
+        <v>113.335282392927</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.927170613095884</v>
+        <v>-7.839189875639692</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.3287864261403</v>
+        <v>113.378025580751</v>
       </c>
       <c r="R2" t="n">
-        <v>142.9547122220439</v>
+        <v>32.74647274213618</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -612,31 +612,31 @@
         <v>44877.10347222222</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.546622452827696</v>
+        <v>-7.96129127356304</v>
       </c>
       <c r="D3" t="n">
-        <v>113.0387077883158</v>
+        <v>113.3552544675357</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.927170613095884</v>
+        <v>-7.989089105274556</v>
       </c>
       <c r="F3" t="n">
-        <v>113.3287864261403</v>
+        <v>113.3475090217036</v>
       </c>
       <c r="G3" t="n">
-        <v>142.9547122220439</v>
+        <v>195.425773541009</v>
       </c>
       <c r="H3" t="n">
-        <v>53.02927486634655</v>
+        <v>3.206497185012513</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1708192615186635</v>
+        <v>0.1675011495850191</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9668106035690233</v>
+        <v>0.9613088319438954</v>
       </c>
       <c r="K3" t="n">
-        <v>122</v>
+        <v>640</v>
       </c>
       <c r="L3" t="n">
         <v>640</v>
@@ -651,13 +651,13 @@
         <v>113.300380121246</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.927170613095884</v>
+        <v>-7.989089105274556</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.3287864261403</v>
+        <v>113.3475090217036</v>
       </c>
       <c r="R3" t="n">
-        <v>142.9547122220439</v>
+        <v>195.425773541009</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.546622452827696</v>
+        <v>-7.926102288494857</v>
       </c>
       <c r="D4" t="n">
-        <v>113.0387077883158</v>
+        <v>113.3671634648504</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.927170613095884</v>
+        <v>-7.965640806314738</v>
       </c>
       <c r="F4" t="n">
-        <v>113.3287864261403</v>
+        <v>113.3915743714693</v>
       </c>
       <c r="G4" t="n">
-        <v>142.9547122220439</v>
+        <v>148.5572331822311</v>
       </c>
       <c r="H4" t="n">
-        <v>53.02927486634655</v>
+        <v>5.15325741564665</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1708192615186635</v>
+        <v>0.1682212131858368</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9836961483388372</v>
+        <v>0.9819490797408548</v>
       </c>
       <c r="K4" t="n">
-        <v>122</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O4" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.927170613095884</v>
+        <v>-7.965640806314738</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.3287864261403</v>
+        <v>113.3915743714693</v>
       </c>
       <c r="R4" t="n">
-        <v>142.9547122220439</v>
+        <v>148.5572331822311</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -742,28 +742,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.935851975517988</v>
+        <v>-7.943522319851359</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3942293442498</v>
+        <v>113.3791845475469</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.941387678881207</v>
+        <v>-7.93509623774929</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3870731743803</v>
+        <v>113.3823580655979</v>
       </c>
       <c r="G5" t="n">
-        <v>232.0081829376357</v>
+        <v>20.4567555795892</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1721819325204474</v>
+        <v>0.1686407747086151</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9880621742921812</v>
+        <v>0.9889994225917201</v>
       </c>
       <c r="K5" t="n">
         <v>448</v>
@@ -781,13 +781,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.941387678881207</v>
+        <v>-7.93509623774929</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3870731743803</v>
+        <v>113.3823580655979</v>
       </c>
       <c r="R5" t="n">
-        <v>232.0081829376357</v>
+        <v>20.4567555795892</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -807,28 +807,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.961704554939073</v>
+        <v>-7.943522319851359</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3982534350317</v>
+        <v>113.3791845475469</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.968892890147505</v>
+        <v>-7.93509623774929</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3927965514963</v>
+        <v>113.3823580655979</v>
       </c>
       <c r="G6" t="n">
-        <v>216.93570199387</v>
+        <v>20.4567555795892</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1725901599184316</v>
+        <v>0.1686407747086151</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9963727598665285</v>
+        <v>0.9944642961142206</v>
       </c>
       <c r="K6" t="n">
         <v>448</v>
@@ -846,13 +846,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.968892890147505</v>
+        <v>-7.93509623774929</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3927965514963</v>
+        <v>113.3823580655979</v>
       </c>
       <c r="R6" t="n">
-        <v>216.93570199387</v>
+        <v>20.4567555795892</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -872,31 +872,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.93658956687915</v>
+        <v>-8.225016297938462</v>
       </c>
       <c r="D7" t="n">
-        <v>113.3870702583051</v>
+        <v>113.1616550455066</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.945029933410848</v>
+        <v>-7.956047255311736</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3839356650109</v>
+        <v>113.3968308216227</v>
       </c>
       <c r="G7" t="n">
-        <v>200.1943212494579</v>
+        <v>40.89796033545344</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>39.55733557103636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1728114456828493</v>
+        <v>0.1687109979315386</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9968824388236475</v>
+        <v>0.9965890832207198</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="L7" t="n">
         <v>448</v>
@@ -911,13 +911,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.945029933410848</v>
+        <v>-7.956047255311736</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3839356650109</v>
+        <v>113.3968308216227</v>
       </c>
       <c r="R7" t="n">
-        <v>200.1943212494579</v>
+        <v>40.89796033545344</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.948416380319064</v>
+        <v>-7.814333575025198</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3947727832923</v>
+        <v>113.4189835525487</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.956285590732064</v>
+        <v>-7.946745369609505</v>
       </c>
       <c r="F8" t="n">
-        <v>113.3903769531832</v>
+        <v>113.3793820597618</v>
       </c>
       <c r="G8" t="n">
-        <v>208.9527941880396</v>
+        <v>196.4994132530685</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>15.35604729386361</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1728871124503115</v>
+        <v>0.1690778794693271</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9970070712850319</v>
+        <v>0.9978072192317542</v>
       </c>
       <c r="K8" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.956285590732064</v>
+        <v>-7.946745369609505</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.3903769531832</v>
+        <v>113.3793820597618</v>
       </c>
       <c r="R8" t="n">
-        <v>208.9527941880396</v>
+        <v>196.4994132530685</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.93434578483743</v>
+        <v>-7.814333575025198</v>
       </c>
       <c r="D9" t="n">
-        <v>113.3899832504918</v>
+        <v>113.4189835525487</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.943072822438574</v>
+        <v>-7.946745369609505</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3877904273481</v>
+        <v>113.3793820597618</v>
       </c>
       <c r="G9" t="n">
-        <v>193.9745843851332</v>
+        <v>196.4994132530685</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>15.35604729386361</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1728961702570467</v>
+        <v>0.1690778794693271</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9975328296956665</v>
+        <v>0.9978315161026738</v>
       </c>
       <c r="K9" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L9" t="n">
         <v>448</v>
@@ -1041,13 +1041,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.943072822438574</v>
+        <v>-7.946745369609505</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3877904273481</v>
+        <v>113.3793820597618</v>
       </c>
       <c r="R9" t="n">
-        <v>193.9745843851332</v>
+        <v>196.4994132530685</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,28 +1067,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.93434578483743</v>
+        <v>-7.932364914074645</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3899832504918</v>
+        <v>113.3840960278918</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.943072822438574</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3877904273481</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="G10" t="n">
-        <v>193.9745843851332</v>
+        <v>194.206326405441</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>1.295905899775964</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1728961702570467</v>
+        <v>0.1690963695774643</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9985079052392184</v>
+        <v>0.9980715396425361</v>
       </c>
       <c r="K10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.943072822438574</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3877904273481</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="R10" t="n">
-        <v>193.9745843851332</v>
+        <v>194.206326405441</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,28 +1132,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.946004835280128</v>
+        <v>-7.932364914074645</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3870632100484</v>
+        <v>113.3840960278918</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.953730407035009</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3824149000138</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="G11" t="n">
-        <v>210.7902234313149</v>
+        <v>194.206326405441</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>1.295905899775964</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1729028126082959</v>
+        <v>0.1690963695774643</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9985390735139615</v>
+        <v>0.9984038066360325</v>
       </c>
       <c r="K11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.953730407035009</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3824149000138</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="R11" t="n">
-        <v>210.7902234313149</v>
+        <v>194.206326405441</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,28 +1197,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.941147373148163</v>
+        <v>-7.932364914074645</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3905914296667</v>
+        <v>113.3840960278918</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.949452260563246</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3871073640762</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="G12" t="n">
-        <v>202.5622880881011</v>
+        <v>194.206326405441</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>1.295905899775964</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1729058436499597</v>
+        <v>0.1690963695774643</v>
       </c>
       <c r="J12" t="n">
-        <v>0.585785671207193</v>
+        <v>0.5857861349207074</v>
       </c>
       <c r="K12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.949452260563246</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3871073640762</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="R12" t="n">
-        <v>202.5622880881011</v>
+        <v>194.206326405441</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,28 +1262,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.942247698770834</v>
+        <v>-7.932364914074645</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3913374779526</v>
+        <v>113.3840960278918</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.950390375560152</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="F13" t="n">
-        <v>113.387482776141</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="G13" t="n">
-        <v>205.1192371889614</v>
+        <v>194.206326405441</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>1.295905899775964</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1729082741409874</v>
+        <v>0.1690963695774643</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9998279464302917</v>
+        <v>0.9995332506122246</v>
       </c>
       <c r="K13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.950390375560152</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.387482776141</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="R13" t="n">
-        <v>205.1192371889614</v>
+        <v>194.206326405441</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,28 +1327,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.93497743739591</v>
+        <v>-7.932364914074645</v>
       </c>
       <c r="D14" t="n">
-        <v>113.4025459960516</v>
+        <v>113.3840960278918</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.954294895968587</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3909535689302</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="G14" t="n">
-        <v>210.7239648155063</v>
+        <v>194.206326405441</v>
       </c>
       <c r="H14" t="n">
-        <v>2.498749005082724</v>
+        <v>1.295905899775964</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1729180726070106</v>
+        <v>0.1690963695774643</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999831281509041</v>
+        <v>0.9997613577522477</v>
       </c>
       <c r="K14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.954294895968587</v>
+        <v>-7.943662855187292</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3909535689302</v>
+        <v>113.3812081687555</v>
       </c>
       <c r="R14" t="n">
-        <v>210.7239648155063</v>
+        <v>194.206326405441</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,28 +1392,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.92568893273445</v>
+        <v>-7.931704885925249</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3966282047625</v>
+        <v>113.3806092839204</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.951653689720641</v>
+        <v>-7.947536443061961</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3851509586955</v>
+        <v>113.3764714394255</v>
       </c>
       <c r="G15" t="n">
-        <v>203.6427942988933</v>
+        <v>194.5128101495441</v>
       </c>
       <c r="H15" t="n">
-        <v>3.151710413276432</v>
+        <v>1.818413712528139</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1729194714748303</v>
+        <v>0.1691074674061562</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9999008213182147</v>
+        <v>0.9997504449474823</v>
       </c>
       <c r="K15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.951653689720641</v>
+        <v>-7.947536443061961</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3851509586955</v>
+        <v>113.3764714394255</v>
       </c>
       <c r="R15" t="n">
-        <v>203.6427942988933</v>
+        <v>194.5128101495441</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,28 +1457,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.942136817407444</v>
+        <v>-7.931704885925249</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3898792570441</v>
+        <v>113.3806092839204</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.950380890131098</v>
+        <v>-7.947536443061961</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3862509242902</v>
+        <v>113.3764714394255</v>
       </c>
       <c r="G16" t="n">
-        <v>203.5515688352019</v>
+        <v>194.5128101495441</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>1.818413712528139</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1729202711171086</v>
+        <v>0.1691074674061562</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9999365962737594</v>
+        <v>0.9997867673416199</v>
       </c>
       <c r="K16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.950380890131098</v>
+        <v>-7.947536443061961</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3862509242902</v>
+        <v>113.3764714394255</v>
       </c>
       <c r="R16" t="n">
-        <v>203.5515688352019</v>
+        <v>194.5128101495441</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,28 +1522,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.939918081870034</v>
+        <v>-7.931704885925249</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3906717879645</v>
+        <v>113.3806092839204</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.948635914067584</v>
+        <v>-7.947536443061961</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3884419184518</v>
+        <v>113.3764714394255</v>
       </c>
       <c r="G17" t="n">
-        <v>194.2154020888845</v>
+        <v>194.5128101495441</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>1.818413712528139</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1729249322885775</v>
+        <v>0.1691074674061562</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9999307697167897</v>
+        <v>0.9998949678548994</v>
       </c>
       <c r="K17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.948635914067584</v>
+        <v>-7.947536443061961</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3884419184518</v>
+        <v>113.3764714394255</v>
       </c>
       <c r="R17" t="n">
-        <v>194.2154020888845</v>
+        <v>194.5128101495441</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,28 +1587,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.939918081870034</v>
+        <v>-7.937090731039494</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3906717879645</v>
+        <v>113.3806339267365</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.948635914067584</v>
+        <v>-7.947639022309905</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3884419184518</v>
+        <v>113.3778938561207</v>
       </c>
       <c r="G18" t="n">
-        <v>194.2154020888845</v>
+        <v>194.4275580551568</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>1.211111776661287</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1729249322885775</v>
+        <v>0.1691100046675392</v>
       </c>
       <c r="J18" t="n">
-        <v>0.99992934721306</v>
+        <v>0.9999064162494532</v>
       </c>
       <c r="K18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.948635914067584</v>
+        <v>-7.947639022309905</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3884419184518</v>
+        <v>113.3778938561207</v>
       </c>
       <c r="R18" t="n">
-        <v>194.2154020888845</v>
+        <v>194.4275580551568</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,28 +1652,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.930349921008439</v>
+        <v>-7.932302701813747</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3992681218296</v>
+        <v>113.3818137982797</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.950498956513697</v>
+        <v>-7.948014915300992</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3902894328216</v>
+        <v>113.3778042570112</v>
       </c>
       <c r="G19" t="n">
-        <v>203.813233148642</v>
+        <v>194.1836147518199</v>
       </c>
       <c r="H19" t="n">
-        <v>2.448970828607757</v>
+        <v>1.802055384810859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1729277700858524</v>
+        <v>0.1691136021123909</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9999320823123063</v>
+        <v>0.9999250358382268</v>
       </c>
       <c r="K19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.950498956513697</v>
+        <v>-7.948014915300992</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3902894328216</v>
+        <v>113.3778042570112</v>
       </c>
       <c r="R19" t="n">
-        <v>203.813233148642</v>
+        <v>194.1836147518199</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,28 +1717,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.930349921008439</v>
+        <v>-7.932423545001386</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3992681218296</v>
+        <v>113.3823116426105</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.950498956513697</v>
+        <v>-7.952265126424391</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3902894328216</v>
+        <v>113.3770923187126</v>
       </c>
       <c r="G20" t="n">
-        <v>203.813233148642</v>
+        <v>194.6021091711648</v>
       </c>
       <c r="H20" t="n">
-        <v>2.448970828607757</v>
+        <v>2.279928754847273</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1729277700858524</v>
+        <v>0.169114133349757</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9999381496048059</v>
+        <v>0.9999326571264477</v>
       </c>
       <c r="K20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.950498956513697</v>
+        <v>-7.952265126424391</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3902894328216</v>
+        <v>113.3770923187126</v>
       </c>
       <c r="R20" t="n">
-        <v>203.813233148642</v>
+        <v>194.6021091711648</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,28 +1782,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.930784964873674</v>
+        <v>-7.933935641820739</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3984703493835</v>
+        <v>113.3820917199969</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.952594025126735</v>
+        <v>-7.952383649114564</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3887041865112</v>
+        <v>113.3772328575177</v>
       </c>
       <c r="G21" t="n">
-        <v>203.9170053381945</v>
+        <v>194.6197276109303</v>
       </c>
       <c r="H21" t="n">
-        <v>2.652860949177557</v>
+        <v>2.119967578079638</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1729281109008081</v>
+        <v>0.1691143514052757</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9999587574651947</v>
+        <v>0.999933326327033</v>
       </c>
       <c r="K21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.952594025126735</v>
+        <v>-7.952383649114564</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3887041865112</v>
+        <v>113.3772328575177</v>
       </c>
       <c r="R21" t="n">
-        <v>203.9170053381945</v>
+        <v>194.6197276109303</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,28 +1847,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.932008453917532</v>
+        <v>-7.933935641820739</v>
       </c>
       <c r="D22" t="n">
-        <v>113.3988740343873</v>
+        <v>113.3820917199969</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.951938814901519</v>
+        <v>-7.952383649114564</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3899690407818</v>
+        <v>113.3772328575177</v>
       </c>
       <c r="G22" t="n">
-        <v>203.8697286998925</v>
+        <v>194.6197276109303</v>
       </c>
       <c r="H22" t="n">
-        <v>2.423448222911395</v>
+        <v>2.119967578079638</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1729291017264576</v>
+        <v>0.1691143514052757</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857864391808946</v>
+        <v>0.5857864386166005</v>
       </c>
       <c r="K22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.951938814901519</v>
+        <v>-7.952383649114564</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3899690407818</v>
+        <v>113.3772328575177</v>
       </c>
       <c r="R22" t="n">
-        <v>203.8697286998925</v>
+        <v>194.6197276109303</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,28 +1912,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.932008453917532</v>
+        <v>-7.930735546699901</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3988740343873</v>
+        <v>113.3831644646909</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.951938814901519</v>
+        <v>-7.952206915234053</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3899690407818</v>
+        <v>113.3774823420989</v>
       </c>
       <c r="G23" t="n">
-        <v>203.8697286998925</v>
+        <v>194.6864278958238</v>
       </c>
       <c r="H23" t="n">
-        <v>2.423448222911395</v>
+        <v>2.468151382606349</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1729291017264576</v>
+        <v>0.1691147355424501</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999927894612668</v>
+        <v>0.9999705214496372</v>
       </c>
       <c r="K23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.951938814901519</v>
+        <v>-7.952206915234053</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3899690407818</v>
+        <v>113.3774823420989</v>
       </c>
       <c r="R23" t="n">
-        <v>203.8697286998925</v>
+        <v>194.6864278958238</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,28 +1977,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.930577736145901</v>
+        <v>-7.9363307350598</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3992551153185</v>
+        <v>113.3816070427228</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.95205298962433</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3896597636311</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="G24" t="n">
-        <v>203.8699177381165</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="H24" t="n">
-        <v>2.611305436908566</v>
+        <v>1.4524713502873</v>
       </c>
       <c r="I24" t="n">
-        <v>0.17292917205435</v>
+        <v>0.1691151142839517</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999990885061856</v>
+        <v>0.999969882184872</v>
       </c>
       <c r="K24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.95205298962433</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3896597636311</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="R24" t="n">
-        <v>203.8699177381165</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,28 +2042,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.932107078777994</v>
+        <v>-7.9363307350598</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3981905387637</v>
+        <v>113.3816070427228</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.951416616657495</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3895673430743</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="G25" t="n">
-        <v>203.8589185981129</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="H25" t="n">
-        <v>2.347762411552878</v>
+        <v>1.4524713502873</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1729292708802717</v>
+        <v>0.1691151142839517</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999904764196226</v>
+        <v>0.9999707692471416</v>
       </c>
       <c r="K25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.951416616657495</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3895673430743</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="R25" t="n">
-        <v>203.8589185981129</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.932107078777994</v>
+        <v>-7.9363307350598</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3981905387637</v>
+        <v>113.3816070427228</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.951416616657495</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3895673430743</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="G26" t="n">
-        <v>203.8589185981129</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="H26" t="n">
-        <v>2.347762411552878</v>
+        <v>1.4524713502873</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1729292708802717</v>
+        <v>0.1691151142839517</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9999904320720423</v>
+        <v>0.9999702622177341</v>
       </c>
       <c r="K26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.951416616657495</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3895673430743</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="R26" t="n">
-        <v>203.8589185981129</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,28 +2172,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.931647608770078</v>
+        <v>-7.9363307350598</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3984024602745</v>
+        <v>113.3816070427228</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.951588459052373</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3894976567213</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="G27" t="n">
-        <v>203.858140797816</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="H27" t="n">
-        <v>2.424506737041943</v>
+        <v>1.4524713502873</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1729293367946654</v>
+        <v>0.1691151142839517</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999902991749878</v>
+        <v>0.9999700131020605</v>
       </c>
       <c r="K27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.951588459052373</v>
+        <v>-7.948992483440768</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3894976567213</v>
+        <v>113.3783656318469</v>
       </c>
       <c r="R27" t="n">
-        <v>203.858140797816</v>
+        <v>194.2269934830118</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,28 +2237,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.93121009264768</v>
+        <v>-7.935001573163057</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3985207687868</v>
+        <v>113.3825449725664</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.951969419520295</v>
+        <v>-7.948921906577493</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3892506956288</v>
+        <v>113.3789864151545</v>
       </c>
       <c r="G28" t="n">
-        <v>203.8575911452319</v>
+        <v>194.2076443647023</v>
       </c>
       <c r="H28" t="n">
-        <v>2.524010932063897</v>
+        <v>1.596711363070815</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1729293645839448</v>
+        <v>0.1691151458214825</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9999900946689858</v>
+        <v>0.9999698579870342</v>
       </c>
       <c r="K28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.951969419520295</v>
+        <v>-7.948921906577493</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3892506956288</v>
+        <v>113.3789864151545</v>
       </c>
       <c r="R28" t="n">
-        <v>203.8575911452319</v>
+        <v>194.2076443647023</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,28 +2302,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.931757624372517</v>
+        <v>-7.935725089773809</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3982389282071</v>
+        <v>113.3819369956138</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.951738748625412</v>
+        <v>-7.94906418042172</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3893168277212</v>
+        <v>113.3785237064973</v>
       </c>
       <c r="G29" t="n">
-        <v>203.8564989784691</v>
+        <v>194.2209084143495</v>
       </c>
       <c r="H29" t="n">
-        <v>2.429372679444343</v>
+        <v>1.530130425114914</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1729293790105</v>
+        <v>0.1691152648452529</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9999900821510528</v>
+        <v>0.9999696637453168</v>
       </c>
       <c r="K29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.951738748625412</v>
+        <v>-7.94906418042172</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3893168277212</v>
+        <v>113.3785237064973</v>
       </c>
       <c r="R29" t="n">
-        <v>203.8564989784691</v>
+        <v>194.2209084143495</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,28 +2367,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.931793524103727</v>
+        <v>-7.935134438766756</v>
       </c>
       <c r="D30" t="n">
-        <v>113.398524857622</v>
+        <v>113.3819145555529</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.951960348478597</v>
+        <v>-7.949002594893251</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3895201305768</v>
+        <v>113.3783691400798</v>
       </c>
       <c r="G30" t="n">
-        <v>203.8557959535809</v>
+        <v>194.2083974304193</v>
       </c>
       <c r="H30" t="n">
-        <v>2.451937531638806</v>
+        <v>1.590731731345557</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1729293811710772</v>
+        <v>0.1691153914989246</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9999900865518883</v>
+        <v>0.9999694311150783</v>
       </c>
       <c r="K30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.951960348478597</v>
+        <v>-7.949002594893251</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3895201305768</v>
+        <v>113.3783691400798</v>
       </c>
       <c r="R30" t="n">
-        <v>203.8557959535809</v>
+        <v>194.2083974304193</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.931940464439733</v>
+        <v>-7.935080164435876</v>
       </c>
       <c r="D31" t="n">
-        <v>113.398504731382</v>
+        <v>113.3817698600656</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.951925328827847</v>
+        <v>-7.949041893553512</v>
       </c>
       <c r="F31" t="n">
-        <v>113.3895809364715</v>
+        <v>113.3782018967505</v>
       </c>
       <c r="G31" t="n">
-        <v>203.8565471586225</v>
+        <v>194.203147044711</v>
       </c>
       <c r="H31" t="n">
-        <v>2.429828323811683</v>
+        <v>1.601427780203694</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1729293892000711</v>
+        <v>0.1691154674727551</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9999900457593704</v>
+        <v>0.9999691622534803</v>
       </c>
       <c r="K31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.951925328827847</v>
+        <v>-7.949041893553512</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.3895809364715</v>
+        <v>113.3782018967505</v>
       </c>
       <c r="R31" t="n">
-        <v>203.8565471586225</v>
+        <v>194.203147044711</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,28 +2497,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.931773990225187</v>
+        <v>-7.935080164435876</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3984977788391</v>
+        <v>113.3817698600656</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.951839282531324</v>
+        <v>-7.949041893553512</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3895380931881</v>
+        <v>113.3782018967505</v>
       </c>
       <c r="G32" t="n">
-        <v>203.8564978641921</v>
+        <v>194.203147044711</v>
       </c>
       <c r="H32" t="n">
-        <v>2.439606144037621</v>
+        <v>1.601427780203694</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1729293908671587</v>
+        <v>0.1691154674727551</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5358983873522942</v>
+        <v>0.5857864394873332</v>
       </c>
       <c r="K32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.951839282531324</v>
+        <v>-7.949041893553512</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3895380931881</v>
+        <v>113.3782018967505</v>
       </c>
       <c r="R32" t="n">
-        <v>203.8564978641921</v>
+        <v>194.203147044711</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,28 +2562,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.931789066852779</v>
+        <v>-7.935181863743059</v>
       </c>
       <c r="D33" t="n">
-        <v>113.3984218638553</v>
+        <v>113.3816694917427</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.951908587253786</v>
+        <v>-7.949102647377718</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3894379550741</v>
+        <v>113.3781116122908</v>
       </c>
       <c r="G33" t="n">
-        <v>203.8565148803516</v>
+        <v>194.2046003452098</v>
       </c>
       <c r="H33" t="n">
-        <v>2.446199732249556</v>
+        <v>1.596741528669094</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1729293949969323</v>
+        <v>0.169115545119429</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999914021220341</v>
+        <v>0.9999993908812261</v>
       </c>
       <c r="K33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.951908587253786</v>
+        <v>-7.949102647377718</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3894379550741</v>
+        <v>113.3781116122908</v>
       </c>
       <c r="R33" t="n">
-        <v>203.8565148803516</v>
+        <v>194.2046003452098</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,28 +2627,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.931855915499844</v>
+        <v>-7.935034595719155</v>
       </c>
       <c r="D34" t="n">
-        <v>113.3983530695536</v>
+        <v>113.3819343928551</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.951882134917201</v>
+        <v>-7.949103214462262</v>
       </c>
       <c r="F34" t="n">
-        <v>113.389410781965</v>
+        <v>113.3783388271817</v>
       </c>
       <c r="G34" t="n">
-        <v>203.8566120206795</v>
+        <v>194.2042304586313</v>
       </c>
       <c r="H34" t="n">
-        <v>2.434857652939851</v>
+        <v>1.613695890771186</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1729293950462735</v>
+        <v>0.1691155517768498</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9999913954557782</v>
+        <v>0.9060394274646515</v>
       </c>
       <c r="K34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.951882134917201</v>
+        <v>-7.949103214462262</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.389410781965</v>
+        <v>113.3783388271817</v>
       </c>
       <c r="R34" t="n">
-        <v>203.8566120206795</v>
+        <v>194.2042304586313</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,28 +2692,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.931801750585626</v>
+        <v>-7.935131730005409</v>
       </c>
       <c r="D35" t="n">
-        <v>113.3984319364823</v>
+        <v>113.3819131210124</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.951922779719037</v>
+        <v>-7.949100437185812</v>
       </c>
       <c r="F35" t="n">
-        <v>113.389447326493</v>
+        <v>113.3783430160613</v>
       </c>
       <c r="G35" t="n">
-        <v>203.8565790502952</v>
+        <v>194.2045132495666</v>
       </c>
       <c r="H35" t="n">
-        <v>2.446384381705311</v>
+        <v>1.602237843997023</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1729293958230111</v>
+        <v>0.1691155527501881</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9999913915138996</v>
+        <v>0.9895872624553129</v>
       </c>
       <c r="K35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.951922779719037</v>
+        <v>-7.949100437185812</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.389447326493</v>
+        <v>113.3783430160613</v>
       </c>
       <c r="R35" t="n">
-        <v>203.8565790502952</v>
+        <v>194.2045132495666</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.931783019260528</v>
+        <v>-7.935131730005409</v>
       </c>
       <c r="D36" t="n">
-        <v>113.3984266810594</v>
+        <v>113.3819131210124</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.951887660736961</v>
+        <v>-7.949100437185812</v>
       </c>
       <c r="F36" t="n">
-        <v>113.389449388178</v>
+        <v>113.3783430160613</v>
       </c>
       <c r="G36" t="n">
-        <v>203.8565819990369</v>
+        <v>194.2045132495666</v>
       </c>
       <c r="H36" t="n">
-        <v>2.444391959701624</v>
+        <v>1.602237843997023</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1729293960742822</v>
+        <v>0.1691155527501881</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9999913880388721</v>
+        <v>0.9959063236634373</v>
       </c>
       <c r="K36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.951887660736961</v>
+        <v>-7.949100437185812</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.389449388178</v>
+        <v>113.3783430160613</v>
       </c>
       <c r="R36" t="n">
-        <v>203.8565819990369</v>
+        <v>194.2045132495666</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,28 +2822,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.93177280134961</v>
+        <v>-7.935157244138734</v>
       </c>
       <c r="D37" t="n">
-        <v>113.3984380256375</v>
+        <v>113.3818407903523</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.951892182829148</v>
+        <v>-7.949100898708978</v>
       </c>
       <c r="F37" t="n">
-        <v>113.3894541507235</v>
+        <v>113.3782770794844</v>
       </c>
       <c r="G37" t="n">
-        <v>203.8565821704696</v>
+        <v>194.2045470384455</v>
       </c>
       <c r="H37" t="n">
-        <v>2.446184112153949</v>
+        <v>1.599364496584327</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1729293961000195</v>
+        <v>0.1691155543103708</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9999907812591602</v>
+        <v>0.9978273930792422</v>
       </c>
       <c r="K37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.951892182829148</v>
+        <v>-7.949100898708978</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.3894541507235</v>
+        <v>113.3782770794844</v>
       </c>
       <c r="R37" t="n">
-        <v>203.8565821704696</v>
+        <v>194.2045470384455</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.93177280134961</v>
+        <v>-7.935157244138734</v>
       </c>
       <c r="D38" t="n">
-        <v>113.3984380256375</v>
+        <v>113.3818407903523</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.951892182829148</v>
+        <v>-7.949100898708978</v>
       </c>
       <c r="F38" t="n">
-        <v>113.3894541507235</v>
+        <v>113.3782770794844</v>
       </c>
       <c r="G38" t="n">
-        <v>203.8565821704696</v>
+        <v>194.2045470384455</v>
       </c>
       <c r="H38" t="n">
-        <v>2.446184112153949</v>
+        <v>1.599364496584327</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1729293961000195</v>
+        <v>0.1691155543103708</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9267566683981214</v>
+        <v>0.9987941493569229</v>
       </c>
       <c r="K38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.951892182829148</v>
+        <v>-7.949100898708978</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3894541507235</v>
+        <v>113.3782770794844</v>
       </c>
       <c r="R38" t="n">
-        <v>203.8565821704696</v>
+        <v>194.2045470384455</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,28 +2952,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.93176915869884</v>
+        <v>-7.935157244138734</v>
       </c>
       <c r="D39" t="n">
-        <v>113.3984412055428</v>
+        <v>113.3818407903523</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.951891194217459</v>
+        <v>-7.949100898708978</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3894561445736</v>
+        <v>113.3782770794844</v>
       </c>
       <c r="G39" t="n">
-        <v>203.8565844521218</v>
+        <v>194.2045470384455</v>
       </c>
       <c r="H39" t="n">
-        <v>2.446506844050216</v>
+        <v>1.599364496584327</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1729293961150859</v>
+        <v>0.1691155543103708</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9778149966403997</v>
+        <v>0.9994159219116696</v>
       </c>
       <c r="K39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.951891194217459</v>
+        <v>-7.949100898708978</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3894561445736</v>
+        <v>113.3782770794844</v>
       </c>
       <c r="R39" t="n">
-        <v>203.8565844521218</v>
+        <v>194.2045470384455</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,28 +3017,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.931770970907572</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3984438261265</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.951899314486158</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3894559481714</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G40" t="n">
-        <v>203.8565846090159</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H40" t="n">
-        <v>2.447273806495648</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1729293961263566</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9906685468469046</v>
+        <v>0.9997847790582384</v>
       </c>
       <c r="K40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.951899314486158</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3894559481714</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R40" t="n">
-        <v>203.8565846090159</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,28 +3082,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.931769075076756</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D41" t="n">
-        <v>113.3984405176029</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.951894521287291</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3894539338488</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G41" t="n">
-        <v>203.8565838245593</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H41" t="n">
-        <v>2.446921517933479</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1729293961322074</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9982179926395743</v>
+        <v>0.9999174313049012</v>
       </c>
       <c r="K41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.951894521287291</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3894539338488</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R41" t="n">
-        <v>203.8565838245593</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,28 +3147,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.931771020923305</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3984407375584</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.951899667095491</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3894527248125</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G42" t="n">
-        <v>203.8565838210217</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H42" t="n">
-        <v>2.447310582165722</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1729293961351877</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5835171694214609</v>
+        <v>0.5857864382310809</v>
       </c>
       <c r="K42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.951899667095491</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3894527248125</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R42" t="n">
-        <v>203.8565838210217</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,28 +3212,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.931770601047662</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3984406295844</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.951897814263927</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3894532566198</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G43" t="n">
-        <v>203.8565840990742</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H43" t="n">
-        <v>2.447136362833599</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1729293961404928</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9995982112534746</v>
+        <v>0.9999989835390313</v>
       </c>
       <c r="K43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.951897814263927</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3894532566198</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R43" t="n">
-        <v>203.8565840990742</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,28 +3277,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.931770601047662</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3984406295844</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.951897814263927</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3894532566198</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G44" t="n">
-        <v>203.8565840990742</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H44" t="n">
-        <v>2.447136362833599</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1729293961404928</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9995982112117378</v>
+        <v>0.9019328834274396</v>
       </c>
       <c r="K44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.951897814263927</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3894532566198</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R44" t="n">
-        <v>203.8565840990742</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,28 +3342,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.931770601047662</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3984406295844</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.951897814263927</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3894532566198</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G45" t="n">
-        <v>203.8565840990742</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H45" t="n">
-        <v>2.447136362833599</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1729293961404928</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9999920456881926</v>
+        <v>0.9513163736295904</v>
       </c>
       <c r="K45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.951897814263927</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3894532566198</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R45" t="n">
-        <v>203.8565840990742</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.931770536240147</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3984385941497</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.951897683772569</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3894512504833</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G46" t="n">
-        <v>203.8565841803976</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H46" t="n">
-        <v>2.447128378261846</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1729293961421506</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9999920457872538</v>
+        <v>0.9861682431875606</v>
       </c>
       <c r="K46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.951897683772569</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3894512504833</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R46" t="n">
-        <v>203.8565841803976</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,28 +3472,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.931770382945968</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D47" t="n">
-        <v>113.3984388208919</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.95189825011831</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3894511558943</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G47" t="n">
-        <v>203.8565841274296</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H47" t="n">
-        <v>2.447215873997075</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1729293961422012</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999920459265104</v>
+        <v>0.9908547448471322</v>
       </c>
       <c r="K47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.95189825011831</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3894511558943</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R47" t="n">
-        <v>203.8565841274296</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,28 +3537,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.931770140189308</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D48" t="n">
-        <v>113.39843876043</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.951897887678641</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3894511488771</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G48" t="n">
-        <v>203.8565841401505</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H48" t="n">
-        <v>2.447201322691989</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1729293961425682</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999920459690085</v>
+        <v>0.9944462190104844</v>
       </c>
       <c r="K48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.951897887678641</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3894511488771</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R48" t="n">
-        <v>203.8565841401505</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,28 +3602,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.931769919655502</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3984388319867</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.951897569154091</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3894512641988</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G49" t="n">
-        <v>203.8565841349952</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H49" t="n">
-        <v>2.447189408482767</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1729293961425687</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999920460007939</v>
+        <v>0.9974891449495833</v>
       </c>
       <c r="K49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.951897569154091</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3894512641988</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R49" t="n">
-        <v>203.8565841349952</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,28 +3667,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.931770067374679</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3984386697434</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.951897724068272</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3894510987346</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G50" t="n">
-        <v>203.8565841461113</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H50" t="n">
-        <v>2.447190283490409</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1729293961426482</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J50" t="n">
-        <v>0.999992046033455</v>
+        <v>0.9984301647319515</v>
       </c>
       <c r="K50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.951897724068272</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3894510987346</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R50" t="n">
-        <v>203.8565841461113</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,28 +3732,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.931770544234709</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3984384606746</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.951897269151391</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3894513057434</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G51" t="n">
-        <v>203.8565841443645</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H51" t="n">
-        <v>2.447076994247902</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1729293961427085</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9999920460648686</v>
+        <v>0.9991943670534614</v>
       </c>
       <c r="K51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.951897269151391</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3894513057434</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R51" t="n">
-        <v>203.8565841443645</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,28 +3797,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.931770544234709</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3984384606746</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.951897269151391</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3894513057434</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G52" t="n">
-        <v>203.8565841443645</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H52" t="n">
-        <v>2.447076994247902</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1729293961427085</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5857864397085671</v>
+        <v>0.5857864173445927</v>
       </c>
       <c r="K52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.951897269151391</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3894513057434</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R52" t="n">
-        <v>203.8565841443645</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,28 +3862,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.931770544234709</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3984384606746</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.951897269151391</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3894513057434</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G53" t="n">
-        <v>203.8565841443645</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H53" t="n">
-        <v>2.447076994247902</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1729293961427085</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999999967629889</v>
+        <v>0.9999195801415046</v>
       </c>
       <c r="K53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.951897269151391</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3894513057434</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R53" t="n">
-        <v>203.8565841443645</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,28 +3927,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.931769945111932</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3984388217543</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.951897458253595</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3894513148524</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G54" t="n">
-        <v>203.8565841442734</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H54" t="n">
-        <v>2.44717282983071</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1729293961427139</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999967629731</v>
+        <v>0.9999993810070401</v>
       </c>
       <c r="K54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.951897458253595</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3894513148524</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R54" t="n">
-        <v>203.8565841442734</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,28 +3992,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.931769846970921</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3984387805286</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.951897350655975</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F55" t="n">
-        <v>113.3894512778517</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G55" t="n">
-        <v>203.8565841444265</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H55" t="n">
-        <v>2.447171680060709</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1729293961427147</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999967629609</v>
+        <v>0.9999993809670371</v>
       </c>
       <c r="K55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.951897350655975</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.3894512778517</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R55" t="n">
-        <v>203.8565841444265</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,28 +4057,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.931769781383726</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3984387893124</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G56" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H56" t="n">
-        <v>2.447187730139071</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1729293961427181</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999999967628259</v>
+        <v>0.9999993894245736</v>
       </c>
       <c r="K56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R56" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,28 +4122,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.931769781383726</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3984387893124</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G57" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H57" t="n">
-        <v>2.447187730139071</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1729293961427181</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9999999967621713</v>
+        <v>0.9999993890694445</v>
       </c>
       <c r="K57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R57" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,28 +4187,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.931769781383726</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D58" t="n">
-        <v>113.3984387893124</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G58" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H58" t="n">
-        <v>2.447187730139071</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1729293961427181</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9999999967615834</v>
+        <v>0.9999993908426814</v>
       </c>
       <c r="K58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R58" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,28 +4252,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.931769781383726</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3984387893124</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G59" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H59" t="n">
-        <v>2.447187730139071</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1729293961427181</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999970169255</v>
+        <v>0.9999993934067071</v>
       </c>
       <c r="K59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.951897417076888</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3894512276884</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R59" t="n">
-        <v>203.8565841443224</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,28 +4317,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.93176975695541</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3984388058608</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.951897401119436</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3894512404547</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G60" t="n">
-        <v>203.8565841443246</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H60" t="n">
-        <v>2.447188760060922</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999970593454</v>
+        <v>0.9999993958176414</v>
       </c>
       <c r="K60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.951897401119436</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3894512404547</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R60" t="n">
-        <v>203.8565841443246</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.93176975695541</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3984388058608</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.951897401119436</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3894512404547</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G61" t="n">
-        <v>203.8565841443246</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H61" t="n">
-        <v>2.447188760060922</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J61" t="n">
-        <v>0.999999997645393</v>
+        <v>0.9999993978239474</v>
       </c>
       <c r="K61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.951897401119436</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3894512404547</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R61" t="n">
-        <v>203.8565841443246</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,28 +4447,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.931769756509338</v>
+        <v>-7.935129287997349</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3984388068378</v>
+        <v>113.3818289122913</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.951897404962925</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3894512395162</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="G62" t="n">
-        <v>203.8565841443269</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="H62" t="n">
-        <v>2.447189281603321</v>
+        <v>1.603026112589999</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155586231238</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5358983873791384</v>
+        <v>0.5857864397789182</v>
       </c>
       <c r="K62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.951897404962925</v>
+        <v>-7.94910486310295</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3894512395162</v>
+        <v>113.3782570333771</v>
       </c>
       <c r="R62" t="n">
-        <v>203.8565841443269</v>
+        <v>194.2045843260455</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,28 +4512,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.931769707437919</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D63" t="n">
-        <v>113.3984388192308</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G63" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H63" t="n">
-        <v>2.447195532622743</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999999985159</v>
+        <v>0.9999999865115521</v>
       </c>
       <c r="K63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R63" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,28 +4577,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.931769707437919</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3984388192308</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G64" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H64" t="n">
-        <v>2.447195532622743</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9999999999987752</v>
+        <v>0.8662488561411188</v>
       </c>
       <c r="K64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R64" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,28 +4642,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.931769707437919</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3984388192308</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G65" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H65" t="n">
-        <v>2.447195532622743</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9999999999991969</v>
+        <v>0.9637690779549363</v>
       </c>
       <c r="K65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R65" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,28 +4707,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.931769707437919</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D66" t="n">
-        <v>113.3984388192308</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G66" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H66" t="n">
-        <v>2.447195532622743</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9999999999994553</v>
+        <v>0.9897462921144891</v>
       </c>
       <c r="K66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R66" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,28 +4772,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.931769707437919</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D67" t="n">
-        <v>113.3984388192308</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G67" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H67" t="n">
-        <v>2.447195532622743</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9999999999997269</v>
+        <v>0.9943746562197199</v>
       </c>
       <c r="K67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R67" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,28 +4837,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.931769707437919</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3984388192308</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G68" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H68" t="n">
-        <v>2.447195532622743</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J68" t="n">
-        <v>0.939871680184484</v>
+        <v>0.9972328675449879</v>
       </c>
       <c r="K68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.951897407304661</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3894512289516</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R68" t="n">
-        <v>203.8565841443252</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,28 +4902,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G69" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H69" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9913568667483076</v>
+        <v>0.9989687599022461</v>
       </c>
       <c r="K69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R69" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,28 +4967,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D70" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G70" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H70" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9927474317061159</v>
+        <v>0.9995951154688013</v>
       </c>
       <c r="K70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R70" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,28 +5032,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D71" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G71" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H71" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9986420690253316</v>
+        <v>0.9995951154504658</v>
       </c>
       <c r="K71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R71" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,28 +5097,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D72" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G72" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H72" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5831627019320869</v>
+        <v>0.5857864144478008</v>
       </c>
       <c r="K72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R72" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,28 +5162,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G73" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H73" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9998909867927007</v>
+        <v>0.9999999988886563</v>
       </c>
       <c r="K73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R73" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,28 +5227,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128811336473</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818194662752</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="G74" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="H74" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603157814198623</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591010312</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9999127643830191</v>
+        <v>0.8922987634651844</v>
       </c>
       <c r="K74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105534334954</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782472926486</v>
       </c>
       <c r="R74" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045893919987</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,28 +5292,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935128931386316</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818235354262</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105469566495</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782514098971</v>
       </c>
       <c r="G75" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045861069035</v>
       </c>
       <c r="H75" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603136591882893</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155591222522</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9999999999999889</v>
+        <v>0.9717262766557824</v>
       </c>
       <c r="K75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105469566495</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782514098971</v>
       </c>
       <c r="R75" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045861069035</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,28 +5357,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.93512903445144</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818267754206</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105398264109</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782546931465</v>
       </c>
       <c r="G76" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045911071132</v>
       </c>
       <c r="H76" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603116626977204</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155592189288</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9999999999999902</v>
+        <v>0.9870444800196869</v>
       </c>
       <c r="K76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105398264109</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782546931465</v>
       </c>
       <c r="R76" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045911071132</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,28 +5422,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129070526163</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818247382828</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.94910549344555</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782526411887</v>
       </c>
       <c r="G77" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045900109087</v>
       </c>
       <c r="H77" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603123398877921</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155592419161</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9999999999999902</v>
+        <v>0.9916393859380733</v>
       </c>
       <c r="K77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.94910549344555</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782526411887</v>
       </c>
       <c r="R77" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045900109087</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,28 +5487,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129358323431</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818277104523</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105448070845</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556972819</v>
       </c>
       <c r="G78" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045946998373</v>
       </c>
       <c r="H78" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603085216560317</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155593522291</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9999999999999944</v>
+        <v>0.9951943040822981</v>
       </c>
       <c r="K78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105448070845</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556972819</v>
       </c>
       <c r="R78" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045946998373</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,28 +5552,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129358323431</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818277104523</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105448070845</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556972819</v>
       </c>
       <c r="G79" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045946998373</v>
       </c>
       <c r="H79" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603085216560317</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155593522291</v>
       </c>
       <c r="J79" t="n">
-        <v>0.999999999999996</v>
+        <v>0.9980082578897582</v>
       </c>
       <c r="K79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105448070845</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556972819</v>
       </c>
       <c r="R79" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045946998373</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,28 +5617,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129358323431</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818277104523</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105448070845</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556972819</v>
       </c>
       <c r="G80" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045946998373</v>
       </c>
       <c r="H80" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603085216560317</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155593522291</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9999999999999964</v>
+        <v>0.9990083900637233</v>
       </c>
       <c r="K80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105448070845</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556972819</v>
       </c>
       <c r="R80" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045946998373</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,28 +5682,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129323400069</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818274739811</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105464771163</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782554472522</v>
       </c>
       <c r="G81" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045960903272</v>
       </c>
       <c r="H81" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603091147753307</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155593825495</v>
       </c>
       <c r="J81" t="n">
-        <v>0.999999999999998</v>
+        <v>0.9990962114873381</v>
       </c>
       <c r="K81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105464771163</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782554472522</v>
       </c>
       <c r="R81" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045960903272</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,28 +5747,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.93512932971379</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818284147667</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105417372823</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782564013152</v>
       </c>
       <c r="G82" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045978103564</v>
       </c>
       <c r="H82" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603084999048555</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155593843519</v>
       </c>
       <c r="J82" t="n">
-        <v>0.585786439731585</v>
+        <v>0.5857863642437527</v>
       </c>
       <c r="K82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105417372823</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782564013152</v>
       </c>
       <c r="R82" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045978103564</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,28 +5812,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129322566972</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818283028717</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.94910540451253</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562903044</v>
       </c>
       <c r="G83" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046000086182</v>
       </c>
       <c r="H83" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603084359269863</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559399043</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999673890871829</v>
       </c>
       <c r="K83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.94910540451253</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562903044</v>
       </c>
       <c r="R83" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046000086182</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,28 +5877,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129382515701</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818276788633</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105466504451</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556658647</v>
       </c>
       <c r="G84" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045996600893</v>
       </c>
       <c r="H84" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603084591160097</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594417458</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999797875323622</v>
       </c>
       <c r="K84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105466504451</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556658647</v>
       </c>
       <c r="R84" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2045996600893</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,28 +5942,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129561661188</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818255562572</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105511613815</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378253576978</v>
       </c>
       <c r="G85" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046017095934</v>
       </c>
       <c r="H85" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603069231449223</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594570413</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999901359785001</v>
       </c>
       <c r="K85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105511613815</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378253576978</v>
       </c>
       <c r="R85" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046017095934</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,28 +6007,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129358073587</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818276905542</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105472543283</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556694676</v>
       </c>
       <c r="G86" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046007956026</v>
       </c>
       <c r="H86" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603088095431166</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594644723</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999933680991011</v>
       </c>
       <c r="K86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105472543283</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782556694676</v>
       </c>
       <c r="R86" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046007956026</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,28 +6072,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129313619238</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818282378316</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105455822401</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562091955</v>
       </c>
       <c r="G87" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046025563513</v>
       </c>
       <c r="H87" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60309128898909</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559473752</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999961030415325</v>
       </c>
       <c r="K87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105455822401</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562091955</v>
       </c>
       <c r="R87" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046025563513</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,28 +6137,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129313619238</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818282378316</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105455822401</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562091955</v>
       </c>
       <c r="G88" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046025563513</v>
       </c>
       <c r="H88" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60309128898909</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559473752</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999976573092199</v>
       </c>
       <c r="K88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105455822401</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562091955</v>
       </c>
       <c r="R88" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046025563513</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,28 +6202,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129383151057</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818282243442</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105459871201</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562126294</v>
       </c>
       <c r="G89" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046018497286</v>
       </c>
       <c r="H89" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603083772943451</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559481696</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999989318956439</v>
       </c>
       <c r="K89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105459871201</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562126294</v>
       </c>
       <c r="R89" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046018497286</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,28 +6267,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129383151057</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818282243442</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105459871201</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562126294</v>
       </c>
       <c r="G90" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046018497286</v>
       </c>
       <c r="H90" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603083772943451</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559481696</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999993863879185</v>
       </c>
       <c r="K90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105459871201</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562126294</v>
       </c>
       <c r="R90" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046018497286</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,28 +6332,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129383151057</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818282243442</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105459871201</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562126294</v>
       </c>
       <c r="G91" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046018497286</v>
       </c>
       <c r="H91" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603083772943451</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559481696</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999999708908233</v>
       </c>
       <c r="K91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105459871201</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782562126294</v>
       </c>
       <c r="R91" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046018497286</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,28 +6397,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129349489966</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818283223757</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105457541239</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782563026042</v>
       </c>
       <c r="G92" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020372574</v>
       </c>
       <c r="H92" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603087368018573</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594844699</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5358983873791384</v>
+        <v>0.585786439779029</v>
       </c>
       <c r="K92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105457541239</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782563026042</v>
       </c>
       <c r="R92" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020372574</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,28 +6462,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129349489966</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818283223757</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105457541239</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782563026042</v>
       </c>
       <c r="G93" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020372574</v>
       </c>
       <c r="H93" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603087368018573</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594844699</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998563474</v>
       </c>
       <c r="K93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105457541239</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782563026042</v>
       </c>
       <c r="R93" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020372574</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,28 +6527,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129349489966</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818283223757</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105457541239</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782563026042</v>
       </c>
       <c r="G94" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020372574</v>
       </c>
       <c r="H94" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603087368018573</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594844699</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998553697</v>
       </c>
       <c r="K94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105457541239</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782563026042</v>
       </c>
       <c r="R94" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020372574</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,28 +6592,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129351395855</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818288322835</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="G95" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="H95" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60308584095991</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559487007</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999999999854007</v>
       </c>
       <c r="K95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="R95" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,28 +6657,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129351395855</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818288322835</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="G96" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="H96" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60308584095991</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559487007</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998368507</v>
       </c>
       <c r="K96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="R96" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,28 +6722,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129351395855</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818288322835</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="G97" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="H97" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60308584095991</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559487007</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0.9320824691400398</v>
       </c>
       <c r="K97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="R97" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,28 +6787,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129351395855</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818288322835</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="G98" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="H98" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60308584095991</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559487007</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9222914849436987</v>
+        <v>0.9704503669745945</v>
       </c>
       <c r="K98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="R98" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,28 +6852,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129351395855</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818288322835</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="G99" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="H99" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60308584095991</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559487007</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9661791264503056</v>
+        <v>0.9848340923825769</v>
       </c>
       <c r="K99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="R99" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,28 +6917,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129351395855</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818288322835</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="G100" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="H100" t="n">
-        <v>2.447195776211807</v>
+        <v>1.60308584095991</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559487007</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9950786913872675</v>
+        <v>0.9952471928755416</v>
       </c>
       <c r="K100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105446133329</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782568159125</v>
       </c>
       <c r="R100" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602046046</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,28 +6982,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G101" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H101" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9966897544142149</v>
+        <v>0.9967168954166664</v>
       </c>
       <c r="K101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R101" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,28 +7047,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G102" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H102" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5820763861834198</v>
+        <v>0.5857860255526818</v>
       </c>
       <c r="K102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R102" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,28 +7112,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G103" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H103" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J103" t="n">
-        <v>0.998568392045567</v>
+        <v>0.9999999998860378</v>
       </c>
       <c r="K103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R103" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,28 +7177,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G104" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H104" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9991590862259849</v>
+        <v>0.8311984848697278</v>
       </c>
       <c r="K104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R104" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,28 +7242,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G105" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H105" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9996820743634227</v>
+        <v>0.8953862912069395</v>
       </c>
       <c r="K105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R105" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,28 +7307,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G106" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H106" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9998361436415479</v>
+        <v>0.9758300142028836</v>
       </c>
       <c r="K106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R106" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,28 +7372,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G107" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H107" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9999539973450399</v>
+        <v>0.9683458712424103</v>
       </c>
       <c r="K107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R107" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,28 +7437,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G108" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H108" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9999797124347192</v>
+        <v>0.9893845408477422</v>
       </c>
       <c r="K108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R108" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,28 +7502,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G109" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H109" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9999937884144272</v>
+        <v>0.9949660078099276</v>
       </c>
       <c r="K109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R109" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,28 +7567,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G110" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H110" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9999996483312046</v>
+        <v>0.9967714922567112</v>
       </c>
       <c r="K110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R110" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,28 +7632,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G111" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H111" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9999996483312046</v>
+        <v>0.9981371226221196</v>
       </c>
       <c r="K111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R111" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,28 +7697,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G112" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H112" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J112" t="n">
-        <v>0.585786439731585</v>
+        <v>0.5857858314294732</v>
       </c>
       <c r="K112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R112" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,28 +7762,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G113" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H113" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9996788249544859</v>
       </c>
       <c r="K113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R113" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,28 +7827,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129339419023</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818290339753</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="G114" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="H114" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603086712735484</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.169115559488294</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9997893685658509</v>
       </c>
       <c r="K114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105441754296</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782570156517</v>
       </c>
       <c r="R114" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020872975</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,28 +7892,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155791893</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292956835</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436640846</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572317246</v>
       </c>
       <c r="G115" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046021279835</v>
       </c>
       <c r="H115" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107188920164</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594883134</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9998685471242427</v>
       </c>
       <c r="K115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436640846</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572317246</v>
       </c>
       <c r="R115" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046021279835</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,28 +7957,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155586533</v>
       </c>
       <c r="D116" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829295685</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436477221</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572317248</v>
       </c>
       <c r="G116" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602092164</v>
       </c>
       <c r="H116" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107193453074</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594886526</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999252619101496</v>
       </c>
       <c r="K116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436477221</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572317248</v>
       </c>
       <c r="R116" t="n">
-        <v>203.8565841443273</v>
+        <v>194.204602092164</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,28 +8022,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595614</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957082</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436757863</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316797</v>
       </c>
       <c r="G117" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020882634</v>
       </c>
       <c r="H117" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107224574423</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594890039</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999581792270327</v>
       </c>
       <c r="K117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436757863</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316797</v>
       </c>
       <c r="R117" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020882634</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595614</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957082</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436757863</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316797</v>
       </c>
       <c r="G118" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020882634</v>
       </c>
       <c r="H118" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107224574423</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594890039</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999742238504361</v>
       </c>
       <c r="K118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436757863</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316797</v>
       </c>
       <c r="R118" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020882634</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,28 +8152,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595614</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957082</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436757863</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316797</v>
       </c>
       <c r="G119" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020882634</v>
       </c>
       <c r="H119" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107224574423</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594890039</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999911155360344</v>
       </c>
       <c r="K119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436757863</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316797</v>
       </c>
       <c r="R119" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020882634</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,28 +8217,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G120" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H120" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999936327593004</v>
       </c>
       <c r="K120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R120" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,28 +8282,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G121" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H121" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J121" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999944251854127</v>
       </c>
       <c r="K121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R121" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,28 +8347,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G122" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H122" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5358983873791384</v>
+        <v>0.5857864397700173</v>
       </c>
       <c r="K122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R122" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,28 +8412,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G123" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H123" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J123" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999961207</v>
       </c>
       <c r="K123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R123" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,28 +8477,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G124" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H124" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999961502</v>
       </c>
       <c r="K124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R124" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,28 +8542,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G125" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H125" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999999999996136</v>
       </c>
       <c r="K125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R125" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,28 +8607,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155595363</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292957086</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="G126" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="H126" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107236418909</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892474</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999961169</v>
       </c>
       <c r="K126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436861458</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3894512270442</v>
+        <v>113.378257231656</v>
       </c>
       <c r="R126" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020788488</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,28 +8672,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155617036</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292956747</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436863054</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316274</v>
       </c>
       <c r="G127" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020780161</v>
       </c>
       <c r="H127" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107234110385</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.16911555948925</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0.9999999999966709</v>
       </c>
       <c r="K127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436863054</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316274</v>
       </c>
       <c r="R127" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020780161</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,28 +8737,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155617036</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292956747</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436863054</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316274</v>
       </c>
       <c r="G128" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020780161</v>
       </c>
       <c r="H128" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107234110385</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.16911555948925</v>
       </c>
       <c r="J128" t="n">
-        <v>0.8577194931596667</v>
+        <v>0.9999999999966656</v>
       </c>
       <c r="K128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436863054</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572316274</v>
       </c>
       <c r="R128" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020780161</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,28 +8802,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609532</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292963957</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436844022</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323513</v>
       </c>
       <c r="G129" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020784183</v>
       </c>
       <c r="H129" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232790649</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892544</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9598513398742358</v>
+        <v>0.9999999999971836</v>
       </c>
       <c r="K129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436844022</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323513</v>
       </c>
       <c r="R129" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020784183</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,28 +8867,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609532</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292963957</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436844022</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323513</v>
       </c>
       <c r="G130" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020784183</v>
       </c>
       <c r="H130" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232790649</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892544</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9865042634185822</v>
+        <v>0.9999999999971758</v>
       </c>
       <c r="K130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436844022</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323513</v>
       </c>
       <c r="R130" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020784183</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,28 +8932,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155624161</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292969938</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436828582</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572329571</v>
       </c>
       <c r="G131" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783218</v>
       </c>
       <c r="H131" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107229340829</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892548</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9945503266705301</v>
+        <v>0.9999999999971698</v>
       </c>
       <c r="K131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436828582</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572329571</v>
       </c>
       <c r="R131" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783218</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,28 +8997,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155624161</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292969938</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436828582</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572329571</v>
       </c>
       <c r="G132" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783218</v>
       </c>
       <c r="H132" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107229340829</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892548</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5810862854775244</v>
+        <v>0.5857864397790489</v>
       </c>
       <c r="K132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436828582</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572329571</v>
       </c>
       <c r="R132" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783218</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,28 +9062,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D133" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G133" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H133" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9974909629920715</v>
+        <v>0.9999999999984317</v>
       </c>
       <c r="K133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R133" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,28 +9127,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D134" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G134" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H134" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9980994178405708</v>
+        <v>0.8836623373176767</v>
       </c>
       <c r="K134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R134" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,28 +9192,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D135" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G135" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H135" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9987128386050378</v>
+        <v>0.9225525060295114</v>
       </c>
       <c r="K135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R135" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,28 +9257,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D136" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G136" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H136" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9995293078785104</v>
+        <v>0.9799162716310063</v>
       </c>
       <c r="K136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R136" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,28 +9322,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D137" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G137" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H137" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9999402979262164</v>
+        <v>0.9605679916480718</v>
       </c>
       <c r="K137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R137" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,28 +9387,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D138" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G138" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H138" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9902929798264019</v>
       </c>
       <c r="K138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R138" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,28 +9452,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D139" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G139" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H139" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9927837936207871</v>
       </c>
       <c r="K139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R139" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,28 +9517,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D140" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G140" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H140" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9945243878304524</v>
       </c>
       <c r="K140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R140" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,28 +9582,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D141" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G141" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H141" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9956262089737559</v>
       </c>
       <c r="K141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R141" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,28 +9647,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D142" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G142" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H142" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J142" t="n">
-        <v>0.585786439731585</v>
+        <v>0.5857854018778058</v>
       </c>
       <c r="K142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R142" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,28 +9712,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D143" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G143" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H143" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9998792412285797</v>
       </c>
       <c r="K143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R143" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,28 +9777,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D144" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G144" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H144" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999550280152707</v>
       </c>
       <c r="K144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R144" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,28 +9842,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D145" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G145" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H145" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999654301437622</v>
       </c>
       <c r="K145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R145" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,28 +9907,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D146" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G146" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H146" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J146" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999700954631682</v>
       </c>
       <c r="K146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R146" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,28 +9972,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D147" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G147" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H147" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J147" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999736027104396</v>
       </c>
       <c r="K147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R147" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,28 +10037,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155609922</v>
       </c>
       <c r="D148" t="n">
-        <v>113.3984388182181</v>
+        <v>113.381829296387</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="G148" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="H148" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232970845</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892562</v>
       </c>
       <c r="J148" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999983075972174</v>
       </c>
       <c r="K148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436845987</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572323422</v>
       </c>
       <c r="R148" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783227</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,28 +10102,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155608409</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292965556</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436842916</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572325112</v>
       </c>
       <c r="G149" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783687</v>
       </c>
       <c r="H149" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232792425</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892583</v>
       </c>
       <c r="J149" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999990768312122</v>
       </c>
       <c r="K149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436842916</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572325112</v>
       </c>
       <c r="R149" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783687</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,28 +10167,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155608409</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292965556</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436842916</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572325112</v>
       </c>
       <c r="G150" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783687</v>
       </c>
       <c r="H150" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232792425</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892583</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999945705198851</v>
       </c>
       <c r="K150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436842916</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572325112</v>
       </c>
       <c r="R150" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783687</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,28 +10232,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.931769705836016</v>
+        <v>-7.935129155608409</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3984388182181</v>
+        <v>113.3818292965556</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436842916</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572325112</v>
       </c>
       <c r="G151" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783687</v>
       </c>
       <c r="H151" t="n">
-        <v>2.447195776211807</v>
+        <v>1.603107232792425</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1729293961427182</v>
+        <v>0.1691155594892583</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999981469049051</v>
       </c>
       <c r="K151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.951897407706222</v>
+        <v>-7.949105436842916</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3894512270442</v>
+        <v>113.3782572325112</v>
       </c>
       <c r="R151" t="n">
-        <v>203.8565841443273</v>
+        <v>194.2046020783687</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>44644.05902777778</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C2" t="n">
-        <v>-7.947867928369328</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D2" t="n">
-        <v>113.3074755112753</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.839189875639692</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F2" t="n">
-        <v>113.378025580751</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G2" t="n">
-        <v>32.74647274213618</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H2" t="n">
-        <v>14.36712313457345</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1641927143608508</v>
+        <v>0.1679254052837848</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9187573774091462</v>
+        <v>0.8933715789130053</v>
       </c>
       <c r="K2" t="n">
-        <v>640</v>
+        <v>1965</v>
       </c>
       <c r="L2" t="n">
-        <v>177</v>
+        <v>1797</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>44644.05902777778</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.79336507804223</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O2" t="n">
-        <v>113.335282392927</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.839189875639692</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.378025580751</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R2" t="n">
-        <v>32.74647274213618</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.96129127356304</v>
+        <v>-8.255056508970146</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3552544675357</v>
+        <v>113.0667176706558</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.989089105274556</v>
+        <v>-8.010079034232739</v>
       </c>
       <c r="F3" t="n">
-        <v>113.3475090217036</v>
+        <v>113.4345186639489</v>
       </c>
       <c r="G3" t="n">
-        <v>195.425773541009</v>
+        <v>56.09242779191669</v>
       </c>
       <c r="H3" t="n">
-        <v>3.206497185012513</v>
+        <v>48.79723557279398</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1675011495850191</v>
+        <v>0.1682815433852565</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9613088319438954</v>
+        <v>0.9628103986004636</v>
       </c>
       <c r="K3" t="n">
-        <v>640</v>
+        <v>722</v>
       </c>
       <c r="L3" t="n">
-        <v>640</v>
+        <v>1797</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O3" t="n">
-        <v>113.300380121246</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.989089105274556</v>
+        <v>-8.010079034232739</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.3475090217036</v>
+        <v>113.4345186639489</v>
       </c>
       <c r="R3" t="n">
-        <v>195.425773541009</v>
+        <v>56.09242779191669</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.926102288494857</v>
+        <v>-8.101897752714503</v>
       </c>
       <c r="D4" t="n">
-        <v>113.3671634648504</v>
+        <v>112.6207535159278</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.965640806314738</v>
+        <v>-7.99321280084413</v>
       </c>
       <c r="F4" t="n">
-        <v>113.3915743714693</v>
+        <v>113.3632245281443</v>
       </c>
       <c r="G4" t="n">
-        <v>148.5572331822311</v>
+        <v>81.64247362790093</v>
       </c>
       <c r="H4" t="n">
-        <v>5.15325741564665</v>
+        <v>82.63446466657469</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1682212131858368</v>
+        <v>0.1693973804906765</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9819490797408548</v>
+        <v>0.9859035126578413</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>1513</v>
       </c>
       <c r="L4" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O4" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.965640806314738</v>
+        <v>-7.99321280084413</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.3915743714693</v>
+        <v>113.3632245281443</v>
       </c>
       <c r="R4" t="n">
-        <v>148.5572331822311</v>
+        <v>81.64247362790093</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -742,31 +742,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.943522319851359</v>
+        <v>-7.738217714529264</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3791845475469</v>
+        <v>113.126709635821</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.93509623774929</v>
+        <v>-7.96020974113866</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3823580655979</v>
+        <v>113.3848862157687</v>
       </c>
       <c r="G5" t="n">
-        <v>20.4567555795892</v>
+        <v>130.9748215291114</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>37.65756543844378</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1686407747086151</v>
+        <v>0.1696169906238353</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9889994225917201</v>
+        <v>0.9910714979141665</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>1040</v>
       </c>
       <c r="L5" t="n">
         <v>448</v>
@@ -781,13 +781,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.93509623774929</v>
+        <v>-7.96020974113866</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3823580655979</v>
+        <v>113.3848862157687</v>
       </c>
       <c r="R5" t="n">
-        <v>20.4567555795892</v>
+        <v>130.9748215291114</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -807,31 +807,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.943522319851359</v>
+        <v>-7.726044914981562</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3791845475469</v>
+        <v>113.0404847906876</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.93509623774929</v>
+        <v>-7.927303158219137</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3823580655979</v>
+        <v>113.3861979675387</v>
       </c>
       <c r="G6" t="n">
-        <v>20.4567555795892</v>
+        <v>120.4631305281684</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>44.171965681355</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1686407747086151</v>
+        <v>0.1697969874684987</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9944642961142206</v>
+        <v>0.9955290670651344</v>
       </c>
       <c r="K6" t="n">
-        <v>448</v>
+        <v>1324</v>
       </c>
       <c r="L6" t="n">
         <v>448</v>
@@ -846,13 +846,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.93509623774929</v>
+        <v>-7.927303158219137</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3823580655979</v>
+        <v>113.3861979675387</v>
       </c>
       <c r="R6" t="n">
-        <v>20.4567555795892</v>
+        <v>120.4631305281684</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -872,31 +872,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.225016297938462</v>
+        <v>-7.726044914981562</v>
       </c>
       <c r="D7" t="n">
-        <v>113.1616550455066</v>
+        <v>113.0404847906876</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.956047255311736</v>
+        <v>-7.927303158219137</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3968308216227</v>
+        <v>113.3861979675387</v>
       </c>
       <c r="G7" t="n">
-        <v>40.89796033545344</v>
+        <v>120.4631305281684</v>
       </c>
       <c r="H7" t="n">
-        <v>39.55733557103636</v>
+        <v>44.171965681355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1687109979315386</v>
+        <v>0.1697969874684987</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9965890832207198</v>
+        <v>0.9982165955223239</v>
       </c>
       <c r="K7" t="n">
-        <v>398</v>
+        <v>1324</v>
       </c>
       <c r="L7" t="n">
         <v>448</v>
@@ -911,13 +911,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.956047255311736</v>
+        <v>-7.927303158219137</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3968308216227</v>
+        <v>113.3861979675387</v>
       </c>
       <c r="R7" t="n">
-        <v>40.89796033545344</v>
+        <v>120.4631305281684</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.814333575025198</v>
+        <v>-7.770920823964929</v>
       </c>
       <c r="D8" t="n">
-        <v>113.4189835525487</v>
+        <v>113.3799398044293</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.946745369609505</v>
+        <v>-7.913133381383831</v>
       </c>
       <c r="F8" t="n">
-        <v>113.3793820597618</v>
+        <v>113.4022789685156</v>
       </c>
       <c r="G8" t="n">
-        <v>196.4994132530685</v>
+        <v>171.1564439659265</v>
       </c>
       <c r="H8" t="n">
-        <v>15.35604729386361</v>
+        <v>16.00363459847289</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1690778794693271</v>
+        <v>0.1699814335786982</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9978072192317542</v>
+        <v>0.9984061581537678</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>177</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.946745369609505</v>
+        <v>-7.913133381383831</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.3793820597618</v>
+        <v>113.4022789685156</v>
       </c>
       <c r="R8" t="n">
-        <v>196.4994132530685</v>
+        <v>171.1564439659265</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.814333575025198</v>
+        <v>-8.41915246918764</v>
       </c>
       <c r="D9" t="n">
-        <v>113.4189835525487</v>
+        <v>113.4360155133922</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.946745369609505</v>
+        <v>-7.954538126498549</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3793820597618</v>
+        <v>113.3715543072167</v>
       </c>
       <c r="G9" t="n">
-        <v>196.4994132530685</v>
+        <v>352.176017860133</v>
       </c>
       <c r="H9" t="n">
-        <v>15.35604729386361</v>
+        <v>52.14762876256662</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1690778794693271</v>
+        <v>0.1701299312214346</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9978315161026738</v>
+        <v>0.9991061019689619</v>
       </c>
       <c r="K9" t="n">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="L9" t="n">
         <v>448</v>
@@ -1041,13 +1041,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.946745369609505</v>
+        <v>-7.954538126498549</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3793820597618</v>
+        <v>113.3715543072167</v>
       </c>
       <c r="R9" t="n">
-        <v>196.4994132530685</v>
+        <v>352.176017860133</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.932364914074645</v>
+        <v>-7.735685288427248</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3840960278918</v>
+        <v>113.3781915615327</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.933736578537498</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3812081687555</v>
+        <v>113.4111180701158</v>
       </c>
       <c r="G10" t="n">
-        <v>194.206326405441</v>
+        <v>170.6495582317482</v>
       </c>
       <c r="H10" t="n">
-        <v>1.295905899775964</v>
+        <v>22.31899116659481</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1690963695774643</v>
+        <v>0.170371898424366</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9980715396425361</v>
+        <v>0.9991286400184149</v>
       </c>
       <c r="K10" t="n">
-        <v>448</v>
+        <v>750</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.933736578537498</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3812081687555</v>
+        <v>113.4111180701158</v>
       </c>
       <c r="R10" t="n">
-        <v>194.206326405441</v>
+        <v>170.6495582317482</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,28 +1132,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.932364914074645</v>
+        <v>-7.914112089196164</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3840960278918</v>
+        <v>113.3782170634299</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.93849667672547</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3778123750454</v>
       </c>
       <c r="G11" t="n">
-        <v>194.206326405441</v>
+        <v>180.9416877020236</v>
       </c>
       <c r="H11" t="n">
-        <v>1.295905899775964</v>
+        <v>2.711808701855622</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1690963695774643</v>
+        <v>0.1704457133801957</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9984038066360325</v>
+        <v>0.9990238497810509</v>
       </c>
       <c r="K11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.93849667672547</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3778123750454</v>
       </c>
       <c r="R11" t="n">
-        <v>194.206326405441</v>
+        <v>180.9416877020236</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,28 +1197,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.932364914074645</v>
+        <v>-7.914112089196164</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3840960278918</v>
+        <v>113.3782170634299</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.93849667672547</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3778123750454</v>
       </c>
       <c r="G12" t="n">
-        <v>194.206326405441</v>
+        <v>180.9416877020236</v>
       </c>
       <c r="H12" t="n">
-        <v>1.295905899775964</v>
+        <v>2.711808701855622</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1690963695774643</v>
+        <v>0.1704457133801957</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857861349207074</v>
+        <v>0.5857861082398321</v>
       </c>
       <c r="K12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.93849667672547</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3778123750454</v>
       </c>
       <c r="R12" t="n">
-        <v>194.206326405441</v>
+        <v>180.9416877020236</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,28 +1262,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.932364914074645</v>
+        <v>-7.914112089196164</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3840960278918</v>
+        <v>113.3782170634299</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.93849667672547</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3778123750454</v>
       </c>
       <c r="G13" t="n">
-        <v>194.206326405441</v>
+        <v>180.9416877020236</v>
       </c>
       <c r="H13" t="n">
-        <v>1.295905899775964</v>
+        <v>2.711808701855622</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1690963695774643</v>
+        <v>0.1704457133801957</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9995332506122246</v>
+        <v>0.9992149563536475</v>
       </c>
       <c r="K13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.93849667672547</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3778123750454</v>
       </c>
       <c r="R13" t="n">
-        <v>194.206326405441</v>
+        <v>180.9416877020236</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,28 +1327,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.932364914074645</v>
+        <v>-7.959868643831213</v>
       </c>
       <c r="D14" t="n">
-        <v>113.3840960278918</v>
+        <v>113.3820176847885</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.941450437054986</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3809932184983</v>
       </c>
       <c r="G14" t="n">
-        <v>194.206326405441</v>
+        <v>356.8468171369818</v>
       </c>
       <c r="H14" t="n">
-        <v>1.295905899775964</v>
+        <v>2.051116313021375</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1690963695774643</v>
+        <v>0.170490767429646</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9997613577522477</v>
+        <v>0.999350932315354</v>
       </c>
       <c r="K14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.943662855187292</v>
+        <v>-7.941450437054986</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3812081687555</v>
+        <v>113.3809932184983</v>
       </c>
       <c r="R14" t="n">
-        <v>194.206326405441</v>
+        <v>356.8468171369818</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,28 +1392,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.931704885925249</v>
+        <v>-7.938271682285249</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3806092839204</v>
+        <v>113.3909766065826</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.947536443061961</v>
+        <v>-7.949340365384529</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3764714394255</v>
+        <v>113.3846938271116</v>
       </c>
       <c r="G15" t="n">
-        <v>194.5128101495441</v>
+        <v>209.3429893996786</v>
       </c>
       <c r="H15" t="n">
-        <v>1.818413712528139</v>
+        <v>1.411935354639404</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1691074674061562</v>
+        <v>0.1705820843619282</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9997504449474823</v>
+        <v>0.9994420528159198</v>
       </c>
       <c r="K15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.947536443061961</v>
+        <v>-7.949340365384529</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3764714394255</v>
+        <v>113.3846938271116</v>
       </c>
       <c r="R15" t="n">
-        <v>194.5128101495441</v>
+        <v>209.3429893996786</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,28 +1457,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.931704885925249</v>
+        <v>-7.938271682285249</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3806092839204</v>
+        <v>113.3909766065826</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.947536443061961</v>
+        <v>-7.949340365384529</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3764714394255</v>
+        <v>113.3846938271116</v>
       </c>
       <c r="G16" t="n">
-        <v>194.5128101495441</v>
+        <v>209.3429893996786</v>
       </c>
       <c r="H16" t="n">
-        <v>1.818413712528139</v>
+        <v>1.411935354639404</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1691074674061562</v>
+        <v>0.1705820843619282</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9997867673416199</v>
+        <v>0.9995759277526822</v>
       </c>
       <c r="K16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.947536443061961</v>
+        <v>-7.949340365384529</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3764714394255</v>
+        <v>113.3846938271116</v>
       </c>
       <c r="R16" t="n">
-        <v>194.5128101495441</v>
+        <v>209.3429893996786</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,28 +1522,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.931704885925249</v>
+        <v>-7.947702122847227</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3806092839204</v>
+        <v>113.3865719485718</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.947536443061961</v>
+        <v>-7.955537129617198</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3764714394255</v>
+        <v>113.382114272635</v>
       </c>
       <c r="G17" t="n">
-        <v>194.5128101495441</v>
+        <v>209.3997860354122</v>
       </c>
       <c r="H17" t="n">
-        <v>1.818413712528139</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1691074674061562</v>
+        <v>0.1706210251935186</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9998949678548994</v>
+        <v>0.9995683064625214</v>
       </c>
       <c r="K17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.947536443061961</v>
+        <v>-7.955537129617198</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3764714394255</v>
+        <v>113.382114272635</v>
       </c>
       <c r="R17" t="n">
-        <v>194.5128101495441</v>
+        <v>209.3997860354122</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,28 +1587,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.937090731039494</v>
+        <v>-7.947702122847227</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3806339267365</v>
+        <v>113.3865719485718</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.947639022309905</v>
+        <v>-7.955537129617198</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3778938561207</v>
+        <v>113.382114272635</v>
       </c>
       <c r="G18" t="n">
-        <v>194.4275580551568</v>
+        <v>209.3997860354122</v>
       </c>
       <c r="H18" t="n">
-        <v>1.211111776661287</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1691100046675392</v>
+        <v>0.1706210251935186</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9999064162494532</v>
+        <v>0.999604522647991</v>
       </c>
       <c r="K18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.947639022309905</v>
+        <v>-7.955537129617198</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3778938561207</v>
+        <v>113.382114272635</v>
       </c>
       <c r="R18" t="n">
-        <v>194.4275580551568</v>
+        <v>209.3997860354122</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,28 +1652,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.932302701813747</v>
+        <v>-7.91899414242556</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3818137982797</v>
+        <v>113.4134441270997</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.948014915300992</v>
+        <v>-7.955525995048466</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3778042570112</v>
+        <v>113.3990398165049</v>
       </c>
       <c r="G19" t="n">
-        <v>194.1836147518199</v>
+        <v>201.3305043703332</v>
       </c>
       <c r="H19" t="n">
-        <v>1.802055384810859</v>
+        <v>4.360917032954333</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1691136021123909</v>
+        <v>0.1706397566016419</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9999250358382268</v>
+        <v>0.9996067259011443</v>
       </c>
       <c r="K19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.948014915300992</v>
+        <v>-7.955525995048466</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3778042570112</v>
+        <v>113.3990398165049</v>
       </c>
       <c r="R19" t="n">
-        <v>194.1836147518199</v>
+        <v>201.3305043703332</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,28 +1717,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.932423545001386</v>
+        <v>-7.916317032781318</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3823116426105</v>
+        <v>113.400305680087</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.952265126424391</v>
+        <v>-7.951466913291271</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3770923187126</v>
+        <v>113.3854899387964</v>
       </c>
       <c r="G20" t="n">
-        <v>194.6021091711648</v>
+        <v>202.6579175163671</v>
       </c>
       <c r="H20" t="n">
-        <v>2.279928754847273</v>
+        <v>4.235400251132539</v>
       </c>
       <c r="I20" t="n">
-        <v>0.169114133349757</v>
+        <v>0.1706499980213441</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9999326571264477</v>
+        <v>0.9996626006977419</v>
       </c>
       <c r="K20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.952265126424391</v>
+        <v>-7.951466913291271</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3770923187126</v>
+        <v>113.3854899387964</v>
       </c>
       <c r="R20" t="n">
-        <v>194.6021091711648</v>
+        <v>202.6579175163671</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,28 +1782,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.933935641820739</v>
+        <v>-7.916481322995805</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3820917199969</v>
+        <v>113.4031380379135</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.952383649114564</v>
+        <v>-7.951016691974005</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3772328575177</v>
+        <v>113.3871872886383</v>
       </c>
       <c r="G21" t="n">
-        <v>194.6197276109303</v>
+        <v>204.5804462522061</v>
       </c>
       <c r="H21" t="n">
-        <v>2.119967578079638</v>
+        <v>4.222876542773905</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1691143514052757</v>
+        <v>0.1706611403727026</v>
       </c>
       <c r="J21" t="n">
-        <v>0.999933326327033</v>
+        <v>0.9996808242919336</v>
       </c>
       <c r="K21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.952383649114564</v>
+        <v>-7.951016691974005</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3772328575177</v>
+        <v>113.3871872886383</v>
       </c>
       <c r="R21" t="n">
-        <v>194.6197276109303</v>
+        <v>204.5804462522061</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,28 +1847,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.933935641820739</v>
+        <v>-7.917916702454285</v>
       </c>
       <c r="D22" t="n">
-        <v>113.3820917199969</v>
+        <v>113.404703815219</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.952383649114564</v>
+        <v>-7.949085954770045</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3772328575177</v>
+        <v>113.3910100273796</v>
       </c>
       <c r="G22" t="n">
-        <v>194.6197276109303</v>
+        <v>203.514430962688</v>
       </c>
       <c r="H22" t="n">
-        <v>2.119967578079638</v>
+        <v>3.779760343050134</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1691143514052757</v>
+        <v>0.1706665099702728</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857864386166005</v>
+        <v>0.5857864090197962</v>
       </c>
       <c r="K22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.952383649114564</v>
+        <v>-7.949085954770045</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3772328575177</v>
+        <v>113.3910100273796</v>
       </c>
       <c r="R22" t="n">
-        <v>194.6197276109303</v>
+        <v>203.514430962688</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,28 +1912,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.930735546699901</v>
+        <v>-7.917916702454285</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3831644646909</v>
+        <v>113.404703815219</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.952206915234053</v>
+        <v>-7.949085954770045</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3774823420989</v>
+        <v>113.3910100273796</v>
       </c>
       <c r="G23" t="n">
-        <v>194.6864278958238</v>
+        <v>203.514430962688</v>
       </c>
       <c r="H23" t="n">
-        <v>2.468151382606349</v>
+        <v>3.779760343050134</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1691147355424501</v>
+        <v>0.1706665099702728</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999705214496372</v>
+        <v>0.9998927692047022</v>
       </c>
       <c r="K23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.952206915234053</v>
+        <v>-7.949085954770045</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3774823420989</v>
+        <v>113.3910100273796</v>
       </c>
       <c r="R23" t="n">
-        <v>194.6864278958238</v>
+        <v>203.514430962688</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,28 +1977,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.9363307350598</v>
+        <v>-7.917744132026058</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3816070427228</v>
+        <v>113.4053187394624</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.9528019363903</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3783656318469</v>
+        <v>113.3898747327368</v>
       </c>
       <c r="G24" t="n">
-        <v>194.2269934830118</v>
+        <v>203.5711337979874</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4524713502873</v>
+        <v>4.25314574250459</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1691151142839517</v>
+        <v>0.170670846405363</v>
       </c>
       <c r="J24" t="n">
-        <v>0.999969882184872</v>
+        <v>0.9998943864935864</v>
       </c>
       <c r="K24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.9528019363903</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3783656318469</v>
+        <v>113.3898747327368</v>
       </c>
       <c r="R24" t="n">
-        <v>194.2269934830118</v>
+        <v>203.5711337979874</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,28 +2042,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.9363307350598</v>
+        <v>-7.917744132026058</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3816070427228</v>
+        <v>113.4053187394624</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.9528019363903</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3783656318469</v>
+        <v>113.3898747327368</v>
       </c>
       <c r="G25" t="n">
-        <v>194.2269934830118</v>
+        <v>203.5711337979874</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4524713502873</v>
+        <v>4.25314574250459</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1691151142839517</v>
+        <v>0.170670846405363</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999707692471416</v>
+        <v>0.9998922787487626</v>
       </c>
       <c r="K25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.9528019363903</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3783656318469</v>
+        <v>113.3898747327368</v>
       </c>
       <c r="R25" t="n">
-        <v>194.2269934830118</v>
+        <v>203.5711337979874</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,28 +2107,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.9363307350598</v>
+        <v>-7.918183291835926</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3816070427228</v>
+        <v>113.4042180225119</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.950973968086616</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3783656318469</v>
+        <v>113.38964995096</v>
       </c>
       <c r="G26" t="n">
-        <v>194.2269934830118</v>
+        <v>203.7495201828353</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4524713502873</v>
+        <v>3.983530878554759</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1691151142839517</v>
+        <v>0.170673034871195</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9999702622177341</v>
+        <v>0.9998957938360465</v>
       </c>
       <c r="K26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.950973968086616</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3783656318469</v>
+        <v>113.38964995096</v>
       </c>
       <c r="R26" t="n">
-        <v>194.2269934830118</v>
+        <v>203.7495201828353</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,28 +2172,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.9363307350598</v>
+        <v>-7.917624474186056</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3816070427228</v>
+        <v>113.4049037045998</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.950955424344479</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3783656318469</v>
+        <v>113.390024685489</v>
       </c>
       <c r="G27" t="n">
-        <v>194.2269934830118</v>
+        <v>203.8505894017848</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4524713502873</v>
+        <v>4.052317677599845</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1691151142839517</v>
+        <v>0.1706745639092326</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999700131020605</v>
+        <v>0.9998943491431822</v>
       </c>
       <c r="K27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.948992483440768</v>
+        <v>-7.950955424344479</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3783656318469</v>
+        <v>113.390024685489</v>
       </c>
       <c r="R27" t="n">
-        <v>194.2269934830118</v>
+        <v>203.8505894017848</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,28 +2237,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.935001573163057</v>
+        <v>-7.917624474186056</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3825449725664</v>
+        <v>113.4049037045998</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.948921906577493</v>
+        <v>-7.950955424344479</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3789864151545</v>
+        <v>113.390024685489</v>
       </c>
       <c r="G28" t="n">
-        <v>194.2076443647023</v>
+        <v>203.8505894017848</v>
       </c>
       <c r="H28" t="n">
-        <v>1.596711363070815</v>
+        <v>4.052317677599845</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1691151458214825</v>
+        <v>0.1706745639092326</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9999698579870342</v>
+        <v>0.9998930846912557</v>
       </c>
       <c r="K28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.948921906577493</v>
+        <v>-7.950955424344479</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3789864151545</v>
+        <v>113.390024685489</v>
       </c>
       <c r="R28" t="n">
-        <v>194.2076443647023</v>
+        <v>203.8505894017848</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,28 +2302,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.935725089773809</v>
+        <v>-7.918280135225645</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3819369956138</v>
+        <v>113.4043876974362</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.94906418042172</v>
+        <v>-7.952533090483195</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3785237064973</v>
+        <v>113.3890891691729</v>
       </c>
       <c r="G29" t="n">
-        <v>194.2209084143495</v>
+        <v>203.8614827109384</v>
       </c>
       <c r="H29" t="n">
-        <v>1.530130425114914</v>
+        <v>4.164764515973709</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1691152648452529</v>
+        <v>0.1706746813552636</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9999696637453168</v>
+        <v>0.9998890778027958</v>
       </c>
       <c r="K29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.94906418042172</v>
+        <v>-7.952533090483195</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3785237064973</v>
+        <v>113.3890891691729</v>
       </c>
       <c r="R29" t="n">
-        <v>194.2209084143495</v>
+        <v>203.8614827109384</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,28 +2367,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.935134438766756</v>
+        <v>-7.918124929003439</v>
       </c>
       <c r="D30" t="n">
-        <v>113.3819145555529</v>
+        <v>113.4049009603228</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.949002594893251</v>
+        <v>-7.951807116313794</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3783691400798</v>
+        <v>113.3898656155844</v>
       </c>
       <c r="G30" t="n">
-        <v>194.2083974304193</v>
+        <v>203.8498848182091</v>
       </c>
       <c r="H30" t="n">
-        <v>1.590731731345557</v>
+        <v>4.094998545275955</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1691153914989246</v>
+        <v>0.1706750105971539</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9999694311150783</v>
+        <v>0.9998874674377778</v>
       </c>
       <c r="K30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.949002594893251</v>
+        <v>-7.951807116313794</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3783691400798</v>
+        <v>113.3898656155844</v>
       </c>
       <c r="R30" t="n">
-        <v>194.2083974304193</v>
+        <v>203.8498848182091</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,28 +2432,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.935080164435876</v>
+        <v>-7.91948776313358</v>
       </c>
       <c r="D31" t="n">
-        <v>113.3817698600656</v>
+        <v>113.4043081749422</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.949041893553512</v>
+        <v>-7.952375879615643</v>
       </c>
       <c r="F31" t="n">
-        <v>113.3782018967505</v>
+        <v>113.3896231681475</v>
       </c>
       <c r="G31" t="n">
-        <v>194.203147044711</v>
+        <v>203.8558143346886</v>
       </c>
       <c r="H31" t="n">
-        <v>1.601427780203694</v>
+        <v>3.99863957690421</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1691154674727551</v>
+        <v>0.1706750606286309</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9999691622534803</v>
+        <v>0.9998866823479516</v>
       </c>
       <c r="K31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.949041893553512</v>
+        <v>-7.952375879615643</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.3782018967505</v>
+        <v>113.3896231681475</v>
       </c>
       <c r="R31" t="n">
-        <v>194.203147044711</v>
+        <v>203.8558143346886</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,28 +2497,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.935080164435876</v>
+        <v>-7.9187356782394</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3817698600656</v>
+        <v>113.404847210497</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.949041893553512</v>
+        <v>-7.952045346301336</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3782018967505</v>
+        <v>113.3899719226413</v>
       </c>
       <c r="G32" t="n">
-        <v>194.203147044711</v>
+        <v>203.8587536000786</v>
       </c>
       <c r="H32" t="n">
-        <v>1.601427780203694</v>
+        <v>4.049985424400656</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1691154674727551</v>
+        <v>0.1706751307071933</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5857864394873332</v>
+        <v>0.5857864352335281</v>
       </c>
       <c r="K32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.949041893553512</v>
+        <v>-7.952045346301336</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3782018967505</v>
+        <v>113.3899719226413</v>
       </c>
       <c r="R32" t="n">
-        <v>194.203147044711</v>
+        <v>203.8587536000786</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,28 +2562,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.935181863743059</v>
+        <v>-7.918988781735165</v>
       </c>
       <c r="D33" t="n">
-        <v>113.3816694917427</v>
+        <v>113.4048444736798</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.949102647377718</v>
+        <v>-7.952025138929545</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3781116122908</v>
+        <v>113.3900913498006</v>
       </c>
       <c r="G33" t="n">
-        <v>194.2046003452098</v>
+        <v>203.8585979897402</v>
       </c>
       <c r="H33" t="n">
-        <v>1.596741528669094</v>
+        <v>4.016749595327989</v>
       </c>
       <c r="I33" t="n">
-        <v>0.169115545119429</v>
+        <v>0.1706751380433185</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999993908812261</v>
+        <v>0.9999910472215017</v>
       </c>
       <c r="K33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.949102647377718</v>
+        <v>-7.952025138929545</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3781116122908</v>
+        <v>113.3900913498006</v>
       </c>
       <c r="R33" t="n">
-        <v>194.2046003452098</v>
+        <v>203.8585979897402</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,28 +2627,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.935034595719155</v>
+        <v>-7.919125279704094</v>
       </c>
       <c r="D34" t="n">
-        <v>113.3819343928551</v>
+        <v>113.4047122308102</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.949103214462262</v>
+        <v>-7.952152416386541</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3783388271817</v>
+        <v>113.3899655504463</v>
       </c>
       <c r="G34" t="n">
-        <v>194.2042304586313</v>
+        <v>203.8552490672081</v>
       </c>
       <c r="H34" t="n">
-        <v>1.613695890771186</v>
+        <v>4.015524696600155</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1691155517768498</v>
+        <v>0.1706751466792922</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9060394274646515</v>
+        <v>0.9999938606581816</v>
       </c>
       <c r="K34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.949103214462262</v>
+        <v>-7.952152416386541</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3783388271817</v>
+        <v>113.3899655504463</v>
       </c>
       <c r="R34" t="n">
-        <v>194.2042304586313</v>
+        <v>203.8552490672081</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,28 +2692,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.935131730005409</v>
+        <v>-7.919883575265776</v>
       </c>
       <c r="D35" t="n">
-        <v>113.3819131210124</v>
+        <v>113.4045674962128</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.949100437185812</v>
+        <v>-7.952171888430906</v>
       </c>
       <c r="F35" t="n">
-        <v>113.3783430160613</v>
+        <v>113.3901494954329</v>
       </c>
       <c r="G35" t="n">
-        <v>194.2045132495666</v>
+        <v>203.8570252661158</v>
       </c>
       <c r="H35" t="n">
-        <v>1.602237843997023</v>
+        <v>3.925749758372306</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1691155527501881</v>
+        <v>0.1706751667939555</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9895872624553129</v>
+        <v>0.9999954394517008</v>
       </c>
       <c r="K35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.949100437185812</v>
+        <v>-7.952171888430906</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3783430160613</v>
+        <v>113.3901494954329</v>
       </c>
       <c r="R35" t="n">
-        <v>194.2045132495666</v>
+        <v>203.8570252661158</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.935131730005409</v>
+        <v>-7.919883575265776</v>
       </c>
       <c r="D36" t="n">
-        <v>113.3819131210124</v>
+        <v>113.4045674962128</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.949100437185812</v>
+        <v>-7.952171888430906</v>
       </c>
       <c r="F36" t="n">
-        <v>113.3783430160613</v>
+        <v>113.3901494954329</v>
       </c>
       <c r="G36" t="n">
-        <v>194.2045132495666</v>
+        <v>203.8570252661158</v>
       </c>
       <c r="H36" t="n">
-        <v>1.602237843997023</v>
+        <v>3.925749758372306</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1691155527501881</v>
+        <v>0.1706751667939555</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9959063236634373</v>
+        <v>0.9999965400848438</v>
       </c>
       <c r="K36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.949100437185812</v>
+        <v>-7.952171888430906</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.3783430160613</v>
+        <v>113.3901494954329</v>
       </c>
       <c r="R36" t="n">
-        <v>194.2045132495666</v>
+        <v>203.8570252661158</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,28 +2822,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.935157244138734</v>
+        <v>-7.919731915907231</v>
       </c>
       <c r="D37" t="n">
-        <v>113.3818407903523</v>
+        <v>113.4046538973473</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.949100898708978</v>
+        <v>-7.952191091392073</v>
       </c>
       <c r="F37" t="n">
-        <v>113.3782770794844</v>
+        <v>113.390159979838</v>
       </c>
       <c r="G37" t="n">
-        <v>194.2045470384455</v>
+        <v>203.8564677793925</v>
       </c>
       <c r="H37" t="n">
-        <v>1.599364496584327</v>
+        <v>3.94650709901151</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1691155543103708</v>
+        <v>0.1706751708710732</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9978273930792422</v>
+        <v>0.9246334847147215</v>
       </c>
       <c r="K37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.949100898708978</v>
+        <v>-7.952191091392073</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.3782770794844</v>
+        <v>113.390159979838</v>
       </c>
       <c r="R37" t="n">
-        <v>194.2045470384455</v>
+        <v>203.8564677793925</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.935157244138734</v>
+        <v>-7.919731915907231</v>
       </c>
       <c r="D38" t="n">
-        <v>113.3818407903523</v>
+        <v>113.4046538973473</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.949100898708978</v>
+        <v>-7.952191091392073</v>
       </c>
       <c r="F38" t="n">
-        <v>113.3782770794844</v>
+        <v>113.390159979838</v>
       </c>
       <c r="G38" t="n">
-        <v>194.2045470384455</v>
+        <v>203.8564677793925</v>
       </c>
       <c r="H38" t="n">
-        <v>1.599364496584327</v>
+        <v>3.94650709901151</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1691155543103708</v>
+        <v>0.1706751708710732</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9987941493569229</v>
+        <v>0.9400476627257378</v>
       </c>
       <c r="K38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.949100898708978</v>
+        <v>-7.952191091392073</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3782770794844</v>
+        <v>113.390159979838</v>
       </c>
       <c r="R38" t="n">
-        <v>194.2045470384455</v>
+        <v>203.8564677793925</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,28 +2952,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.935157244138734</v>
+        <v>-7.919630711782168</v>
       </c>
       <c r="D39" t="n">
-        <v>113.3818407903523</v>
+        <v>113.4046866043483</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.949100898708978</v>
+        <v>-7.95222421460385</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3782770794844</v>
+        <v>113.3901326243786</v>
       </c>
       <c r="G39" t="n">
-        <v>194.2045470384455</v>
+        <v>203.8565842217273</v>
       </c>
       <c r="H39" t="n">
-        <v>1.599364496584327</v>
+        <v>3.962842803759374</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1691155543103708</v>
+        <v>0.1706751720013782</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9994159219116696</v>
+        <v>0.9222214577022213</v>
       </c>
       <c r="K39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.949100898708978</v>
+        <v>-7.95222421460385</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3782770794844</v>
+        <v>113.3901326243786</v>
       </c>
       <c r="R39" t="n">
-        <v>194.2045470384455</v>
+        <v>203.8565842217273</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,28 +3017,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919391689450885</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4046981470656</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952123809245207</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900822484601</v>
       </c>
       <c r="G40" t="n">
-        <v>194.2045843260455</v>
+        <v>203.85662060396</v>
       </c>
       <c r="H40" t="n">
-        <v>1.603026112589999</v>
+        <v>3.979697633827412</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751725291085</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9997847790582384</v>
+        <v>0.9724243174142326</v>
       </c>
       <c r="K40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952123809245207</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900822484601</v>
       </c>
       <c r="R40" t="n">
-        <v>194.2045843260455</v>
+        <v>203.85662060396</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,28 +3082,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919444249564616</v>
       </c>
       <c r="D41" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4046812369116</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.95212860675609</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900866624908</v>
       </c>
       <c r="G41" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566253656488</v>
       </c>
       <c r="H41" t="n">
-        <v>1.603026112589999</v>
+        <v>3.973890573051049</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751726535325</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9999174313049012</v>
+        <v>0.9902558560467609</v>
       </c>
       <c r="K41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.95212860675609</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900866624908</v>
       </c>
       <c r="R41" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566253656488</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,28 +3147,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919444249564616</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4046812369116</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.95212860675609</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900866624908</v>
       </c>
       <c r="G42" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566253656488</v>
       </c>
       <c r="H42" t="n">
-        <v>1.603026112589999</v>
+        <v>3.973890573051049</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751726535325</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5857864382310809</v>
+        <v>0.5857809441135466</v>
       </c>
       <c r="K42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.95212860675609</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900866624908</v>
       </c>
       <c r="R42" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566253656488</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,28 +3212,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919444249564616</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4046812369116</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.95212860675609</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900866624908</v>
       </c>
       <c r="G43" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566253656488</v>
       </c>
       <c r="H43" t="n">
-        <v>1.603026112589999</v>
+        <v>3.973890573051049</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751726535325</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9999989835390313</v>
+        <v>0.9999998836937285</v>
       </c>
       <c r="K43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.95212860675609</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900866624908</v>
       </c>
       <c r="R43" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566253656488</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,28 +3277,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919396939243694</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3818289122913</v>
+        <v>113.404724210777</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952143625286578</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901018100533</v>
       </c>
       <c r="G44" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566163768762</v>
       </c>
       <c r="H44" t="n">
-        <v>1.603026112589999</v>
+        <v>3.981468538541854</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751732057237</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9019328834274396</v>
+        <v>0.9999998825574041</v>
       </c>
       <c r="K44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952143625286578</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901018100533</v>
       </c>
       <c r="R44" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8566163768762</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,28 +3342,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919428266019255</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4046930951467</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952139900599831</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900863585931</v>
       </c>
       <c r="G45" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565984384152</v>
       </c>
       <c r="H45" t="n">
-        <v>1.603026112589999</v>
+        <v>3.977206262612538</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751732235713</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9513163736295904</v>
+        <v>0.9999998822870667</v>
       </c>
       <c r="K45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952139900599831</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3900863585931</v>
       </c>
       <c r="R45" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565984384152</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919446869307073</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047209070002</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952159664331232</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901136524663</v>
       </c>
       <c r="G46" t="n">
-        <v>194.2045843260455</v>
+        <v>203.856597131084</v>
       </c>
       <c r="H46" t="n">
-        <v>1.603026112589999</v>
+        <v>3.977347314838852</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751735871082</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9861682431875606</v>
+        <v>0.9999998921104888</v>
       </c>
       <c r="K46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952159664331232</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901136524663</v>
       </c>
       <c r="R46" t="n">
-        <v>194.2045843260455</v>
+        <v>203.856597131084</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,28 +3472,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919476057461209</v>
       </c>
       <c r="D47" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047072924605</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952170555117657</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901082172324</v>
       </c>
       <c r="G47" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565836280516</v>
       </c>
       <c r="H47" t="n">
-        <v>1.603026112589999</v>
+        <v>3.975122219028738</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751736968752</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9908547448471322</v>
+        <v>0.9999999049770193</v>
       </c>
       <c r="K47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952170555117657</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901082172324</v>
       </c>
       <c r="R47" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565836280516</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,28 +3537,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919416611231282</v>
       </c>
       <c r="D48" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047196341012</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952149556007797</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901033920392</v>
       </c>
       <c r="G48" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565831308799</v>
       </c>
       <c r="H48" t="n">
-        <v>1.603026112589999</v>
+        <v>3.979796788032374</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737153392</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9944462190104844</v>
+        <v>0.9999999049868392</v>
       </c>
       <c r="K48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952149556007797</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901033920392</v>
       </c>
       <c r="R48" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565831308799</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,28 +3602,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919416611231282</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047196341012</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952149556007797</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901033920392</v>
       </c>
       <c r="G49" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565831308799</v>
       </c>
       <c r="H49" t="n">
-        <v>1.603026112589999</v>
+        <v>3.979796788032374</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737153392</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9974891449495833</v>
+        <v>0.9999999139768482</v>
       </c>
       <c r="K49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952149556007797</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901033920392</v>
       </c>
       <c r="R49" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565831308799</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,28 +3667,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919427688431913</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047284639926</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952149825963924</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901170471498</v>
       </c>
       <c r="G50" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565839534401</v>
       </c>
       <c r="H50" t="n">
-        <v>1.603026112589999</v>
+        <v>3.97848281692314</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737524879</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9984301647319515</v>
+        <v>0.9999999178308249</v>
       </c>
       <c r="K50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952149825963924</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901170471498</v>
       </c>
       <c r="R50" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565839534401</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,28 +3732,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919424070031273</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047247936017</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952159573466064</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901074080433</v>
       </c>
       <c r="G51" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565840194606</v>
       </c>
       <c r="H51" t="n">
-        <v>1.603026112589999</v>
+        <v>3.9801079092588</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737651204</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9991943670534614</v>
+        <v>0.9999999201006997</v>
       </c>
       <c r="K51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952159573466064</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901074080433</v>
       </c>
       <c r="R51" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565840194606</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,28 +3797,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919428815719479</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047292716051</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952162058316247</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901128953179</v>
       </c>
       <c r="G52" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565842803915</v>
       </c>
       <c r="H52" t="n">
-        <v>1.603026112589999</v>
+        <v>3.979833033803954</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737675997</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5857864173445927</v>
+        <v>0.5857864397593812</v>
       </c>
       <c r="K52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952162058316247</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901128953179</v>
       </c>
       <c r="R52" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565842803915</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,28 +3862,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919423560845885</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047295130849</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952155933044653</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901135257612</v>
       </c>
       <c r="G53" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841596566</v>
       </c>
       <c r="H53" t="n">
-        <v>1.603026112589999</v>
+        <v>3.979727202926152</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737787879</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999195801415046</v>
+        <v>0.9999999960997066</v>
       </c>
       <c r="K53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952155933044653</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901135257612</v>
       </c>
       <c r="R53" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841596566</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,28 +3927,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919423560845885</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047295130849</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952155933044653</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901135257612</v>
       </c>
       <c r="G54" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841596566</v>
       </c>
       <c r="H54" t="n">
-        <v>1.603026112589999</v>
+        <v>3.979727202926152</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737787879</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999993810070401</v>
+        <v>0.9999999964009865</v>
       </c>
       <c r="K54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952155933044653</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901135257612</v>
       </c>
       <c r="R54" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841596566</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,28 +3992,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919421694201893</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047288184982</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.9521566605373</v>
       </c>
       <c r="F55" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901116728007</v>
       </c>
       <c r="G55" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841292982</v>
       </c>
       <c r="H55" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980042609514422</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737789468</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999993809670371</v>
+        <v>0.9999999972017017</v>
       </c>
       <c r="K55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.9521566605373</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901116728007</v>
       </c>
       <c r="R55" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841292982</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,28 +4057,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919421694201893</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047288184982</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.9521566605373</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901116728007</v>
       </c>
       <c r="G56" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841292982</v>
       </c>
       <c r="H56" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980042609514422</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737789468</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999993894245736</v>
+        <v>0.9999999979103515</v>
       </c>
       <c r="K56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.9521566605373</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901116728007</v>
       </c>
       <c r="R56" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841292982</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,28 +4122,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919421694201893</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047288184982</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.9521566605373</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901116728007</v>
       </c>
       <c r="G57" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841292982</v>
       </c>
       <c r="H57" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980042609514422</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737789468</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9999993890694445</v>
+        <v>0.9999999987796815</v>
       </c>
       <c r="K57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.9521566605373</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901116728007</v>
       </c>
       <c r="R57" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841292982</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,28 +4187,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.91942147722201</v>
       </c>
       <c r="D58" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047300397481</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156898972581</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901126906678</v>
       </c>
       <c r="G58" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841528759</v>
       </c>
       <c r="H58" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980097981789948</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737794074</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9999993908426814</v>
+        <v>0.9999999996804259</v>
       </c>
       <c r="K58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156898972581</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901126906678</v>
       </c>
       <c r="R58" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841528759</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,28 +4252,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.91942147722201</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047300397481</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156898972581</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901126906678</v>
       </c>
       <c r="G59" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841528759</v>
       </c>
       <c r="H59" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980097981789948</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737794074</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999993934067071</v>
+        <v>0.9999999997724729</v>
       </c>
       <c r="K59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156898972581</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901126906678</v>
       </c>
       <c r="R59" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841528759</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,28 +4317,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919421508321473</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047297915445</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156923459074</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901124454212</v>
       </c>
       <c r="G60" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841455251</v>
       </c>
       <c r="H60" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980097177527801</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737794923</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999993958176414</v>
+        <v>0.9999999998754701</v>
       </c>
       <c r="K60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156923459074</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901124454212</v>
       </c>
       <c r="R60" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841455251</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919421508321473</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047297915445</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156923459074</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901124454212</v>
       </c>
       <c r="G61" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841455251</v>
       </c>
       <c r="H61" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980097177527801</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737794923</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9999993978239474</v>
+        <v>0.999999999950409</v>
       </c>
       <c r="K61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156923459074</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901124454212</v>
       </c>
       <c r="R61" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841455251</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,28 +4447,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.935129287997349</v>
+        <v>-7.919421590735716</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3818289122913</v>
+        <v>113.4047301962759</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156928803759</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901128845668</v>
       </c>
       <c r="G62" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841451794</v>
       </c>
       <c r="H62" t="n">
-        <v>1.603026112589999</v>
+        <v>3.980087807032457</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1691155586231238</v>
+        <v>0.1706751737795031</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857864397789182</v>
+        <v>0.5857864397593827</v>
       </c>
       <c r="K62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.94910486310295</v>
+        <v>-7.952156928803759</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3782570333771</v>
+        <v>113.3901128845668</v>
       </c>
       <c r="R62" t="n">
-        <v>194.2045843260455</v>
+        <v>203.8565841451794</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,28 +4512,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421483087007</v>
       </c>
       <c r="D63" t="n">
-        <v>113.3818194662752</v>
+        <v>113.404730104581</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156911805604</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901127523952</v>
       </c>
       <c r="G63" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841436165</v>
       </c>
       <c r="H63" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980098828711521</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.170675173779519</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999865115521</v>
+        <v>0.9999999999853124</v>
       </c>
       <c r="K63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156911805604</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901127523952</v>
       </c>
       <c r="R63" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841436165</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,28 +4577,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421509382273</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047299560525</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156838847244</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3782472926486</v>
+        <v>113.390112648189</v>
       </c>
       <c r="G64" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841439402</v>
       </c>
       <c r="H64" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980086760991266</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795286</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8662488561411188</v>
+        <v>0.9999999999909743</v>
       </c>
       <c r="K64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156838847244</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3782472926486</v>
+        <v>113.390112648189</v>
       </c>
       <c r="R64" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841439402</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,28 +4642,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421530201697</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3818194662752</v>
+        <v>113.404729957405</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156851899933</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126530088</v>
       </c>
       <c r="G65" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841445395</v>
       </c>
       <c r="H65" t="n">
-        <v>1.603157814198623</v>
+        <v>3.98008581669289</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795308</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9637690779549363</v>
+        <v>0.9999999999930829</v>
       </c>
       <c r="K65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156851899933</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126530088</v>
       </c>
       <c r="R65" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841445395</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,28 +4707,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421463967622</v>
       </c>
       <c r="D66" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047299188189</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156808087445</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126044124</v>
       </c>
       <c r="G66" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443625</v>
       </c>
       <c r="H66" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980088542810897</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795323</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9897462921144891</v>
+        <v>0.9999999999960154</v>
       </c>
       <c r="K66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156808087445</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126044124</v>
       </c>
       <c r="R66" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443625</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,28 +4772,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421504796478</v>
       </c>
       <c r="D67" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047300101551</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156836812387</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901127011525</v>
       </c>
       <c r="G67" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841442308</v>
       </c>
       <c r="H67" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980087071155448</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795332</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9943746562197199</v>
+        <v>0.8536709436649456</v>
       </c>
       <c r="K67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156836812387</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901127011525</v>
       </c>
       <c r="R67" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841442308</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,28 +4837,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421592134364</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3818194662752</v>
+        <v>113.404729961824</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156851095318</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126854422</v>
       </c>
       <c r="G68" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443238</v>
       </c>
       <c r="H68" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980078188788246</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795343</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9972328675449879</v>
+        <v>0.9480076115892799</v>
       </c>
       <c r="K68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156851095318</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126854422</v>
       </c>
       <c r="R68" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443238</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,28 +4902,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421451514713</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047300222337</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156828459924</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126931688</v>
       </c>
       <c r="G69" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443192</v>
       </c>
       <c r="H69" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980092533877289</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795348</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9989687599022461</v>
+        <v>0.9348061559411732</v>
       </c>
       <c r="K69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156828459924</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126931688</v>
       </c>
       <c r="R69" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443192</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,28 +4967,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421451514713</v>
       </c>
       <c r="D70" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047300222337</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156828459924</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126931688</v>
       </c>
       <c r="G70" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443192</v>
       </c>
       <c r="H70" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980092533877289</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795348</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9995951154688013</v>
+        <v>0.9837915317316864</v>
       </c>
       <c r="K70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156828459924</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126931688</v>
       </c>
       <c r="R70" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443192</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,28 +5032,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421455884771</v>
       </c>
       <c r="D71" t="n">
-        <v>113.3818194662752</v>
+        <v>113.404729988666</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156791070939</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126782493</v>
       </c>
       <c r="G71" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443204</v>
       </c>
       <c r="H71" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980087456613266</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.1706751737795349</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9995951154504658</v>
+        <v>0.9942251552859384</v>
       </c>
       <c r="K71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156791070939</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126782493</v>
       </c>
       <c r="R71" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443204</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,28 +5097,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421436885777</v>
       </c>
       <c r="D72" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047299996408</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156798041619</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126776275</v>
       </c>
       <c r="G72" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443228</v>
       </c>
       <c r="H72" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980090614130608</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.170675173779535</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5857864144478008</v>
+        <v>0.5857839251660241</v>
       </c>
       <c r="K72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156798041619</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126776275</v>
       </c>
       <c r="R72" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443228</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,28 +5162,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421436885777</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047299996408</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156798041619</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126776275</v>
       </c>
       <c r="G73" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443228</v>
       </c>
       <c r="H73" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980090614130608</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.170675173779535</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9999999988886563</v>
+        <v>0.9993706838686914</v>
       </c>
       <c r="K73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156798041619</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126776275</v>
       </c>
       <c r="R73" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443228</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,28 +5227,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.935128811336473</v>
+        <v>-7.919421475048036</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3818194662752</v>
+        <v>113.4047299843822</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156799617838</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126787058</v>
       </c>
       <c r="G74" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443266</v>
       </c>
       <c r="H74" t="n">
-        <v>1.603157814198623</v>
+        <v>3.980086165825238</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1691155591010312</v>
+        <v>0.170675173779535</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8922987634651844</v>
+        <v>0.9995428979288623</v>
       </c>
       <c r="K74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.949105534334954</v>
+        <v>-7.952156799617838</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3782472926486</v>
+        <v>113.3901126787058</v>
       </c>
       <c r="R74" t="n">
-        <v>194.2045893919987</v>
+        <v>203.8565841443266</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,28 +5292,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.935128931386316</v>
+        <v>-7.919421444725295</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3818235354262</v>
+        <v>113.4047300004678</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.949105469566495</v>
+        <v>-7.952156800505948</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3782514098971</v>
+        <v>113.3901126808546</v>
       </c>
       <c r="G75" t="n">
-        <v>194.2045861069035</v>
+        <v>203.856584144327</v>
       </c>
       <c r="H75" t="n">
-        <v>1.603136591882893</v>
+        <v>3.980089960589475</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1691155591222522</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9717262766557824</v>
+        <v>0.9997717543951161</v>
       </c>
       <c r="K75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.949105469566495</v>
+        <v>-7.952156800505948</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3782514098971</v>
+        <v>113.3901126808546</v>
       </c>
       <c r="R75" t="n">
-        <v>194.2045861069035</v>
+        <v>203.856584144327</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,28 +5357,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.93512903445144</v>
+        <v>-7.919421444725295</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3818267754206</v>
+        <v>113.4047300004678</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.949105398264109</v>
+        <v>-7.952156800505948</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3782546931465</v>
+        <v>113.3901126808546</v>
       </c>
       <c r="G76" t="n">
-        <v>194.2045911071132</v>
+        <v>203.856584144327</v>
       </c>
       <c r="H76" t="n">
-        <v>1.603116626977204</v>
+        <v>3.980089960589475</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1691155592189288</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9870444800196869</v>
+        <v>0.9999139459371805</v>
       </c>
       <c r="K76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.949105398264109</v>
+        <v>-7.952156800505948</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3782546931465</v>
+        <v>113.3901126808546</v>
       </c>
       <c r="R76" t="n">
-        <v>194.2045911071132</v>
+        <v>203.856584144327</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,28 +5422,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.935129070526163</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3818247382828</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.94910549344555</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3782526411887</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G77" t="n">
-        <v>194.2045900109087</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H77" t="n">
-        <v>1.603123398877921</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1691155592419161</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9916393859380733</v>
+        <v>0.9999300839298235</v>
       </c>
       <c r="K77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.94910549344555</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3782526411887</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R77" t="n">
-        <v>194.2045900109087</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,28 +5487,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.935129358323431</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3818277104523</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.949105448070845</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3782556972819</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G78" t="n">
-        <v>194.2045946998373</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H78" t="n">
-        <v>1.603085216560317</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1691155593522291</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9951943040822981</v>
+        <v>0.9999783826106613</v>
       </c>
       <c r="K78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.949105448070845</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3782556972819</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R78" t="n">
-        <v>194.2045946998373</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,28 +5552,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.935129358323431</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3818277104523</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.949105448070845</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3782556972819</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G79" t="n">
-        <v>194.2045946998373</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H79" t="n">
-        <v>1.603085216560317</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1691155593522291</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9980082578897582</v>
+        <v>0.9999921237591129</v>
       </c>
       <c r="K79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.949105448070845</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3782556972819</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R79" t="n">
-        <v>194.2045946998373</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,28 +5617,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.935129358323431</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3818277104523</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.949105448070845</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3782556972819</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G80" t="n">
-        <v>194.2045946998373</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H80" t="n">
-        <v>1.603085216560317</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1691155593522291</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9990083900637233</v>
+        <v>0.9476590195193297</v>
       </c>
       <c r="K80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.949105448070845</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3782556972819</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R80" t="n">
-        <v>194.2045946998373</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,28 +5682,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.935129323400069</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3818274739811</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.949105464771163</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3782554472522</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G81" t="n">
-        <v>194.2045960903272</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H81" t="n">
-        <v>1.603091147753307</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1691155593825495</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9990962114873381</v>
+        <v>0.980469795340859</v>
       </c>
       <c r="K81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.949105464771163</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3782554472522</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R81" t="n">
-        <v>194.2045960903272</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,28 +5747,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.93512932971379</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3818284147667</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.949105417372823</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3782564013152</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G82" t="n">
-        <v>194.2045978103564</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H82" t="n">
-        <v>1.603084999048555</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1691155593843519</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857863642437527</v>
+        <v>0.5857613013975862</v>
       </c>
       <c r="K82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.949105417372823</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3782564013152</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R82" t="n">
-        <v>194.2045978103564</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,28 +5812,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.935129322566972</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3818283028717</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.94910540451253</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3782562903044</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G83" t="n">
-        <v>194.2046000086182</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H83" t="n">
-        <v>1.603084359269863</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I83" t="n">
-        <v>0.169115559399043</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999673890871829</v>
+        <v>0.9999999999996045</v>
       </c>
       <c r="K83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.94910540451253</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3782562903044</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R83" t="n">
-        <v>194.2046000086182</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,28 +5877,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.935129382515701</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3818276788633</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.949105466504451</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3782556658647</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G84" t="n">
-        <v>194.2045996600893</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H84" t="n">
-        <v>1.603084591160097</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1691155594417458</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999797875323622</v>
+        <v>0.9999999999996045</v>
       </c>
       <c r="K84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.949105466504451</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3782556658647</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R84" t="n">
-        <v>194.2045996600893</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,28 +5942,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.935129561661188</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3818255562572</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.949105511613815</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F85" t="n">
-        <v>113.378253576978</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G85" t="n">
-        <v>194.2046017095934</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H85" t="n">
-        <v>1.603069231449223</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1691155594570413</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999901359785001</v>
+        <v>0.9999999999996045</v>
       </c>
       <c r="K85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.949105511613815</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.378253576978</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R85" t="n">
-        <v>194.2046017095934</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,28 +6007,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.935129358073587</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3818276905542</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.949105472543283</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3782556694676</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G86" t="n">
-        <v>194.2046007956026</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H86" t="n">
-        <v>1.603088095431166</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1691155594644723</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999933680991011</v>
+        <v>0.9999999999996039</v>
       </c>
       <c r="K86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.949105472543283</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3782556694676</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R86" t="n">
-        <v>194.2046007956026</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,28 +6072,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.935129313619238</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3818282378316</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.949105455822401</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3782562091955</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G87" t="n">
-        <v>194.2046025563513</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H87" t="n">
-        <v>1.60309128898909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I87" t="n">
-        <v>0.169115559473752</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999961030415325</v>
+        <v>0.9999999999996039</v>
       </c>
       <c r="K87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.949105455822401</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3782562091955</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R87" t="n">
-        <v>194.2046025563513</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,28 +6137,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.935129313619238</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3818282378316</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.949105455822401</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3782562091955</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G88" t="n">
-        <v>194.2046025563513</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H88" t="n">
-        <v>1.60309128898909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I88" t="n">
-        <v>0.169115559473752</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999976573092199</v>
+        <v>0.9999999999996037</v>
       </c>
       <c r="K88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.949105455822401</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3782562091955</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R88" t="n">
-        <v>194.2046025563513</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,28 +6202,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.935129383151057</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3818282243442</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.949105459871201</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3782562126294</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G89" t="n">
-        <v>194.2046018497286</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H89" t="n">
-        <v>1.603083772943451</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I89" t="n">
-        <v>0.169115559481696</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9999989318956439</v>
+        <v>0.9999999999996037</v>
       </c>
       <c r="K89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.949105459871201</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3782562126294</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R89" t="n">
-        <v>194.2046018497286</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,28 +6267,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.935129383151057</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3818282243442</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.949105459871201</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3782562126294</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G90" t="n">
-        <v>194.2046018497286</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H90" t="n">
-        <v>1.603083772943451</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I90" t="n">
-        <v>0.169115559481696</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9999993863879185</v>
+        <v>0.9999999999996037</v>
       </c>
       <c r="K90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.949105459871201</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3782562126294</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R90" t="n">
-        <v>194.2046018497286</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,28 +6332,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.935129383151057</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3818282243442</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.949105459871201</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3782562126294</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G91" t="n">
-        <v>194.2046018497286</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H91" t="n">
-        <v>1.603083772943451</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I91" t="n">
-        <v>0.169115559481696</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J91" t="n">
-        <v>0.999999708908233</v>
+        <v>0.9999999999996037</v>
       </c>
       <c r="K91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.949105459871201</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3782562126294</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R91" t="n">
-        <v>194.2046018497286</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,28 +6397,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.935129349489966</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3818283223757</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.949105457541239</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3782563026042</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G92" t="n">
-        <v>194.2046020372574</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H92" t="n">
-        <v>1.603087368018573</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1691155594844699</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J92" t="n">
-        <v>0.585786439779029</v>
+        <v>0.5857864397593829</v>
       </c>
       <c r="K92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.949105457541239</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3782563026042</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R92" t="n">
-        <v>194.2046020372574</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,28 +6462,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.935129349489966</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3818283223757</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.949105457541239</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3782563026042</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G93" t="n">
-        <v>194.2046020372574</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H93" t="n">
-        <v>1.603087368018573</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1691155594844699</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9999999998563474</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.949105457541239</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3782563026042</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R93" t="n">
-        <v>194.2046020372574</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,28 +6527,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.935129349489966</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3818283223757</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.949105457541239</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3782563026042</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G94" t="n">
-        <v>194.2046020372574</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H94" t="n">
-        <v>1.603087368018573</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1691155594844699</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9999999998553697</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.949105457541239</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3782563026042</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R94" t="n">
-        <v>194.2046020372574</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,28 +6592,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.935129351395855</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3818288322835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G95" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H95" t="n">
-        <v>1.60308584095991</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I95" t="n">
-        <v>0.169115559487007</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J95" t="n">
-        <v>0.999999999854007</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R95" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,28 +6657,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.935129351395855</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3818288322835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G96" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H96" t="n">
-        <v>1.60308584095991</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I96" t="n">
-        <v>0.169115559487007</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9999999998368507</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R96" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,28 +6722,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.935129351395855</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3818288322835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G97" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H97" t="n">
-        <v>1.60308584095991</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I97" t="n">
-        <v>0.169115559487007</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9320824691400398</v>
+        <v>0.9405692983734951</v>
       </c>
       <c r="K97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R97" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,28 +6787,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.935129351395855</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3818288322835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G98" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H98" t="n">
-        <v>1.60308584095991</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I98" t="n">
-        <v>0.169115559487007</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9704503669745945</v>
+        <v>0.8859437644890745</v>
       </c>
       <c r="K98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R98" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,28 +6852,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.935129351395855</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3818288322835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G99" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H99" t="n">
-        <v>1.60308584095991</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I99" t="n">
-        <v>0.169115559487007</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9848340923825769</v>
+        <v>0.9092733573895534</v>
       </c>
       <c r="K99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R99" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,28 +6917,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.935129351395855</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3818288322835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G100" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H100" t="n">
-        <v>1.60308584095991</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I100" t="n">
-        <v>0.169115559487007</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9952471928755416</v>
+        <v>0.9590235490603326</v>
       </c>
       <c r="K100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.949105446133329</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3782568159125</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R100" t="n">
-        <v>194.204602046046</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,28 +6982,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G101" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H101" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I101" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9967168954166664</v>
+        <v>0.9865961716479623</v>
       </c>
       <c r="K101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R101" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,28 +7047,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G102" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H102" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I102" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5857860255526818</v>
+        <v>0.5857812631259455</v>
       </c>
       <c r="K102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R102" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,28 +7112,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G103" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H103" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I103" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9999999998860378</v>
+        <v>0.9995973165938178</v>
       </c>
       <c r="K103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R103" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,28 +7177,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G104" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H104" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I104" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J104" t="n">
-        <v>0.8311984848697278</v>
+        <v>0.9999014906357157</v>
       </c>
       <c r="K104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R104" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,28 +7242,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G105" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H105" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I105" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8953862912069395</v>
+        <v>0.9999513661953182</v>
       </c>
       <c r="K105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R105" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,28 +7307,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G106" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H106" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I106" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9758300142028836</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R106" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,28 +7372,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G107" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H107" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I107" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9683458712424103</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R107" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,28 +7437,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G108" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H108" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I108" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9893845408477422</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R108" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,28 +7502,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G109" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H109" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I109" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9949660078099276</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R109" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,28 +7567,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G110" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H110" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I110" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9967714922567112</v>
+        <v>0.9441458268199799</v>
       </c>
       <c r="K110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R110" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,28 +7632,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G111" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H111" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I111" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9981371226221196</v>
+        <v>0.9888877341741178</v>
       </c>
       <c r="K111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R111" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,28 +7697,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G112" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H112" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I112" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5857858314294732</v>
+        <v>0.58576024416106</v>
       </c>
       <c r="K112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R112" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,28 +7762,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G113" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H113" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I113" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9996788249544859</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R113" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,28 +7827,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.935129339419023</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3818290339753</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G114" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H114" t="n">
-        <v>1.603086712735484</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I114" t="n">
-        <v>0.169115559488294</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9997893685658509</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.949105441754296</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3782570156517</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R114" t="n">
-        <v>194.2046020872975</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,28 +7892,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.935129155791893</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3818292956835</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.949105436640846</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3782572317246</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G115" t="n">
-        <v>194.2046021279835</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H115" t="n">
-        <v>1.603107188920164</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1691155594883134</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9998685471242427</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.949105436640846</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3782572317246</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R115" t="n">
-        <v>194.2046021279835</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,28 +7957,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.935129155586533</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D116" t="n">
-        <v>113.381829295685</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.949105436477221</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3782572317248</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G116" t="n">
-        <v>194.204602092164</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H116" t="n">
-        <v>1.603107193453074</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1691155594886526</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9999252619101496</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.949105436477221</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3782572317248</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R116" t="n">
-        <v>194.204602092164</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,28 +8022,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.935129155595614</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3818292957082</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.949105436757863</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3782572316797</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G117" t="n">
-        <v>194.2046020882634</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H117" t="n">
-        <v>1.603107224574423</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1691155594890039</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9999581792270327</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.949105436757863</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3782572316797</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R117" t="n">
-        <v>194.2046020882634</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.935129155595614</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3818292957082</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.949105436757863</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3782572316797</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G118" t="n">
-        <v>194.2046020882634</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H118" t="n">
-        <v>1.603107224574423</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1691155594890039</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9999742238504361</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.949105436757863</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3782572316797</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R118" t="n">
-        <v>194.2046020882634</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,28 +8152,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.935129155595614</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3818292957082</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.949105436757863</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3782572316797</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G119" t="n">
-        <v>194.2046020882634</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H119" t="n">
-        <v>1.603107224574423</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1691155594890039</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9999911155360344</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.949105436757863</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3782572316797</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R119" t="n">
-        <v>194.2046020882634</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,28 +8217,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F120" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G120" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H120" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9999936327593004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R120" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,28 +8282,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F121" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G121" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H121" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J121" t="n">
-        <v>0.9999944251854127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R121" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,28 +8347,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F122" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G122" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H122" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857864397700173</v>
+        <v>0.5857864397593828</v>
       </c>
       <c r="K122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R122" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,28 +8412,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F123" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G123" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H123" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J123" t="n">
-        <v>0.9999999999961207</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R123" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,28 +8477,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F124" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G124" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H124" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9999999999961502</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R124" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,28 +8542,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F125" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G125" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H125" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J125" t="n">
-        <v>0.999999999996136</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R125" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,28 +8607,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.935129155595363</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3818292957086</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F126" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G126" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H126" t="n">
-        <v>1.603107236418909</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1691155594892474</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9999999999961169</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.949105436861458</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.378257231656</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R126" t="n">
-        <v>194.2046020788488</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,28 +8672,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.935129155617036</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3818292956747</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.949105436863054</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3782572316274</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G127" t="n">
-        <v>194.2046020780161</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H127" t="n">
-        <v>1.603107234110385</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I127" t="n">
-        <v>0.16911555948925</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9999999999966709</v>
+        <v>0.9047264856099946</v>
       </c>
       <c r="K127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.949105436863054</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3782572316274</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R127" t="n">
-        <v>194.2046020780161</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,28 +8737,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.935129155617036</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3818292956747</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.949105436863054</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3782572316274</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G128" t="n">
-        <v>194.2046020780161</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H128" t="n">
-        <v>1.603107234110385</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I128" t="n">
-        <v>0.16911555948925</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9999999999966656</v>
+        <v>0.9491220658302907</v>
       </c>
       <c r="K128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.949105436863054</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3782572316274</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R128" t="n">
-        <v>194.2046020780161</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,28 +8802,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.935129155609532</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3818292963957</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.949105436844022</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3782572323513</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G129" t="n">
-        <v>194.2046020784183</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H129" t="n">
-        <v>1.603107232790649</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1691155594892544</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9999999999971836</v>
+        <v>0.9706273435260574</v>
       </c>
       <c r="K129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.949105436844022</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3782572323513</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R129" t="n">
-        <v>194.2046020784183</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,28 +8867,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.935129155609532</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3818292963957</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.949105436844022</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3782572323513</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G130" t="n">
-        <v>194.2046020784183</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H130" t="n">
-        <v>1.603107232790649</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1691155594892544</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9999999999971758</v>
+        <v>0.9916200353848555</v>
       </c>
       <c r="K130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.949105436844022</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3782572323513</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R130" t="n">
-        <v>194.2046020784183</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,28 +8932,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.935129155624161</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3818292969938</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.949105436828582</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3782572329571</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G131" t="n">
-        <v>194.2046020783218</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H131" t="n">
-        <v>1.603107229340829</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1691155594892548</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9999999999971698</v>
+        <v>0.9933880831259417</v>
       </c>
       <c r="K131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.949105436828582</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3782572329571</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R131" t="n">
-        <v>194.2046020783218</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,28 +8997,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.935129155624161</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3818292969938</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.949105436828582</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3782572329571</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G132" t="n">
-        <v>194.2046020783218</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H132" t="n">
-        <v>1.603107229340829</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1691155594892548</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5857864397790489</v>
+        <v>0.5857796246434241</v>
       </c>
       <c r="K132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.949105436828582</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3782572329571</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R132" t="n">
-        <v>194.2046020783218</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,28 +9062,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D133" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G133" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H133" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9999999999984317</v>
+        <v>0.9987571408326035</v>
       </c>
       <c r="K133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R133" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,28 +9127,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D134" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G134" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H134" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J134" t="n">
-        <v>0.8836623373176767</v>
+        <v>0.9989838362178757</v>
       </c>
       <c r="K134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R134" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,28 +9192,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D135" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G135" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H135" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9225525060295114</v>
+        <v>0.999342775808329</v>
       </c>
       <c r="K135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R135" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,28 +9257,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D136" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G136" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H136" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9799162716310063</v>
+        <v>0.9995443352057795</v>
       </c>
       <c r="K136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R136" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,28 +9322,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D137" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G137" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H137" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J137" t="n">
-        <v>0.9605679916480718</v>
+        <v>0.999712655331459</v>
       </c>
       <c r="K137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R137" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,28 +9387,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D138" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G138" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H138" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9902929798264019</v>
+        <v>0.9998062923044129</v>
       </c>
       <c r="K138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R138" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,28 +9452,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D139" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G139" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H139" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9927837936207871</v>
+        <v>0.9998258117171255</v>
       </c>
       <c r="K139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R139" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,28 +9517,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D140" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G140" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H140" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9945243878304524</v>
+        <v>0.9366628136663933</v>
       </c>
       <c r="K140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R140" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,28 +9582,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D141" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G141" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H141" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9956262089737559</v>
+        <v>0.9779347191864203</v>
       </c>
       <c r="K141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R141" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,28 +9647,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D142" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G142" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H142" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857854018778058</v>
+        <v>0.5857522089871963</v>
       </c>
       <c r="K142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R142" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,28 +9712,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D143" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G143" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H143" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9998792412285797</v>
+        <v>0.9999860096763902</v>
       </c>
       <c r="K143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R143" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,28 +9777,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D144" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G144" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H144" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9999550280152707</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R144" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,28 +9842,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D145" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G145" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H145" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9999654301437622</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R145" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,28 +9907,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D146" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G146" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H146" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J146" t="n">
-        <v>0.9999700954631682</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R146" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,28 +9972,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D147" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G147" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H147" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J147" t="n">
-        <v>0.9999736027104396</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R147" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,28 +10037,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.935129155609922</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D148" t="n">
-        <v>113.381829296387</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G148" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H148" t="n">
-        <v>1.603107232970845</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1691155594892562</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J148" t="n">
-        <v>0.999983075972174</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.949105436845987</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3782572323422</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R148" t="n">
-        <v>194.2046020783227</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,28 +10102,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.935129155608409</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3818292965556</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.949105436842916</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3782572325112</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G149" t="n">
-        <v>194.2046020783687</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H149" t="n">
-        <v>1.603107232792425</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1691155594892583</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J149" t="n">
-        <v>0.999990768312122</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.949105436842916</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3782572325112</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R149" t="n">
-        <v>194.2046020783687</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,28 +10167,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.935129155608409</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3818292965556</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.949105436842916</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3782572325112</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G150" t="n">
-        <v>194.2046020783687</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H150" t="n">
-        <v>1.603107232792425</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1691155594892583</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9999945705198851</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.949105436842916</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3782572325112</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R150" t="n">
-        <v>194.2046020783687</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,28 +10232,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.935129155608409</v>
+        <v>-7.919421448461443</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3818292965556</v>
+        <v>113.4047300057614</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.949105436842916</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3782572325112</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="G151" t="n">
-        <v>194.2046020783687</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="H151" t="n">
-        <v>1.603107232792425</v>
+        <v>3.980089978369283</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1691155594892583</v>
+        <v>0.1706751737795351</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9999981469049051</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.949105436842916</v>
+        <v>-7.952156804388329</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3782572325112</v>
+        <v>113.3901126860828</v>
       </c>
       <c r="R151" t="n">
-        <v>194.2046020783687</v>
+        <v>203.8565841443267</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>45128.39027777778</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.153593526264119</v>
+        <v>-7.719589428539689</v>
       </c>
       <c r="D2" t="n">
-        <v>113.3311362201217</v>
+        <v>113.0692652918578</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.905215714332474</v>
       </c>
       <c r="F2" t="n">
-        <v>113.4647183977525</v>
+        <v>113.3192434162308</v>
       </c>
       <c r="G2" t="n">
-        <v>38.13208364715861</v>
+        <v>126.8694796031224</v>
       </c>
       <c r="H2" t="n">
-        <v>23.8222295006408</v>
+        <v>34.41505674874435</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1679254052837848</v>
+        <v>0.1704961104386556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8933715789130053</v>
+        <v>0.8740292382666105</v>
       </c>
       <c r="K2" t="n">
-        <v>1965</v>
+        <v>1346</v>
       </c>
       <c r="L2" t="n">
-        <v>1797</v>
+        <v>1150</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>45128.39027777778</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.84901089388539</v>
       </c>
       <c r="O2" t="n">
-        <v>113.491685257373</v>
+        <v>113.303858808655</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.985054109717519</v>
+        <v>-7.905215714332474</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.4647183977525</v>
+        <v>113.3192434162308</v>
       </c>
       <c r="R2" t="n">
-        <v>38.13208364715861</v>
+        <v>126.8694796031224</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.255056508970146</v>
+        <v>-8.018776372398985</v>
       </c>
       <c r="D3" t="n">
-        <v>113.0667176706558</v>
+        <v>113.3253477654735</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.010079034232739</v>
+        <v>-7.974596616578423</v>
       </c>
       <c r="F3" t="n">
-        <v>113.4345186639489</v>
+        <v>113.3440469823906</v>
       </c>
       <c r="G3" t="n">
-        <v>56.09242779191669</v>
+        <v>22.74168170067791</v>
       </c>
       <c r="H3" t="n">
-        <v>48.79723557279398</v>
+        <v>5.326625180273354</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1682815433852565</v>
+        <v>0.1719329085030804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9628103986004636</v>
+        <v>0.9426955172617935</v>
       </c>
       <c r="K3" t="n">
-        <v>722</v>
+        <v>1705</v>
       </c>
       <c r="L3" t="n">
-        <v>1797</v>
+        <v>640</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45488.02986111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.98235949442294</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O3" t="n">
-        <v>113.491685257373</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P3" t="n">
-        <v>-8.010079034232739</v>
+        <v>-7.974596616578423</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.4345186639489</v>
+        <v>113.3440469823906</v>
       </c>
       <c r="R3" t="n">
-        <v>56.09242779191669</v>
+        <v>22.74168170067791</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -677,31 +677,31 @@
         <v>44877.10347222222</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.101897752714503</v>
+        <v>-8.018776372398985</v>
       </c>
       <c r="D4" t="n">
-        <v>112.6207535159278</v>
+        <v>113.3253477654735</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.99321280084413</v>
+        <v>-7.974596616578423</v>
       </c>
       <c r="F4" t="n">
-        <v>113.3632245281443</v>
+        <v>113.3440469823906</v>
       </c>
       <c r="G4" t="n">
-        <v>81.64247362790093</v>
+        <v>22.74168170067791</v>
       </c>
       <c r="H4" t="n">
-        <v>82.63446466657469</v>
+        <v>5.326625180273354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1693973804906765</v>
+        <v>0.1719329085030804</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9859035126578413</v>
+        <v>0.9773599552280652</v>
       </c>
       <c r="K4" t="n">
-        <v>1513</v>
+        <v>1705</v>
       </c>
       <c r="L4" t="n">
         <v>640</v>
@@ -716,13 +716,13 @@
         <v>113.300380121246</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.99321280084413</v>
+        <v>-7.974596616578423</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.3632245281443</v>
+        <v>113.3440469823906</v>
       </c>
       <c r="R4" t="n">
-        <v>81.64247362790093</v>
+        <v>22.74168170067791</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -739,55 +739,55 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.738217714529264</v>
+        <v>-8.027069577914261</v>
       </c>
       <c r="D5" t="n">
-        <v>113.126709635821</v>
+        <v>113.3413229229386</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.96020974113866</v>
+        <v>-7.957667531050113</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3848862157687</v>
+        <v>113.3518447060147</v>
       </c>
       <c r="G5" t="n">
-        <v>130.9748215291114</v>
+        <v>8.538985059369793</v>
       </c>
       <c r="H5" t="n">
-        <v>37.65756543844378</v>
+        <v>7.803643599054814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1696169906238353</v>
+        <v>0.1722302064518231</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9910714979141665</v>
+        <v>0.9894917117796753</v>
       </c>
       <c r="K5" t="n">
-        <v>1040</v>
+        <v>1705</v>
       </c>
       <c r="L5" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O5" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.96020974113866</v>
+        <v>-7.957667531050113</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3848862157687</v>
+        <v>113.3518447060147</v>
       </c>
       <c r="R5" t="n">
-        <v>130.9748215291114</v>
+        <v>8.538985059369793</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -804,55 +804,55 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.726044914981562</v>
+        <v>-8.033871002117559</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0404847906876</v>
+        <v>113.3409904443866</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.927303158219137</v>
+        <v>-7.987703269528294</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3861979675387</v>
+        <v>113.3819073726659</v>
       </c>
       <c r="G6" t="n">
-        <v>120.4631305281684</v>
+        <v>41.2736391557513</v>
       </c>
       <c r="H6" t="n">
-        <v>44.171965681355</v>
+        <v>6.830247167908669</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1697969874684987</v>
+        <v>0.1725224437534801</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9955290670651344</v>
+        <v>0.9941729443358277</v>
       </c>
       <c r="K6" t="n">
-        <v>1324</v>
+        <v>1705</v>
       </c>
       <c r="L6" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O6" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.927303158219137</v>
+        <v>-7.987703269528294</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3861979675387</v>
+        <v>113.3819073726659</v>
       </c>
       <c r="R6" t="n">
-        <v>120.4631305281684</v>
+        <v>41.2736391557513</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -869,55 +869,55 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.726044914981562</v>
+        <v>-8.033871002117559</v>
       </c>
       <c r="D7" t="n">
-        <v>113.0404847906876</v>
+        <v>113.3409904443866</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.927303158219137</v>
+        <v>-7.987703269528294</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3861979675387</v>
+        <v>113.3819073726659</v>
       </c>
       <c r="G7" t="n">
-        <v>120.4631305281684</v>
+        <v>41.2736391557513</v>
       </c>
       <c r="H7" t="n">
-        <v>44.171965681355</v>
+        <v>6.830247167908669</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1697969874684987</v>
+        <v>0.1725224437534801</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9982165955223239</v>
+        <v>0.9972764513044139</v>
       </c>
       <c r="K7" t="n">
-        <v>1324</v>
+        <v>1705</v>
       </c>
       <c r="L7" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O7" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.927303158219137</v>
+        <v>-7.987703269528294</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3861979675387</v>
+        <v>113.3819073726659</v>
       </c>
       <c r="R7" t="n">
-        <v>120.4631305281684</v>
+        <v>41.2736391557513</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.770920823964929</v>
+        <v>-7.982951098337787</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3799398044293</v>
+        <v>113.4068653347977</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.913133381383831</v>
+        <v>-7.941793268994033</v>
       </c>
       <c r="F8" t="n">
-        <v>113.4022789685156</v>
+        <v>113.4043123263285</v>
       </c>
       <c r="G8" t="n">
-        <v>171.1564439659265</v>
+        <v>356.4844634778329</v>
       </c>
       <c r="H8" t="n">
-        <v>16.00363459847289</v>
+        <v>4.585169283024213</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1699814335786982</v>
+        <v>0.1725671815850905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9984061581537678</v>
+        <v>0.9973336734520649</v>
       </c>
       <c r="K8" t="n">
-        <v>177</v>
+        <v>448</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.913133381383831</v>
+        <v>-7.941793268994033</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.4022789685156</v>
+        <v>113.4043123263285</v>
       </c>
       <c r="R8" t="n">
-        <v>171.1564439659265</v>
+        <v>356.4844634778329</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -999,55 +999,55 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.41915246918764</v>
+        <v>-8.007216308474788</v>
       </c>
       <c r="D9" t="n">
-        <v>113.4360155133922</v>
+        <v>113.3326088257528</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.954538126498549</v>
+        <v>-7.966494017369675</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3715543072167</v>
+        <v>113.368635675386</v>
       </c>
       <c r="G9" t="n">
-        <v>352.176017860133</v>
+        <v>41.22457471530996</v>
       </c>
       <c r="H9" t="n">
-        <v>52.14762876256662</v>
+        <v>6.020135804391243</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1701299312214346</v>
+        <v>0.1727448662674463</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9991061019689619</v>
+        <v>0.9973302837441415</v>
       </c>
       <c r="K9" t="n">
-        <v>429</v>
+        <v>1705</v>
       </c>
       <c r="L9" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O9" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.954538126498549</v>
+        <v>-7.966494017369675</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3715543072167</v>
+        <v>113.368635675386</v>
       </c>
       <c r="R9" t="n">
-        <v>352.176017860133</v>
+        <v>41.22457471530996</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.735685288427248</v>
+        <v>-8.004402605577127</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3781915615327</v>
+        <v>113.3324153932479</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.933736578537498</v>
+        <v>-7.964648827259435</v>
       </c>
       <c r="F10" t="n">
-        <v>113.4111180701158</v>
+        <v>113.3707776915338</v>
       </c>
       <c r="G10" t="n">
-        <v>170.6495582317482</v>
+        <v>43.70331678207191</v>
       </c>
       <c r="H10" t="n">
-        <v>22.31899116659481</v>
+        <v>6.114339252221916</v>
       </c>
       <c r="I10" t="n">
-        <v>0.170371898424366</v>
+        <v>0.1728143375570551</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9991286400184149</v>
+        <v>0.9976734378964105</v>
       </c>
       <c r="K10" t="n">
-        <v>750</v>
+        <v>1705</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.933736578537498</v>
+        <v>-7.964648827259435</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.4111180701158</v>
+        <v>113.3707776915338</v>
       </c>
       <c r="R10" t="n">
-        <v>170.6495582317482</v>
+        <v>43.70331678207191</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,31 +1132,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.914112089196164</v>
+        <v>-8.004402605577127</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3782170634299</v>
+        <v>113.3324153932479</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.93849667672547</v>
+        <v>-7.964648827259435</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3778123750454</v>
+        <v>113.3707776915338</v>
       </c>
       <c r="G11" t="n">
-        <v>180.9416877020236</v>
+        <v>43.70331678207191</v>
       </c>
       <c r="H11" t="n">
-        <v>2.711808701855622</v>
+        <v>6.114339252221916</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1704457133801957</v>
+        <v>0.1728143375570551</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9990238497810509</v>
+        <v>0.9979617854069388</v>
       </c>
       <c r="K11" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.93849667672547</v>
+        <v>-7.964648827259435</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3778123750454</v>
+        <v>113.3707776915338</v>
       </c>
       <c r="R11" t="n">
-        <v>180.9416877020236</v>
+        <v>43.70331678207191</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.914112089196164</v>
+        <v>-8.009178441799968</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3782170634299</v>
+        <v>113.3348420731802</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.93849667672547</v>
+        <v>-7.947219556058015</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3778123750454</v>
+        <v>113.3677692653538</v>
       </c>
       <c r="G12" t="n">
-        <v>180.9416877020236</v>
+        <v>27.7597763430611</v>
       </c>
       <c r="H12" t="n">
-        <v>2.711808701855622</v>
+        <v>7.785405455129859</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1704457133801957</v>
+        <v>0.1728162666648347</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857861082398321</v>
+        <v>0.5857849901784189</v>
       </c>
       <c r="K12" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.93849667672547</v>
+        <v>-7.947219556058015</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3778123750454</v>
+        <v>113.3677692653538</v>
       </c>
       <c r="R12" t="n">
-        <v>180.9416877020236</v>
+        <v>27.7597763430611</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,31 +1262,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.914112089196164</v>
+        <v>-8.022865389725842</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3782170634299</v>
+        <v>113.3385681589015</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.93849667672547</v>
+        <v>-7.951166526483987</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3778123750454</v>
+        <v>113.3778299601006</v>
       </c>
       <c r="G13" t="n">
-        <v>180.9416877020236</v>
+        <v>28.47287453078669</v>
       </c>
       <c r="H13" t="n">
-        <v>2.711808701855622</v>
+        <v>9.069345258382391</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1704457133801957</v>
+        <v>0.1728463357633716</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9992149563536475</v>
+        <v>0.9984145381653877</v>
       </c>
       <c r="K13" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.93849667672547</v>
+        <v>-7.951166526483987</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3778123750454</v>
+        <v>113.3778299601006</v>
       </c>
       <c r="R13" t="n">
-        <v>180.9416877020236</v>
+        <v>28.47287453078669</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,31 +1327,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.959868643831213</v>
+        <v>-8.01498174091779</v>
       </c>
       <c r="D14" t="n">
-        <v>113.3820176847885</v>
+        <v>113.3600304768281</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.941450437054986</v>
+        <v>-7.958021560365631</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3809932184983</v>
+        <v>113.3892699324297</v>
       </c>
       <c r="G14" t="n">
-        <v>356.8468171369818</v>
+        <v>26.94865935727584</v>
       </c>
       <c r="H14" t="n">
-        <v>2.051116313021375</v>
+        <v>7.10508935474449</v>
       </c>
       <c r="I14" t="n">
-        <v>0.170490767429646</v>
+        <v>0.172856205785556</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999350932315354</v>
+        <v>0.9983890558072239</v>
       </c>
       <c r="K14" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.941450437054986</v>
+        <v>-7.958021560365631</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3809932184983</v>
+        <v>113.3892699324297</v>
       </c>
       <c r="R14" t="n">
-        <v>356.8468171369818</v>
+        <v>26.94865935727584</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,31 +1392,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.938271682285249</v>
+        <v>-8.014133781838609</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3909766065826</v>
+        <v>113.3515291726259</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.949340365384529</v>
+        <v>-7.953571744981112</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3846938271116</v>
+        <v>113.3883040362476</v>
       </c>
       <c r="G15" t="n">
-        <v>209.3429893996786</v>
+        <v>31.02275931604566</v>
       </c>
       <c r="H15" t="n">
-        <v>1.411935354639404</v>
+        <v>7.857997689999483</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1705820843619282</v>
+        <v>0.172918027682289</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9994420528159198</v>
+        <v>0.9982826910305677</v>
       </c>
       <c r="K15" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.949340365384529</v>
+        <v>-7.953571744981112</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3846938271116</v>
+        <v>113.3883040362476</v>
       </c>
       <c r="R15" t="n">
-        <v>209.3429893996786</v>
+        <v>31.02275931604566</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,31 +1457,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.938271682285249</v>
+        <v>-8.014133781838609</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3909766065826</v>
+        <v>113.3515291726259</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.949340365384529</v>
+        <v>-7.953571744981112</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3846938271116</v>
+        <v>113.3883040362476</v>
       </c>
       <c r="G16" t="n">
-        <v>209.3429893996786</v>
+        <v>31.02275931604566</v>
       </c>
       <c r="H16" t="n">
-        <v>1.411935354639404</v>
+        <v>7.857997689999483</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1705820843619282</v>
+        <v>0.172918027682289</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9995759277526822</v>
+        <v>0.9982830130479439</v>
       </c>
       <c r="K16" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.949340365384529</v>
+        <v>-7.953571744981112</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3846938271116</v>
+        <v>113.3883040362476</v>
       </c>
       <c r="R16" t="n">
-        <v>209.3429893996786</v>
+        <v>31.02275931604566</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.947702122847227</v>
+        <v>-8.014133781838609</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3865719485718</v>
+        <v>113.3515291726259</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.955537129617198</v>
+        <v>-7.953571744981112</v>
       </c>
       <c r="F17" t="n">
-        <v>113.382114272635</v>
+        <v>113.3883040362476</v>
       </c>
       <c r="G17" t="n">
-        <v>209.3997860354122</v>
+        <v>31.02275931604566</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>7.857997689999483</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1706210251935186</v>
+        <v>0.172918027682289</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9995683064625214</v>
+        <v>0.9982919440974322</v>
       </c>
       <c r="K17" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.955537129617198</v>
+        <v>-7.953571744981112</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.382114272635</v>
+        <v>113.3883040362476</v>
       </c>
       <c r="R17" t="n">
-        <v>209.3997860354122</v>
+        <v>31.02275931604566</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.947702122847227</v>
+        <v>-8.014642904086402</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3865719485718</v>
+        <v>113.3472040589804</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.955537129617198</v>
+        <v>-7.954808492099117</v>
       </c>
       <c r="F18" t="n">
-        <v>113.382114272635</v>
+        <v>113.3836579818265</v>
       </c>
       <c r="G18" t="n">
-        <v>209.3997860354122</v>
+        <v>31.10680383717838</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>7.770451793195363</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1706210251935186</v>
+        <v>0.1729319883196683</v>
       </c>
       <c r="J18" t="n">
-        <v>0.999604522647991</v>
+        <v>0.99827598688372</v>
       </c>
       <c r="K18" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.955537129617198</v>
+        <v>-7.954808492099117</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.382114272635</v>
+        <v>113.3836579818265</v>
       </c>
       <c r="R18" t="n">
-        <v>209.3997860354122</v>
+        <v>31.10680383717838</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.91899414242556</v>
+        <v>-8.014642904086402</v>
       </c>
       <c r="D19" t="n">
-        <v>113.4134441270997</v>
+        <v>113.3472040589804</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.955525995048466</v>
+        <v>-7.954808492099117</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3990398165049</v>
+        <v>113.3836579818265</v>
       </c>
       <c r="G19" t="n">
-        <v>201.3305043703332</v>
+        <v>31.10680383717838</v>
       </c>
       <c r="H19" t="n">
-        <v>4.360917032954333</v>
+        <v>7.770451793195363</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1706397566016419</v>
+        <v>0.1729319883196683</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9996067259011443</v>
+        <v>0.9982260931188932</v>
       </c>
       <c r="K19" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.955525995048466</v>
+        <v>-7.954808492099117</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3990398165049</v>
+        <v>113.3836579818265</v>
       </c>
       <c r="R19" t="n">
-        <v>201.3305043703332</v>
+        <v>31.10680383717838</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.916317032781318</v>
+        <v>-8.019995830922259</v>
       </c>
       <c r="D20" t="n">
-        <v>113.400305680087</v>
+        <v>113.3462076464991</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.951466913291271</v>
+        <v>-7.955981578546637</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3854899387964</v>
+        <v>113.3855741993558</v>
       </c>
       <c r="G20" t="n">
-        <v>202.6579175163671</v>
+        <v>31.3440924920894</v>
       </c>
       <c r="H20" t="n">
-        <v>4.235400251132539</v>
+        <v>8.334148720332932</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1706499980213441</v>
+        <v>0.1729325680553569</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9996626006977419</v>
+        <v>0.9982155604197903</v>
       </c>
       <c r="K20" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.951466913291271</v>
+        <v>-7.955981578546637</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3854899387964</v>
+        <v>113.3855741993558</v>
       </c>
       <c r="R20" t="n">
-        <v>202.6579175163671</v>
+        <v>31.3440924920894</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.916481322995805</v>
+        <v>-8.019995830922259</v>
       </c>
       <c r="D21" t="n">
-        <v>113.4031380379135</v>
+        <v>113.3462076464991</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.951016691974005</v>
+        <v>-7.955981578546637</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3871872886383</v>
+        <v>113.3855741993558</v>
       </c>
       <c r="G21" t="n">
-        <v>204.5804462522061</v>
+        <v>31.3440924920894</v>
       </c>
       <c r="H21" t="n">
-        <v>4.222876542773905</v>
+        <v>8.334148720332932</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1706611403727026</v>
+        <v>0.1729325680553569</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9996808242919336</v>
+        <v>0.9982154889496693</v>
       </c>
       <c r="K21" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.951016691974005</v>
+        <v>-7.955981578546637</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3871872886383</v>
+        <v>113.3855741993558</v>
       </c>
       <c r="R21" t="n">
-        <v>204.5804462522061</v>
+        <v>31.3440924920894</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.917916702454285</v>
+        <v>-8.019963453722061</v>
       </c>
       <c r="D22" t="n">
-        <v>113.404703815219</v>
+        <v>113.34597663677</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.949085954770045</v>
+        <v>-7.955869083111749</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3910100273796</v>
+        <v>113.3851634503393</v>
       </c>
       <c r="G22" t="n">
-        <v>203.514430962688</v>
+        <v>31.19596767160729</v>
       </c>
       <c r="H22" t="n">
-        <v>3.779760343050134</v>
+        <v>8.331491149236488</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1706665099702728</v>
+        <v>0.1729327999096046</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857864090197962</v>
+        <v>0.5857852805171301</v>
       </c>
       <c r="K22" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.949085954770045</v>
+        <v>-7.955869083111749</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3910100273796</v>
+        <v>113.3851634503393</v>
       </c>
       <c r="R22" t="n">
-        <v>203.514430962688</v>
+        <v>31.19596767160729</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.917916702454285</v>
+        <v>-8.012921715460601</v>
       </c>
       <c r="D23" t="n">
-        <v>113.404703815219</v>
+        <v>113.3476937586479</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.949085954770045</v>
+        <v>-7.954426504161376</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3910100273796</v>
+        <v>113.3836296523886</v>
       </c>
       <c r="G23" t="n">
-        <v>203.514430962688</v>
+        <v>31.31818898443952</v>
       </c>
       <c r="H23" t="n">
-        <v>3.779760343050134</v>
+        <v>7.613537262111509</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1706665099702728</v>
+        <v>0.1729335488105143</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9998927692047022</v>
+        <v>0.998540469128489</v>
       </c>
       <c r="K23" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.949085954770045</v>
+        <v>-7.954426504161376</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3910100273796</v>
+        <v>113.3836296523886</v>
       </c>
       <c r="R23" t="n">
-        <v>203.514430962688</v>
+        <v>31.31818898443952</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.917744132026058</v>
+        <v>-8.014955216805198</v>
       </c>
       <c r="D24" t="n">
-        <v>113.4053187394624</v>
+        <v>113.3471238398768</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.9528019363903</v>
+        <v>-7.955812857270469</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3898747327368</v>
+        <v>113.3833505262253</v>
       </c>
       <c r="G24" t="n">
-        <v>203.5711337979874</v>
+        <v>31.24327793415549</v>
       </c>
       <c r="H24" t="n">
-        <v>4.25314574250459</v>
+        <v>7.69165458503563</v>
       </c>
       <c r="I24" t="n">
-        <v>0.170670846405363</v>
+        <v>0.1729352410392784</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9998943864935864</v>
+        <v>0.9985380570227835</v>
       </c>
       <c r="K24" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.9528019363903</v>
+        <v>-7.955812857270469</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3898747327368</v>
+        <v>113.3833505262253</v>
       </c>
       <c r="R24" t="n">
-        <v>203.5711337979874</v>
+        <v>31.24327793415549</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.917744132026058</v>
+        <v>-8.019446120839365</v>
       </c>
       <c r="D25" t="n">
-        <v>113.4053187394624</v>
+        <v>113.3461060589864</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.9528019363903</v>
+        <v>-7.957152188418849</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3898747327368</v>
+        <v>113.3843378913062</v>
       </c>
       <c r="G25" t="n">
-        <v>203.5711337979874</v>
+        <v>31.29295025037654</v>
       </c>
       <c r="H25" t="n">
-        <v>4.25314574250459</v>
+        <v>8.105780466459263</v>
       </c>
       <c r="I25" t="n">
-        <v>0.170670846405363</v>
+        <v>0.1729353386861014</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9998922787487626</v>
+        <v>0.9985359231457112</v>
       </c>
       <c r="K25" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.9528019363903</v>
+        <v>-7.957152188418849</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3898747327368</v>
+        <v>113.3843378913062</v>
       </c>
       <c r="R25" t="n">
-        <v>203.5711337979874</v>
+        <v>31.29295025037654</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.918183291835926</v>
+        <v>-8.018803484239813</v>
       </c>
       <c r="D26" t="n">
-        <v>113.4042180225119</v>
+        <v>113.3459706638489</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.950973968086616</v>
+        <v>-7.957170551399957</v>
       </c>
       <c r="F26" t="n">
-        <v>113.38964995096</v>
+        <v>113.3837944309175</v>
       </c>
       <c r="G26" t="n">
-        <v>203.7495201828353</v>
+        <v>31.29133570169061</v>
       </c>
       <c r="H26" t="n">
-        <v>3.983530878554759</v>
+        <v>8.019635284348626</v>
       </c>
       <c r="I26" t="n">
-        <v>0.170673034871195</v>
+        <v>0.1729358134321764</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9998957938360465</v>
+        <v>0.9985317520107748</v>
       </c>
       <c r="K26" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.950973968086616</v>
+        <v>-7.957170551399957</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.38964995096</v>
+        <v>113.3837944309175</v>
       </c>
       <c r="R26" t="n">
-        <v>203.7495201828353</v>
+        <v>31.29133570169061</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.917624474186056</v>
+        <v>-8.017361913628477</v>
       </c>
       <c r="D27" t="n">
-        <v>113.4049037045998</v>
+        <v>113.3463191699581</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.950955424344479</v>
+        <v>-7.956687974606584</v>
       </c>
       <c r="F27" t="n">
-        <v>113.390024685489</v>
+        <v>113.3835506691702</v>
       </c>
       <c r="G27" t="n">
-        <v>203.8505894017848</v>
+        <v>31.28880055452191</v>
       </c>
       <c r="H27" t="n">
-        <v>4.052317677599845</v>
+        <v>7.894642859226463</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1706745639092326</v>
+        <v>0.172936045288511</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9998943491431822</v>
+        <v>0.998527948694952</v>
       </c>
       <c r="K27" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.950955424344479</v>
+        <v>-7.956687974606584</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.390024685489</v>
+        <v>113.3835506691702</v>
       </c>
       <c r="R27" t="n">
-        <v>203.8505894017848</v>
+        <v>31.28880055452191</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.917624474186056</v>
+        <v>-8.015517109115722</v>
       </c>
       <c r="D28" t="n">
-        <v>113.4049037045998</v>
+        <v>113.3470852952356</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.950955424344479</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="F28" t="n">
-        <v>113.390024685489</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="G28" t="n">
-        <v>203.8505894017848</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="H28" t="n">
-        <v>4.052317677599845</v>
+        <v>7.655678237921319</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1706745639092326</v>
+        <v>0.1729362125409667</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9998930846912557</v>
+        <v>0.9985252443959814</v>
       </c>
       <c r="K28" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.950955424344479</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.390024685489</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="R28" t="n">
-        <v>203.8505894017848</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.918280135225645</v>
+        <v>-8.015517109115722</v>
       </c>
       <c r="D29" t="n">
-        <v>113.4043876974362</v>
+        <v>113.3470852952356</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.952533090483195</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3890891691729</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="G29" t="n">
-        <v>203.8614827109384</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="H29" t="n">
-        <v>4.164764515973709</v>
+        <v>7.655678237921319</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1706746813552636</v>
+        <v>0.1729362125409667</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9998890778027958</v>
+        <v>0.9985224858389293</v>
       </c>
       <c r="K29" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.952533090483195</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3890891691729</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="R29" t="n">
-        <v>203.8614827109384</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.918124929003439</v>
+        <v>-8.015517109115722</v>
       </c>
       <c r="D30" t="n">
-        <v>113.4049009603228</v>
+        <v>113.3470852952356</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.951807116313794</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3898656155844</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="G30" t="n">
-        <v>203.8498848182091</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="H30" t="n">
-        <v>4.094998545275955</v>
+        <v>7.655678237921319</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1706750105971539</v>
+        <v>0.1729362125409667</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9998874674377778</v>
+        <v>0.9985205328352295</v>
       </c>
       <c r="K30" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.951807116313794</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3898656155844</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="R30" t="n">
-        <v>203.8498848182091</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,31 +2432,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-7.91948776313358</v>
+        <v>-8.015517109115722</v>
       </c>
       <c r="D31" t="n">
-        <v>113.4043081749422</v>
+        <v>113.3470852952356</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.952375879615643</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="F31" t="n">
-        <v>113.3896231681475</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="G31" t="n">
-        <v>203.8558143346886</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="H31" t="n">
-        <v>3.99863957690421</v>
+        <v>7.655678237921319</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1706750606286309</v>
+        <v>0.1729362125409667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9998866823479516</v>
+        <v>0.9985201380540557</v>
       </c>
       <c r="K31" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.952375879615643</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.3896231681475</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="R31" t="n">
-        <v>203.8558143346886</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.9187356782394</v>
+        <v>-8.015517109115722</v>
       </c>
       <c r="D32" t="n">
-        <v>113.404847210497</v>
+        <v>113.3470852952356</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.952045346301336</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3899719226413</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="G32" t="n">
-        <v>203.8587536000786</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="H32" t="n">
-        <v>4.049985424400656</v>
+        <v>7.655678237921319</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1706751307071933</v>
+        <v>0.1729362125409667</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5857864352335281</v>
+        <v>0.4807404993110608</v>
       </c>
       <c r="K32" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.952045346301336</v>
+        <v>-7.956676264551763</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3899719226413</v>
+        <v>113.3831839974534</v>
       </c>
       <c r="R32" t="n">
-        <v>203.8587536000786</v>
+        <v>31.28317970521891</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,31 +2562,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.918988781735165</v>
+        <v>-8.016184995834008</v>
       </c>
       <c r="D33" t="n">
-        <v>113.4048444736798</v>
+        <v>113.3464002842219</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.952025138929545</v>
+        <v>-7.956530176312437</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3900913498006</v>
+        <v>113.3830017881101</v>
       </c>
       <c r="G33" t="n">
-        <v>203.8585979897402</v>
+        <v>31.28558146291966</v>
       </c>
       <c r="H33" t="n">
-        <v>4.016749595327989</v>
+        <v>7.761777871500169</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1706751380433185</v>
+        <v>0.1729362213972858</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9999910472215017</v>
+        <v>0.910463489720867</v>
       </c>
       <c r="K33" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.952025138929545</v>
+        <v>-7.956530176312437</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3900913498006</v>
+        <v>113.3830017881101</v>
       </c>
       <c r="R33" t="n">
-        <v>203.8585979897402</v>
+        <v>31.28558146291966</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,31 +2627,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.919125279704094</v>
+        <v>-8.016184995834008</v>
       </c>
       <c r="D34" t="n">
-        <v>113.4047122308102</v>
+        <v>113.3464002842219</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.952152416386541</v>
+        <v>-7.956530176312437</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3899655504463</v>
+        <v>113.3830017881101</v>
       </c>
       <c r="G34" t="n">
-        <v>203.8552490672081</v>
+        <v>31.28558146291966</v>
       </c>
       <c r="H34" t="n">
-        <v>4.015524696600155</v>
+        <v>7.761777871500169</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1706751466792922</v>
+        <v>0.1729362213972858</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9999938606581816</v>
+        <v>0.9908561543725551</v>
       </c>
       <c r="K34" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.952152416386541</v>
+        <v>-7.956530176312437</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3899655504463</v>
+        <v>113.3830017881101</v>
       </c>
       <c r="R34" t="n">
-        <v>203.8552490672081</v>
+        <v>31.28558146291966</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,31 +2692,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.919883575265776</v>
+        <v>-8.016134043525758</v>
       </c>
       <c r="D35" t="n">
-        <v>113.4045674962128</v>
+        <v>113.3465295471029</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.952171888430906</v>
+        <v>-7.956572619566354</v>
       </c>
       <c r="F35" t="n">
-        <v>113.3901494954329</v>
+        <v>113.383072357882</v>
       </c>
       <c r="G35" t="n">
-        <v>203.8570252661158</v>
+        <v>31.28461065052675</v>
       </c>
       <c r="H35" t="n">
-        <v>3.925749758372306</v>
+        <v>7.749546589362903</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1706751667939555</v>
+        <v>0.1729362360505773</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9999954394517008</v>
+        <v>0.9968741313647032</v>
       </c>
       <c r="K35" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.952171888430906</v>
+        <v>-7.956572619566354</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3901494954329</v>
+        <v>113.383072357882</v>
       </c>
       <c r="R35" t="n">
-        <v>203.8570252661158</v>
+        <v>31.28461065052675</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,31 +2757,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.919883575265776</v>
+        <v>-8.014801094331675</v>
       </c>
       <c r="D36" t="n">
-        <v>113.4045674962128</v>
+        <v>113.3472906654373</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.952171888430906</v>
+        <v>-7.956559169331699</v>
       </c>
       <c r="F36" t="n">
-        <v>113.3901494954329</v>
+        <v>113.383024047221</v>
       </c>
       <c r="G36" t="n">
-        <v>203.8570252661158</v>
+        <v>31.28468512284504</v>
       </c>
       <c r="H36" t="n">
-        <v>3.925749758372306</v>
+        <v>7.5778768955234</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1706751667939555</v>
+        <v>0.1729362378304759</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9999965400848438</v>
+        <v>0.9987508055806086</v>
       </c>
       <c r="K36" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.952171888430906</v>
+        <v>-7.956559169331699</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.3901494954329</v>
+        <v>113.383024047221</v>
       </c>
       <c r="R36" t="n">
-        <v>203.8570252661158</v>
+        <v>31.28468512284504</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,31 +2822,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.919731915907231</v>
+        <v>-8.014801094331675</v>
       </c>
       <c r="D37" t="n">
-        <v>113.4046538973473</v>
+        <v>113.3472906654373</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.952191091392073</v>
+        <v>-7.956559169331699</v>
       </c>
       <c r="F37" t="n">
-        <v>113.390159979838</v>
+        <v>113.383024047221</v>
       </c>
       <c r="G37" t="n">
-        <v>203.8564677793925</v>
+        <v>31.28468512284504</v>
       </c>
       <c r="H37" t="n">
-        <v>3.94650709901151</v>
+        <v>7.5778768955234</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1706751708710732</v>
+        <v>0.1729362378304759</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9246334847147215</v>
+        <v>0.9987508016150093</v>
       </c>
       <c r="K37" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.952191091392073</v>
+        <v>-7.956559169331699</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.390159979838</v>
+        <v>113.383024047221</v>
       </c>
       <c r="R37" t="n">
-        <v>203.8564677793925</v>
+        <v>31.28468512284504</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,31 +2887,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.919731915907231</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D38" t="n">
-        <v>113.4046538973473</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.952191091392073</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F38" t="n">
-        <v>113.390159979838</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G38" t="n">
-        <v>203.8564677793925</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H38" t="n">
-        <v>3.94650709901151</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1706751708710732</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9400476627257378</v>
+        <v>0.9987507814163336</v>
       </c>
       <c r="K38" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.952191091392073</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.390159979838</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R38" t="n">
-        <v>203.8564677793925</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,31 +2952,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.919630711782168</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D39" t="n">
-        <v>113.4046866043483</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.95222421460385</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3901326243786</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G39" t="n">
-        <v>203.8565842217273</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H39" t="n">
-        <v>3.962842803759374</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1706751720013782</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9222214577022213</v>
+        <v>0.9987507640338799</v>
       </c>
       <c r="K39" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.95222421460385</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3901326243786</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R39" t="n">
-        <v>203.8565842217273</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,31 +3017,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.919391689450885</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D40" t="n">
-        <v>113.4046981470656</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.952123809245207</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3900822484601</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G40" t="n">
-        <v>203.85662060396</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H40" t="n">
-        <v>3.979697633827412</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1706751725291085</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9724243174142326</v>
+        <v>0.9987507579440155</v>
       </c>
       <c r="K40" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.952123809245207</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3900822484601</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R40" t="n">
-        <v>203.85662060396</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,31 +3082,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.919444249564616</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D41" t="n">
-        <v>113.4046812369116</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.95212860675609</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3900866624908</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G41" t="n">
-        <v>203.8566253656488</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H41" t="n">
-        <v>3.973890573051049</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1706751726535325</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9902558560467609</v>
+        <v>0.9986645888731396</v>
       </c>
       <c r="K41" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.95212860675609</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3900866624908</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R41" t="n">
-        <v>203.8566253656488</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.919444249564616</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D42" t="n">
-        <v>113.4046812369116</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.95212860675609</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3900866624908</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G42" t="n">
-        <v>203.8566253656488</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H42" t="n">
-        <v>3.973890573051049</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1706751726535325</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5857809441135466</v>
+        <v>0.5852845661025282</v>
       </c>
       <c r="K42" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.95212860675609</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3900866624908</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R42" t="n">
-        <v>203.8566253656488</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-7.919444249564616</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D43" t="n">
-        <v>113.4046812369116</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.95212860675609</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3900866624908</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G43" t="n">
-        <v>203.8566253656488</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H43" t="n">
-        <v>3.973890573051049</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1706751726535325</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9999998836937285</v>
+        <v>0.9999999747089541</v>
       </c>
       <c r="K43" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.95212860675609</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3900866624908</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R43" t="n">
-        <v>203.8566253656488</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,31 +3277,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-7.919396939243694</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D44" t="n">
-        <v>113.404724210777</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.952143625286578</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3901018100533</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G44" t="n">
-        <v>203.8566163768762</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H44" t="n">
-        <v>3.981468538541854</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1706751732057237</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9999998825574041</v>
+        <v>0.9999999753785674</v>
       </c>
       <c r="K44" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.952143625286578</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3901018100533</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R44" t="n">
-        <v>203.8566163768762</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,31 +3342,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-7.919428266019255</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D45" t="n">
-        <v>113.4046930951467</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.952139900599831</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3900863585931</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G45" t="n">
-        <v>203.8565984384152</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H45" t="n">
-        <v>3.977206262612538</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1706751732235713</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9999998822870667</v>
+        <v>0.9999999790697396</v>
       </c>
       <c r="K45" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.952139900599831</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3900863585931</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R45" t="n">
-        <v>203.8565984384152</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,31 +3407,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-7.919446869307073</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D46" t="n">
-        <v>113.4047209070002</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.952159664331232</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3901136524663</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G46" t="n">
-        <v>203.856597131084</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H46" t="n">
-        <v>3.977347314838852</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1706751735871082</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9999998921104888</v>
+        <v>0.9999999773160712</v>
       </c>
       <c r="K46" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.952159664331232</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3901136524663</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R46" t="n">
-        <v>203.856597131084</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-7.919476057461209</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D47" t="n">
-        <v>113.4047072924605</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.952170555117657</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3901082172324</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G47" t="n">
-        <v>203.8565836280516</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H47" t="n">
-        <v>3.975122219028738</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1706751736968752</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999999049770193</v>
+        <v>0.9999999783752691</v>
       </c>
       <c r="K47" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.952170555117657</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3901082172324</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R47" t="n">
-        <v>203.8565836280516</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,31 +3537,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.919416611231282</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D48" t="n">
-        <v>113.4047196341012</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.952149556007797</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3901033920392</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G48" t="n">
-        <v>203.8565831308799</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H48" t="n">
-        <v>3.979796788032374</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1706751737153392</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999999049868392</v>
+        <v>0.9999999784820244</v>
       </c>
       <c r="K48" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.952149556007797</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3901033920392</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R48" t="n">
-        <v>203.8565831308799</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,31 +3602,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.919416611231282</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D49" t="n">
-        <v>113.4047196341012</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.952149556007797</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3901033920392</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G49" t="n">
-        <v>203.8565831308799</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H49" t="n">
-        <v>3.979796788032374</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1706751737153392</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999999139768482</v>
+        <v>0.9999999776704758</v>
       </c>
       <c r="K49" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.952149556007797</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3901033920392</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R49" t="n">
-        <v>203.8565831308799</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,31 +3667,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-7.919427688431913</v>
+        <v>-8.014567131281749</v>
       </c>
       <c r="D50" t="n">
-        <v>113.4047284639926</v>
+        <v>113.3474625313688</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.952149825963924</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3901170471498</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="G50" t="n">
-        <v>203.8565839534401</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="H50" t="n">
-        <v>3.97848281692314</v>
+        <v>7.543450236405444</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1706751737524879</v>
+        <v>0.1729362441881535</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9999999178308249</v>
+        <v>0.9999999798866515</v>
       </c>
       <c r="K50" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.952149825963924</v>
+        <v>-7.956589690370822</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3901170471498</v>
+        <v>113.3830333800354</v>
       </c>
       <c r="R50" t="n">
-        <v>203.8565839534401</v>
+        <v>31.28449196649983</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-7.919424070031273</v>
+        <v>-8.015670957254303</v>
       </c>
       <c r="D51" t="n">
-        <v>113.4047247936017</v>
+        <v>113.3467903772119</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.952159573466064</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3901074080433</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="G51" t="n">
-        <v>203.8565840194606</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="H51" t="n">
-        <v>3.9801079092588</v>
+        <v>7.686486220496374</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1706751737651204</v>
+        <v>0.1729362446002689</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9999999201006997</v>
+        <v>0.9999999819479249</v>
       </c>
       <c r="K51" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.952159573466064</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3901074080433</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="R51" t="n">
-        <v>203.8565840194606</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,31 +3797,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-7.919428815719479</v>
+        <v>-8.015670957254303</v>
       </c>
       <c r="D52" t="n">
-        <v>113.4047292716051</v>
+        <v>113.3467903772119</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.952162058316247</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3901128953179</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="G52" t="n">
-        <v>203.8565842803915</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="H52" t="n">
-        <v>3.979833033803954</v>
+        <v>7.686486220496374</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1706751737675997</v>
+        <v>0.1729362446002689</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5857864397593812</v>
+        <v>0.5857864397315015</v>
       </c>
       <c r="K52" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.952162058316247</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3901128953179</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="R52" t="n">
-        <v>203.8565842803915</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,31 +3862,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-7.919423560845885</v>
+        <v>-8.015670957254303</v>
       </c>
       <c r="D53" t="n">
-        <v>113.4047295130849</v>
+        <v>113.3467903772119</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.952155933044653</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3901135257612</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="G53" t="n">
-        <v>203.8565841596566</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="H53" t="n">
-        <v>3.979727202926152</v>
+        <v>7.686486220496374</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1706751737787879</v>
+        <v>0.1729362446002689</v>
       </c>
       <c r="J53" t="n">
-        <v>0.9999999960997066</v>
+        <v>0.999999998656772</v>
       </c>
       <c r="K53" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.952155933044653</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3901135257612</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="R53" t="n">
-        <v>203.8565841596566</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,31 +3927,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-7.919423560845885</v>
+        <v>-8.015670957254303</v>
       </c>
       <c r="D54" t="n">
-        <v>113.4047295130849</v>
+        <v>113.3467903772119</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.952155933044653</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3901135257612</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="G54" t="n">
-        <v>203.8565841596566</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="H54" t="n">
-        <v>3.979727202926152</v>
+        <v>7.686486220496374</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1706751737787879</v>
+        <v>0.1729362446002689</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9999999964009865</v>
+        <v>0.9538343808585827</v>
       </c>
       <c r="K54" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.952155933044653</v>
+        <v>-7.956594086248897</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3901135257612</v>
+        <v>113.3830356156825</v>
       </c>
       <c r="R54" t="n">
-        <v>203.8565841596566</v>
+        <v>31.28440454172441</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,31 +3992,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-7.919421694201893</v>
+        <v>-8.014466445823384</v>
       </c>
       <c r="D55" t="n">
-        <v>113.4047288184982</v>
+        <v>113.3475244303349</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.9521566605373</v>
+        <v>-7.956592304741193</v>
       </c>
       <c r="F55" t="n">
-        <v>113.3901116728007</v>
+        <v>113.3830319035438</v>
       </c>
       <c r="G55" t="n">
-        <v>203.8565841292982</v>
+        <v>31.28449202431441</v>
       </c>
       <c r="H55" t="n">
-        <v>3.980042609514422</v>
+        <v>7.530010244270685</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1706751737789468</v>
+        <v>0.1729362446535698</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9999999972017017</v>
+        <v>0.990849477455616</v>
       </c>
       <c r="K55" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.9521566605373</v>
+        <v>-7.956592304741193</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.3901116728007</v>
+        <v>113.3830319035438</v>
       </c>
       <c r="R55" t="n">
-        <v>203.8565841292982</v>
+        <v>31.28449202431441</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-7.919421694201893</v>
+        <v>-8.014466445823384</v>
       </c>
       <c r="D56" t="n">
-        <v>113.4047288184982</v>
+        <v>113.3475244303349</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.9521566605373</v>
+        <v>-7.956592304741193</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3901116728007</v>
+        <v>113.3830319035438</v>
       </c>
       <c r="G56" t="n">
-        <v>203.8565841292982</v>
+        <v>31.28449202431441</v>
       </c>
       <c r="H56" t="n">
-        <v>3.980042609514422</v>
+        <v>7.530010244270685</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1706751737789468</v>
+        <v>0.1729362446535698</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9999999979103515</v>
+        <v>0.9958980815180619</v>
       </c>
       <c r="K56" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.9521566605373</v>
+        <v>-7.956592304741193</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3901116728007</v>
+        <v>113.3830319035438</v>
       </c>
       <c r="R56" t="n">
-        <v>203.8565841292982</v>
+        <v>31.28449202431441</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,31 +4122,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.919421694201893</v>
+        <v>-8.014826473030192</v>
       </c>
       <c r="D57" t="n">
-        <v>113.4047288184982</v>
+        <v>113.3473362267111</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.9521566605373</v>
+        <v>-7.956607600526676</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3901116728007</v>
+        <v>113.3830551560886</v>
       </c>
       <c r="G57" t="n">
-        <v>203.8565841292982</v>
+        <v>31.28446193141401</v>
       </c>
       <c r="H57" t="n">
-        <v>3.980042609514422</v>
+        <v>7.574859679093357</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1706751737789468</v>
+        <v>0.1729362446963303</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9999999987796815</v>
+        <v>0.9978157855280532</v>
       </c>
       <c r="K57" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.9521566605373</v>
+        <v>-7.956607600526676</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3901116728007</v>
+        <v>113.3830551560886</v>
       </c>
       <c r="R57" t="n">
-        <v>203.8565841292982</v>
+        <v>31.28446193141401</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,31 +4187,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-7.91942147722201</v>
+        <v>-8.014826473030192</v>
       </c>
       <c r="D58" t="n">
-        <v>113.4047300397481</v>
+        <v>113.3473362267111</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.952156898972581</v>
+        <v>-7.956607600526676</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3901126906678</v>
+        <v>113.3830551560886</v>
       </c>
       <c r="G58" t="n">
-        <v>203.8565841528759</v>
+        <v>31.28446193141401</v>
       </c>
       <c r="H58" t="n">
-        <v>3.980097981789948</v>
+        <v>7.574859679093357</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1706751737794074</v>
+        <v>0.1729362446963303</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9999999996804259</v>
+        <v>0.9987272793517695</v>
       </c>
       <c r="K58" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.952156898972581</v>
+        <v>-7.956607600526676</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3901126906678</v>
+        <v>113.3830551560886</v>
       </c>
       <c r="R58" t="n">
-        <v>203.8565841528759</v>
+        <v>31.28446193141401</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,31 +4252,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.91942147722201</v>
+        <v>-8.014821250165019</v>
       </c>
       <c r="D59" t="n">
-        <v>113.4047300397481</v>
+        <v>113.3473080229432</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.952156898972581</v>
+        <v>-7.956592533691857</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3901126906678</v>
+        <v>113.3830329962723</v>
       </c>
       <c r="G59" t="n">
-        <v>203.8565841528759</v>
+        <v>31.28446610970299</v>
       </c>
       <c r="H59" t="n">
-        <v>3.980097981789948</v>
+        <v>7.576140780471873</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1706751737794074</v>
+        <v>0.1729362449726067</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9999999997724729</v>
+        <v>0.9992613119858353</v>
       </c>
       <c r="K59" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.952156898972581</v>
+        <v>-7.956592533691857</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3901126906678</v>
+        <v>113.3830329962723</v>
       </c>
       <c r="R59" t="n">
-        <v>203.8565841528759</v>
+        <v>31.28446610970299</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,31 +4317,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.919421508321473</v>
+        <v>-8.014821250165019</v>
       </c>
       <c r="D60" t="n">
-        <v>113.4047297915445</v>
+        <v>113.3473080229432</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.952156923459074</v>
+        <v>-7.956592533691857</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3901124454212</v>
+        <v>113.3830329962723</v>
       </c>
       <c r="G60" t="n">
-        <v>203.8565841455251</v>
+        <v>31.28446610970299</v>
       </c>
       <c r="H60" t="n">
-        <v>3.980097177527801</v>
+        <v>7.576140780471873</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1706751737794923</v>
+        <v>0.1729362449726067</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9999999998754701</v>
+        <v>0.9997613436017188</v>
       </c>
       <c r="K60" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.952156923459074</v>
+        <v>-7.956592533691857</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3901124454212</v>
+        <v>113.3830329962723</v>
       </c>
       <c r="R60" t="n">
-        <v>203.8565841455251</v>
+        <v>31.28446610970299</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,31 +4382,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.919421508321473</v>
+        <v>-8.014821250165019</v>
       </c>
       <c r="D61" t="n">
-        <v>113.4047297915445</v>
+        <v>113.3473080229432</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.952156923459074</v>
+        <v>-7.956592533691857</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3901124454212</v>
+        <v>113.3830329962723</v>
       </c>
       <c r="G61" t="n">
-        <v>203.8565841455251</v>
+        <v>31.28446610970299</v>
       </c>
       <c r="H61" t="n">
-        <v>3.980097177527801</v>
+        <v>7.576140780471873</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1706751737794923</v>
+        <v>0.1729362449726067</v>
       </c>
       <c r="J61" t="n">
-        <v>0.999999999950409</v>
+        <v>0.9998558387449942</v>
       </c>
       <c r="K61" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.952156923459074</v>
+        <v>-7.956592533691857</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3901124454212</v>
+        <v>113.3830329962723</v>
       </c>
       <c r="R61" t="n">
-        <v>203.8565841455251</v>
+        <v>31.28446610970299</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-7.919421590735716</v>
+        <v>-8.014569764233592</v>
       </c>
       <c r="D62" t="n">
-        <v>113.4047301962759</v>
+        <v>113.3474625328017</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.952156928803759</v>
+        <v>-7.956593111803734</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3901128845668</v>
+        <v>113.3830328655116</v>
       </c>
       <c r="G62" t="n">
-        <v>203.8565841451794</v>
+        <v>31.28446872601781</v>
       </c>
       <c r="H62" t="n">
-        <v>3.980087807032457</v>
+        <v>7.543345790815476</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1706751737795031</v>
+        <v>0.1729362450183446</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857864397593827</v>
+        <v>0.5857864340461464</v>
       </c>
       <c r="K62" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.952156928803759</v>
+        <v>-7.956593111803734</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3901128845668</v>
+        <v>113.3830328655116</v>
       </c>
       <c r="R62" t="n">
-        <v>203.8565841451794</v>
+        <v>31.28446872601781</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,31 +4512,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-7.919421483087007</v>
+        <v>-8.014565165909955</v>
       </c>
       <c r="D63" t="n">
-        <v>113.404730104581</v>
+        <v>113.3474631940796</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.952156911805604</v>
+        <v>-7.956591804429146</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3901127523952</v>
+        <v>113.3830314910033</v>
       </c>
       <c r="G63" t="n">
-        <v>203.8565841436165</v>
+        <v>31.28445683305094</v>
       </c>
       <c r="H63" t="n">
-        <v>3.980098828711521</v>
+        <v>7.542916665361766</v>
       </c>
       <c r="I63" t="n">
-        <v>0.170675173779519</v>
+        <v>0.1729362451528036</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999999853124</v>
+        <v>0.9999999982979715</v>
       </c>
       <c r="K63" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.952156911805604</v>
+        <v>-7.956591804429146</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3901127523952</v>
+        <v>113.3830314910033</v>
       </c>
       <c r="R63" t="n">
-        <v>203.8565841436165</v>
+        <v>31.28445683305094</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,31 +4577,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.919421509382273</v>
+        <v>-8.014828533872551</v>
       </c>
       <c r="D64" t="n">
-        <v>113.4047299560525</v>
+        <v>113.3473291953422</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.952156838847244</v>
+        <v>-7.956605973499685</v>
       </c>
       <c r="F64" t="n">
-        <v>113.390112648189</v>
+        <v>113.3830503633808</v>
       </c>
       <c r="G64" t="n">
-        <v>203.8565841439402</v>
+        <v>31.28444502546542</v>
       </c>
       <c r="H64" t="n">
-        <v>3.980086760991266</v>
+        <v>7.575338137316359</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1706751737795286</v>
+        <v>0.1729362452175252</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9999999999909743</v>
+        <v>0.9999999979815897</v>
       </c>
       <c r="K64" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.952156838847244</v>
+        <v>-7.956605973499685</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.390112648189</v>
+        <v>113.3830503633808</v>
       </c>
       <c r="R64" t="n">
-        <v>203.8565841439402</v>
+        <v>31.28444502546542</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,31 +4642,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.919421530201697</v>
+        <v>-8.014828533872551</v>
       </c>
       <c r="D65" t="n">
-        <v>113.404729957405</v>
+        <v>113.3473291953422</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.952156851899933</v>
+        <v>-7.956605973499685</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3901126530088</v>
+        <v>113.3830503633808</v>
       </c>
       <c r="G65" t="n">
-        <v>203.8565841445395</v>
+        <v>31.28444502546542</v>
       </c>
       <c r="H65" t="n">
-        <v>3.98008581669289</v>
+        <v>7.575338137316359</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1706751737795308</v>
+        <v>0.1729362452175252</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9999999999930829</v>
+        <v>0.8429976433863694</v>
       </c>
       <c r="K65" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.952156851899933</v>
+        <v>-7.956605973499685</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3901126530088</v>
+        <v>113.3830503633808</v>
       </c>
       <c r="R65" t="n">
-        <v>203.8565841445395</v>
+        <v>31.28444502546542</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,31 +4707,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.919421463967622</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D66" t="n">
-        <v>113.4047299188189</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.952156808087445</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3901126044124</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G66" t="n">
-        <v>203.8565841443625</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H66" t="n">
-        <v>3.980088542810897</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1706751737795323</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9999999999960154</v>
+        <v>0.9923195029662634</v>
       </c>
       <c r="K66" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.952156808087445</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3901126044124</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R66" t="n">
-        <v>203.8565841443625</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,31 +4772,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.919421504796478</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D67" t="n">
-        <v>113.4047300101551</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.952156836812387</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3901127011525</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G67" t="n">
-        <v>203.8565841442308</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H67" t="n">
-        <v>3.980087071155448</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1706751737795332</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8536709436649456</v>
+        <v>0.9714698209311058</v>
       </c>
       <c r="K67" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.952156836812387</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3901127011525</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R67" t="n">
-        <v>203.8565841442308</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,31 +4837,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.919421592134364</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D68" t="n">
-        <v>113.404729961824</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.952156851095318</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3901126854422</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G68" t="n">
-        <v>203.8565841443238</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H68" t="n">
-        <v>3.980078188788246</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1706751737795343</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9480076115892799</v>
+        <v>0.9954515028366085</v>
       </c>
       <c r="K68" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.952156851095318</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3901126854422</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R68" t="n">
-        <v>203.8565841443238</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,31 +4902,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.919421451514713</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D69" t="n">
-        <v>113.4047300222337</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.952156828459924</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3901126931688</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G69" t="n">
-        <v>203.8565841443192</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H69" t="n">
-        <v>3.980092533877289</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1706751737795348</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9348061559411732</v>
+        <v>0.9977874213654291</v>
       </c>
       <c r="K69" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.952156828459924</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3901126931688</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R69" t="n">
-        <v>203.8565841443192</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,31 +4967,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-7.919421451514713</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D70" t="n">
-        <v>113.4047300222337</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.952156828459924</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3901126931688</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G70" t="n">
-        <v>203.8565841443192</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H70" t="n">
-        <v>3.980092533877289</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1706751737795348</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9837915317316864</v>
+        <v>0.9980351950057647</v>
       </c>
       <c r="K70" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.952156828459924</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3901126931688</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R70" t="n">
-        <v>203.8565841443192</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.919421455884771</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D71" t="n">
-        <v>113.404729988666</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.952156791070939</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3901126782493</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G71" t="n">
-        <v>203.8565841443204</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H71" t="n">
-        <v>3.980087456613266</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1706751737795349</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9942251552859384</v>
+        <v>0.9981821949757622</v>
       </c>
       <c r="K71" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.952156791070939</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3901126782493</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R71" t="n">
-        <v>203.8565841443204</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,31 +5097,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-7.919421436885777</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D72" t="n">
-        <v>113.4047299996408</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.952156798041619</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3901126776275</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G72" t="n">
-        <v>203.8565841443228</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H72" t="n">
-        <v>3.980090614130608</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I72" t="n">
-        <v>0.170675173779535</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5857839251660241</v>
+        <v>0.5848292617657087</v>
       </c>
       <c r="K72" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.952156798041619</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3901126776275</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R72" t="n">
-        <v>203.8565841443228</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,31 +5162,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-7.919421436885777</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D73" t="n">
-        <v>113.4047299996408</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.952156798041619</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3901126776275</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G73" t="n">
-        <v>203.8565841443228</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H73" t="n">
-        <v>3.980090614130608</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I73" t="n">
-        <v>0.170675173779535</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9993706838686914</v>
+        <v>0.9988736220246504</v>
       </c>
       <c r="K73" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.952156798041619</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3901126776275</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R73" t="n">
-        <v>203.8565841443228</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,31 +5227,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-7.919421475048036</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D74" t="n">
-        <v>113.4047299843822</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.952156799617838</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3901126787058</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G74" t="n">
-        <v>203.8565841443266</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H74" t="n">
-        <v>3.980086165825238</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I74" t="n">
-        <v>0.170675173779535</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9995428979288623</v>
+        <v>0.9991126925985853</v>
       </c>
       <c r="K74" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.952156799617838</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3901126787058</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R74" t="n">
-        <v>203.8565841443266</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,31 +5292,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-7.919421444725295</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D75" t="n">
-        <v>113.4047300004678</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.952156800505948</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3901126808546</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G75" t="n">
-        <v>203.856584144327</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H75" t="n">
-        <v>3.980089960589475</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9997717543951161</v>
+        <v>0.9992016063051864</v>
       </c>
       <c r="K75" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.952156800505948</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3901126808546</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R75" t="n">
-        <v>203.856584144327</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,31 +5357,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.919421444725295</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D76" t="n">
-        <v>113.4047300004678</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.952156800505948</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3901126808546</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G76" t="n">
-        <v>203.856584144327</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H76" t="n">
-        <v>3.980089960589475</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9999139459371805</v>
+        <v>0.9993415433921805</v>
       </c>
       <c r="K76" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.952156800505948</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3901126808546</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R76" t="n">
-        <v>203.856584144327</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,31 +5422,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D77" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G77" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H77" t="n">
-        <v>3.980089978369283</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9999300839298235</v>
+        <v>0.9994269693532822</v>
       </c>
       <c r="K77" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R77" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,31 +5487,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D78" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G78" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H78" t="n">
-        <v>3.980089978369283</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9999783826106613</v>
+        <v>0.9994971495892007</v>
       </c>
       <c r="K78" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R78" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014568849434131</v>
       </c>
       <c r="D79" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3474623928526</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="G79" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="H79" t="n">
-        <v>3.980089978369283</v>
+        <v>7.543299643523969</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452247876</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9999921237591129</v>
+        <v>0.9995330028436479</v>
       </c>
       <c r="K79" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956592541615633</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830324911601</v>
       </c>
       <c r="R79" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28445233406233</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,31 +5617,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.01482848050934</v>
       </c>
       <c r="D80" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473298950584</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606391664826</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830507770787</v>
       </c>
       <c r="G80" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444732725488</v>
       </c>
       <c r="H80" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575276973254558</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.172936245230377</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9476590195193297</v>
+        <v>0.9995330028258793</v>
       </c>
       <c r="K80" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606391664826</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830507770787</v>
       </c>
       <c r="R80" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444732725488</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,31 +5682,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014828870299652</v>
       </c>
       <c r="D81" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473293076431</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606410697666</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830504139931</v>
       </c>
       <c r="G81" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844450948954</v>
       </c>
       <c r="H81" t="n">
-        <v>3.980089978369283</v>
+        <v>7.5753250319287</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452643826</v>
       </c>
       <c r="J81" t="n">
-        <v>0.980469795340859</v>
+        <v>0.9997518616396036</v>
       </c>
       <c r="K81" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606410697666</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830504139931</v>
       </c>
       <c r="R81" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844450948954</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,31 +5747,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014828870299652</v>
       </c>
       <c r="D82" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473293076431</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606410697666</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830504139931</v>
       </c>
       <c r="G82" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844450948954</v>
       </c>
       <c r="H82" t="n">
-        <v>3.980089978369283</v>
+        <v>7.5753250319287</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452643826</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857613013975862</v>
+        <v>0.5857864206289164</v>
       </c>
       <c r="K82" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606410697666</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830504139931</v>
       </c>
       <c r="R82" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844450948954</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,31 +5812,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014828498889434</v>
       </c>
       <c r="D83" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473291109882</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606079549133</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830501944884</v>
       </c>
       <c r="G83" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444643319334</v>
       </c>
       <c r="H83" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575319901123211</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452669628</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999999996045</v>
+        <v>0.9999999995525268</v>
       </c>
       <c r="K83" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956606079549133</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830501944884</v>
       </c>
       <c r="R83" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444643319334</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,31 +5877,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014828630605324</v>
       </c>
       <c r="D84" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473291626158</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95660629600556</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830501952162</v>
       </c>
       <c r="G84" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444719535191</v>
       </c>
       <c r="H84" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575308937035374</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362452807396</v>
       </c>
       <c r="J84" t="n">
-        <v>0.9999999999996045</v>
+        <v>0.999999999539426</v>
       </c>
       <c r="K84" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95660629600556</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830501952162</v>
       </c>
       <c r="R84" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444719535191</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,31 +5942,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820042076883</v>
       </c>
       <c r="D85" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473071166593</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659207405846</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830316041237</v>
       </c>
       <c r="G85" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444714857174</v>
       </c>
       <c r="H85" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576041878428779</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.172936245321891</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999999996045</v>
+        <v>0.9999999995040356</v>
       </c>
       <c r="K85" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659207405846</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830316041237</v>
       </c>
       <c r="R85" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444714857174</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820042076883</v>
       </c>
       <c r="D86" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473071166593</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659207405846</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830316041237</v>
       </c>
       <c r="G86" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444714857174</v>
       </c>
       <c r="H86" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576041878428779</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.172936245321891</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999999999996039</v>
+        <v>0.9999999994950803</v>
       </c>
       <c r="K86" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659207405846</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830316041237</v>
       </c>
       <c r="R86" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444714857174</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,31 +6072,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820042076883</v>
       </c>
       <c r="D87" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473071166593</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659207405846</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830316041237</v>
       </c>
       <c r="G87" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444714857174</v>
       </c>
       <c r="H87" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576041878428779</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.172936245321891</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9999999999996039</v>
+        <v>0.999999999477641</v>
       </c>
       <c r="K87" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659207405846</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830316041237</v>
       </c>
       <c r="R87" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444714857174</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,31 +6137,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821484533073</v>
       </c>
       <c r="D88" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473082064021</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593095639961</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830329503403</v>
       </c>
       <c r="G88" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444584848968</v>
       </c>
       <c r="H88" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576096532529245</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453345676</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9999999999996037</v>
+        <v>0.9280335681635622</v>
       </c>
       <c r="K88" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593095639961</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830329503403</v>
       </c>
       <c r="R88" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444584848968</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,31 +6202,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820056266943</v>
       </c>
       <c r="D89" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473120438872</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="G89" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="H89" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575705707877927</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453440648</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9999999999996037</v>
+        <v>0.9691508980134889</v>
       </c>
       <c r="K89" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="R89" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,31 +6267,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820056266943</v>
       </c>
       <c r="D90" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473120438872</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="G90" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="H90" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575705707877927</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453440648</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9999999999996037</v>
+        <v>0.9919098832053366</v>
       </c>
       <c r="K90" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="R90" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,31 +6332,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820056266943</v>
       </c>
       <c r="D91" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473120438872</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="G91" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="H91" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575705707877927</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453440648</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9999999999996037</v>
+        <v>0.9972537687389655</v>
       </c>
       <c r="K91" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="R91" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,31 +6397,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820056266943</v>
       </c>
       <c r="D92" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473120438872</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="G92" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="H92" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575705707877927</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453440648</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5857864397593829</v>
+        <v>0.5857848896690908</v>
       </c>
       <c r="K92" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="R92" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,31 +6462,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820056266943</v>
       </c>
       <c r="D93" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473120438872</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="G93" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="H93" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575705707877927</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453440648</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999996941467</v>
       </c>
       <c r="K93" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="R93" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,31 +6527,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014820056266943</v>
       </c>
       <c r="D94" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473120438872</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="G94" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="H94" t="n">
-        <v>3.980089978369283</v>
+        <v>7.575705707877927</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453440648</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9999999999999996</v>
+        <v>0.9999999996881119</v>
       </c>
       <c r="K94" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956594672272706</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830349467395</v>
       </c>
       <c r="R94" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444749768957</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,31 +6592,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822471263773</v>
       </c>
       <c r="D95" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473089510529</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593864681667</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830338304719</v>
       </c>
       <c r="G95" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444717178811</v>
       </c>
       <c r="H95" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576124961580077</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453488036</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999996959801</v>
       </c>
       <c r="K95" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593864681667</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830338304719</v>
       </c>
       <c r="R95" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444717178811</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,31 +6657,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822471263773</v>
       </c>
       <c r="D96" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473089510529</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593864681667</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830338304719</v>
       </c>
       <c r="G96" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444717178811</v>
       </c>
       <c r="H96" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576124961580077</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453488036</v>
       </c>
       <c r="J96" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8910714314530755</v>
       </c>
       <c r="K96" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593864681667</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830338304719</v>
       </c>
       <c r="R96" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444717178811</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,31 +6722,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822471263773</v>
       </c>
       <c r="D97" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473089510529</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593864681667</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830338304719</v>
       </c>
       <c r="G97" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444717178811</v>
       </c>
       <c r="H97" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576124961580077</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453488036</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9405692983734951</v>
+        <v>0.9865143971934912</v>
       </c>
       <c r="K97" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593864681667</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830338304719</v>
       </c>
       <c r="R97" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444717178811</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,31 +6787,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.01482225033576</v>
       </c>
       <c r="D98" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473087148541</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659364761331</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830335911179</v>
       </c>
       <c r="G98" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444662491247</v>
       </c>
       <c r="H98" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576124415487589</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453512447</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8859437644890745</v>
+        <v>0.8634863014396117</v>
       </c>
       <c r="K98" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659364761331</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830335911179</v>
       </c>
       <c r="R98" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444662491247</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,31 +6852,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.01482225033576</v>
       </c>
       <c r="D99" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473087148541</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659364761331</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830335911179</v>
       </c>
       <c r="G99" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444662491247</v>
       </c>
       <c r="H99" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576124415487589</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453512447</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9092733573895534</v>
+        <v>0.9855612344444521</v>
       </c>
       <c r="K99" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659364761331</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830335911179</v>
       </c>
       <c r="R99" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444662491247</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,31 +6917,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822074283948</v>
       </c>
       <c r="D100" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083157005</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593403236442</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830332338852</v>
       </c>
       <c r="G100" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444664193944</v>
       </c>
       <c r="H100" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576133306400745</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453523252</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9590235490603326</v>
+        <v>0.9942408993814417</v>
       </c>
       <c r="K100" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593403236442</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830332338852</v>
       </c>
       <c r="R100" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444664193944</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,31 +6982,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D101" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G101" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H101" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9865961716479623</v>
+        <v>0.9968213662500051</v>
       </c>
       <c r="K101" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R101" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,31 +7047,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D102" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G102" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H102" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5857812631259455</v>
+        <v>0.5857845758019141</v>
       </c>
       <c r="K102" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R102" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,31 +7112,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D103" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G103" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H103" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9995973165938178</v>
+        <v>0.9989160736463532</v>
       </c>
       <c r="K103" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R103" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,31 +7177,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D104" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G104" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H104" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9999014906357157</v>
+        <v>0.9990765296287466</v>
       </c>
       <c r="K104" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R104" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,31 +7242,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D105" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G105" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H105" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9999513661953182</v>
+        <v>0.9993368020224395</v>
       </c>
       <c r="K105" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R105" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,31 +7307,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D106" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G106" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H106" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J106" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999336802021744</v>
       </c>
       <c r="K106" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R106" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,31 +7372,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821968818769</v>
       </c>
       <c r="D107" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083376989</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="G107" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="H107" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121189976907</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453575558</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9998554976123194</v>
       </c>
       <c r="K107" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.95659339073853</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331984828</v>
       </c>
       <c r="R107" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463833646</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,31 +7437,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821970505803</v>
       </c>
       <c r="D108" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083360426</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="G108" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="H108" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121334719804</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453576623</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999287117638389</v>
       </c>
       <c r="K108" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="R108" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821970505803</v>
       </c>
       <c r="D109" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083360426</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="G109" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="H109" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121334719804</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453576623</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9167922521000508</v>
       </c>
       <c r="K109" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="R109" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,31 +7567,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821970505803</v>
       </c>
       <c r="D110" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083360426</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="G110" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="H110" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121334719804</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453576623</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9441458268199799</v>
+        <v>0.9703758327063946</v>
       </c>
       <c r="K110" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="R110" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,31 +7632,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821970505803</v>
       </c>
       <c r="D111" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083360426</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="G111" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="H111" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121334719804</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453576623</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9888877341741178</v>
+        <v>0.9948199526912156</v>
       </c>
       <c r="K111" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="R111" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,31 +7697,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014821970505803</v>
       </c>
       <c r="D112" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083360426</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="G112" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="H112" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576121334719804</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453576623</v>
       </c>
       <c r="J112" t="n">
-        <v>0.58576024416106</v>
+        <v>0.5857833905811708</v>
       </c>
       <c r="K112" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593391310868</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830331975054</v>
       </c>
       <c r="R112" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444637979797</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,31 +7762,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822203334864</v>
       </c>
       <c r="D113" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473084727272</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593538257748</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333870438</v>
       </c>
       <c r="G113" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444648753729</v>
       </c>
       <c r="H113" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576132517206936</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453578899</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998382507</v>
       </c>
       <c r="K113" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593538257748</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333870438</v>
       </c>
       <c r="R113" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444648753729</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,31 +7827,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822260826241</v>
       </c>
       <c r="D114" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083252276</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="G114" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="H114" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576148103942586</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453580971</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998381262</v>
       </c>
       <c r="K114" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="R114" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,31 +7892,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822260826241</v>
       </c>
       <c r="D115" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083252276</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="G115" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="H115" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576148103942586</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453580971</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998600897</v>
       </c>
       <c r="K115" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="R115" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,31 +7957,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822260826241</v>
       </c>
       <c r="D116" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083252276</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="G116" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="H116" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576148103942586</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453580971</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998939613</v>
       </c>
       <c r="K116" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="R116" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822260826241</v>
       </c>
       <c r="D117" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083252276</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="G117" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="H117" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576148103942586</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453580971</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999998817211</v>
       </c>
       <c r="K117" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="R117" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,31 +8087,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822260826241</v>
       </c>
       <c r="D118" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083252276</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="G118" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="H118" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576148103942586</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453580971</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9916081995826925</v>
       </c>
       <c r="K118" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="R118" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,31 +8152,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822260826241</v>
       </c>
       <c r="D119" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083252276</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="G119" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="H119" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576148103942586</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453580971</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9916081995823571</v>
       </c>
       <c r="K119" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593475888638</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333129364</v>
       </c>
       <c r="R119" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463891585</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,31 +8217,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822532953346</v>
       </c>
       <c r="D120" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083367953</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="G120" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="H120" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576171215642064</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453586715</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9949611194642261</v>
       </c>
       <c r="K120" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="R120" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,31 +8282,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822532953346</v>
       </c>
       <c r="D121" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083367953</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="G121" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="H121" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576171215642064</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453586715</v>
       </c>
       <c r="J121" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9961388720637959</v>
       </c>
       <c r="K121" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="R121" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,31 +8347,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822532953346</v>
       </c>
       <c r="D122" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083367953</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="G122" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="H122" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576171215642064</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453586715</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857864397593828</v>
+        <v>0.5857838002504867</v>
       </c>
       <c r="K122" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="R122" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,31 +8412,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822532953346</v>
       </c>
       <c r="D123" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083367953</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="G123" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="H123" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576171215642064</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453586715</v>
       </c>
       <c r="J123" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.999999999996968</v>
       </c>
       <c r="K123" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593570402092</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830334335328</v>
       </c>
       <c r="R123" t="n">
-        <v>203.8565841443267</v>
+        <v>31.28444642648939</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,31 +8477,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D124" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G124" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H124" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999965612</v>
       </c>
       <c r="K124" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R124" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,31 +8542,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D125" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G125" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H125" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999965432</v>
       </c>
       <c r="K125" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R125" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,31 +8607,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D126" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G126" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H126" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0.9999999999968829</v>
       </c>
       <c r="K126" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R126" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,31 +8672,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D127" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G127" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H127" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9047264856099946</v>
+        <v>0.9137041054198113</v>
       </c>
       <c r="K127" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R127" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,31 +8737,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D128" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G128" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H128" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9491220658302907</v>
+        <v>0.9845014089414066</v>
       </c>
       <c r="K128" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R128" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,31 +8802,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D129" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G129" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H129" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9706273435260574</v>
+        <v>0.989870275766765</v>
       </c>
       <c r="K129" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R129" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D130" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G130" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H130" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9916200353848555</v>
+        <v>0.9949539330413529</v>
       </c>
       <c r="K130" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R130" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,31 +8932,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D131" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G131" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H131" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9933880831259417</v>
+        <v>0.9246137555496516</v>
       </c>
       <c r="K131" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R131" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D132" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G132" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H132" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5857796246434241</v>
+        <v>0.5856299942102062</v>
       </c>
       <c r="K132" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R132" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,31 +9062,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D133" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G133" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H133" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9987571408326035</v>
+        <v>0.9992636991196899</v>
       </c>
       <c r="K133" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R133" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,31 +9127,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D134" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G134" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H134" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9989838362178757</v>
+        <v>0.9996480704541443</v>
       </c>
       <c r="K134" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R134" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,31 +9192,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D135" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G135" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H135" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J135" t="n">
-        <v>0.999342775808329</v>
+        <v>0.9998323781807633</v>
       </c>
       <c r="K135" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R135" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,31 +9257,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D136" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G136" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H136" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9995443352057795</v>
+        <v>0.9998955072272302</v>
       </c>
       <c r="K136" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R136" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,31 +9322,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D137" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G137" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H137" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J137" t="n">
-        <v>0.999712655331459</v>
+        <v>0.999925779193363</v>
       </c>
       <c r="K137" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R137" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D138" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G138" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H138" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9998062923044129</v>
+        <v>0.9999611855127991</v>
       </c>
       <c r="K138" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R138" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,31 +9452,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D139" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G139" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H139" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9998258117171255</v>
+        <v>0.9999736311255395</v>
       </c>
       <c r="K139" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R139" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,31 +9517,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D140" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G140" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H140" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J140" t="n">
-        <v>0.9366628136663933</v>
+        <v>0.8487451758993579</v>
       </c>
       <c r="K140" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R140" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,31 +9582,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D141" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G141" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H141" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9779347191864203</v>
+        <v>0.9693110016899789</v>
       </c>
       <c r="K141" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R141" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,31 +9647,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D142" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G142" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H142" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857522089871963</v>
+        <v>0.5857476989674808</v>
       </c>
       <c r="K142" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R142" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D143" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G143" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H143" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9999860096763902</v>
+        <v>0.9999999999980269</v>
       </c>
       <c r="K143" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R143" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,31 +9777,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D144" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G144" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H144" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999980871</v>
       </c>
       <c r="K144" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R144" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,31 +9842,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D145" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G145" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H145" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999980949</v>
       </c>
       <c r="K145" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R145" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,31 +9907,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D146" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G146" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H146" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J146" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999983704</v>
       </c>
       <c r="K146" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R146" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,31 +9972,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D147" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G147" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H147" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J147" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999981821</v>
       </c>
       <c r="K147" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R147" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,31 +10037,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D148" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G148" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H148" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J148" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8893902384034182</v>
       </c>
       <c r="K148" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R148" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,31 +10102,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D149" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G149" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H149" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J149" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9514263085423423</v>
       </c>
       <c r="K149" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R149" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,31 +10167,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D150" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G150" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H150" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9898182793539468</v>
       </c>
       <c r="K150" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R150" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,31 +10232,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-7.919421448461443</v>
+        <v>-8.014822244286561</v>
       </c>
       <c r="D151" t="n">
-        <v>113.4047300057614</v>
+        <v>113.3473083885808</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="G151" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="H151" t="n">
-        <v>3.980089978369283</v>
+        <v>7.576141830114429</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1706751737795351</v>
+        <v>0.1729362453589635</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9962441771174758</v>
       </c>
       <c r="K151" t="n">
-        <v>448</v>
+        <v>1705</v>
       </c>
       <c r="L151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.952156804388329</v>
+        <v>-7.956593507576108</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3901126860828</v>
+        <v>113.3830333467191</v>
       </c>
       <c r="R151" t="n">
-        <v>203.8565841443267</v>
+        <v>31.2844463996355</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -565,10 +565,10 @@
         <v>34.41505674874435</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1704961104386556</v>
+        <v>0.1703913888432026</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8740292382666105</v>
+        <v>0.8513478916140149</v>
       </c>
       <c r="K2" t="n">
         <v>1346</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.018776372398985</v>
+        <v>-7.970091564124109</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3253477654735</v>
+        <v>113.3789183088626</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.974596616578423</v>
+        <v>-7.976702981319232</v>
       </c>
       <c r="F3" t="n">
-        <v>113.3440469823906</v>
+        <v>113.3850743038592</v>
       </c>
       <c r="G3" t="n">
-        <v>22.74168170067791</v>
+        <v>137.3208306715142</v>
       </c>
       <c r="H3" t="n">
-        <v>5.326625180273354</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1719329085030804</v>
+        <v>0.1717704894647381</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9426955172617935</v>
+        <v>0.9286170354799225</v>
       </c>
       <c r="K3" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O3" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.974596616578423</v>
+        <v>-7.976702981319232</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.3440469823906</v>
+        <v>113.3850743038592</v>
       </c>
       <c r="R3" t="n">
-        <v>22.74168170067791</v>
+        <v>137.3208306715142</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.018776372398985</v>
+        <v>-7.974666415873893</v>
       </c>
       <c r="D4" t="n">
-        <v>113.3253477654735</v>
+        <v>113.4038295591115</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.974596616578423</v>
+        <v>-7.983405645938871</v>
       </c>
       <c r="F4" t="n">
-        <v>113.3440469823906</v>
+        <v>113.4059725194385</v>
       </c>
       <c r="G4" t="n">
-        <v>22.74168170067791</v>
+        <v>166.3507837823159</v>
       </c>
       <c r="H4" t="n">
-        <v>5.326625180273354</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1719329085030804</v>
+        <v>0.1721589713514692</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9773599552280652</v>
+        <v>0.9732392699929459</v>
       </c>
       <c r="K4" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L4" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O4" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.974596616578423</v>
+        <v>-7.983405645938871</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.3440469823906</v>
+        <v>113.4059725194385</v>
       </c>
       <c r="R4" t="n">
-        <v>22.74168170067791</v>
+        <v>166.3507837823159</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -739,55 +739,55 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.027069577914261</v>
+        <v>-7.957145064323297</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3413229229386</v>
+        <v>113.3901911169971</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.957667531050113</v>
+        <v>-7.966138105671611</v>
       </c>
       <c r="F5" t="n">
-        <v>113.3518447060147</v>
+        <v>113.390134514338</v>
       </c>
       <c r="G5" t="n">
-        <v>8.538985059369793</v>
+        <v>180.3571379682267</v>
       </c>
       <c r="H5" t="n">
-        <v>7.803643599054814</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1722302064518231</v>
+        <v>0.1725616259723485</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9894917117796753</v>
+        <v>0.9873842598505764</v>
       </c>
       <c r="K5" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O5" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.957667531050113</v>
+        <v>-7.966138105671611</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.3518447060147</v>
+        <v>113.390134514338</v>
       </c>
       <c r="R5" t="n">
-        <v>8.538985059369793</v>
+        <v>180.3571379682267</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -804,55 +804,55 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C6" t="n">
-        <v>-8.033871002117559</v>
+        <v>-7.977570774607881</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3409904443866</v>
+        <v>113.3785946547453</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.987703269528294</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3819073726659</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="G6" t="n">
-        <v>41.2736391557513</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="H6" t="n">
-        <v>6.830247167908669</v>
+        <v>3.287075901610288</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1725224437534801</v>
+        <v>0.1728891255417742</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9941729443358277</v>
+        <v>0.9923422818355199</v>
       </c>
       <c r="K6" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L6" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O6" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.987703269528294</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3819073726659</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="R6" t="n">
-        <v>41.2736391557513</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -869,55 +869,55 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.033871002117559</v>
+        <v>-7.977570774607881</v>
       </c>
       <c r="D7" t="n">
-        <v>113.3409904443866</v>
+        <v>113.3785946547453</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.987703269528294</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3819073726659</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="G7" t="n">
-        <v>41.2736391557513</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="H7" t="n">
-        <v>6.830247167908669</v>
+        <v>3.287075901610288</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1725224437534801</v>
+        <v>0.1728891255417742</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9972764513044139</v>
+        <v>0.9947031292341942</v>
       </c>
       <c r="K7" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O7" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.987703269528294</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3819073726659</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="R7" t="n">
-        <v>41.2736391557513</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,28 +937,28 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.982951098337787</v>
+        <v>-7.977570774607881</v>
       </c>
       <c r="D8" t="n">
-        <v>113.4068653347977</v>
+        <v>113.3785946547453</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.941793268994033</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="F8" t="n">
-        <v>113.4043123263285</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="G8" t="n">
-        <v>356.4844634778329</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="H8" t="n">
-        <v>4.585169283024213</v>
+        <v>3.287075901610288</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1725671815850905</v>
+        <v>0.1728891255417742</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9973336734520649</v>
+        <v>0.9951247353975895</v>
       </c>
       <c r="K8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.941793268994033</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.4043123263285</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="R8" t="n">
-        <v>356.4844634778329</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -999,55 +999,55 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.007216308474788</v>
+        <v>-7.977570774607881</v>
       </c>
       <c r="D9" t="n">
-        <v>113.3326088257528</v>
+        <v>113.3785946547453</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.966494017369675</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="F9" t="n">
-        <v>113.368635675386</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="G9" t="n">
-        <v>41.22457471530996</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="H9" t="n">
-        <v>6.020135804391243</v>
+        <v>3.287075901610288</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1727448662674463</v>
+        <v>0.1728891255417742</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9973302837441415</v>
+        <v>0.9961296178442414</v>
       </c>
       <c r="K9" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L9" t="n">
-        <v>640</v>
+        <v>448</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>44877.10347222222</v>
+        <v>44785.47361111111</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.96386844576088</v>
+        <v>-7.90590090675314</v>
       </c>
       <c r="O9" t="n">
-        <v>113.300380121246</v>
+        <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.966494017369675</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.368635675386</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="R9" t="n">
-        <v>41.22457471530996</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.004402605577127</v>
+        <v>-7.977570774607881</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3324153932479</v>
+        <v>113.3785946547453</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.964648827259435</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3707776915338</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="G10" t="n">
-        <v>43.70331678207191</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="H10" t="n">
-        <v>6.114339252221916</v>
+        <v>3.287075901610288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1728143375570551</v>
+        <v>0.1728891255417742</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9976734378964105</v>
+        <v>0.9964896862360023</v>
       </c>
       <c r="K10" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.964648827259435</v>
+        <v>-7.949768855385877</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3707776915338</v>
+        <v>113.3887388115477</v>
       </c>
       <c r="R10" t="n">
-        <v>43.70331678207191</v>
+        <v>19.86821475221745</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,31 +1132,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-8.004402605577127</v>
+        <v>-7.939214852264083</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3324153932479</v>
+        <v>113.3828943024183</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.964648827259435</v>
+        <v>-7.947958992840148</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3707776915338</v>
+        <v>113.3807720487951</v>
       </c>
       <c r="G11" t="n">
-        <v>43.70331678207191</v>
+        <v>193.5160059420237</v>
       </c>
       <c r="H11" t="n">
-        <v>6.114339252221916</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1728143375570551</v>
+        <v>0.1729101907516697</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9979617854069388</v>
+        <v>0.996666863405788</v>
       </c>
       <c r="K11" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.964648827259435</v>
+        <v>-7.947958992840148</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3707776915338</v>
+        <v>113.3807720487951</v>
       </c>
       <c r="R11" t="n">
-        <v>43.70331678207191</v>
+        <v>193.5160059420237</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-8.009178441799968</v>
+        <v>-7.939214852264083</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3348420731802</v>
+        <v>113.3828943024183</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.947219556058015</v>
+        <v>-7.947958992840148</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3677692653538</v>
+        <v>113.3807720487951</v>
       </c>
       <c r="G12" t="n">
-        <v>27.7597763430611</v>
+        <v>193.5160059420237</v>
       </c>
       <c r="H12" t="n">
-        <v>7.785405455129859</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1728162666648347</v>
+        <v>0.1729101907516697</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857849901784189</v>
+        <v>0.5857823206941308</v>
       </c>
       <c r="K12" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.947219556058015</v>
+        <v>-7.947958992840148</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3677692653538</v>
+        <v>113.3807720487951</v>
       </c>
       <c r="R12" t="n">
-        <v>27.7597763430611</v>
+        <v>193.5160059420237</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,31 +1262,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-8.022865389725842</v>
+        <v>-7.944170964263311</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3385681589015</v>
+        <v>113.3914663659358</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.951166526483987</v>
+        <v>-7.952261783500453</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3778299601006</v>
+        <v>113.3875018857619</v>
       </c>
       <c r="G13" t="n">
-        <v>28.47287453078669</v>
+        <v>205.8865699657014</v>
       </c>
       <c r="H13" t="n">
-        <v>9.069345258382391</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1728463357633716</v>
+        <v>0.1729199391859107</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9984145381653877</v>
+        <v>0.9978915547197775</v>
       </c>
       <c r="K13" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.951166526483987</v>
+        <v>-7.952261783500453</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3778299601006</v>
+        <v>113.3875018857619</v>
       </c>
       <c r="R13" t="n">
-        <v>28.47287453078669</v>
+        <v>205.8865699657014</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,31 +1327,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-8.01498174091779</v>
+        <v>-7.945659716436548</v>
       </c>
       <c r="D14" t="n">
-        <v>113.3600304768281</v>
+        <v>113.3972329693109</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.958021560365631</v>
+        <v>-7.954237179240523</v>
       </c>
       <c r="F14" t="n">
-        <v>113.3892699324297</v>
+        <v>113.393854571792</v>
       </c>
       <c r="G14" t="n">
-        <v>26.94865935727584</v>
+        <v>201.3097136874549</v>
       </c>
       <c r="H14" t="n">
-        <v>7.10508935474449</v>
+        <v>1.02376720668693</v>
       </c>
       <c r="I14" t="n">
-        <v>0.172856205785556</v>
+        <v>0.1729368751352274</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9983890558072239</v>
+        <v>0.9982507739216355</v>
       </c>
       <c r="K14" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.958021560365631</v>
+        <v>-7.954237179240523</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3892699324297</v>
+        <v>113.393854571792</v>
       </c>
       <c r="R14" t="n">
-        <v>26.94865935727584</v>
+        <v>201.3097136874549</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,31 +1392,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-8.014133781838609</v>
+        <v>-7.943765139169736</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3515291726259</v>
+        <v>113.3911351817574</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.953571744981112</v>
+        <v>-7.952360212961133</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3883040362476</v>
+        <v>113.3871792390287</v>
       </c>
       <c r="G15" t="n">
-        <v>31.02275931604566</v>
+        <v>204.5049172549351</v>
       </c>
       <c r="H15" t="n">
-        <v>7.857997689999483</v>
+        <v>1.05033927769625</v>
       </c>
       <c r="I15" t="n">
-        <v>0.172918027682289</v>
+        <v>0.1729402332257659</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9982826910305677</v>
+        <v>0.9986492942451261</v>
       </c>
       <c r="K15" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.953571744981112</v>
+        <v>-7.952360212961133</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3883040362476</v>
+        <v>113.3871792390287</v>
       </c>
       <c r="R15" t="n">
-        <v>31.02275931604566</v>
+        <v>204.5049172549351</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,31 +1457,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-8.014133781838609</v>
+        <v>-7.944798061474016</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3515291726259</v>
+        <v>113.3955483178065</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.953571744981112</v>
+        <v>-7.953051684237742</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3883040362476</v>
+        <v>113.3918786800107</v>
       </c>
       <c r="G16" t="n">
-        <v>31.02275931604566</v>
+        <v>203.7654357787663</v>
       </c>
       <c r="H16" t="n">
-        <v>7.857997689999483</v>
+        <v>1.002797000684153</v>
       </c>
       <c r="I16" t="n">
-        <v>0.172918027682289</v>
+        <v>0.1729460707011691</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9982830130479439</v>
+        <v>0.9987548817078348</v>
       </c>
       <c r="K16" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.953571744981112</v>
+        <v>-7.953051684237742</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3883040362476</v>
+        <v>113.3918786800107</v>
       </c>
       <c r="R16" t="n">
-        <v>31.02275931604566</v>
+        <v>203.7654357787663</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-8.014133781838609</v>
+        <v>-7.940392375393276</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3515291726259</v>
+        <v>113.3931659886091</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.953571744981112</v>
+        <v>-7.950211646346075</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3883040362476</v>
+        <v>113.3887767440099</v>
       </c>
       <c r="G17" t="n">
-        <v>31.02275931604566</v>
+        <v>203.8792479832546</v>
       </c>
       <c r="H17" t="n">
-        <v>7.857997689999483</v>
+        <v>1.194067055004437</v>
       </c>
       <c r="I17" t="n">
-        <v>0.172918027682289</v>
+        <v>0.1729491466611276</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9982919440974322</v>
+        <v>0.9990603634870074</v>
       </c>
       <c r="K17" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.953571744981112</v>
+        <v>-7.950211646346075</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3883040362476</v>
+        <v>113.3887767440099</v>
       </c>
       <c r="R17" t="n">
-        <v>31.02275931604566</v>
+        <v>203.8792479832546</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-8.014642904086402</v>
+        <v>-7.940392375393276</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3472040589804</v>
+        <v>113.3931659886091</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.954808492099117</v>
+        <v>-7.950211646346075</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3836579818265</v>
+        <v>113.3887767440099</v>
       </c>
       <c r="G18" t="n">
-        <v>31.10680383717838</v>
+        <v>203.8792479832546</v>
       </c>
       <c r="H18" t="n">
-        <v>7.770451793195363</v>
+        <v>1.194067055004437</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1729319883196683</v>
+        <v>0.1729491466611276</v>
       </c>
       <c r="J18" t="n">
-        <v>0.99827598688372</v>
+        <v>0.9991799920481111</v>
       </c>
       <c r="K18" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.954808492099117</v>
+        <v>-7.950211646346075</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3836579818265</v>
+        <v>113.3887767440099</v>
       </c>
       <c r="R18" t="n">
-        <v>31.10680383717838</v>
+        <v>203.8792479832546</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-8.014642904086402</v>
+        <v>-7.940392375393276</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3472040589804</v>
+        <v>113.3931659886091</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.954808492099117</v>
+        <v>-7.950211646346075</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3836579818265</v>
+        <v>113.3887767440099</v>
       </c>
       <c r="G19" t="n">
-        <v>31.10680383717838</v>
+        <v>203.8792479832546</v>
       </c>
       <c r="H19" t="n">
-        <v>7.770451793195363</v>
+        <v>1.194067055004437</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1729319883196683</v>
+        <v>0.1729491466611276</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9982260931188932</v>
+        <v>0.9991689225546168</v>
       </c>
       <c r="K19" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.954808492099117</v>
+        <v>-7.950211646346075</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3836579818265</v>
+        <v>113.3887767440099</v>
       </c>
       <c r="R19" t="n">
-        <v>31.10680383717838</v>
+        <v>203.8792479832546</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-8.019995830922259</v>
+        <v>-7.944293901579533</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3462076464991</v>
+        <v>113.3911386527967</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.955981578546637</v>
+        <v>-7.952943467301811</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3855741993558</v>
+        <v>113.3872690269759</v>
       </c>
       <c r="G20" t="n">
-        <v>31.3440924920894</v>
+        <v>203.8968995783793</v>
       </c>
       <c r="H20" t="n">
-        <v>8.334148720332932</v>
+        <v>1.051968929352845</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1729325680553569</v>
+        <v>0.1729492453251325</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9982155604197903</v>
+        <v>0.9991431534773433</v>
       </c>
       <c r="K20" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.955981578546637</v>
+        <v>-7.952943467301811</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3855741993558</v>
+        <v>113.3872690269759</v>
       </c>
       <c r="R20" t="n">
-        <v>31.3440924920894</v>
+        <v>203.8968995783793</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-8.019995830922259</v>
+        <v>-7.944232053569883</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3462076464991</v>
+        <v>113.3931030184428</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.955981578546637</v>
+        <v>-7.952802572944204</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3855741993558</v>
+        <v>113.3892827920215</v>
       </c>
       <c r="G21" t="n">
-        <v>31.3440924920894</v>
+        <v>203.8191809617664</v>
       </c>
       <c r="H21" t="n">
-        <v>8.334148720332932</v>
+        <v>1.041730069561171</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1729325680553569</v>
+        <v>0.1729502262111977</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9982154889496693</v>
+        <v>0.999179955966382</v>
       </c>
       <c r="K21" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.955981578546637</v>
+        <v>-7.952802572944204</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3855741993558</v>
+        <v>113.3892827920215</v>
       </c>
       <c r="R21" t="n">
-        <v>31.3440924920894</v>
+        <v>203.8191809617664</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-8.019963453722061</v>
+        <v>-7.941282248931428</v>
       </c>
       <c r="D22" t="n">
-        <v>113.34597663677</v>
+        <v>113.3933573176257</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.955869083111749</v>
+        <v>-7.951554292891318</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3851634503393</v>
+        <v>113.3887764482725</v>
       </c>
       <c r="G22" t="n">
-        <v>31.19596767160729</v>
+        <v>203.8294290417517</v>
       </c>
       <c r="H22" t="n">
-        <v>8.331491149236488</v>
+        <v>1.248646213902044</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1729327999096046</v>
+        <v>0.1729504032421857</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857852805171301</v>
+        <v>0.5857861845420236</v>
       </c>
       <c r="K22" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.955869083111749</v>
+        <v>-7.951554292891318</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3851634503393</v>
+        <v>113.3887764482725</v>
       </c>
       <c r="R22" t="n">
-        <v>31.19596767160729</v>
+        <v>203.8294290417517</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-8.012921715460601</v>
+        <v>-7.944383955944071</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3476937586479</v>
+        <v>113.3926468664014</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.954426504161376</v>
+        <v>-7.952761434878513</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3836296523886</v>
+        <v>113.3889060386489</v>
       </c>
       <c r="G23" t="n">
-        <v>31.31818898443952</v>
+        <v>203.8568545094929</v>
       </c>
       <c r="H23" t="n">
-        <v>7.613537262111509</v>
+        <v>1.018562212969568</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1729335488105143</v>
+        <v>0.1729508599658692</v>
       </c>
       <c r="J23" t="n">
-        <v>0.998540469128489</v>
+        <v>0.9999644138375163</v>
       </c>
       <c r="K23" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.954426504161376</v>
+        <v>-7.952761434878513</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3836296523886</v>
+        <v>113.3889060386489</v>
       </c>
       <c r="R23" t="n">
-        <v>31.31818898443952</v>
+        <v>203.8568545094929</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-8.014955216805198</v>
+        <v>-7.943480420714248</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3471238398768</v>
+        <v>113.3931855491571</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.955812857270469</v>
+        <v>-7.952445011221384</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3833505262253</v>
+        <v>113.3891823224593</v>
       </c>
       <c r="G24" t="n">
-        <v>31.24327793415549</v>
+        <v>203.858105547607</v>
       </c>
       <c r="H24" t="n">
-        <v>7.69165458503563</v>
+        <v>1.08995590057442</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1729352410392784</v>
+        <v>0.1729508971001666</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9985380570227835</v>
+        <v>0.9999643583480445</v>
       </c>
       <c r="K24" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.955812857270469</v>
+        <v>-7.952445011221384</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3833505262253</v>
+        <v>113.3891823224593</v>
       </c>
       <c r="R24" t="n">
-        <v>31.24327793415549</v>
+        <v>203.858105547607</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-8.019446120839365</v>
+        <v>-7.943170621277479</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3461060589864</v>
+        <v>113.3930599615343</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.957152188418849</v>
+        <v>-7.95225324836075</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3843378913062</v>
+        <v>113.3890048085567</v>
       </c>
       <c r="G25" t="n">
-        <v>31.29295025037654</v>
+        <v>203.8540173143451</v>
       </c>
       <c r="H25" t="n">
-        <v>8.105780466459263</v>
+        <v>1.104272512557813</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1729353386861014</v>
+        <v>0.1729509290669217</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9985359231457112</v>
+        <v>0.9999693849799064</v>
       </c>
       <c r="K25" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.957152188418849</v>
+        <v>-7.95225324836075</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3843378913062</v>
+        <v>113.3890048085567</v>
       </c>
       <c r="R25" t="n">
-        <v>31.29295025037654</v>
+        <v>203.8540173143451</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-8.018803484239813</v>
+        <v>-7.943545518616204</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3459706638489</v>
+        <v>113.3925761308665</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.957170551399957</v>
+        <v>-7.952237531183342</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3837944309175</v>
+        <v>113.3886946383456</v>
       </c>
       <c r="G26" t="n">
-        <v>31.29133570169061</v>
+        <v>203.8580532221621</v>
       </c>
       <c r="H26" t="n">
-        <v>8.019635284348626</v>
+        <v>1.056814132883104</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1729358134321764</v>
+        <v>0.1729509411253649</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9985317520107748</v>
+        <v>0.9999862738573292</v>
       </c>
       <c r="K26" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.957170551399957</v>
+        <v>-7.952237531183342</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3837944309175</v>
+        <v>113.3886946383456</v>
       </c>
       <c r="R26" t="n">
-        <v>31.29133570169061</v>
+        <v>203.8580532221621</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-8.017361913628477</v>
+        <v>-7.94304199378201</v>
       </c>
       <c r="D27" t="n">
-        <v>113.3463191699581</v>
+        <v>113.393062783403</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.956687974606584</v>
+        <v>-7.952187862218869</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3835506691702</v>
+        <v>113.3889789515696</v>
       </c>
       <c r="G27" t="n">
-        <v>31.28880055452191</v>
+        <v>203.8563207257764</v>
       </c>
       <c r="H27" t="n">
-        <v>7.894642859226463</v>
+        <v>1.111981228377769</v>
       </c>
       <c r="I27" t="n">
-        <v>0.172936045288511</v>
+        <v>0.1729509660138104</v>
       </c>
       <c r="J27" t="n">
-        <v>0.998527948694952</v>
+        <v>0.9999861663487079</v>
       </c>
       <c r="K27" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.956687974606584</v>
+        <v>-7.952187862218869</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3835506691702</v>
+        <v>113.3889789515696</v>
       </c>
       <c r="R27" t="n">
-        <v>31.28880055452191</v>
+        <v>203.8563207257764</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-8.015517109115722</v>
+        <v>-7.943268349942975</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3470852952356</v>
+        <v>113.3928733453602</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.952205764338614</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888825725369</v>
       </c>
       <c r="G28" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8564287248105</v>
       </c>
       <c r="H28" t="n">
-        <v>7.655678237921319</v>
+        <v>1.086637632956232</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1729362125409667</v>
+        <v>0.1729509720882438</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9985252443959814</v>
+        <v>0.9999859218475423</v>
       </c>
       <c r="K28" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.952205764338614</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888825725369</v>
       </c>
       <c r="R28" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8564287248105</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-8.015517109115722</v>
+        <v>-7.943367961232727</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3470852952356</v>
+        <v>113.3928114974094</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.952144070167393</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888927268036</v>
       </c>
       <c r="G29" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8565657235524</v>
       </c>
       <c r="H29" t="n">
-        <v>7.655678237921319</v>
+        <v>1.067026718805198</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1729362125409667</v>
+        <v>0.1729509721387154</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9985224858389293</v>
+        <v>0.99998561127917</v>
       </c>
       <c r="K29" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.952144070167393</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888927268036</v>
       </c>
       <c r="R29" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8565657235524</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-8.015517109115722</v>
+        <v>-7.943233691616467</v>
       </c>
       <c r="D30" t="n">
-        <v>113.3470852952356</v>
+        <v>113.3929086486952</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.95223971056934</v>
       </c>
       <c r="F30" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888872049396</v>
       </c>
       <c r="G30" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8566233545814</v>
       </c>
       <c r="H30" t="n">
-        <v>7.655678237921319</v>
+        <v>1.094980443520035</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1729362125409667</v>
+        <v>0.1729509736082028</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9985205328352295</v>
+        <v>0.9999853332754913</v>
       </c>
       <c r="K30" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L30" t="n">
         <v>448</v>
@@ -2406,13 +2406,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P30" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.95223971056934</v>
       </c>
       <c r="Q30" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888872049396</v>
       </c>
       <c r="R30" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8566233545814</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -2432,31 +2432,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C31" t="n">
-        <v>-8.015517109115722</v>
+        <v>-7.943233691616467</v>
       </c>
       <c r="D31" t="n">
-        <v>113.3470852952356</v>
+        <v>113.3929086486952</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.95223971056934</v>
       </c>
       <c r="F31" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888872049396</v>
       </c>
       <c r="G31" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8566233545814</v>
       </c>
       <c r="H31" t="n">
-        <v>7.655678237921319</v>
+        <v>1.094980443520035</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1729362125409667</v>
+        <v>0.1729509736082028</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9985201380540557</v>
+        <v>0.9999850987098753</v>
       </c>
       <c r="K31" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L31" t="n">
         <v>448</v>
@@ -2471,13 +2471,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.95223971056934</v>
       </c>
       <c r="Q31" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888872049396</v>
       </c>
       <c r="R31" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8566233545814</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -2497,31 +2497,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C32" t="n">
-        <v>-8.015517109115722</v>
+        <v>-7.943423609737181</v>
       </c>
       <c r="D32" t="n">
-        <v>113.3470852952356</v>
+        <v>113.3927905847076</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="F32" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="G32" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="H32" t="n">
-        <v>7.655678237921319</v>
+        <v>1.069217830428211</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1729362125409667</v>
+        <v>0.1729509744720422</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4807404993110608</v>
+        <v>0.4807407015135871</v>
       </c>
       <c r="K32" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L32" t="n">
         <v>448</v>
@@ -2536,13 +2536,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P32" t="n">
-        <v>-7.956676264551763</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3831839974534</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="R32" t="n">
-        <v>31.28317970521891</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="S32" t="b">
         <v>0</v>
@@ -2562,31 +2562,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C33" t="n">
-        <v>-8.016184995834008</v>
+        <v>-7.943423609737181</v>
       </c>
       <c r="D33" t="n">
-        <v>113.3464002842219</v>
+        <v>113.3927905847076</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.956530176312437</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="F33" t="n">
-        <v>113.3830017881101</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="G33" t="n">
-        <v>31.28558146291966</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="H33" t="n">
-        <v>7.761777871500169</v>
+        <v>1.069217830428211</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1729362213972858</v>
+        <v>0.1729509744720422</v>
       </c>
       <c r="J33" t="n">
-        <v>0.910463489720867</v>
+        <v>0.9256570478776641</v>
       </c>
       <c r="K33" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L33" t="n">
         <v>448</v>
@@ -2601,13 +2601,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P33" t="n">
-        <v>-7.956530176312437</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.3830017881101</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="R33" t="n">
-        <v>31.28558146291966</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="S33" t="b">
         <v>0</v>
@@ -2627,31 +2627,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C34" t="n">
-        <v>-8.016184995834008</v>
+        <v>-7.943423609737181</v>
       </c>
       <c r="D34" t="n">
-        <v>113.3464002842219</v>
+        <v>113.3927905847076</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.956530176312437</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="F34" t="n">
-        <v>113.3830017881101</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="G34" t="n">
-        <v>31.28558146291966</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="H34" t="n">
-        <v>7.761777871500169</v>
+        <v>1.069217830428211</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1729362213972858</v>
+        <v>0.1729509744720422</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9908561543725551</v>
+        <v>0.9341873040288061</v>
       </c>
       <c r="K34" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L34" t="n">
         <v>448</v>
@@ -2666,13 +2666,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P34" t="n">
-        <v>-7.956530176312437</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="Q34" t="n">
-        <v>113.3830017881101</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="R34" t="n">
-        <v>31.28558146291966</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="S34" t="b">
         <v>0</v>
@@ -2692,31 +2692,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C35" t="n">
-        <v>-8.016134043525758</v>
+        <v>-7.943423609737181</v>
       </c>
       <c r="D35" t="n">
-        <v>113.3465295471029</v>
+        <v>113.3927905847076</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.956572619566354</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="F35" t="n">
-        <v>113.383072357882</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="G35" t="n">
-        <v>31.28461065052675</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="H35" t="n">
-        <v>7.749546589362903</v>
+        <v>1.069217830428211</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1729362360505773</v>
+        <v>0.1729509744720422</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9968741313647032</v>
+        <v>0.9714568254612116</v>
       </c>
       <c r="K35" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L35" t="n">
         <v>448</v>
@@ -2731,13 +2731,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P35" t="n">
-        <v>-7.956572619566354</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.383072357882</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="R35" t="n">
-        <v>31.28461065052675</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="S35" t="b">
         <v>0</v>
@@ -2757,31 +2757,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C36" t="n">
-        <v>-8.014801094331675</v>
+        <v>-7.943423609737181</v>
       </c>
       <c r="D36" t="n">
-        <v>113.3472906654373</v>
+        <v>113.3927905847076</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.956559169331699</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="F36" t="n">
-        <v>113.383024047221</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="G36" t="n">
-        <v>31.28468512284504</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="H36" t="n">
-        <v>7.5778768955234</v>
+        <v>1.069217830428211</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1729362378304759</v>
+        <v>0.1729509744720422</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9987508055806086</v>
+        <v>0.9902178312737867</v>
       </c>
       <c r="K36" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L36" t="n">
         <v>448</v>
@@ -2796,13 +2796,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P36" t="n">
-        <v>-7.956559169331699</v>
+        <v>-7.952217738953056</v>
       </c>
       <c r="Q36" t="n">
-        <v>113.383024047221</v>
+        <v>113.3888637635806</v>
       </c>
       <c r="R36" t="n">
-        <v>31.28468512284504</v>
+        <v>203.8565832902644</v>
       </c>
       <c r="S36" t="b">
         <v>0</v>
@@ -2822,31 +2822,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C37" t="n">
-        <v>-8.014801094331675</v>
+        <v>-7.943423337399272</v>
       </c>
       <c r="D37" t="n">
-        <v>113.3472906654373</v>
+        <v>113.3927998508396</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.956559169331699</v>
+        <v>-7.95221845800731</v>
       </c>
       <c r="F37" t="n">
-        <v>113.383024047221</v>
+        <v>113.3888725868584</v>
       </c>
       <c r="G37" t="n">
-        <v>31.28468512284504</v>
+        <v>203.8565841666364</v>
       </c>
       <c r="H37" t="n">
-        <v>7.5778768955234</v>
+        <v>1.069338374484816</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1729362378304759</v>
+        <v>0.1729509744989755</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9987508016150093</v>
+        <v>0.9956961352817453</v>
       </c>
       <c r="K37" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L37" t="n">
         <v>448</v>
@@ -2861,13 +2861,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P37" t="n">
-        <v>-7.956559169331699</v>
+        <v>-7.95221845800731</v>
       </c>
       <c r="Q37" t="n">
-        <v>113.383024047221</v>
+        <v>113.3888725868584</v>
       </c>
       <c r="R37" t="n">
-        <v>31.28468512284504</v>
+        <v>203.8565841666364</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -2887,31 +2887,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C38" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943423337399272</v>
       </c>
       <c r="D38" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927998508396</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.95221845800731</v>
       </c>
       <c r="F38" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888725868584</v>
       </c>
       <c r="G38" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841666364</v>
       </c>
       <c r="H38" t="n">
-        <v>7.543450236405444</v>
+        <v>1.069338374484816</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509744989755</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9987507814163336</v>
+        <v>0.9971773070146989</v>
       </c>
       <c r="K38" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L38" t="n">
         <v>448</v>
@@ -2926,13 +2926,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P38" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.95221845800731</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888725868584</v>
       </c>
       <c r="R38" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841666364</v>
       </c>
       <c r="S38" t="b">
         <v>0</v>
@@ -2952,31 +2952,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C39" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943425914493309</v>
       </c>
       <c r="D39" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927975842267</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216910525605</v>
       </c>
       <c r="F39" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888721619835</v>
       </c>
       <c r="G39" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565842613454</v>
       </c>
       <c r="H39" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068836895349158</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.172950974500071</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9987507640338799</v>
+        <v>0.9982867472363647</v>
       </c>
       <c r="K39" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L39" t="n">
         <v>448</v>
@@ -2991,13 +2991,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P39" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216910525605</v>
       </c>
       <c r="Q39" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888721619835</v>
       </c>
       <c r="R39" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565842613454</v>
       </c>
       <c r="S39" t="b">
         <v>0</v>
@@ -3017,31 +3017,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C40" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943425914493309</v>
       </c>
       <c r="D40" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927975842267</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216910525605</v>
       </c>
       <c r="F40" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888721619835</v>
       </c>
       <c r="G40" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565842613454</v>
       </c>
       <c r="H40" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068836895349158</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.172950974500071</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9987507579440155</v>
+        <v>0.9983079544813124</v>
       </c>
       <c r="K40" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L40" t="n">
         <v>448</v>
@@ -3056,13 +3056,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P40" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216910525605</v>
       </c>
       <c r="Q40" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888721619835</v>
       </c>
       <c r="R40" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565842613454</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -3082,31 +3082,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C41" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943425914493309</v>
       </c>
       <c r="D41" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927975842267</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216910525605</v>
       </c>
       <c r="F41" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888721619835</v>
       </c>
       <c r="G41" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565842613454</v>
       </c>
       <c r="H41" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068836895349158</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.172950974500071</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9986645888731396</v>
+        <v>0.9986370025355149</v>
       </c>
       <c r="K41" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L41" t="n">
         <v>448</v>
@@ -3121,13 +3121,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P41" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216910525605</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888721619835</v>
       </c>
       <c r="R41" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565842613454</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -3147,31 +3147,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C42" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943426040245839</v>
       </c>
       <c r="D42" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927973488359</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952217052179045</v>
       </c>
       <c r="F42" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888719195185</v>
       </c>
       <c r="G42" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841139871</v>
       </c>
       <c r="H42" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068838827419745</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745015112</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5852845661025282</v>
+        <v>0.5857859652439548</v>
       </c>
       <c r="K42" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L42" t="n">
         <v>448</v>
@@ -3186,13 +3186,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P42" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952217052179045</v>
       </c>
       <c r="Q42" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888719195185</v>
       </c>
       <c r="R42" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841139871</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -3212,31 +3212,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C43" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943424170842455</v>
       </c>
       <c r="D43" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927959730048</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204383387</v>
       </c>
       <c r="F43" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888700875097</v>
       </c>
       <c r="G43" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841612862</v>
       </c>
       <c r="H43" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068963038343846</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745026426</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9999999747089541</v>
+        <v>0.9999999932049604</v>
       </c>
       <c r="K43" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L43" t="n">
         <v>448</v>
@@ -3251,13 +3251,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P43" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204383387</v>
       </c>
       <c r="Q43" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888700875097</v>
       </c>
       <c r="R43" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841612862</v>
       </c>
       <c r="S43" t="b">
         <v>0</v>
@@ -3277,31 +3277,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C44" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943424170842455</v>
       </c>
       <c r="D44" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927959730048</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204383387</v>
       </c>
       <c r="F44" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888700875097</v>
       </c>
       <c r="G44" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841612862</v>
       </c>
       <c r="H44" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068963038343846</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745026426</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9999999753785674</v>
+        <v>0.9999999933945489</v>
       </c>
       <c r="K44" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L44" t="n">
         <v>448</v>
@@ -3316,13 +3316,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P44" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204383387</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888700875097</v>
       </c>
       <c r="R44" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841612862</v>
       </c>
       <c r="S44" t="b">
         <v>0</v>
@@ -3342,31 +3342,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C45" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943424170842455</v>
       </c>
       <c r="D45" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927959730048</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204383387</v>
       </c>
       <c r="F45" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888700875097</v>
       </c>
       <c r="G45" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841612862</v>
       </c>
       <c r="H45" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068963038343846</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745026426</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9999999790697396</v>
+        <v>0.9999999934384358</v>
       </c>
       <c r="K45" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L45" t="n">
         <v>448</v>
@@ -3381,13 +3381,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P45" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204383387</v>
       </c>
       <c r="Q45" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888700875097</v>
       </c>
       <c r="R45" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841612862</v>
       </c>
       <c r="S45" t="b">
         <v>0</v>
@@ -3407,31 +3407,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.94342495151222</v>
       </c>
       <c r="D46" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927960458067</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216077207508</v>
       </c>
       <c r="F46" t="n">
-        <v>113.3830333800354</v>
+        <v>113.388870565693</v>
       </c>
       <c r="G46" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841549348</v>
       </c>
       <c r="H46" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068852659337472</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.172950974502855</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9999999773160712</v>
+        <v>0.9999999934391726</v>
       </c>
       <c r="K46" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L46" t="n">
         <v>448</v>
@@ -3446,13 +3446,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P46" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216077207508</v>
       </c>
       <c r="Q46" t="n">
-        <v>113.3830333800354</v>
+        <v>113.388870565693</v>
       </c>
       <c r="R46" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841549348</v>
       </c>
       <c r="S46" t="b">
         <v>0</v>
@@ -3472,31 +3472,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C47" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943424096549228</v>
       </c>
       <c r="D47" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927962228341</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216021434545</v>
       </c>
       <c r="F47" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888703858627</v>
       </c>
       <c r="G47" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841389007</v>
       </c>
       <c r="H47" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068949827440871</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745029177</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9999999783752691</v>
+        <v>0.9999999933841905</v>
       </c>
       <c r="K47" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L47" t="n">
         <v>448</v>
@@ -3511,13 +3511,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P47" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216021434545</v>
       </c>
       <c r="Q47" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888703858627</v>
       </c>
       <c r="R47" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841389007</v>
       </c>
       <c r="S47" t="b">
         <v>0</v>
@@ -3537,31 +3537,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C48" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943423749059381</v>
       </c>
       <c r="D48" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927961680982</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952215822665325</v>
       </c>
       <c r="F48" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888702647197</v>
       </c>
       <c r="G48" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841445487</v>
       </c>
       <c r="H48" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068967909446404</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745029639</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9999999784820244</v>
+        <v>0.9999999940639475</v>
       </c>
       <c r="K48" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L48" t="n">
         <v>448</v>
@@ -3576,13 +3576,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P48" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952215822665325</v>
       </c>
       <c r="Q48" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888702647197</v>
       </c>
       <c r="R48" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841445487</v>
       </c>
       <c r="S48" t="b">
         <v>0</v>
@@ -3602,31 +3602,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C49" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943424445762483</v>
       </c>
       <c r="D49" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927962393935</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952215873954845</v>
       </c>
       <c r="F49" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888706242097</v>
       </c>
       <c r="G49" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841465756</v>
       </c>
       <c r="H49" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068889437889274</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745029829</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9999999776704758</v>
+        <v>0.9999999962846304</v>
       </c>
       <c r="K49" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L49" t="n">
         <v>448</v>
@@ -3641,13 +3641,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P49" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952215873954845</v>
       </c>
       <c r="Q49" t="n">
-        <v>113.3830333800354</v>
+        <v>113.3888706242097</v>
       </c>
       <c r="R49" t="n">
-        <v>31.28449196649983</v>
+        <v>203.8565841465756</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
@@ -3667,31 +3667,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C50" t="n">
-        <v>-8.014567131281749</v>
+        <v>-7.943424785131974</v>
       </c>
       <c r="D50" t="n">
-        <v>113.3474625313688</v>
+        <v>113.3927962086969</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204561996</v>
       </c>
       <c r="F50" t="n">
-        <v>113.3830333800354</v>
+        <v>113.388870597423</v>
       </c>
       <c r="G50" t="n">
-        <v>31.28449196649983</v>
+        <v>203.856584144569</v>
       </c>
       <c r="H50" t="n">
-        <v>7.543450236405444</v>
+        <v>1.068888372517613</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1729362441881535</v>
+        <v>0.1729509745029941</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9999999798866515</v>
+        <v>0.9999999966627857</v>
       </c>
       <c r="K50" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L50" t="n">
         <v>448</v>
@@ -3706,13 +3706,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P50" t="n">
-        <v>-7.956589690370822</v>
+        <v>-7.952216204561996</v>
       </c>
       <c r="Q50" t="n">
-        <v>113.3830333800354</v>
+        <v>113.388870597423</v>
       </c>
       <c r="R50" t="n">
-        <v>31.28449196649983</v>
+        <v>203.856584144569</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C51" t="n">
-        <v>-8.015670957254303</v>
+        <v>-7.943424409629107</v>
       </c>
       <c r="D51" t="n">
-        <v>113.3467903772119</v>
+        <v>113.3927964609954</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952216098466733</v>
       </c>
       <c r="F51" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888707294244</v>
       </c>
       <c r="G51" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841443764</v>
       </c>
       <c r="H51" t="n">
-        <v>7.686486220496374</v>
+        <v>1.068921128006844</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1729362446002689</v>
+        <v>0.1729509745030073</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9999999819479249</v>
+        <v>0.9999999983354519</v>
       </c>
       <c r="K51" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L51" t="n">
         <v>448</v>
@@ -3771,13 +3771,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P51" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952216098466733</v>
       </c>
       <c r="Q51" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888707294244</v>
       </c>
       <c r="R51" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841443764</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -3797,31 +3797,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C52" t="n">
-        <v>-8.015670957254303</v>
+        <v>-7.943424409629107</v>
       </c>
       <c r="D52" t="n">
-        <v>113.3467903772119</v>
+        <v>113.3927964609954</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952216098466733</v>
       </c>
       <c r="F52" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888707294244</v>
       </c>
       <c r="G52" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841443764</v>
       </c>
       <c r="H52" t="n">
-        <v>7.686486220496374</v>
+        <v>1.068921128006844</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1729362446002689</v>
+        <v>0.1729509745030073</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5857864397315015</v>
+        <v>0.5857864397313223</v>
       </c>
       <c r="K52" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L52" t="n">
         <v>448</v>
@@ -3836,13 +3836,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P52" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952216098466733</v>
       </c>
       <c r="Q52" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888707294244</v>
       </c>
       <c r="R52" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841443764</v>
       </c>
       <c r="S52" t="b">
         <v>0</v>
@@ -3862,31 +3862,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C53" t="n">
-        <v>-8.015670957254303</v>
+        <v>-7.943424656216096</v>
       </c>
       <c r="D53" t="n">
-        <v>113.3467903772119</v>
+        <v>113.3927961658464</v>
       </c>
       <c r="E53" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952215928393307</v>
       </c>
       <c r="F53" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888706203277</v>
       </c>
       <c r="G53" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841445109</v>
       </c>
       <c r="H53" t="n">
-        <v>7.686486220496374</v>
+        <v>1.068870469020615</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1729362446002689</v>
+        <v>0.1729509745030162</v>
       </c>
       <c r="J53" t="n">
-        <v>0.999999998656772</v>
+        <v>0.9999999999236178</v>
       </c>
       <c r="K53" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L53" t="n">
         <v>448</v>
@@ -3901,13 +3901,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P53" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952215928393307</v>
       </c>
       <c r="Q53" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888706203277</v>
       </c>
       <c r="R53" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841445109</v>
       </c>
       <c r="S53" t="b">
         <v>0</v>
@@ -3927,31 +3927,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C54" t="n">
-        <v>-8.015670957254303</v>
+        <v>-7.943424656216096</v>
       </c>
       <c r="D54" t="n">
-        <v>113.3467903772119</v>
+        <v>113.3927961658464</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952215928393307</v>
       </c>
       <c r="F54" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888706203277</v>
       </c>
       <c r="G54" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841445109</v>
       </c>
       <c r="H54" t="n">
-        <v>7.686486220496374</v>
+        <v>1.068870469020615</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1729362446002689</v>
+        <v>0.1729509745030162</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9538343808585827</v>
+        <v>0.9999999999236149</v>
       </c>
       <c r="K54" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L54" t="n">
         <v>448</v>
@@ -3966,13 +3966,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P54" t="n">
-        <v>-7.956594086248897</v>
+        <v>-7.952215928393307</v>
       </c>
       <c r="Q54" t="n">
-        <v>113.3830356156825</v>
+        <v>113.3888706203277</v>
       </c>
       <c r="R54" t="n">
-        <v>31.28440454172441</v>
+        <v>203.8565841445109</v>
       </c>
       <c r="S54" t="b">
         <v>0</v>
@@ -3992,31 +3992,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C55" t="n">
-        <v>-8.014466445823384</v>
+        <v>-7.943424396627699</v>
       </c>
       <c r="D55" t="n">
-        <v>113.3475244303349</v>
+        <v>113.3927962006725</v>
       </c>
       <c r="E55" t="n">
-        <v>-7.956592304741193</v>
+        <v>-7.952215912065505</v>
       </c>
       <c r="F55" t="n">
-        <v>113.3830319035438</v>
+        <v>113.3888705465312</v>
       </c>
       <c r="G55" t="n">
-        <v>31.28449202431441</v>
+        <v>203.8565841443065</v>
       </c>
       <c r="H55" t="n">
-        <v>7.530010244270685</v>
+        <v>1.068900045467776</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1729362446535698</v>
+        <v>0.1729509745030164</v>
       </c>
       <c r="J55" t="n">
-        <v>0.990849477455616</v>
+        <v>0.9999999999236111</v>
       </c>
       <c r="K55" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L55" t="n">
         <v>448</v>
@@ -4031,13 +4031,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P55" t="n">
-        <v>-7.956592304741193</v>
+        <v>-7.952215912065505</v>
       </c>
       <c r="Q55" t="n">
-        <v>113.3830319035438</v>
+        <v>113.3888705465312</v>
       </c>
       <c r="R55" t="n">
-        <v>31.28449202431441</v>
+        <v>203.8565841443065</v>
       </c>
       <c r="S55" t="b">
         <v>0</v>
@@ -4057,31 +4057,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C56" t="n">
-        <v>-8.014466445823384</v>
+        <v>-7.943424396627699</v>
       </c>
       <c r="D56" t="n">
-        <v>113.3475244303349</v>
+        <v>113.3927962006725</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.956592304741193</v>
+        <v>-7.952215912065505</v>
       </c>
       <c r="F56" t="n">
-        <v>113.3830319035438</v>
+        <v>113.3888705465312</v>
       </c>
       <c r="G56" t="n">
-        <v>31.28449202431441</v>
+        <v>203.8565841443065</v>
       </c>
       <c r="H56" t="n">
-        <v>7.530010244270685</v>
+        <v>1.068900045467776</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1729362446535698</v>
+        <v>0.1729509745030164</v>
       </c>
       <c r="J56" t="n">
-        <v>0.9958980815180619</v>
+        <v>0.9999999999235598</v>
       </c>
       <c r="K56" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L56" t="n">
         <v>448</v>
@@ -4096,13 +4096,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P56" t="n">
-        <v>-7.956592304741193</v>
+        <v>-7.952215912065505</v>
       </c>
       <c r="Q56" t="n">
-        <v>113.3830319035438</v>
+        <v>113.3888705465312</v>
       </c>
       <c r="R56" t="n">
-        <v>31.28449202431441</v>
+        <v>203.8565841443065</v>
       </c>
       <c r="S56" t="b">
         <v>0</v>
@@ -4122,31 +4122,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C57" t="n">
-        <v>-8.014826473030192</v>
+        <v>-7.943424396627699</v>
       </c>
       <c r="D57" t="n">
-        <v>113.3473362267111</v>
+        <v>113.3927962006725</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.956607600526676</v>
+        <v>-7.952215912065505</v>
       </c>
       <c r="F57" t="n">
-        <v>113.3830551560886</v>
+        <v>113.3888705465312</v>
       </c>
       <c r="G57" t="n">
-        <v>31.28446193141401</v>
+        <v>203.8565841443065</v>
       </c>
       <c r="H57" t="n">
-        <v>7.574859679093357</v>
+        <v>1.068900045467776</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1729362446963303</v>
+        <v>0.1729509745030164</v>
       </c>
       <c r="J57" t="n">
-        <v>0.9978157855280532</v>
+        <v>0.9999999999235178</v>
       </c>
       <c r="K57" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L57" t="n">
         <v>448</v>
@@ -4161,13 +4161,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.956607600526676</v>
+        <v>-7.952215912065505</v>
       </c>
       <c r="Q57" t="n">
-        <v>113.3830551560886</v>
+        <v>113.3888705465312</v>
       </c>
       <c r="R57" t="n">
-        <v>31.28446193141401</v>
+        <v>203.8565841443065</v>
       </c>
       <c r="S57" t="b">
         <v>0</v>
@@ -4187,31 +4187,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C58" t="n">
-        <v>-8.014826473030192</v>
+        <v>-7.943424084392163</v>
       </c>
       <c r="D58" t="n">
-        <v>113.3473362267111</v>
+        <v>113.3927964975188</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.956607600526676</v>
+        <v>-7.952216008347333</v>
       </c>
       <c r="F58" t="n">
-        <v>113.3830551560886</v>
+        <v>113.3888706609619</v>
       </c>
       <c r="G58" t="n">
-        <v>31.28446193141401</v>
+        <v>203.8565841443152</v>
       </c>
       <c r="H58" t="n">
-        <v>7.574859679093357</v>
+        <v>1.068949714395551</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1729362446963303</v>
+        <v>0.1729509745030178</v>
       </c>
       <c r="J58" t="n">
-        <v>0.9987272793517695</v>
+        <v>0.9999999999234435</v>
       </c>
       <c r="K58" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L58" t="n">
         <v>448</v>
@@ -4226,13 +4226,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.956607600526676</v>
+        <v>-7.952216008347333</v>
       </c>
       <c r="Q58" t="n">
-        <v>113.3830551560886</v>
+        <v>113.3888706609619</v>
       </c>
       <c r="R58" t="n">
-        <v>31.28446193141401</v>
+        <v>203.8565841443152</v>
       </c>
       <c r="S58" t="b">
         <v>0</v>
@@ -4252,31 +4252,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C59" t="n">
-        <v>-8.014821250165019</v>
+        <v>-7.94342440483002</v>
       </c>
       <c r="D59" t="n">
-        <v>113.3473080229432</v>
+        <v>113.3927963085446</v>
       </c>
       <c r="E59" t="n">
-        <v>-7.956592533691857</v>
+        <v>-7.95221598236047</v>
       </c>
       <c r="F59" t="n">
-        <v>113.3830329962723</v>
+        <v>113.3888706266764</v>
       </c>
       <c r="G59" t="n">
-        <v>31.28446610970299</v>
+        <v>203.8565841443399</v>
       </c>
       <c r="H59" t="n">
-        <v>7.576140780471873</v>
+        <v>1.068907594902568</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1729362449726067</v>
+        <v>0.1729509745030191</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9992613119858353</v>
+        <v>0.9999999999232585</v>
       </c>
       <c r="K59" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L59" t="n">
         <v>448</v>
@@ -4291,13 +4291,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.956592533691857</v>
+        <v>-7.95221598236047</v>
       </c>
       <c r="Q59" t="n">
-        <v>113.3830329962723</v>
+        <v>113.3888706266764</v>
       </c>
       <c r="R59" t="n">
-        <v>31.28446610970299</v>
+        <v>203.8565841443399</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4317,31 +4317,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C60" t="n">
-        <v>-8.014821250165019</v>
+        <v>-7.94342440483002</v>
       </c>
       <c r="D60" t="n">
-        <v>113.3473080229432</v>
+        <v>113.3927963085446</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.956592533691857</v>
+        <v>-7.95221598236047</v>
       </c>
       <c r="F60" t="n">
-        <v>113.3830329962723</v>
+        <v>113.3888706266764</v>
       </c>
       <c r="G60" t="n">
-        <v>31.28446610970299</v>
+        <v>203.8565841443399</v>
       </c>
       <c r="H60" t="n">
-        <v>7.576140780471873</v>
+        <v>1.068907594902568</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1729362449726067</v>
+        <v>0.1729509745030191</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9997613436017188</v>
+        <v>0.9999999999231213</v>
       </c>
       <c r="K60" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L60" t="n">
         <v>448</v>
@@ -4356,13 +4356,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.956592533691857</v>
+        <v>-7.95221598236047</v>
       </c>
       <c r="Q60" t="n">
-        <v>113.3830329962723</v>
+        <v>113.3888706266764</v>
       </c>
       <c r="R60" t="n">
-        <v>31.28446610970299</v>
+        <v>203.8565841443399</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -4382,31 +4382,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C61" t="n">
-        <v>-8.014821250165019</v>
+        <v>-7.943424464844195</v>
       </c>
       <c r="D61" t="n">
-        <v>113.3473080229432</v>
+        <v>113.392796274267</v>
       </c>
       <c r="E61" t="n">
-        <v>-7.956592533691857</v>
+        <v>-7.952215977794784</v>
       </c>
       <c r="F61" t="n">
-        <v>113.3830329962723</v>
+        <v>113.3888706212357</v>
       </c>
       <c r="G61" t="n">
-        <v>31.28446610970299</v>
+        <v>203.8565841443075</v>
       </c>
       <c r="H61" t="n">
-        <v>7.576140780471873</v>
+        <v>1.068899743063377</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1729362449726067</v>
+        <v>0.1729509745030191</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9998558387449942</v>
+        <v>0.9999999999240994</v>
       </c>
       <c r="K61" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L61" t="n">
         <v>448</v>
@@ -4421,13 +4421,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P61" t="n">
-        <v>-7.956592533691857</v>
+        <v>-7.952215977794784</v>
       </c>
       <c r="Q61" t="n">
-        <v>113.3830329962723</v>
+        <v>113.3888706212357</v>
       </c>
       <c r="R61" t="n">
-        <v>31.28446610970299</v>
+        <v>203.8565841443075</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -4447,31 +4447,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C62" t="n">
-        <v>-8.014569764233592</v>
+        <v>-7.943424381563823</v>
       </c>
       <c r="D62" t="n">
-        <v>113.3474625328017</v>
+        <v>113.3927963115165</v>
       </c>
       <c r="E62" t="n">
-        <v>-7.956593111803734</v>
+        <v>-7.952215959198473</v>
       </c>
       <c r="F62" t="n">
-        <v>113.3830328655116</v>
+        <v>113.3888706296021</v>
       </c>
       <c r="G62" t="n">
-        <v>31.28446872601781</v>
+        <v>203.8565841443233</v>
       </c>
       <c r="H62" t="n">
-        <v>7.543345790815476</v>
+        <v>1.06890760757147</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1729362450183446</v>
+        <v>0.1729509745030193</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5857864340461464</v>
+        <v>0.4807407015351221</v>
       </c>
       <c r="K62" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L62" t="n">
         <v>448</v>
@@ -4486,13 +4486,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P62" t="n">
-        <v>-7.956593111803734</v>
+        <v>-7.952215959198473</v>
       </c>
       <c r="Q62" t="n">
-        <v>113.3830328655116</v>
+        <v>113.3888706296021</v>
       </c>
       <c r="R62" t="n">
-        <v>31.28446872601781</v>
+        <v>203.8565841443233</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -4512,31 +4512,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C63" t="n">
-        <v>-8.014565165909955</v>
+        <v>-7.943424382474376</v>
       </c>
       <c r="D63" t="n">
-        <v>113.3474631940796</v>
+        <v>113.3927963078858</v>
       </c>
       <c r="E63" t="n">
-        <v>-7.956591804429146</v>
+        <v>-7.952215973937439</v>
       </c>
       <c r="F63" t="n">
-        <v>113.3830314910033</v>
+        <v>113.3888706197964</v>
       </c>
       <c r="G63" t="n">
-        <v>31.28445683305094</v>
+        <v>203.8565841443234</v>
       </c>
       <c r="H63" t="n">
-        <v>7.542916665361766</v>
+        <v>1.068909288876663</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1729362451528036</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J63" t="n">
-        <v>0.9999999982979715</v>
+        <v>0.8786497255409385</v>
       </c>
       <c r="K63" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L63" t="n">
         <v>448</v>
@@ -4551,13 +4551,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P63" t="n">
-        <v>-7.956591804429146</v>
+        <v>-7.952215973937439</v>
       </c>
       <c r="Q63" t="n">
-        <v>113.3830314910033</v>
+        <v>113.3888706197964</v>
       </c>
       <c r="R63" t="n">
-        <v>31.28445683305094</v>
+        <v>203.8565841443234</v>
       </c>
       <c r="S63" t="b">
         <v>0</v>
@@ -4577,31 +4577,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C64" t="n">
-        <v>-8.014828533872551</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D64" t="n">
-        <v>113.3473291953422</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.956605973499685</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F64" t="n">
-        <v>113.3830503633808</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G64" t="n">
-        <v>31.28444502546542</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H64" t="n">
-        <v>7.575338137316359</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1729362452175252</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9999999979815897</v>
+        <v>0.9924877361871621</v>
       </c>
       <c r="K64" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L64" t="n">
         <v>448</v>
@@ -4616,13 +4616,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P64" t="n">
-        <v>-7.956605973499685</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q64" t="n">
-        <v>113.3830503633808</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R64" t="n">
-        <v>31.28444502546542</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S64" t="b">
         <v>0</v>
@@ -4642,31 +4642,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C65" t="n">
-        <v>-8.014828533872551</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D65" t="n">
-        <v>113.3473291953422</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E65" t="n">
-        <v>-7.956605973499685</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F65" t="n">
-        <v>113.3830503633808</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G65" t="n">
-        <v>31.28444502546542</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H65" t="n">
-        <v>7.575338137316359</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1729362452175252</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8429976433863694</v>
+        <v>0.9174015805938563</v>
       </c>
       <c r="K65" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L65" t="n">
         <v>448</v>
@@ -4681,13 +4681,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P65" t="n">
-        <v>-7.956605973499685</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q65" t="n">
-        <v>113.3830503633808</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R65" t="n">
-        <v>31.28444502546542</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S65" t="b">
         <v>0</v>
@@ -4707,31 +4707,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C66" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D66" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E66" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F66" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G66" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H66" t="n">
-        <v>7.543299643523969</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9923195029662634</v>
+        <v>0.9802943579986355</v>
       </c>
       <c r="K66" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L66" t="n">
         <v>448</v>
@@ -4746,13 +4746,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P66" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q66" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R66" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -4772,31 +4772,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C67" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D67" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F67" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G67" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H67" t="n">
-        <v>7.543299643523969</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9714698209311058</v>
+        <v>0.9914643106851749</v>
       </c>
       <c r="K67" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L67" t="n">
         <v>448</v>
@@ -4811,13 +4811,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P67" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q67" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R67" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -4837,31 +4837,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C68" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D68" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E68" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F68" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G68" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H68" t="n">
-        <v>7.543299643523969</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9954515028366085</v>
+        <v>0.9955016203267328</v>
       </c>
       <c r="K68" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L68" t="n">
         <v>448</v>
@@ -4876,13 +4876,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P68" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q68" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R68" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S68" t="b">
         <v>0</v>
@@ -4902,31 +4902,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C69" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D69" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E69" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F69" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G69" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H69" t="n">
-        <v>7.543299643523969</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J69" t="n">
-        <v>0.9977874213654291</v>
+        <v>0.9969649118270778</v>
       </c>
       <c r="K69" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L69" t="n">
         <v>448</v>
@@ -4941,13 +4941,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P69" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q69" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R69" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S69" t="b">
         <v>0</v>
@@ -4967,31 +4967,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C70" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.9434244531616</v>
       </c>
       <c r="D70" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962675462</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="F70" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="G70" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="H70" t="n">
-        <v>7.543299643523969</v>
+        <v>1.068900346378754</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030194</v>
       </c>
       <c r="J70" t="n">
-        <v>0.9980351950057647</v>
+        <v>0.9982645517480045</v>
       </c>
       <c r="K70" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L70" t="n">
         <v>448</v>
@@ -5006,13 +5006,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P70" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.95221597107434</v>
       </c>
       <c r="Q70" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706122991</v>
       </c>
       <c r="R70" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443269</v>
       </c>
       <c r="S70" t="b">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C71" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D71" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F71" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G71" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H71" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9981821949757622</v>
+        <v>0.998468935689008</v>
       </c>
       <c r="K71" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L71" t="n">
         <v>448</v>
@@ -5071,13 +5071,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P71" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q71" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R71" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S71" t="b">
         <v>0</v>
@@ -5097,31 +5097,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C72" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D72" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F72" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G72" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H72" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5848292617657087</v>
+        <v>0.5857862308781344</v>
       </c>
       <c r="K72" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L72" t="n">
         <v>448</v>
@@ -5136,13 +5136,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P72" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q72" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R72" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -5162,31 +5162,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C73" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D73" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F73" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G73" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H73" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9988736220246504</v>
+        <v>0.9999999999999993</v>
       </c>
       <c r="K73" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L73" t="n">
         <v>448</v>
@@ -5201,13 +5201,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P73" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q73" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R73" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S73" t="b">
         <v>0</v>
@@ -5227,31 +5227,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C74" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D74" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E74" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F74" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G74" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H74" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9991126925985853</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="K74" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L74" t="n">
         <v>448</v>
@@ -5266,13 +5266,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P74" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q74" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R74" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S74" t="b">
         <v>0</v>
@@ -5292,31 +5292,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C75" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D75" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E75" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F75" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G75" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H75" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9992016063051864</v>
+        <v>0.9220458068239478</v>
       </c>
       <c r="K75" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L75" t="n">
         <v>448</v>
@@ -5331,13 +5331,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P75" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q75" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R75" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S75" t="b">
         <v>0</v>
@@ -5357,31 +5357,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C76" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D76" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E76" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F76" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G76" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H76" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9993415433921805</v>
+        <v>0.9871270472590085</v>
       </c>
       <c r="K76" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L76" t="n">
         <v>448</v>
@@ -5396,13 +5396,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P76" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q76" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R76" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S76" t="b">
         <v>0</v>
@@ -5422,31 +5422,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C77" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D77" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E77" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F77" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G77" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H77" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J77" t="n">
-        <v>0.9994269693532822</v>
+        <v>0.9951042454302789</v>
       </c>
       <c r="K77" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L77" t="n">
         <v>448</v>
@@ -5461,13 +5461,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P77" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q77" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R77" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S77" t="b">
         <v>0</v>
@@ -5487,31 +5487,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C78" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D78" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E78" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F78" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G78" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H78" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J78" t="n">
-        <v>0.9994971495892007</v>
+        <v>0.9980481192481445</v>
       </c>
       <c r="K78" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L78" t="n">
         <v>448</v>
@@ -5526,13 +5526,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P78" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q78" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R78" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S78" t="b">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C79" t="n">
-        <v>-8.014568849434131</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D79" t="n">
-        <v>113.3474623928526</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F79" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G79" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H79" t="n">
-        <v>7.543299643523969</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1729362452247876</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9995330028436479</v>
+        <v>0.9985053014539486</v>
       </c>
       <c r="K79" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L79" t="n">
         <v>448</v>
@@ -5591,13 +5591,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P79" t="n">
-        <v>-7.956592541615633</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q79" t="n">
-        <v>113.3830324911601</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R79" t="n">
-        <v>31.28445233406233</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S79" t="b">
         <v>0</v>
@@ -5617,31 +5617,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C80" t="n">
-        <v>-8.01482848050934</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D80" t="n">
-        <v>113.3473298950584</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.956606391664826</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F80" t="n">
-        <v>113.3830507770787</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G80" t="n">
-        <v>31.28444732725488</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H80" t="n">
-        <v>7.575276973254558</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I80" t="n">
-        <v>0.172936245230377</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9995330028258793</v>
+        <v>0.9990341858767647</v>
       </c>
       <c r="K80" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L80" t="n">
         <v>448</v>
@@ -5656,13 +5656,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P80" t="n">
-        <v>-7.956606391664826</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q80" t="n">
-        <v>113.3830507770787</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R80" t="n">
-        <v>31.28444732725488</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -5682,31 +5682,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C81" t="n">
-        <v>-8.014828870299652</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D81" t="n">
-        <v>113.3473293076431</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.956606410697666</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F81" t="n">
-        <v>113.3830504139931</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G81" t="n">
-        <v>31.2844450948954</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H81" t="n">
-        <v>7.5753250319287</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1729362452643826</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9997518616396036</v>
+        <v>0.9995318322057651</v>
       </c>
       <c r="K81" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L81" t="n">
         <v>448</v>
@@ -5721,13 +5721,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P81" t="n">
-        <v>-7.956606410697666</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q81" t="n">
-        <v>113.3830504139931</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R81" t="n">
-        <v>31.2844450948954</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S81" t="b">
         <v>0</v>
@@ -5747,31 +5747,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C82" t="n">
-        <v>-8.014828870299652</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D82" t="n">
-        <v>113.3473293076431</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.956606410697666</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F82" t="n">
-        <v>113.3830504139931</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G82" t="n">
-        <v>31.2844450948954</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H82" t="n">
-        <v>7.5753250319287</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1729362452643826</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J82" t="n">
-        <v>0.5857864206289164</v>
+        <v>0.5857864189611339</v>
       </c>
       <c r="K82" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L82" t="n">
         <v>448</v>
@@ -5786,13 +5786,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P82" t="n">
-        <v>-7.956606410697666</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q82" t="n">
-        <v>113.3830504139931</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R82" t="n">
-        <v>31.2844450948954</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S82" t="b">
         <v>0</v>
@@ -5812,31 +5812,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C83" t="n">
-        <v>-8.014828498889434</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D83" t="n">
-        <v>113.3473291109882</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.956606079549133</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F83" t="n">
-        <v>113.3830501944884</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G83" t="n">
-        <v>31.28444643319334</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H83" t="n">
-        <v>7.575319901123211</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1729362452669628</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J83" t="n">
-        <v>0.9999999995525268</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K83" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L83" t="n">
         <v>448</v>
@@ -5851,13 +5851,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P83" t="n">
-        <v>-7.956606079549133</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q83" t="n">
-        <v>113.3830501944884</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R83" t="n">
-        <v>31.28444643319334</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S83" t="b">
         <v>0</v>
@@ -5877,31 +5877,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C84" t="n">
-        <v>-8.014828630605324</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D84" t="n">
-        <v>113.3473291626158</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E84" t="n">
-        <v>-7.95660629600556</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F84" t="n">
-        <v>113.3830501952162</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G84" t="n">
-        <v>31.28444719535191</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H84" t="n">
-        <v>7.575308937035374</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1729362452807396</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J84" t="n">
-        <v>0.999999999539426</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K84" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L84" t="n">
         <v>448</v>
@@ -5916,13 +5916,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P84" t="n">
-        <v>-7.95660629600556</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q84" t="n">
-        <v>113.3830501952162</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R84" t="n">
-        <v>31.28444719535191</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S84" t="b">
         <v>0</v>
@@ -5942,31 +5942,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C85" t="n">
-        <v>-8.014820042076883</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D85" t="n">
-        <v>113.3473071166593</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E85" t="n">
-        <v>-7.95659207405846</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F85" t="n">
-        <v>113.3830316041237</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G85" t="n">
-        <v>31.28444714857174</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H85" t="n">
-        <v>7.576041878428779</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I85" t="n">
-        <v>0.172936245321891</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J85" t="n">
-        <v>0.9999999995040356</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K85" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L85" t="n">
         <v>448</v>
@@ -5981,13 +5981,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P85" t="n">
-        <v>-7.95659207405846</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q85" t="n">
-        <v>113.3830316041237</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R85" t="n">
-        <v>31.28444714857174</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S85" t="b">
         <v>0</v>
@@ -6007,31 +6007,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C86" t="n">
-        <v>-8.014820042076883</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D86" t="n">
-        <v>113.3473071166593</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E86" t="n">
-        <v>-7.95659207405846</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F86" t="n">
-        <v>113.3830316041237</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G86" t="n">
-        <v>31.28444714857174</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H86" t="n">
-        <v>7.576041878428779</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I86" t="n">
-        <v>0.172936245321891</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9999999994950803</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K86" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L86" t="n">
         <v>448</v>
@@ -6046,13 +6046,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P86" t="n">
-        <v>-7.95659207405846</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q86" t="n">
-        <v>113.3830316041237</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R86" t="n">
-        <v>31.28444714857174</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S86" t="b">
         <v>0</v>
@@ -6072,31 +6072,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C87" t="n">
-        <v>-8.014820042076883</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D87" t="n">
-        <v>113.3473071166593</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E87" t="n">
-        <v>-7.95659207405846</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F87" t="n">
-        <v>113.3830316041237</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G87" t="n">
-        <v>31.28444714857174</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H87" t="n">
-        <v>7.576041878428779</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I87" t="n">
-        <v>0.172936245321891</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J87" t="n">
-        <v>0.999999999477641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K87" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L87" t="n">
         <v>448</v>
@@ -6111,13 +6111,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P87" t="n">
-        <v>-7.95659207405846</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q87" t="n">
-        <v>113.3830316041237</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R87" t="n">
-        <v>31.28444714857174</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S87" t="b">
         <v>0</v>
@@ -6137,31 +6137,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C88" t="n">
-        <v>-8.014821484533073</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D88" t="n">
-        <v>113.3473082064021</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E88" t="n">
-        <v>-7.956593095639961</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F88" t="n">
-        <v>113.3830329503403</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G88" t="n">
-        <v>31.28444584848968</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H88" t="n">
-        <v>7.576096532529245</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1729362453345676</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9280335681635622</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K88" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L88" t="n">
         <v>448</v>
@@ -6176,13 +6176,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P88" t="n">
-        <v>-7.956593095639961</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q88" t="n">
-        <v>113.3830329503403</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R88" t="n">
-        <v>31.28444584848968</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -6202,31 +6202,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C89" t="n">
-        <v>-8.014820056266943</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D89" t="n">
-        <v>113.3473120438872</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F89" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G89" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H89" t="n">
-        <v>7.575705707877927</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1729362453440648</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9691508980134889</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K89" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L89" t="n">
         <v>448</v>
@@ -6241,13 +6241,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P89" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q89" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R89" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S89" t="b">
         <v>0</v>
@@ -6267,31 +6267,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C90" t="n">
-        <v>-8.014820056266943</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D90" t="n">
-        <v>113.3473120438872</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E90" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F90" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G90" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H90" t="n">
-        <v>7.575705707877927</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1729362453440648</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9919098832053366</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K90" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L90" t="n">
         <v>448</v>
@@ -6306,13 +6306,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P90" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q90" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R90" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S90" t="b">
         <v>0</v>
@@ -6332,31 +6332,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C91" t="n">
-        <v>-8.014820056266943</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D91" t="n">
-        <v>113.3473120438872</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F91" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G91" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H91" t="n">
-        <v>7.575705707877927</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1729362453440648</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9972537687389655</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K91" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L91" t="n">
         <v>448</v>
@@ -6371,13 +6371,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P91" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q91" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R91" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S91" t="b">
         <v>0</v>
@@ -6397,31 +6397,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C92" t="n">
-        <v>-8.014820056266943</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D92" t="n">
-        <v>113.3473120438872</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E92" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F92" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G92" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H92" t="n">
-        <v>7.575705707877927</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1729362453440648</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5857848896690908</v>
+        <v>0.4807407015351221</v>
       </c>
       <c r="K92" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L92" t="n">
         <v>448</v>
@@ -6436,13 +6436,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P92" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q92" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R92" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S92" t="b">
         <v>0</v>
@@ -6462,31 +6462,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C93" t="n">
-        <v>-8.014820056266943</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D93" t="n">
-        <v>113.3473120438872</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E93" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F93" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G93" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H93" t="n">
-        <v>7.575705707877927</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1729362453440648</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J93" t="n">
-        <v>0.9999999996941467</v>
+        <v>0.8933518569199954</v>
       </c>
       <c r="K93" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L93" t="n">
         <v>448</v>
@@ -6501,13 +6501,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P93" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q93" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R93" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -6527,31 +6527,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C94" t="n">
-        <v>-8.014820056266943</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D94" t="n">
-        <v>113.3473120438872</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F94" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G94" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H94" t="n">
-        <v>7.575705707877927</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1729362453440648</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9999999996881119</v>
+        <v>0.999619010590597</v>
       </c>
       <c r="K94" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L94" t="n">
         <v>448</v>
@@ -6566,13 +6566,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P94" t="n">
-        <v>-7.956594672272706</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q94" t="n">
-        <v>113.3830349467395</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R94" t="n">
-        <v>31.28444749768957</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S94" t="b">
         <v>0</v>
@@ -6592,31 +6592,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C95" t="n">
-        <v>-8.014822471263773</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D95" t="n">
-        <v>113.3473089510529</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.956593864681667</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F95" t="n">
-        <v>113.3830338304719</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G95" t="n">
-        <v>31.28444717178811</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H95" t="n">
-        <v>7.576124961580077</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1729362453488036</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J95" t="n">
-        <v>0.9999999996959801</v>
+        <v>0.94912305097667</v>
       </c>
       <c r="K95" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L95" t="n">
         <v>448</v>
@@ -6631,13 +6631,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P95" t="n">
-        <v>-7.956593864681667</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q95" t="n">
-        <v>113.3830338304719</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R95" t="n">
-        <v>31.28444717178811</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
@@ -6657,31 +6657,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C96" t="n">
-        <v>-8.014822471263773</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D96" t="n">
-        <v>113.3473089510529</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.956593864681667</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F96" t="n">
-        <v>113.3830338304719</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G96" t="n">
-        <v>31.28444717178811</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H96" t="n">
-        <v>7.576124961580077</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1729362453488036</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J96" t="n">
-        <v>0.8910714314530755</v>
+        <v>0.9777792795382955</v>
       </c>
       <c r="K96" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L96" t="n">
         <v>448</v>
@@ -6696,13 +6696,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P96" t="n">
-        <v>-7.956593864681667</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q96" t="n">
-        <v>113.3830338304719</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R96" t="n">
-        <v>31.28444717178811</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -6722,31 +6722,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C97" t="n">
-        <v>-8.014822471263773</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D97" t="n">
-        <v>113.3473089510529</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E97" t="n">
-        <v>-7.956593864681667</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F97" t="n">
-        <v>113.3830338304719</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G97" t="n">
-        <v>31.28444717178811</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H97" t="n">
-        <v>7.576124961580077</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1729362453488036</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9865143971934912</v>
+        <v>0.9895446283625863</v>
       </c>
       <c r="K97" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L97" t="n">
         <v>448</v>
@@ -6761,13 +6761,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P97" t="n">
-        <v>-7.956593864681667</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q97" t="n">
-        <v>113.3830338304719</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R97" t="n">
-        <v>31.28444717178811</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S97" t="b">
         <v>0</v>
@@ -6787,31 +6787,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C98" t="n">
-        <v>-8.01482225033576</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D98" t="n">
-        <v>113.3473087148541</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.95659364761331</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F98" t="n">
-        <v>113.3830335911179</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G98" t="n">
-        <v>31.28444662491247</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H98" t="n">
-        <v>7.576124415487589</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1729362453512447</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J98" t="n">
-        <v>0.8634863014396117</v>
+        <v>0.99353373603027</v>
       </c>
       <c r="K98" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L98" t="n">
         <v>448</v>
@@ -6826,13 +6826,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P98" t="n">
-        <v>-7.95659364761331</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q98" t="n">
-        <v>113.3830335911179</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R98" t="n">
-        <v>31.28444662491247</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S98" t="b">
         <v>0</v>
@@ -6852,31 +6852,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C99" t="n">
-        <v>-8.01482225033576</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D99" t="n">
-        <v>113.3473087148541</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E99" t="n">
-        <v>-7.95659364761331</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F99" t="n">
-        <v>113.3830335911179</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G99" t="n">
-        <v>31.28444662491247</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H99" t="n">
-        <v>7.576124415487589</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1729362453512447</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9855612344444521</v>
+        <v>0.9974066613659621</v>
       </c>
       <c r="K99" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L99" t="n">
         <v>448</v>
@@ -6891,13 +6891,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P99" t="n">
-        <v>-7.95659364761331</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q99" t="n">
-        <v>113.3830335911179</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R99" t="n">
-        <v>31.28444662491247</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S99" t="b">
         <v>0</v>
@@ -6917,31 +6917,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C100" t="n">
-        <v>-8.014822074283948</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D100" t="n">
-        <v>113.3473083157005</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E100" t="n">
-        <v>-7.956593403236442</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F100" t="n">
-        <v>113.3830332338852</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G100" t="n">
-        <v>31.28444664193944</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H100" t="n">
-        <v>7.576133306400745</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1729362453523252</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9942408993814417</v>
+        <v>0.9985132181404274</v>
       </c>
       <c r="K100" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L100" t="n">
         <v>448</v>
@@ -6956,13 +6956,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P100" t="n">
-        <v>-7.956593403236442</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q100" t="n">
-        <v>113.3830332338852</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R100" t="n">
-        <v>31.28444664193944</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S100" t="b">
         <v>0</v>
@@ -6982,31 +6982,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C101" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D101" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F101" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G101" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H101" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J101" t="n">
-        <v>0.9968213662500051</v>
+        <v>0.9987240425676477</v>
       </c>
       <c r="K101" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L101" t="n">
         <v>448</v>
@@ -7021,13 +7021,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P101" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q101" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R101" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S101" t="b">
         <v>0</v>
@@ -7047,31 +7047,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C102" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D102" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F102" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G102" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H102" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J102" t="n">
-        <v>0.5857845758019141</v>
+        <v>0.5857861096366376</v>
       </c>
       <c r="K102" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L102" t="n">
         <v>448</v>
@@ -7086,13 +7086,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P102" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q102" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R102" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S102" t="b">
         <v>0</v>
@@ -7112,31 +7112,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C103" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D103" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E103" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F103" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G103" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H103" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9989160736463532</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K103" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L103" t="n">
         <v>448</v>
@@ -7151,13 +7151,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P103" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q103" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R103" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S103" t="b">
         <v>0</v>
@@ -7177,31 +7177,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C104" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D104" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E104" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F104" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G104" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H104" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J104" t="n">
-        <v>0.9990765296287466</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L104" t="n">
         <v>448</v>
@@ -7216,13 +7216,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P104" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q104" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R104" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S104" t="b">
         <v>0</v>
@@ -7242,31 +7242,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C105" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D105" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E105" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F105" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G105" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H105" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J105" t="n">
-        <v>0.9993368020224395</v>
+        <v>0.910040227578028</v>
       </c>
       <c r="K105" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L105" t="n">
         <v>448</v>
@@ -7281,13 +7281,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P105" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q105" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R105" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S105" t="b">
         <v>0</v>
@@ -7307,31 +7307,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C106" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D106" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E106" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F106" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G106" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H106" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J106" t="n">
-        <v>0.999336802021744</v>
+        <v>0.9697878049590622</v>
       </c>
       <c r="K106" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L106" t="n">
         <v>448</v>
@@ -7346,13 +7346,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P106" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q106" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R106" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S106" t="b">
         <v>0</v>
@@ -7372,31 +7372,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C107" t="n">
-        <v>-8.014821968818769</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D107" t="n">
-        <v>113.3473083376989</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E107" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F107" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G107" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H107" t="n">
-        <v>7.576121189976907</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1729362453575558</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J107" t="n">
-        <v>0.9998554976123194</v>
+        <v>0.9910040659630552</v>
       </c>
       <c r="K107" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L107" t="n">
         <v>448</v>
@@ -7411,13 +7411,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P107" t="n">
-        <v>-7.95659339073853</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q107" t="n">
-        <v>113.3830331984828</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R107" t="n">
-        <v>31.2844463833646</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S107" t="b">
         <v>0</v>
@@ -7437,31 +7437,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C108" t="n">
-        <v>-8.014821970505803</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D108" t="n">
-        <v>113.3473083360426</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E108" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F108" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G108" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H108" t="n">
-        <v>7.576121334719804</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1729362453576623</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9999287117638389</v>
+        <v>0.9940940023672205</v>
       </c>
       <c r="K108" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L108" t="n">
         <v>448</v>
@@ -7476,13 +7476,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P108" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q108" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R108" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S108" t="b">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C109" t="n">
-        <v>-8.014821970505803</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D109" t="n">
-        <v>113.3473083360426</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E109" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F109" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G109" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H109" t="n">
-        <v>7.576121334719804</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1729362453576623</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J109" t="n">
-        <v>0.9167922521000508</v>
+        <v>0.9977423932322564</v>
       </c>
       <c r="K109" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L109" t="n">
         <v>448</v>
@@ -7541,13 +7541,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P109" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q109" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R109" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S109" t="b">
         <v>0</v>
@@ -7567,31 +7567,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C110" t="n">
-        <v>-8.014821970505803</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D110" t="n">
-        <v>113.3473083360426</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E110" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F110" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G110" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H110" t="n">
-        <v>7.576121334719804</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1729362453576623</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J110" t="n">
-        <v>0.9703758327063946</v>
+        <v>0.998077984419475</v>
       </c>
       <c r="K110" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L110" t="n">
         <v>448</v>
@@ -7606,13 +7606,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P110" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q110" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R110" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S110" t="b">
         <v>0</v>
@@ -7632,31 +7632,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C111" t="n">
-        <v>-8.014821970505803</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D111" t="n">
-        <v>113.3473083360426</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E111" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F111" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G111" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H111" t="n">
-        <v>7.576121334719804</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1729362453576623</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J111" t="n">
-        <v>0.9948199526912156</v>
+        <v>0.999468258898662</v>
       </c>
       <c r="K111" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L111" t="n">
         <v>448</v>
@@ -7671,13 +7671,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P111" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q111" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R111" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -7697,31 +7697,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C112" t="n">
-        <v>-8.014821970505803</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D112" t="n">
-        <v>113.3473083360426</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E112" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F112" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G112" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H112" t="n">
-        <v>7.576121334719804</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1729362453576623</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J112" t="n">
-        <v>0.5857833905811708</v>
+        <v>0.5857864165387533</v>
       </c>
       <c r="K112" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L112" t="n">
         <v>448</v>
@@ -7736,13 +7736,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P112" t="n">
-        <v>-7.956593391310868</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q112" t="n">
-        <v>113.3830331975054</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R112" t="n">
-        <v>31.28444637979797</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S112" t="b">
         <v>0</v>
@@ -7762,31 +7762,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C113" t="n">
-        <v>-8.014822203334864</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D113" t="n">
-        <v>113.3473084727272</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E113" t="n">
-        <v>-7.956593538257748</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F113" t="n">
-        <v>113.3830333870438</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G113" t="n">
-        <v>31.28444648753729</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H113" t="n">
-        <v>7.576132517206936</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1729362453578899</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J113" t="n">
-        <v>0.9999999998382507</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K113" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L113" t="n">
         <v>448</v>
@@ -7801,13 +7801,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P113" t="n">
-        <v>-7.956593538257748</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q113" t="n">
-        <v>113.3830333870438</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R113" t="n">
-        <v>31.28444648753729</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S113" t="b">
         <v>0</v>
@@ -7827,31 +7827,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C114" t="n">
-        <v>-8.014822260826241</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D114" t="n">
-        <v>113.3473083252276</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E114" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F114" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G114" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H114" t="n">
-        <v>7.576148103942586</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1729362453580971</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J114" t="n">
-        <v>0.9999999998381262</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K114" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L114" t="n">
         <v>448</v>
@@ -7866,13 +7866,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P114" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q114" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R114" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S114" t="b">
         <v>0</v>
@@ -7892,31 +7892,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C115" t="n">
-        <v>-8.014822260826241</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D115" t="n">
-        <v>113.3473083252276</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E115" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F115" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G115" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H115" t="n">
-        <v>7.576148103942586</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1729362453580971</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9999999998600897</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K115" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L115" t="n">
         <v>448</v>
@@ -7931,13 +7931,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P115" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q115" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R115" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S115" t="b">
         <v>0</v>
@@ -7957,31 +7957,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C116" t="n">
-        <v>-8.014822260826241</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D116" t="n">
-        <v>113.3473083252276</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F116" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G116" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H116" t="n">
-        <v>7.576148103942586</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1729362453580971</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J116" t="n">
-        <v>0.9999999998939613</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K116" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L116" t="n">
         <v>448</v>
@@ -7996,13 +7996,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P116" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q116" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R116" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S116" t="b">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C117" t="n">
-        <v>-8.014822260826241</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D117" t="n">
-        <v>113.3473083252276</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E117" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F117" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G117" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H117" t="n">
-        <v>7.576148103942586</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1729362453580971</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J117" t="n">
-        <v>0.9999999998817211</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K117" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L117" t="n">
         <v>448</v>
@@ -8061,13 +8061,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P117" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q117" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R117" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S117" t="b">
         <v>0</v>
@@ -8087,31 +8087,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C118" t="n">
-        <v>-8.014822260826241</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D118" t="n">
-        <v>113.3473083252276</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E118" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F118" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G118" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H118" t="n">
-        <v>7.576148103942586</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1729362453580971</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J118" t="n">
-        <v>0.9916081995826925</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K118" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L118" t="n">
         <v>448</v>
@@ -8126,13 +8126,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P118" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q118" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R118" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S118" t="b">
         <v>0</v>
@@ -8152,31 +8152,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C119" t="n">
-        <v>-8.014822260826241</v>
+        <v>-7.943424433209649</v>
       </c>
       <c r="D119" t="n">
-        <v>113.3473083252276</v>
+        <v>113.3927962782302</v>
       </c>
       <c r="E119" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="F119" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="G119" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H119" t="n">
-        <v>7.576148103942586</v>
+        <v>1.06890152071622</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1729362453580971</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J119" t="n">
-        <v>0.9916081995823571</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K119" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L119" t="n">
         <v>448</v>
@@ -8191,13 +8191,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P119" t="n">
-        <v>-7.956593475888638</v>
+        <v>-7.952215960781089</v>
       </c>
       <c r="Q119" t="n">
-        <v>113.3830333129364</v>
+        <v>113.3888706186704</v>
       </c>
       <c r="R119" t="n">
-        <v>31.2844463891585</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S119" t="b">
         <v>0</v>
@@ -8217,31 +8217,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C120" t="n">
-        <v>-8.014822532953346</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D120" t="n">
-        <v>113.3473083367953</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E120" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F120" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G120" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H120" t="n">
-        <v>7.576171215642064</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1729362453586715</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J120" t="n">
-        <v>0.9949611194642261</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L120" t="n">
         <v>448</v>
@@ -8256,13 +8256,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P120" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q120" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R120" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S120" t="b">
         <v>0</v>
@@ -8282,31 +8282,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C121" t="n">
-        <v>-8.014822532953346</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D121" t="n">
-        <v>113.3473083367953</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E121" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F121" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G121" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H121" t="n">
-        <v>7.576171215642064</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1729362453586715</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J121" t="n">
-        <v>0.9961388720637959</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L121" t="n">
         <v>448</v>
@@ -8321,13 +8321,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P121" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q121" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R121" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S121" t="b">
         <v>0</v>
@@ -8347,31 +8347,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C122" t="n">
-        <v>-8.014822532953346</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D122" t="n">
-        <v>113.3473083367953</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F122" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G122" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H122" t="n">
-        <v>7.576171215642064</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1729362453586715</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J122" t="n">
-        <v>0.5857838002504867</v>
+        <v>0.5358983873788243</v>
       </c>
       <c r="K122" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L122" t="n">
         <v>448</v>
@@ -8386,13 +8386,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P122" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q122" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R122" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S122" t="b">
         <v>0</v>
@@ -8412,31 +8412,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C123" t="n">
-        <v>-8.014822532953346</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D123" t="n">
-        <v>113.3473083367953</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F123" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G123" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H123" t="n">
-        <v>7.576171215642064</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1729362453586715</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J123" t="n">
-        <v>0.999999999996968</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K123" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L123" t="n">
         <v>448</v>
@@ -8451,13 +8451,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P123" t="n">
-        <v>-7.956593570402092</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q123" t="n">
-        <v>113.3830334335328</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R123" t="n">
-        <v>31.28444642648939</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S123" t="b">
         <v>0</v>
@@ -8477,31 +8477,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C124" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D124" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E124" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F124" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G124" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H124" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9999999999965612</v>
+        <v>0.8718546322972374</v>
       </c>
       <c r="K124" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L124" t="n">
         <v>448</v>
@@ -8516,13 +8516,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P124" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q124" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R124" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -8542,31 +8542,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C125" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D125" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F125" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G125" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H125" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J125" t="n">
-        <v>0.9999999999965432</v>
+        <v>0.9354007283591002</v>
       </c>
       <c r="K125" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L125" t="n">
         <v>448</v>
@@ -8581,13 +8581,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P125" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q125" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R125" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -8607,31 +8607,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C126" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D126" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E126" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F126" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G126" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H126" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I126" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J126" t="n">
-        <v>0.9999999999968829</v>
+        <v>0.9715345220471693</v>
       </c>
       <c r="K126" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L126" t="n">
         <v>448</v>
@@ -8646,13 +8646,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P126" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q126" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R126" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -8672,31 +8672,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C127" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D127" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E127" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F127" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G127" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H127" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J127" t="n">
-        <v>0.9137041054198113</v>
+        <v>0.9847370840849479</v>
       </c>
       <c r="K127" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L127" t="n">
         <v>448</v>
@@ -8711,13 +8711,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P127" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q127" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R127" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -8737,31 +8737,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C128" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D128" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E128" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F128" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G128" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H128" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J128" t="n">
-        <v>0.9845014089414066</v>
+        <v>0.9925712514902377</v>
       </c>
       <c r="K128" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L128" t="n">
         <v>448</v>
@@ -8776,13 +8776,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P128" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q128" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R128" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -8802,31 +8802,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C129" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D129" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E129" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F129" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G129" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H129" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J129" t="n">
-        <v>0.989870275766765</v>
+        <v>0.996675953934791</v>
       </c>
       <c r="K129" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L129" t="n">
         <v>448</v>
@@ -8841,13 +8841,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P129" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q129" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R129" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S129" t="b">
         <v>0</v>
@@ -8867,31 +8867,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C130" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D130" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E130" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F130" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G130" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H130" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9949539330413529</v>
+        <v>0.9973594645652091</v>
       </c>
       <c r="K130" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L130" t="n">
         <v>448</v>
@@ -8906,13 +8906,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P130" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q130" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R130" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S130" t="b">
         <v>0</v>
@@ -8932,31 +8932,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C131" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D131" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E131" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F131" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G131" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H131" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J131" t="n">
-        <v>0.9246137555496516</v>
+        <v>0.9986643365685871</v>
       </c>
       <c r="K131" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L131" t="n">
         <v>448</v>
@@ -8971,13 +8971,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P131" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q131" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R131" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S131" t="b">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C132" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D132" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E132" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F132" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G132" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H132" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J132" t="n">
-        <v>0.5856299942102062</v>
+        <v>0.5857863771354817</v>
       </c>
       <c r="K132" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L132" t="n">
         <v>448</v>
@@ -9036,13 +9036,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P132" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q132" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R132" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S132" t="b">
         <v>0</v>
@@ -9062,31 +9062,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C133" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D133" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E133" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F133" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G133" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H133" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J133" t="n">
-        <v>0.9992636991196899</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L133" t="n">
         <v>448</v>
@@ -9101,13 +9101,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P133" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q133" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R133" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S133" t="b">
         <v>0</v>
@@ -9127,31 +9127,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C134" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D134" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E134" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F134" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G134" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H134" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J134" t="n">
-        <v>0.9996480704541443</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K134" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L134" t="n">
         <v>448</v>
@@ -9166,13 +9166,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P134" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q134" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R134" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S134" t="b">
         <v>0</v>
@@ -9192,31 +9192,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C135" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D135" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E135" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F135" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G135" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H135" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J135" t="n">
-        <v>0.9998323781807633</v>
+        <v>0.8905317821549024</v>
       </c>
       <c r="K135" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L135" t="n">
         <v>448</v>
@@ -9231,13 +9231,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P135" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q135" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R135" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S135" t="b">
         <v>0</v>
@@ -9257,31 +9257,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C136" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D136" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E136" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F136" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G136" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H136" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9998955072272302</v>
+        <v>0.9584047067415566</v>
       </c>
       <c r="K136" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L136" t="n">
         <v>448</v>
@@ -9296,13 +9296,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P136" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q136" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R136" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S136" t="b">
         <v>0</v>
@@ -9322,31 +9322,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C137" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D137" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E137" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F137" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G137" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H137" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J137" t="n">
-        <v>0.999925779193363</v>
+        <v>0.9916685853810842</v>
       </c>
       <c r="K137" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L137" t="n">
         <v>448</v>
@@ -9361,13 +9361,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P137" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q137" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R137" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S137" t="b">
         <v>0</v>
@@ -9387,31 +9387,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C138" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D138" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E138" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F138" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G138" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H138" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J138" t="n">
-        <v>0.9999611855127991</v>
+        <v>0.995387484435711</v>
       </c>
       <c r="K138" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L138" t="n">
         <v>448</v>
@@ -9426,13 +9426,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P138" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q138" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R138" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S138" t="b">
         <v>0</v>
@@ -9452,31 +9452,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C139" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D139" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E139" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F139" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G139" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H139" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J139" t="n">
-        <v>0.9999736311255395</v>
+        <v>0.9980720764835865</v>
       </c>
       <c r="K139" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L139" t="n">
         <v>448</v>
@@ -9491,13 +9491,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P139" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q139" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R139" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S139" t="b">
         <v>0</v>
@@ -9517,31 +9517,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C140" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D140" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E140" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F140" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G140" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H140" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J140" t="n">
-        <v>0.8487451758993579</v>
+        <v>0.9984254137456745</v>
       </c>
       <c r="K140" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L140" t="n">
         <v>448</v>
@@ -9556,13 +9556,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P140" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q140" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R140" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S140" t="b">
         <v>0</v>
@@ -9582,31 +9582,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C141" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D141" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F141" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G141" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H141" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J141" t="n">
-        <v>0.9693110016899789</v>
+        <v>0.9986225664487964</v>
       </c>
       <c r="K141" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L141" t="n">
         <v>448</v>
@@ -9621,13 +9621,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P141" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q141" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R141" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S141" t="b">
         <v>0</v>
@@ -9647,31 +9647,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C142" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D142" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E142" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F142" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G142" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H142" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5857476989674808</v>
+        <v>0.5857860066545421</v>
       </c>
       <c r="K142" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L142" t="n">
         <v>448</v>
@@ -9686,13 +9686,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P142" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q142" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R142" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S142" t="b">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C143" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D143" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F143" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G143" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H143" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J143" t="n">
-        <v>0.9999999999980269</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K143" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L143" t="n">
         <v>448</v>
@@ -9751,13 +9751,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P143" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q143" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R143" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S143" t="b">
         <v>0</v>
@@ -9777,31 +9777,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C144" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D144" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E144" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F144" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G144" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H144" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J144" t="n">
-        <v>0.9999999999980871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K144" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L144" t="n">
         <v>448</v>
@@ -9816,13 +9816,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P144" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q144" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R144" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S144" t="b">
         <v>0</v>
@@ -9842,31 +9842,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C145" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D145" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E145" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F145" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G145" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H145" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J145" t="n">
-        <v>0.9999999999980949</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K145" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L145" t="n">
         <v>448</v>
@@ -9881,13 +9881,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P145" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q145" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R145" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S145" t="b">
         <v>0</v>
@@ -9907,31 +9907,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C146" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D146" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E146" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F146" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G146" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H146" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J146" t="n">
-        <v>0.9999999999983704</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K146" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L146" t="n">
         <v>448</v>
@@ -9946,13 +9946,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P146" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q146" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R146" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S146" t="b">
         <v>0</v>
@@ -9972,31 +9972,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C147" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D147" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E147" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F147" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G147" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H147" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I147" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J147" t="n">
-        <v>0.9999999999981821</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K147" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L147" t="n">
         <v>448</v>
@@ -10011,13 +10011,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P147" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q147" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R147" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -10037,31 +10037,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C148" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D148" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E148" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F148" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G148" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H148" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J148" t="n">
-        <v>0.8893902384034182</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K148" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L148" t="n">
         <v>448</v>
@@ -10076,13 +10076,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P148" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q148" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R148" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S148" t="b">
         <v>0</v>
@@ -10102,31 +10102,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C149" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D149" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E149" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F149" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G149" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H149" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J149" t="n">
-        <v>0.9514263085423423</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K149" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L149" t="n">
         <v>448</v>
@@ -10141,13 +10141,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P149" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q149" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R149" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S149" t="b">
         <v>0</v>
@@ -10167,31 +10167,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C150" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D150" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E150" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F150" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G150" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H150" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J150" t="n">
-        <v>0.9898182793539468</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K150" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L150" t="n">
         <v>448</v>
@@ -10206,13 +10206,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P150" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q150" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R150" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S150" t="b">
         <v>0</v>
@@ -10232,31 +10232,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C151" t="n">
-        <v>-8.014822244286561</v>
+        <v>-7.943424433139551</v>
       </c>
       <c r="D151" t="n">
-        <v>113.3473083885808</v>
+        <v>113.3927962764647</v>
       </c>
       <c r="E151" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="F151" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="G151" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="H151" t="n">
-        <v>7.576141830114429</v>
+        <v>1.068901438045529</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1729362453589635</v>
+        <v>0.1729509745030195</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9962441771174758</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="K151" t="n">
-        <v>1705</v>
+        <v>448</v>
       </c>
       <c r="L151" t="n">
         <v>448</v>
@@ -10271,13 +10271,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P151" t="n">
-        <v>-7.956593507576108</v>
+        <v>-7.952215960031041</v>
       </c>
       <c r="Q151" t="n">
-        <v>113.3830333467191</v>
+        <v>113.3888706172085</v>
       </c>
       <c r="R151" t="n">
-        <v>31.2844463996355</v>
+        <v>203.8565841443265</v>
       </c>
       <c r="S151" t="b">
         <v>1</v>

--- a/output/ga_results/ga_prediction_data_for_lstm.xlsx
+++ b/output/ga_results/ga_prediction_data_for_lstm.xlsx
@@ -544,55 +544,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45128.39027777778</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C2" t="n">
-        <v>-7.719589428539689</v>
+        <v>-8.153593526264119</v>
       </c>
       <c r="D2" t="n">
-        <v>113.0692652918578</v>
+        <v>113.3311362201217</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.905215714332474</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="F2" t="n">
-        <v>113.3192434162308</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="G2" t="n">
-        <v>126.8694796031224</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="H2" t="n">
-        <v>34.41505674874435</v>
+        <v>23.8222295006408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1703913888432026</v>
+        <v>0.1671185173304143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8513478916140149</v>
+        <v>0.8943930878893671</v>
       </c>
       <c r="K2" t="n">
-        <v>1346</v>
+        <v>1965</v>
       </c>
       <c r="L2" t="n">
-        <v>1150</v>
+        <v>1797</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45128.39027777778</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.84901089388539</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O2" t="n">
-        <v>113.303858808655</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.905215714332474</v>
+        <v>-7.985054109717519</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.3192434162308</v>
+        <v>113.4647183977525</v>
       </c>
       <c r="R2" t="n">
-        <v>126.8694796031224</v>
+        <v>38.13208364715861</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
@@ -609,55 +609,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.970091564124109</v>
+        <v>-8.255056508970146</v>
       </c>
       <c r="D3" t="n">
-        <v>113.3789183088626</v>
+        <v>113.0667176706558</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.976702981319232</v>
+        <v>-8.010079034232739</v>
       </c>
       <c r="F3" t="n">
-        <v>113.3850743038592</v>
+        <v>113.4345186639489</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3208306715142</v>
+        <v>56.09242779191669</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>48.79723557279398</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1717704894647381</v>
+        <v>0.1676378848976542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9286170354799225</v>
+        <v>0.963090913275063</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>722</v>
       </c>
       <c r="L3" t="n">
-        <v>448</v>
+        <v>1797</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>45488.02986111111</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.98235949442294</v>
       </c>
       <c r="O3" t="n">
-        <v>113.40414682924</v>
+        <v>113.491685257373</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.976702981319232</v>
+        <v>-8.010079034232739</v>
       </c>
       <c r="Q3" t="n">
-        <v>113.3850743038592</v>
+        <v>113.4345186639489</v>
       </c>
       <c r="R3" t="n">
-        <v>137.3208306715142</v>
+        <v>56.09242779191669</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -674,55 +674,55 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.974666415873893</v>
+        <v>-8.101897752714503</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4038295591115</v>
+        <v>112.6207535159278</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.983405645938871</v>
+        <v>-7.99321280084413</v>
       </c>
       <c r="F4" t="n">
-        <v>113.4059725194385</v>
+        <v>113.3632245281443</v>
       </c>
       <c r="G4" t="n">
-        <v>166.3507837823159</v>
+        <v>81.64247362790093</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>82.63446466657469</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1721589713514692</v>
+        <v>0.1690173646828597</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9732392699929459</v>
+        <v>0.9838184746391631</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>1513</v>
       </c>
       <c r="L4" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O4" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.983405645938871</v>
+        <v>-7.99321280084413</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.4059725194385</v>
+        <v>113.3632245281443</v>
       </c>
       <c r="R4" t="n">
-        <v>166.3507837823159</v>
+        <v>81.64247362790093</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -739,55 +739,55 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.957145064323297</v>
+        <v>-7.092933848756257</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3901911169971</v>
+        <v>112.5807713039495</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.966138105671611</v>
+        <v>-7.979184788795803</v>
       </c>
       <c r="F5" t="n">
-        <v>113.390134514338</v>
+        <v>113.3465095745694</v>
       </c>
       <c r="G5" t="n">
-        <v>180.3571379682267</v>
+        <v>139.467581887735</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>129.7553828823886</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1725616259723485</v>
+        <v>0.1693890977025849</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9873842598505764</v>
+        <v>0.9921781263935482</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O5" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.966138105671611</v>
+        <v>-7.979184788795803</v>
       </c>
       <c r="Q5" t="n">
-        <v>113.390134514338</v>
+        <v>113.3465095745694</v>
       </c>
       <c r="R5" t="n">
-        <v>180.3571379682267</v>
+        <v>139.467581887735</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
@@ -804,55 +804,55 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.977570774607881</v>
+        <v>-7.092933848756257</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3785946547453</v>
+        <v>112.5807713039495</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.979184788795803</v>
       </c>
       <c r="F6" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3465095745694</v>
       </c>
       <c r="G6" t="n">
-        <v>19.86821475221745</v>
+        <v>139.467581887735</v>
       </c>
       <c r="H6" t="n">
-        <v>3.287075901610288</v>
+        <v>129.7553828823886</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1728891255417742</v>
+        <v>0.1693890977025849</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9923422818355199</v>
+        <v>0.9955126818611598</v>
       </c>
       <c r="K6" t="n">
-        <v>448</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>448</v>
+        <v>640</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44785.47361111111</v>
+        <v>44877.10347222222</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.90590090675314</v>
+        <v>-7.96386844576088</v>
       </c>
       <c r="O6" t="n">
-        <v>113.40414682924</v>
+        <v>113.300380121246</v>
       </c>
       <c r="P6" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.979184788795803</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3465095745694</v>
       </c>
       <c r="R6" t="n">
-        <v>19.86821475221745</v>
+        <v>139.467581887735</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -872,31 +872,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.977570774607881</v>
+        <v>-8.215052811328203</v>
       </c>
       <c r="D7" t="n">
-        <v>113.3785946547453</v>
+        <v>113.1078270690063</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.948261483831484</v>
       </c>
       <c r="F7" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3633706058358</v>
       </c>
       <c r="G7" t="n">
-        <v>19.86821475221745</v>
+        <v>43.49883644050329</v>
       </c>
       <c r="H7" t="n">
-        <v>3.287075901610288</v>
+        <v>40.88426704828213</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1728891255417742</v>
+        <v>0.1697319319871955</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9947031292341942</v>
+        <v>0.9972319225331684</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>1490</v>
       </c>
       <c r="L7" t="n">
         <v>448</v>
@@ -911,13 +911,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.948261483831484</v>
       </c>
       <c r="Q7" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3633706058358</v>
       </c>
       <c r="R7" t="n">
-        <v>19.86821475221745</v>
+        <v>43.49883644050329</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -937,31 +937,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.977570774607881</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3785946547453</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F8" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G8" t="n">
-        <v>19.86821475221745</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H8" t="n">
-        <v>3.287075901610288</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1728891255417742</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9951247353975895</v>
+        <v>0.997534189794848</v>
       </c>
       <c r="K8" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L8" t="n">
         <v>448</v>
@@ -976,13 +976,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q8" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R8" t="n">
-        <v>19.86821475221745</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.977570774607881</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D9" t="n">
-        <v>113.3785946547453</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F9" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G9" t="n">
-        <v>19.86821475221745</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H9" t="n">
-        <v>3.287075901610288</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1728891255417742</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9961296178442414</v>
+        <v>0.99798658055582</v>
       </c>
       <c r="K9" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L9" t="n">
         <v>448</v>
@@ -1041,13 +1041,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P9" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q9" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R9" t="n">
-        <v>19.86821475221745</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -1067,31 +1067,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C10" t="n">
-        <v>-7.977570774607881</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D10" t="n">
-        <v>113.3785946547453</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F10" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G10" t="n">
-        <v>19.86821475221745</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H10" t="n">
-        <v>3.287075901610288</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1728891255417742</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9964896862360023</v>
+        <v>0.9979364601941924</v>
       </c>
       <c r="K10" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L10" t="n">
         <v>448</v>
@@ -1106,13 +1106,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.949768855385877</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q10" t="n">
-        <v>113.3887388115477</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R10" t="n">
-        <v>19.86821475221745</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1132,31 +1132,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C11" t="n">
-        <v>-7.939214852264083</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D11" t="n">
-        <v>113.3828943024183</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.947958992840148</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F11" t="n">
-        <v>113.3807720487951</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G11" t="n">
-        <v>193.5160059420237</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1729101907516697</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J11" t="n">
-        <v>0.996666863405788</v>
+        <v>0.9979800900800249</v>
       </c>
       <c r="K11" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L11" t="n">
         <v>448</v>
@@ -1171,13 +1171,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.947958992840148</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3807720487951</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R11" t="n">
-        <v>193.5160059420237</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C12" t="n">
-        <v>-7.939214852264083</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D12" t="n">
-        <v>113.3828943024183</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.947958992840148</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F12" t="n">
-        <v>113.3807720487951</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G12" t="n">
-        <v>193.5160059420237</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1729101907516697</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5857823206941308</v>
+        <v>0.5857852623300956</v>
       </c>
       <c r="K12" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L12" t="n">
         <v>448</v>
@@ -1236,13 +1236,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.947958992840148</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q12" t="n">
-        <v>113.3807720487951</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R12" t="n">
-        <v>193.5160059420237</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -1262,31 +1262,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.944170964263311</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D13" t="n">
-        <v>113.3914663659358</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.952261783500453</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F13" t="n">
-        <v>113.3875018857619</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G13" t="n">
-        <v>205.8865699657014</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1729199391859107</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9978915547197775</v>
+        <v>0.9987265048470508</v>
       </c>
       <c r="K13" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L13" t="n">
         <v>448</v>
@@ -1301,13 +1301,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.952261783500453</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q13" t="n">
-        <v>113.3875018857619</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R13" t="n">
-        <v>205.8865699657014</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1327,31 +1327,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C14" t="n">
-        <v>-7.945659716436548</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D14" t="n">
-        <v>113.3972329693109</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.954237179240523</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F14" t="n">
-        <v>113.393854571792</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G14" t="n">
-        <v>201.3097136874549</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02376720668693</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1729368751352274</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9982507739216355</v>
+        <v>0.9987644825436661</v>
       </c>
       <c r="K14" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L14" t="n">
         <v>448</v>
@@ -1366,13 +1366,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.954237179240523</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.393854571792</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R14" t="n">
-        <v>201.3097136874549</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1392,31 +1392,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C15" t="n">
-        <v>-7.943765139169736</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D15" t="n">
-        <v>113.3911351817574</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.952360212961133</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F15" t="n">
-        <v>113.3871792390287</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G15" t="n">
-        <v>204.5049172549351</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H15" t="n">
-        <v>1.05033927769625</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1729402332257659</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9986492942451261</v>
+        <v>0.9987433964243196</v>
       </c>
       <c r="K15" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L15" t="n">
         <v>448</v>
@@ -1431,13 +1431,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.952360212961133</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q15" t="n">
-        <v>113.3871792390287</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R15" t="n">
-        <v>204.5049172549351</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -1457,31 +1457,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C16" t="n">
-        <v>-7.944798061474016</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D16" t="n">
-        <v>113.3955483178065</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.953051684237742</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F16" t="n">
-        <v>113.3918786800107</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G16" t="n">
-        <v>203.7654357787663</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H16" t="n">
-        <v>1.002797000684153</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1729460707011691</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9987548817078348</v>
+        <v>0.9987932389672575</v>
       </c>
       <c r="K16" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L16" t="n">
         <v>448</v>
@@ -1496,13 +1496,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.953051684237742</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q16" t="n">
-        <v>113.3918786800107</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R16" t="n">
-        <v>203.7654357787663</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1522,31 +1522,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C17" t="n">
-        <v>-7.940392375393276</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D17" t="n">
-        <v>113.3931659886091</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.950211646346075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F17" t="n">
-        <v>113.3887767440099</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G17" t="n">
-        <v>203.8792479832546</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H17" t="n">
-        <v>1.194067055004437</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1729491466611276</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9990603634870074</v>
+        <v>0.99871223269397</v>
       </c>
       <c r="K17" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L17" t="n">
         <v>448</v>
@@ -1561,13 +1561,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.950211646346075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3887767440099</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R17" t="n">
-        <v>203.8792479832546</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1587,31 +1587,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C18" t="n">
-        <v>-7.940392375393276</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D18" t="n">
-        <v>113.3931659886091</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.950211646346075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F18" t="n">
-        <v>113.3887767440099</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G18" t="n">
-        <v>203.8792479832546</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H18" t="n">
-        <v>1.194067055004437</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1729491466611276</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9991799920481111</v>
+        <v>0.9986527376151387</v>
       </c>
       <c r="K18" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L18" t="n">
         <v>448</v>
@@ -1626,13 +1626,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.950211646346075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q18" t="n">
-        <v>113.3887767440099</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R18" t="n">
-        <v>203.8792479832546</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1652,31 +1652,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.940392375393276</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D19" t="n">
-        <v>113.3931659886091</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.950211646346075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F19" t="n">
-        <v>113.3887767440099</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G19" t="n">
-        <v>203.8792479832546</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H19" t="n">
-        <v>1.194067055004437</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1729491466611276</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9991689225546168</v>
+        <v>0.9985612849180975</v>
       </c>
       <c r="K19" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L19" t="n">
         <v>448</v>
@@ -1691,13 +1691,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.950211646346075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q19" t="n">
-        <v>113.3887767440099</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R19" t="n">
-        <v>203.8792479832546</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1717,31 +1717,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C20" t="n">
-        <v>-7.944293901579533</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D20" t="n">
-        <v>113.3911386527967</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.952943467301811</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F20" t="n">
-        <v>113.3872690269759</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G20" t="n">
-        <v>203.8968995783793</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H20" t="n">
-        <v>1.051968929352845</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1729492453251325</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9991431534773433</v>
+        <v>0.9985608335017796</v>
       </c>
       <c r="K20" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L20" t="n">
         <v>448</v>
@@ -1756,13 +1756,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.952943467301811</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3872690269759</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R20" t="n">
-        <v>203.8968995783793</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1782,31 +1782,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.944232053569883</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D21" t="n">
-        <v>113.3931030184428</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.952802572944204</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F21" t="n">
-        <v>113.3892827920215</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G21" t="n">
-        <v>203.8191809617664</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H21" t="n">
-        <v>1.041730069561171</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1729502262111977</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J21" t="n">
-        <v>0.999179955966382</v>
+        <v>0.998523411900292</v>
       </c>
       <c r="K21" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L21" t="n">
         <v>448</v>
@@ -1821,13 +1821,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.952802572944204</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q21" t="n">
-        <v>113.3892827920215</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R21" t="n">
-        <v>203.8191809617664</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -1847,31 +1847,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C22" t="n">
-        <v>-7.941282248931428</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D22" t="n">
-        <v>113.3933573176257</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.951554292891318</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F22" t="n">
-        <v>113.3887764482725</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G22" t="n">
-        <v>203.8294290417517</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H22" t="n">
-        <v>1.248646213902044</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1729504032421857</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5857861845420236</v>
+        <v>0.585785663423116</v>
       </c>
       <c r="K22" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L22" t="n">
         <v>448</v>
@@ -1886,13 +1886,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P22" t="n">
-        <v>-7.951554292891318</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q22" t="n">
-        <v>113.3887764482725</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R22" t="n">
-        <v>203.8294290417517</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S22" t="b">
         <v>0</v>
@@ -1912,31 +1912,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C23" t="n">
-        <v>-7.944383955944071</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D23" t="n">
-        <v>113.3926468664014</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.952761434878513</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F23" t="n">
-        <v>113.3889060386489</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G23" t="n">
-        <v>203.8568545094929</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H23" t="n">
-        <v>1.018562212969568</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1729508599658692</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9999644138375163</v>
+        <v>0.9998819769441211</v>
       </c>
       <c r="K23" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L23" t="n">
         <v>448</v>
@@ -1951,13 +1951,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P23" t="n">
-        <v>-7.952761434878513</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3889060386489</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R23" t="n">
-        <v>203.8568545094929</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S23" t="b">
         <v>0</v>
@@ -1977,31 +1977,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C24" t="n">
-        <v>-7.943480420714248</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D24" t="n">
-        <v>113.3931855491571</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.952445011221384</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F24" t="n">
-        <v>113.3891823224593</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G24" t="n">
-        <v>203.858105547607</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H24" t="n">
-        <v>1.08995590057442</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1729508971001666</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9999643583480445</v>
+        <v>0.9998800066673301</v>
       </c>
       <c r="K24" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L24" t="n">
         <v>448</v>
@@ -2016,13 +2016,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.952445011221384</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q24" t="n">
-        <v>113.3891823224593</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R24" t="n">
-        <v>203.858105547607</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S24" t="b">
         <v>0</v>
@@ -2042,31 +2042,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.943170621277479</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D25" t="n">
-        <v>113.3930599615343</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.95225324836075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F25" t="n">
-        <v>113.3890048085567</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G25" t="n">
-        <v>203.8540173143451</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H25" t="n">
-        <v>1.104272512557813</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1729509290669217</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9999693849799064</v>
+        <v>0.9998798308822405</v>
       </c>
       <c r="K25" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L25" t="n">
         <v>448</v>
@@ -2081,13 +2081,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.95225324836075</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q25" t="n">
-        <v>113.3890048085567</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R25" t="n">
-        <v>203.8540173143451</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S25" t="b">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.943545518616204</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D26" t="n">
-        <v>113.3925761308665</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.952237531183342</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F26" t="n">
-        <v>113.3886946383456</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G26" t="n">
-        <v>203.8580532221621</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H26" t="n">
-        <v>1.056814132883104</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1729509411253649</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9999862738573292</v>
+        <v>0.9999069883043803</v>
       </c>
       <c r="K26" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L26" t="n">
         <v>448</v>
@@ -2146,13 +2146,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.952237531183342</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3886946383456</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R26" t="n">
-        <v>203.8580532221621</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S26" t="b">
         <v>0</v>
@@ -2172,31 +2172,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C27" t="n">
-        <v>-7.94304199378201</v>
+        <v>-7.775879658870506</v>
       </c>
       <c r="D27" t="n">
-        <v>113.393062783403</v>
+        <v>113.4532763418044</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.952187862218869</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3889789515696</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="G27" t="n">
-        <v>203.8563207257764</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="H27" t="n">
-        <v>1.111981228377769</v>
+        <v>21.10278673606226</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1729509660138104</v>
+        <v>0.1700753529470459</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9999861663487079</v>
+        <v>0.9999088733769972</v>
       </c>
       <c r="K27" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L27" t="n">
         <v>448</v>
@@ -2211,13 +2211,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.952187862218869</v>
+        <v>-7.953192665095322</v>
       </c>
       <c r="Q27" t="n">
-        <v>113.3889789515696</v>
+        <v>113.3849783630978</v>
       </c>
       <c r="R27" t="n">
-        <v>203.8563207257764</v>
+        <v>200.8802025813238</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -2237,31 +2237,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.943268349942975</v>
+        <v>-7.776049947699862</v>
       </c>
       <c r="D28" t="n">
-        <v>113.3928733453602</v>
+        <v>113.4571611251813</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.952205764338614</v>
+        <v>-7.952102677398561</v>
       </c>
       <c r="F28" t="n">
-        <v>113.3888825725369</v>
+        <v>113.3825366260819</v>
       </c>
       <c r="G28" t="n">
-        <v>203.8564287248105</v>
+        <v>202.771928377245</v>
       </c>
       <c r="H28" t="n">
-        <v>1.086637632956232</v>
+        <v>21.23186194180784</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1729509720882438</v>
+        <v>0.1701007958903899</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9999859218475423</v>
+        <v>0.9998994514163774</v>
       </c>
       <c r="K28" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L28" t="n">
         <v>448</v>
@@ -2276,13 +2276,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P28" t="n">
-        <v>-7.952205764338614</v>
+        <v>-7.952102677398561</v>
       </c>
       <c r="Q28" t="n">
-        <v>113.3888825725369</v>
+        <v>113.3825366260819</v>
       </c>
       <c r="R28" t="n">
-        <v>203.8564287248105</v>
+        <v>202.771928377245</v>
       </c>
       <c r="S28" t="b">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C29" t="n">
-        <v>-7.943367961232727</v>
+        <v>-7.775973069929677</v>
       </c>
       <c r="D29" t="n">
-        <v>113.3928114974094</v>
+        <v>113.4563496206208</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.952144070167393</v>
+        <v>-7.951582340494551</v>
       </c>
       <c r="F29" t="n">
-        <v>113.3888927268036</v>
+        <v>113.3808626363963</v>
       </c>
       <c r="G29" t="n">
-        <v>203.8565657235524</v>
+        <v>203.0598946300925</v>
       </c>
       <c r="H29" t="n">
-        <v>1.067026718805198</v>
+        <v>21.22344693729257</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1729509721387154</v>
+        <v>0.1701012341763738</v>
       </c>
       <c r="J29" t="n">
-        <v>0.99998561127917</v>
+        <v>0.9998833076932242</v>
       </c>
       <c r="K29" t="n">
-        <v>448</v>
+        <v>374</v>
       </c>
       <c r="L29" t="n">
         <v>448</v>
@@ -2341,13 +2341,13 @@
         <v>113.40414682924</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.952144070167393</v>
+        <v>-7.951582340494551</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3888927268036</v>
+        <v>113.3808626363963</v>
       </c>
       <c r="R29" t="n">
-        <v>203.8565657235524</v>
+        <v>203.0598946300925</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -2367,31 +2367,31 @@
         <v>44785.47361111111</v>
       </c>
       <c r="C30" t="n">
-        <v>-7.943233691616467</v>
+        <v>-7.775990269155092</v>
       </c>
       <c r="D30" t="n">
-        <v>1